--- a/Design/Data/ReEchoData.xlsx
+++ b/Design/Data/ReEchoData.xlsx
@@ -510,9 +510,9 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="tblParts" displayName="tblParts" ref="A45:N123" headerRowCount="1">
-  <autoFilter ref="A45:N123"/>
-  <tableColumns count="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="tblParts" displayName="tblParts" ref="A45:P123" headerRowCount="1">
+  <autoFilter ref="A45:P123"/>
+  <tableColumns count="16">
     <tableColumn id="1" name="Id"/>
     <tableColumn id="2" name="PartId"/>
     <tableColumn id="3" name="WeaponTypeId"/>
@@ -527,14 +527,16 @@
     <tableColumn id="12" name="DisabledReason"/>
     <tableColumn id="13" name="SourceSheet"/>
     <tableColumn id="14" name="SourceRow"/>
+    <tableColumn id="15" name="ShopEnabled"/>
+    <tableColumn id="16" name="ShopPrice"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="tblPartEffects" displayName="tblPartEffects" ref="P45:AI55" headerRowCount="1">
-  <autoFilter ref="P45:AI55"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="tblPartEffects" displayName="tblPartEffects" ref="R45:AK55" headerRowCount="1">
+  <autoFilter ref="R45:AK55"/>
   <tableColumns count="20">
     <tableColumn id="16" name="Id"/>
     <tableColumn id="17" name="PartId"/>
@@ -16324,12 +16326,12 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI123"/>
+  <dimension ref="A1:AK123"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="13.81640625" defaultRowHeight="13"/>
   <cols>
     <col width="25" customWidth="1" style="32" min="1" max="1"/>
@@ -16346,26 +16348,28 @@
     <col width="40" customWidth="1" style="32" min="12" max="12"/>
     <col width="18" customWidth="1" style="32" min="13" max="13"/>
     <col width="16" customWidth="1" style="32" min="14" max="14"/>
-    <col width="25" customWidth="1" style="32" min="16" max="16"/>
-    <col width="25" customWidth="1" style="32" min="17" max="17"/>
-    <col width="16" customWidth="1" style="32" min="18" max="18"/>
-    <col width="16" customWidth="1" style="32" min="19" max="19"/>
+    <col width="14" customWidth="1" style="32" min="15" max="15"/>
+    <col width="11" customWidth="1" style="32" min="16" max="16"/>
+    <col width="25" customWidth="1" style="32" min="18" max="18"/>
+    <col width="25" customWidth="1" style="32" min="19" max="19"/>
     <col width="16" customWidth="1" style="32" min="20" max="20"/>
     <col width="16" customWidth="1" style="32" min="21" max="21"/>
     <col width="16" customWidth="1" style="32" min="22" max="22"/>
     <col width="16" customWidth="1" style="32" min="23" max="23"/>
-    <col width="25" customWidth="1" style="32" min="24" max="24"/>
-    <col width="25" customWidth="1" style="32" min="25" max="25"/>
+    <col width="16" customWidth="1" style="32" min="24" max="24"/>
+    <col width="16" customWidth="1" style="32" min="25" max="25"/>
     <col width="25" customWidth="1" style="32" min="26" max="26"/>
-    <col width="16" customWidth="1" style="32" min="27" max="27"/>
-    <col width="16" customWidth="1" style="32" min="28" max="28"/>
+    <col width="25" customWidth="1" style="32" min="27" max="27"/>
+    <col width="25" customWidth="1" style="32" min="28" max="28"/>
     <col width="16" customWidth="1" style="32" min="29" max="29"/>
     <col width="16" customWidth="1" style="32" min="30" max="30"/>
     <col width="16" customWidth="1" style="32" min="31" max="31"/>
     <col width="16" customWidth="1" style="32" min="32" max="32"/>
-    <col width="40" customWidth="1" style="32" min="33" max="33"/>
-    <col width="18" customWidth="1" style="32" min="34" max="34"/>
-    <col width="16" customWidth="1" style="32" min="35" max="35"/>
+    <col width="16" customWidth="1" style="32" min="33" max="33"/>
+    <col width="16" customWidth="1" style="32" min="34" max="34"/>
+    <col width="40" customWidth="1" style="32" min="35" max="35"/>
+    <col width="18" customWidth="1" style="32" min="36" max="36"/>
+    <col width="16" customWidth="1" style="32" min="37" max="37"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" s="32">
@@ -17713,7 +17717,7 @@
           <t>tblParts → parts.csv</t>
         </is>
       </c>
-      <c r="P44" s="34" t="inlineStr">
+      <c r="R44" s="34" t="inlineStr">
         <is>
           <t>tblPartEffects → part_effects.csv</t>
         </is>
@@ -17790,102 +17794,112 @@
           <t>SourceRow</t>
         </is>
       </c>
-      <c r="P45" s="29" t="inlineStr">
+      <c r="O45" t="inlineStr" s="29">
+        <is>
+          <t xml:space="preserve">ShopEnabled</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr" s="29">
+        <is>
+          <t xml:space="preserve">ShopPrice</t>
+        </is>
+      </c>
+      <c r="R45" s="29" t="inlineStr">
         <is>
           <t>Id</t>
         </is>
       </c>
-      <c r="Q45" s="29" t="inlineStr">
+      <c r="S45" s="29" t="inlineStr">
         <is>
           <t>PartId</t>
         </is>
       </c>
-      <c r="R45" s="29" t="inlineStr">
+      <c r="T45" s="29" t="inlineStr">
         <is>
           <t>Order</t>
         </is>
       </c>
-      <c r="S45" s="29" t="inlineStr">
+      <c r="U45" s="29" t="inlineStr">
         <is>
           <t>Trigger</t>
         </is>
       </c>
-      <c r="T45" s="29" t="inlineStr">
+      <c r="V45" s="29" t="inlineStr">
         <is>
           <t>EffectKind</t>
         </is>
       </c>
-      <c r="U45" s="29" t="inlineStr">
+      <c r="W45" s="29" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="V45" s="29" t="inlineStr">
+      <c r="X45" s="29" t="inlineStr">
         <is>
           <t>ValueOp</t>
         </is>
       </c>
-      <c r="W45" s="29" t="inlineStr">
+      <c r="Y45" s="29" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="X45" s="29" t="inlineStr">
+      <c r="Z45" s="29" t="inlineStr">
         <is>
           <t>BehaviorId</t>
         </is>
       </c>
-      <c r="Y45" s="29" t="inlineStr">
+      <c r="AA45" s="29" t="inlineStr">
         <is>
           <t>FormulaId</t>
         </is>
       </c>
-      <c r="Z45" s="29" t="inlineStr">
+      <c r="AB45" s="29" t="inlineStr">
         <is>
           <t>AttackPatternId</t>
         </is>
       </c>
-      <c r="AA45" s="29" t="inlineStr">
+      <c r="AC45" s="29" t="inlineStr">
         <is>
           <t>ParamName</t>
         </is>
       </c>
-      <c r="AB45" s="29" t="inlineStr">
+      <c r="AD45" s="29" t="inlineStr">
         <is>
           <t>ParamValue</t>
         </is>
       </c>
-      <c r="AC45" s="29" t="inlineStr">
+      <c r="AE45" s="29" t="inlineStr">
         <is>
           <t>DurationSeconds</t>
         </is>
       </c>
-      <c r="AD45" s="29" t="inlineStr">
+      <c r="AF45" s="29" t="inlineStr">
         <is>
           <t>CooldownSeconds</t>
         </is>
       </c>
-      <c r="AE45" s="29" t="inlineStr">
+      <c r="AG45" s="29" t="inlineStr">
         <is>
           <t>StackPolicy</t>
         </is>
       </c>
-      <c r="AF45" s="29" t="inlineStr">
+      <c r="AH45" s="29" t="inlineStr">
         <is>
           <t>Enabled</t>
         </is>
       </c>
-      <c r="AG45" s="29" t="inlineStr">
+      <c r="AI45" s="29" t="inlineStr">
         <is>
           <t>DisabledReason</t>
         </is>
       </c>
-      <c r="AH45" s="29" t="inlineStr">
+      <c r="AJ45" s="29" t="inlineStr">
         <is>
           <t>SourceSheet</t>
         </is>
       </c>
-      <c r="AI45" s="29" t="inlineStr">
+      <c r="AK45" s="29" t="inlineStr">
         <is>
           <t>SourceRow</t>
         </is>
@@ -17959,98 +17973,106 @@
           <t>2</t>
         </is>
       </c>
-      <c r="P46" s="31" t="inlineStr">
+      <c r="O46" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+      <c r="P46" t="n" s="31">
+        <v>10</v>
+      </c>
+      <c r="R46" s="31" t="inlineStr">
         <is>
           <t>PE_CORE_PRIMORDIAL_CHANNEL</t>
         </is>
       </c>
-      <c r="Q46" s="31" t="inlineStr">
+      <c r="S46" s="31" t="inlineStr">
         <is>
           <t>P_CORE_PRIMORDIAL</t>
         </is>
       </c>
-      <c r="R46" s="31" t="inlineStr">
+      <c r="T46" s="31" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="S46" s="31" t="inlineStr">
+      <c r="U46" s="31" t="inlineStr">
         <is>
           <t>OnEquip</t>
         </is>
       </c>
-      <c r="T46" s="31" t="inlineStr">
+      <c r="V46" s="31" t="inlineStr">
         <is>
           <t>WeaponDamageChannel</t>
         </is>
       </c>
-      <c r="U46" s="31" t="inlineStr">
+      <c r="W46" s="31" t="inlineStr">
         <is>
           <t>DamageChannel</t>
         </is>
       </c>
-      <c r="V46" s="31" t="inlineStr">
+      <c r="X46" s="31" t="inlineStr">
         <is>
           <t>Override</t>
         </is>
       </c>
-      <c r="W46" s="31" t="inlineStr">
+      <c r="Y46" s="31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="X46" s="31" t="inlineStr">
+      <c r="Z46" s="31" t="inlineStr">
         <is>
           <t>Part.CoreDamageChannel</t>
         </is>
       </c>
-      <c r="Y46" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="Z46" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AA46" s="31" t="inlineStr">
         <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB46" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC46" s="31" t="inlineStr">
+        <is>
           <t>Physical</t>
         </is>
       </c>
-      <c r="AB46" s="31" t="inlineStr">
+      <c r="AD46" s="31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AC46" s="31" t="inlineStr">
+      <c r="AE46" s="31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AD46" s="31" t="inlineStr">
+      <c r="AF46" s="31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AE46" s="31" t="inlineStr">
+      <c r="AG46" s="31" t="inlineStr">
         <is>
           <t>Unique</t>
         </is>
       </c>
-      <c r="AF46" s="31" t="inlineStr">
+      <c r="AH46" s="31" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="AG46" s="31" t="n"/>
-      <c r="AH46" s="31" t="inlineStr">
+      <c r="AI46" s="31" t="n"/>
+      <c r="AJ46" s="31" t="inlineStr">
         <is>
           <t>武器插槽C</t>
         </is>
       </c>
-      <c r="AI46" s="31" t="inlineStr">
+      <c r="AK46" s="31" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -18124,98 +18146,106 @@
           <t>3</t>
         </is>
       </c>
-      <c r="P47" s="31" t="inlineStr">
+      <c r="O47" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+      <c r="P47" t="n" s="31">
+        <v>10</v>
+      </c>
+      <c r="R47" s="31" t="inlineStr">
         <is>
           <t>PE_CORE_TIDE_CHANNEL</t>
         </is>
       </c>
-      <c r="Q47" s="31" t="inlineStr">
+      <c r="S47" s="31" t="inlineStr">
         <is>
           <t>P_CORE_TIDE</t>
         </is>
       </c>
-      <c r="R47" s="31" t="inlineStr">
+      <c r="T47" s="31" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="S47" s="31" t="inlineStr">
+      <c r="U47" s="31" t="inlineStr">
         <is>
           <t>OnEquip</t>
         </is>
       </c>
-      <c r="T47" s="31" t="inlineStr">
+      <c r="V47" s="31" t="inlineStr">
         <is>
           <t>WeaponDamageChannel</t>
         </is>
       </c>
-      <c r="U47" s="31" t="inlineStr">
+      <c r="W47" s="31" t="inlineStr">
         <is>
           <t>DamageChannel</t>
         </is>
       </c>
-      <c r="V47" s="31" t="inlineStr">
+      <c r="X47" s="31" t="inlineStr">
         <is>
           <t>Override</t>
         </is>
       </c>
-      <c r="W47" s="31" t="inlineStr">
+      <c r="Y47" s="31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="X47" s="31" t="inlineStr">
+      <c r="Z47" s="31" t="inlineStr">
         <is>
           <t>Part.CoreDamageChannel</t>
         </is>
       </c>
-      <c r="Y47" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="Z47" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AA47" s="31" t="inlineStr">
         <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB47" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC47" s="31" t="inlineStr">
+        <is>
           <t>Water</t>
         </is>
       </c>
-      <c r="AB47" s="31" t="inlineStr">
+      <c r="AD47" s="31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AC47" s="31" t="inlineStr">
+      <c r="AE47" s="31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AD47" s="31" t="inlineStr">
+      <c r="AF47" s="31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AE47" s="31" t="inlineStr">
+      <c r="AG47" s="31" t="inlineStr">
         <is>
           <t>Unique</t>
         </is>
       </c>
-      <c r="AF47" s="31" t="inlineStr">
+      <c r="AH47" s="31" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="AG47" s="31" t="n"/>
-      <c r="AH47" s="31" t="inlineStr">
+      <c r="AI47" s="31" t="n"/>
+      <c r="AJ47" s="31" t="inlineStr">
         <is>
           <t>武器插槽C</t>
         </is>
       </c>
-      <c r="AI47" s="31" t="inlineStr">
+      <c r="AK47" s="31" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -18289,98 +18319,106 @@
           <t>4</t>
         </is>
       </c>
-      <c r="P48" s="31" t="inlineStr">
+      <c r="O48" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+      <c r="P48" t="n" s="31">
+        <v>10</v>
+      </c>
+      <c r="R48" s="31" t="inlineStr">
         <is>
           <t>PE_CORE_FOREST_CHANNEL</t>
         </is>
       </c>
-      <c r="Q48" s="31" t="inlineStr">
+      <c r="S48" s="31" t="inlineStr">
         <is>
           <t>P_CORE_FOREST</t>
         </is>
       </c>
-      <c r="R48" s="31" t="inlineStr">
+      <c r="T48" s="31" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="S48" s="31" t="inlineStr">
+      <c r="U48" s="31" t="inlineStr">
         <is>
           <t>OnEquip</t>
         </is>
       </c>
-      <c r="T48" s="31" t="inlineStr">
+      <c r="V48" s="31" t="inlineStr">
         <is>
           <t>WeaponDamageChannel</t>
         </is>
       </c>
-      <c r="U48" s="31" t="inlineStr">
+      <c r="W48" s="31" t="inlineStr">
         <is>
           <t>DamageChannel</t>
         </is>
       </c>
-      <c r="V48" s="31" t="inlineStr">
+      <c r="X48" s="31" t="inlineStr">
         <is>
           <t>Override</t>
         </is>
       </c>
-      <c r="W48" s="31" t="inlineStr">
+      <c r="Y48" s="31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="X48" s="31" t="inlineStr">
+      <c r="Z48" s="31" t="inlineStr">
         <is>
           <t>Part.CoreDamageChannel</t>
         </is>
       </c>
-      <c r="Y48" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="Z48" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AA48" s="31" t="inlineStr">
         <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB48" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC48" s="31" t="inlineStr">
+        <is>
           <t>Grass</t>
         </is>
       </c>
-      <c r="AB48" s="31" t="inlineStr">
+      <c r="AD48" s="31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AC48" s="31" t="inlineStr">
+      <c r="AE48" s="31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AD48" s="31" t="inlineStr">
+      <c r="AF48" s="31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AE48" s="31" t="inlineStr">
+      <c r="AG48" s="31" t="inlineStr">
         <is>
           <t>Unique</t>
         </is>
       </c>
-      <c r="AF48" s="31" t="inlineStr">
+      <c r="AH48" s="31" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="AG48" s="31" t="n"/>
-      <c r="AH48" s="31" t="inlineStr">
+      <c r="AI48" s="31" t="n"/>
+      <c r="AJ48" s="31" t="inlineStr">
         <is>
           <t>武器插槽C</t>
         </is>
       </c>
-      <c r="AI48" s="31" t="inlineStr">
+      <c r="AK48" s="31" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -18454,98 +18492,106 @@
           <t>5</t>
         </is>
       </c>
-      <c r="P49" s="31" t="inlineStr">
+      <c r="O49" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+      <c r="P49" t="n" s="31">
+        <v>10</v>
+      </c>
+      <c r="R49" s="31" t="inlineStr">
         <is>
           <t>PE_CORE_FLAME_CHANNEL</t>
         </is>
       </c>
-      <c r="Q49" s="31" t="inlineStr">
+      <c r="S49" s="31" t="inlineStr">
         <is>
           <t>P_CORE_FLAME</t>
         </is>
       </c>
-      <c r="R49" s="31" t="inlineStr">
+      <c r="T49" s="31" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="S49" s="31" t="inlineStr">
+      <c r="U49" s="31" t="inlineStr">
         <is>
           <t>OnEquip</t>
         </is>
       </c>
-      <c r="T49" s="31" t="inlineStr">
+      <c r="V49" s="31" t="inlineStr">
         <is>
           <t>WeaponDamageChannel</t>
         </is>
       </c>
-      <c r="U49" s="31" t="inlineStr">
+      <c r="W49" s="31" t="inlineStr">
         <is>
           <t>DamageChannel</t>
         </is>
       </c>
-      <c r="V49" s="31" t="inlineStr">
+      <c r="X49" s="31" t="inlineStr">
         <is>
           <t>Override</t>
         </is>
       </c>
-      <c r="W49" s="31" t="inlineStr">
+      <c r="Y49" s="31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="X49" s="31" t="inlineStr">
+      <c r="Z49" s="31" t="inlineStr">
         <is>
           <t>Part.CoreDamageChannel</t>
         </is>
       </c>
-      <c r="Y49" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="Z49" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AA49" s="31" t="inlineStr">
         <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB49" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC49" s="31" t="inlineStr">
+        <is>
           <t>Flame</t>
         </is>
       </c>
-      <c r="AB49" s="31" t="inlineStr">
+      <c r="AD49" s="31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AC49" s="31" t="inlineStr">
+      <c r="AE49" s="31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AD49" s="31" t="inlineStr">
+      <c r="AF49" s="31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AE49" s="31" t="inlineStr">
+      <c r="AG49" s="31" t="inlineStr">
         <is>
           <t>Unique</t>
         </is>
       </c>
-      <c r="AF49" s="31" t="inlineStr">
+      <c r="AH49" s="31" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="AG49" s="31" t="n"/>
-      <c r="AH49" s="31" t="inlineStr">
+      <c r="AI49" s="31" t="n"/>
+      <c r="AJ49" s="31" t="inlineStr">
         <is>
           <t>武器插槽C</t>
         </is>
       </c>
-      <c r="AI49" s="31" t="inlineStr">
+      <c r="AK49" s="31" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -18619,98 +18665,106 @@
           <t>6</t>
         </is>
       </c>
-      <c r="P50" s="31" t="inlineStr">
+      <c r="O50" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+      <c r="P50" t="n" s="31">
+        <v>10</v>
+      </c>
+      <c r="R50" s="31" t="inlineStr">
         <is>
           <t>PE_CORE_THUNDER_CHANNEL</t>
         </is>
       </c>
-      <c r="Q50" s="31" t="inlineStr">
+      <c r="S50" s="31" t="inlineStr">
         <is>
           <t>P_CORE_THUNDER</t>
         </is>
       </c>
-      <c r="R50" s="31" t="inlineStr">
+      <c r="T50" s="31" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="S50" s="31" t="inlineStr">
+      <c r="U50" s="31" t="inlineStr">
         <is>
           <t>OnEquip</t>
         </is>
       </c>
-      <c r="T50" s="31" t="inlineStr">
+      <c r="V50" s="31" t="inlineStr">
         <is>
           <t>WeaponDamageChannel</t>
         </is>
       </c>
-      <c r="U50" s="31" t="inlineStr">
+      <c r="W50" s="31" t="inlineStr">
         <is>
           <t>DamageChannel</t>
         </is>
       </c>
-      <c r="V50" s="31" t="inlineStr">
+      <c r="X50" s="31" t="inlineStr">
         <is>
           <t>Override</t>
         </is>
       </c>
-      <c r="W50" s="31" t="inlineStr">
+      <c r="Y50" s="31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="X50" s="31" t="inlineStr">
+      <c r="Z50" s="31" t="inlineStr">
         <is>
           <t>Part.CoreDamageChannel</t>
         </is>
       </c>
-      <c r="Y50" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="Z50" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AA50" s="31" t="inlineStr">
         <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB50" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC50" s="31" t="inlineStr">
+        <is>
           <t>Lightning</t>
         </is>
       </c>
-      <c r="AB50" s="31" t="inlineStr">
+      <c r="AD50" s="31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AC50" s="31" t="inlineStr">
+      <c r="AE50" s="31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AD50" s="31" t="inlineStr">
+      <c r="AF50" s="31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AE50" s="31" t="inlineStr">
+      <c r="AG50" s="31" t="inlineStr">
         <is>
           <t>Unique</t>
         </is>
       </c>
-      <c r="AF50" s="31" t="inlineStr">
+      <c r="AH50" s="31" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="AG50" s="31" t="n"/>
-      <c r="AH50" s="31" t="inlineStr">
+      <c r="AI50" s="31" t="n"/>
+      <c r="AJ50" s="31" t="inlineStr">
         <is>
           <t>武器插槽C</t>
         </is>
       </c>
-      <c r="AI50" s="31" t="inlineStr">
+      <c r="AK50" s="31" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -18783,98 +18837,106 @@
           <t>7</t>
         </is>
       </c>
-      <c r="P51" s="31" t="inlineStr">
+      <c r="O51" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+      <c r="P51" t="n" s="31">
+        <v>10</v>
+      </c>
+      <c r="R51" s="31" t="inlineStr">
         <is>
           <t>PE_CORE_PRISM_CHANNEL</t>
         </is>
       </c>
-      <c r="Q51" s="31" t="inlineStr">
+      <c r="S51" s="31" t="inlineStr">
         <is>
           <t>P_CORE_PRISM</t>
         </is>
       </c>
-      <c r="R51" s="31" t="inlineStr">
+      <c r="T51" s="31" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="S51" s="31" t="inlineStr">
+      <c r="U51" s="31" t="inlineStr">
         <is>
           <t>OnEquip</t>
         </is>
       </c>
-      <c r="T51" s="31" t="inlineStr">
+      <c r="V51" s="31" t="inlineStr">
         <is>
           <t>WeaponDamageChannel</t>
         </is>
       </c>
-      <c r="U51" s="31" t="inlineStr">
+      <c r="W51" s="31" t="inlineStr">
         <is>
           <t>DamageChannel</t>
         </is>
       </c>
-      <c r="V51" s="31" t="inlineStr">
+      <c r="X51" s="31" t="inlineStr">
         <is>
           <t>Override</t>
         </is>
       </c>
-      <c r="W51" s="31" t="inlineStr">
+      <c r="Y51" s="31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="X51" s="31" t="inlineStr">
+      <c r="Z51" s="31" t="inlineStr">
         <is>
           <t>Part.CoreDamageChannel</t>
         </is>
       </c>
-      <c r="Y51" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="Z51" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AA51" s="31" t="inlineStr">
         <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB51" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC51" s="31" t="inlineStr">
+        <is>
           <t>RandomElement</t>
         </is>
       </c>
-      <c r="AB51" s="31" t="inlineStr">
+      <c r="AD51" s="31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AC51" s="31" t="inlineStr">
+      <c r="AE51" s="31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AD51" s="31" t="inlineStr">
+      <c r="AF51" s="31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AE51" s="31" t="inlineStr">
+      <c r="AG51" s="31" t="inlineStr">
         <is>
           <t>Unique</t>
         </is>
       </c>
-      <c r="AF51" s="31" t="inlineStr">
+      <c r="AH51" s="31" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="AG51" s="31" t="n"/>
-      <c r="AH51" s="31" t="inlineStr">
+      <c r="AI51" s="31" t="n"/>
+      <c r="AJ51" s="31" t="inlineStr">
         <is>
           <t>武器插槽C</t>
         </is>
       </c>
-      <c r="AI51" s="31" t="inlineStr">
+      <c r="AK51" s="31" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -18947,98 +19009,106 @@
           <t>8</t>
         </is>
       </c>
-      <c r="P52" s="31" t="inlineStr">
+      <c r="O52" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+      <c r="P52" t="n" s="31">
+        <v>10</v>
+      </c>
+      <c r="R52" s="31" t="inlineStr">
         <is>
           <t>PE_DAGGER_THRUST_PATTERN</t>
         </is>
       </c>
-      <c r="Q52" s="31" t="inlineStr">
+      <c r="S52" s="31" t="inlineStr">
         <is>
           <t>P_DAGGER_THRUST_GRIP</t>
         </is>
       </c>
-      <c r="R52" s="31" t="inlineStr">
+      <c r="T52" s="31" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="S52" s="31" t="inlineStr">
+      <c r="U52" s="31" t="inlineStr">
         <is>
           <t>OnEquip</t>
         </is>
       </c>
-      <c r="T52" s="31" t="inlineStr">
+      <c r="V52" s="31" t="inlineStr">
         <is>
           <t>AttackPatternReplacement</t>
         </is>
       </c>
-      <c r="U52" s="31" t="inlineStr">
+      <c r="W52" s="31" t="inlineStr">
         <is>
           <t>AttackPattern</t>
         </is>
       </c>
-      <c r="V52" s="31" t="inlineStr">
+      <c r="X52" s="31" t="inlineStr">
         <is>
           <t>Override</t>
         </is>
       </c>
-      <c r="W52" s="31" t="inlineStr">
+      <c r="Y52" s="31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="X52" s="31" t="inlineStr">
+      <c r="Z52" s="31" t="inlineStr">
         <is>
           <t>Part.AttackPatternReplacement</t>
         </is>
       </c>
-      <c r="Y52" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="Z52" s="31" t="inlineStr">
+      <c r="AA52" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB52" s="31" t="inlineStr">
         <is>
           <t>Pattern.DaggerDashOnly</t>
         </is>
       </c>
-      <c r="AA52" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="AB52" s="31" t="inlineStr">
+      <c r="AC52" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD52" s="31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AC52" s="31" t="inlineStr">
+      <c r="AE52" s="31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AD52" s="31" t="inlineStr">
+      <c r="AF52" s="31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AE52" s="31" t="inlineStr">
+      <c r="AG52" s="31" t="inlineStr">
         <is>
           <t>Unique</t>
         </is>
       </c>
-      <c r="AF52" s="31" t="inlineStr">
+      <c r="AH52" s="31" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="AG52" s="31" t="n"/>
-      <c r="AH52" s="31" t="inlineStr">
+      <c r="AI52" s="31" t="n"/>
+      <c r="AJ52" s="31" t="inlineStr">
         <is>
           <t>武器插槽C</t>
         </is>
       </c>
-      <c r="AI52" s="31" t="inlineStr">
+      <c r="AK52" s="31" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -19111,61 +19181,59 @@
           <t>9</t>
         </is>
       </c>
-      <c r="P53" s="31" t="inlineStr">
+      <c r="O53" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+      <c r="P53" t="n" s="31">
+        <v>10</v>
+      </c>
+      <c r="R53" s="31" t="inlineStr">
         <is>
           <t>PE_DAGGER_THRUST_COOLDOWN</t>
         </is>
       </c>
-      <c r="Q53" s="31" t="inlineStr">
+      <c r="S53" s="31" t="inlineStr">
         <is>
           <t>P_DAGGER_THRUST_GRIP</t>
         </is>
       </c>
-      <c r="R53" s="31" t="inlineStr">
+      <c r="T53" s="31" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="S53" s="31" t="inlineStr">
+      <c r="U53" s="31" t="inlineStr">
         <is>
           <t>OnEquip</t>
         </is>
       </c>
-      <c r="T53" s="31" t="inlineStr">
+      <c r="V53" s="31" t="inlineStr">
         <is>
           <t>StatModifier</t>
         </is>
       </c>
-      <c r="U53" s="31" t="inlineStr">
+      <c r="W53" s="31" t="inlineStr">
         <is>
           <t>AttackIntervalSeconds</t>
         </is>
       </c>
-      <c r="V53" s="31" t="inlineStr">
+      <c r="X53" s="31" t="inlineStr">
         <is>
           <t>Override</t>
         </is>
       </c>
-      <c r="W53" s="31" t="inlineStr">
+      <c r="Y53" s="31" t="inlineStr">
         <is>
           <t>0.4</t>
         </is>
       </c>
-      <c r="X53" s="31" t="inlineStr">
+      <c r="Z53" s="31" t="inlineStr">
         <is>
           <t>Part.StatModifier</t>
         </is>
       </c>
-      <c r="Y53" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="Z53" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AA53" s="31" t="inlineStr">
         <is>
           <t>None</t>
@@ -19173,36 +19241,46 @@
       </c>
       <c r="AB53" s="31" t="inlineStr">
         <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC53" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD53" s="31" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AC53" s="31" t="inlineStr">
+      <c r="AE53" s="31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AD53" s="31" t="inlineStr">
+      <c r="AF53" s="31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AE53" s="31" t="inlineStr">
+      <c r="AG53" s="31" t="inlineStr">
         <is>
           <t>Unique</t>
         </is>
       </c>
-      <c r="AF53" s="31" t="inlineStr">
+      <c r="AH53" s="31" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="AG53" s="31" t="n"/>
-      <c r="AH53" s="31" t="inlineStr">
+      <c r="AI53" s="31" t="n"/>
+      <c r="AJ53" s="31" t="inlineStr">
         <is>
           <t>武器插槽C</t>
         </is>
       </c>
-      <c r="AI53" s="31" t="inlineStr">
+      <c r="AK53" s="31" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -19275,61 +19353,59 @@
           <t>10</t>
         </is>
       </c>
-      <c r="P54" s="31" t="inlineStr">
+      <c r="O54" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P54" t="n" s="31">
+        <v>0</v>
+      </c>
+      <c r="R54" s="31" t="inlineStr">
         <is>
           <t>PE_DAGGER_STRENGTH_SPEED</t>
         </is>
       </c>
-      <c r="Q54" s="31" t="inlineStr">
+      <c r="S54" s="31" t="inlineStr">
         <is>
           <t>P_DAGGER_STRENGTH_GRIP</t>
         </is>
       </c>
-      <c r="R54" s="31" t="inlineStr">
+      <c r="T54" s="31" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="S54" s="31" t="inlineStr">
+      <c r="U54" s="31" t="inlineStr">
         <is>
           <t>OnEquip</t>
         </is>
       </c>
-      <c r="T54" s="31" t="inlineStr">
+      <c r="V54" s="31" t="inlineStr">
         <is>
           <t>StatModifier</t>
         </is>
       </c>
-      <c r="U54" s="31" t="inlineStr">
+      <c r="W54" s="31" t="inlineStr">
         <is>
           <t>AttackSpeed</t>
         </is>
       </c>
-      <c r="V54" s="31" t="inlineStr">
+      <c r="X54" s="31" t="inlineStr">
         <is>
           <t>Multiply</t>
         </is>
       </c>
-      <c r="W54" s="31" t="inlineStr">
+      <c r="Y54" s="31" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="X54" s="31" t="inlineStr">
+      <c r="Z54" s="31" t="inlineStr">
         <is>
           <t>Part.StatModifier</t>
         </is>
       </c>
-      <c r="Y54" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="Z54" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AA54" s="31" t="inlineStr">
         <is>
           <t>None</t>
@@ -19337,36 +19413,46 @@
       </c>
       <c r="AB54" s="31" t="inlineStr">
         <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC54" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD54" s="31" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AC54" s="31" t="inlineStr">
+      <c r="AE54" s="31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AD54" s="31" t="inlineStr">
+      <c r="AF54" s="31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AE54" s="31" t="inlineStr">
+      <c r="AG54" s="31" t="inlineStr">
         <is>
           <t>Stackable</t>
         </is>
       </c>
-      <c r="AF54" s="31" t="inlineStr">
+      <c r="AH54" s="31" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="AG54" s="31" t="n"/>
-      <c r="AH54" s="31" t="inlineStr">
+      <c r="AI54" s="31" t="n"/>
+      <c r="AJ54" s="31" t="inlineStr">
         <is>
           <t>武器插槽C</t>
         </is>
       </c>
-      <c r="AI54" s="31" t="inlineStr">
+      <c r="AK54" s="31" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -19439,98 +19525,106 @@
           <t>11</t>
         </is>
       </c>
-      <c r="P55" s="31" t="inlineStr">
+      <c r="O55" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P55" t="n" s="31">
+        <v>0</v>
+      </c>
+      <c r="R55" s="31" t="inlineStr">
         <is>
           <t>PE_DAGGER_HOLY_KILL_HEAL</t>
         </is>
       </c>
-      <c r="Q55" s="31" t="inlineStr">
+      <c r="S55" s="31" t="inlineStr">
         <is>
           <t>P_DAGGER_HOLY_BLADE</t>
         </is>
       </c>
-      <c r="R55" s="31" t="inlineStr">
+      <c r="T55" s="31" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="S55" s="31" t="inlineStr">
+      <c r="U55" s="31" t="inlineStr">
         <is>
           <t>OnKill</t>
         </is>
       </c>
-      <c r="T55" s="31" t="inlineStr">
+      <c r="V55" s="31" t="inlineStr">
         <is>
           <t>UniqueBehavior</t>
         </is>
       </c>
-      <c r="U55" s="31" t="inlineStr">
+      <c r="W55" s="31" t="inlineStr">
         <is>
           <t>OnKill</t>
         </is>
       </c>
-      <c r="V55" s="31" t="inlineStr">
+      <c r="X55" s="31" t="inlineStr">
         <is>
           <t>Add</t>
         </is>
       </c>
-      <c r="W55" s="31" t="inlineStr">
+      <c r="Y55" s="31" t="inlineStr">
         <is>
           <t>0.05</t>
         </is>
       </c>
-      <c r="X55" s="31" t="inlineStr">
+      <c r="Z55" s="31" t="inlineStr">
         <is>
           <t>Part.OnKillHealPercent</t>
         </is>
       </c>
-      <c r="Y55" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="Z55" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AA55" s="31" t="inlineStr">
         <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB55" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC55" s="31" t="inlineStr">
+        <is>
           <t>HealMaxHpPercent</t>
         </is>
       </c>
-      <c r="AB55" s="31" t="inlineStr">
+      <c r="AD55" s="31" t="inlineStr">
         <is>
           <t>0.05</t>
         </is>
       </c>
-      <c r="AC55" s="31" t="inlineStr">
+      <c r="AE55" s="31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AD55" s="31" t="inlineStr">
+      <c r="AF55" s="31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AE55" s="31" t="inlineStr">
+      <c r="AG55" s="31" t="inlineStr">
         <is>
           <t>Stackable</t>
         </is>
       </c>
-      <c r="AF55" s="31" t="inlineStr">
+      <c r="AH55" s="31" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="AG55" s="31" t="n"/>
-      <c r="AH55" s="31" t="inlineStr">
+      <c r="AI55" s="31" t="n"/>
+      <c r="AJ55" s="31" t="inlineStr">
         <is>
           <t>武器插槽C</t>
         </is>
       </c>
-      <c r="AI55" s="31" t="inlineStr">
+      <c r="AK55" s="31" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -19607,6 +19701,14 @@
           <t>12</t>
         </is>
       </c>
+      <c r="O56" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P56" t="n" s="31">
+        <v>0</v>
+      </c>
     </row>
     <row r="57" ht="22" customHeight="1" s="32">
       <c r="A57" s="31" t="inlineStr">
@@ -19679,6 +19781,14 @@
           <t>13</t>
         </is>
       </c>
+      <c r="O57" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P57" t="n" s="31">
+        <v>0</v>
+      </c>
     </row>
     <row r="58" ht="22" customHeight="1" s="32">
       <c r="A58" s="31" t="inlineStr">
@@ -19747,6 +19857,14 @@
           <t>14</t>
         </is>
       </c>
+      <c r="O58" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+      <c r="P58" t="n" s="31">
+        <v>10</v>
+      </c>
     </row>
     <row r="59" ht="22" customHeight="1" s="32">
       <c r="A59" s="31" t="inlineStr">
@@ -19819,6 +19937,14 @@
           <t>15</t>
         </is>
       </c>
+      <c r="O59" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P59" t="n" s="31">
+        <v>0</v>
+      </c>
     </row>
     <row r="60" ht="30" customHeight="1" s="32">
       <c r="A60" s="31" t="inlineStr">
@@ -19892,6 +20018,14 @@
           <t>16</t>
         </is>
       </c>
+      <c r="O60" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P60" t="n" s="31">
+        <v>0</v>
+      </c>
     </row>
     <row r="61" ht="22" customHeight="1" s="32">
       <c r="A61" s="31" t="inlineStr">
@@ -19964,6 +20098,14 @@
           <t>17</t>
         </is>
       </c>
+      <c r="O61" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P61" t="n" s="31">
+        <v>0</v>
+      </c>
     </row>
     <row r="62" ht="22" customHeight="1" s="32">
       <c r="A62" s="31" t="inlineStr">
@@ -20036,6 +20178,14 @@
           <t>18</t>
         </is>
       </c>
+      <c r="O62" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P62" t="n" s="31">
+        <v>0</v>
+      </c>
     </row>
     <row r="63" ht="22" customHeight="1" s="32">
       <c r="A63" s="31" t="inlineStr">
@@ -20104,6 +20254,14 @@
           <t>19</t>
         </is>
       </c>
+      <c r="O63" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P63" t="n" s="31">
+        <v>0</v>
+      </c>
     </row>
     <row r="64" ht="22" customHeight="1" s="32">
       <c r="A64" s="31" t="inlineStr">
@@ -20176,6 +20334,14 @@
           <t>20</t>
         </is>
       </c>
+      <c r="O64" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P64" t="n" s="31">
+        <v>0</v>
+      </c>
     </row>
     <row r="65" ht="22" customHeight="1" s="32">
       <c r="A65" s="31" t="inlineStr">
@@ -20244,6 +20410,14 @@
           <t>21</t>
         </is>
       </c>
+      <c r="O65" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P65" t="n" s="31">
+        <v>0</v>
+      </c>
     </row>
     <row r="66" ht="22" customHeight="1" s="32">
       <c r="A66" s="31" t="inlineStr">
@@ -20312,6 +20486,14 @@
           <t>22</t>
         </is>
       </c>
+      <c r="O66" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P66" t="n" s="31">
+        <v>0</v>
+      </c>
     </row>
     <row r="67" ht="22" customHeight="1" s="32">
       <c r="A67" s="31" t="inlineStr">
@@ -20380,6 +20562,14 @@
           <t>23</t>
         </is>
       </c>
+      <c r="O67" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P67" t="n" s="31">
+        <v>0</v>
+      </c>
     </row>
     <row r="68" ht="22" customHeight="1" s="32">
       <c r="A68" s="31" t="inlineStr">
@@ -20448,6 +20638,14 @@
           <t>24</t>
         </is>
       </c>
+      <c r="O68" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P68" t="n" s="31">
+        <v>0</v>
+      </c>
     </row>
     <row r="69" ht="22" customHeight="1" s="32">
       <c r="A69" s="31" t="inlineStr">
@@ -20516,6 +20714,14 @@
           <t>25</t>
         </is>
       </c>
+      <c r="O69" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P69" t="n" s="31">
+        <v>0</v>
+      </c>
     </row>
     <row r="70" ht="22" customHeight="1" s="32">
       <c r="A70" s="31" t="inlineStr">
@@ -20584,6 +20790,14 @@
           <t>26</t>
         </is>
       </c>
+      <c r="O70" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P70" t="n" s="31">
+        <v>0</v>
+      </c>
     </row>
     <row r="71" ht="22" customHeight="1" s="32">
       <c r="A71" s="31" t="inlineStr">
@@ -20652,6 +20866,14 @@
           <t>27</t>
         </is>
       </c>
+      <c r="O71" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P71" t="n" s="31">
+        <v>0</v>
+      </c>
     </row>
     <row r="72" ht="22" customHeight="1" s="32">
       <c r="A72" s="31" t="inlineStr">
@@ -20720,6 +20942,14 @@
           <t>28</t>
         </is>
       </c>
+      <c r="O72" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P72" t="n" s="31">
+        <v>0</v>
+      </c>
     </row>
     <row r="73" ht="22" customHeight="1" s="32">
       <c r="A73" s="31" t="inlineStr">
@@ -20788,6 +21018,14 @@
           <t>29</t>
         </is>
       </c>
+      <c r="O73" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P73" t="n" s="31">
+        <v>0</v>
+      </c>
     </row>
     <row r="74" ht="22" customHeight="1" s="32">
       <c r="A74" s="31" t="inlineStr">
@@ -20856,6 +21094,14 @@
           <t>30</t>
         </is>
       </c>
+      <c r="O74" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P74" t="n" s="31">
+        <v>0</v>
+      </c>
     </row>
     <row r="75" ht="22" customHeight="1" s="32">
       <c r="A75" s="31" t="inlineStr">
@@ -20924,6 +21170,14 @@
           <t>31</t>
         </is>
       </c>
+      <c r="O75" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P75" t="n" s="31">
+        <v>0</v>
+      </c>
     </row>
     <row r="76" ht="22" customHeight="1" s="32">
       <c r="A76" s="31" t="inlineStr">
@@ -20992,6 +21246,14 @@
           <t>32</t>
         </is>
       </c>
+      <c r="O76" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P76" t="n" s="31">
+        <v>0</v>
+      </c>
     </row>
     <row r="77" ht="22" customHeight="1" s="32">
       <c r="A77" s="31" t="inlineStr">
@@ -21060,6 +21322,14 @@
           <t>33</t>
         </is>
       </c>
+      <c r="O77" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P77" t="n" s="31">
+        <v>0</v>
+      </c>
     </row>
     <row r="78" ht="22" customHeight="1" s="32">
       <c r="A78" s="31" t="inlineStr">
@@ -21127,6 +21397,14 @@
         <is>
           <t>34</t>
         </is>
+      </c>
+      <c r="O78" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P78" t="n" s="31">
+        <v>0</v>
       </c>
     </row>
     <row r="79" ht="75" customHeight="1" s="32">
@@ -21200,6 +21478,14 @@
           <t>35</t>
         </is>
       </c>
+      <c r="O79" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P79" t="n" s="31">
+        <v>0</v>
+      </c>
     </row>
     <row r="80" ht="22" customHeight="1" s="32">
       <c r="A80" s="31" t="inlineStr">
@@ -21268,6 +21554,14 @@
           <t>36</t>
         </is>
       </c>
+      <c r="O80" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P80" t="n" s="31">
+        <v>0</v>
+      </c>
     </row>
     <row r="81" ht="22" customHeight="1" s="32">
       <c r="A81" s="31" t="inlineStr">
@@ -21336,6 +21630,14 @@
           <t>37</t>
         </is>
       </c>
+      <c r="O81" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P81" t="n" s="31">
+        <v>0</v>
+      </c>
     </row>
     <row r="82" ht="22" customHeight="1" s="32">
       <c r="A82" s="31" t="inlineStr">
@@ -21404,6 +21706,14 @@
           <t>38</t>
         </is>
       </c>
+      <c r="O82" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P82" t="n" s="31">
+        <v>0</v>
+      </c>
     </row>
     <row r="83" ht="22" customHeight="1" s="32">
       <c r="A83" s="31" t="inlineStr">
@@ -21472,6 +21782,14 @@
           <t>39</t>
         </is>
       </c>
+      <c r="O83" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P83" t="n" s="31">
+        <v>0</v>
+      </c>
     </row>
     <row r="84" ht="22" customHeight="1" s="32">
       <c r="A84" s="31" t="inlineStr">
@@ -21540,6 +21858,14 @@
           <t>40</t>
         </is>
       </c>
+      <c r="O84" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P84" t="n" s="31">
+        <v>0</v>
+      </c>
     </row>
     <row r="85" ht="22" customHeight="1" s="32">
       <c r="A85" s="31" t="inlineStr">
@@ -21607,6 +21933,14 @@
         <is>
           <t>41</t>
         </is>
+      </c>
+      <c r="O85" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P85" t="n" s="31">
+        <v>0</v>
       </c>
     </row>
     <row r="86" ht="45" customHeight="1" s="32">
@@ -21678,6 +22012,14 @@
           <t>42</t>
         </is>
       </c>
+      <c r="O86" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P86" t="n" s="31">
+        <v>0</v>
+      </c>
     </row>
     <row r="87" ht="22" customHeight="1" s="32">
       <c r="A87" s="31" t="inlineStr">
@@ -21746,6 +22088,14 @@
           <t>43</t>
         </is>
       </c>
+      <c r="O87" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P87" t="n" s="31">
+        <v>0</v>
+      </c>
     </row>
     <row r="88" ht="22" customHeight="1" s="32">
       <c r="A88" s="31" t="inlineStr">
@@ -21814,6 +22164,14 @@
           <t>44</t>
         </is>
       </c>
+      <c r="O88" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P88" t="n" s="31">
+        <v>0</v>
+      </c>
     </row>
     <row r="89" ht="22" customHeight="1" s="32">
       <c r="A89" s="31" t="inlineStr">
@@ -21882,6 +22240,14 @@
           <t>45</t>
         </is>
       </c>
+      <c r="O89" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P89" t="n" s="31">
+        <v>0</v>
+      </c>
     </row>
     <row r="90" ht="22" customHeight="1" s="32">
       <c r="A90" s="31" t="inlineStr">
@@ -21950,6 +22316,14 @@
           <t>46</t>
         </is>
       </c>
+      <c r="O90" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P90" t="n" s="31">
+        <v>0</v>
+      </c>
     </row>
     <row r="91" ht="22" customHeight="1" s="32">
       <c r="A91" s="31" t="inlineStr">
@@ -22018,6 +22392,14 @@
           <t>47</t>
         </is>
       </c>
+      <c r="O91" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P91" t="n" s="31">
+        <v>0</v>
+      </c>
     </row>
     <row r="92" ht="22" customHeight="1" s="32">
       <c r="A92" s="31" t="inlineStr">
@@ -22086,6 +22468,14 @@
           <t>48</t>
         </is>
       </c>
+      <c r="O92" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P92" t="n" s="31">
+        <v>0</v>
+      </c>
     </row>
     <row r="93" ht="22" customHeight="1" s="32">
       <c r="A93" s="31" t="inlineStr">
@@ -22154,6 +22544,14 @@
           <t>49</t>
         </is>
       </c>
+      <c r="O93" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P93" t="n" s="31">
+        <v>0</v>
+      </c>
     </row>
     <row r="94" ht="22" customHeight="1" s="32">
       <c r="A94" s="31" t="inlineStr">
@@ -22222,6 +22620,14 @@
           <t>50</t>
         </is>
       </c>
+      <c r="O94" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P94" t="n" s="31">
+        <v>0</v>
+      </c>
     </row>
     <row r="95" ht="22" customHeight="1" s="32">
       <c r="A95" s="31" t="inlineStr">
@@ -22290,6 +22696,14 @@
           <t>51</t>
         </is>
       </c>
+      <c r="O95" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P95" t="n" s="31">
+        <v>0</v>
+      </c>
     </row>
     <row r="96" ht="22" customHeight="1" s="32">
       <c r="A96" s="31" t="inlineStr">
@@ -22358,6 +22772,14 @@
           <t>52</t>
         </is>
       </c>
+      <c r="O96" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P96" t="n" s="31">
+        <v>0</v>
+      </c>
     </row>
     <row r="97" ht="22" customHeight="1" s="32">
       <c r="A97" s="31" t="inlineStr">
@@ -22426,6 +22848,14 @@
           <t>53</t>
         </is>
       </c>
+      <c r="O97" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P97" t="n" s="31">
+        <v>0</v>
+      </c>
     </row>
     <row r="98" ht="22" customHeight="1" s="32">
       <c r="A98" s="31" t="inlineStr">
@@ -22494,6 +22924,14 @@
           <t>54</t>
         </is>
       </c>
+      <c r="O98" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P98" t="n" s="31">
+        <v>0</v>
+      </c>
     </row>
     <row r="99" ht="22" customHeight="1" s="32">
       <c r="A99" s="31" t="inlineStr">
@@ -22562,6 +23000,14 @@
           <t>55</t>
         </is>
       </c>
+      <c r="O99" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P99" t="n" s="31">
+        <v>0</v>
+      </c>
     </row>
     <row r="100" ht="22" customHeight="1" s="32">
       <c r="A100" s="31" t="inlineStr">
@@ -22630,6 +23076,14 @@
           <t>56</t>
         </is>
       </c>
+      <c r="O100" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P100" t="n" s="31">
+        <v>0</v>
+      </c>
     </row>
     <row r="101" ht="22" customHeight="1" s="32">
       <c r="A101" s="31" t="inlineStr">
@@ -22698,6 +23152,14 @@
           <t>57</t>
         </is>
       </c>
+      <c r="O101" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P101" t="n" s="31">
+        <v>0</v>
+      </c>
     </row>
     <row r="102" ht="22" customHeight="1" s="32">
       <c r="A102" s="31" t="inlineStr">
@@ -22766,6 +23228,14 @@
           <t>58</t>
         </is>
       </c>
+      <c r="O102" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P102" t="n" s="31">
+        <v>0</v>
+      </c>
     </row>
     <row r="103" ht="22" customHeight="1" s="32">
       <c r="A103" s="31" t="inlineStr">
@@ -22834,6 +23304,14 @@
           <t>59</t>
         </is>
       </c>
+      <c r="O103" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P103" t="n" s="31">
+        <v>0</v>
+      </c>
     </row>
     <row r="104" ht="22" customHeight="1" s="32">
       <c r="A104" s="31" t="inlineStr">
@@ -22902,6 +23380,14 @@
           <t>60</t>
         </is>
       </c>
+      <c r="O104" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P104" t="n" s="31">
+        <v>0</v>
+      </c>
     </row>
     <row r="105" ht="22" customHeight="1" s="32">
       <c r="A105" s="31" t="inlineStr">
@@ -22970,6 +23456,14 @@
           <t>61</t>
         </is>
       </c>
+      <c r="O105" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P105" t="n" s="31">
+        <v>0</v>
+      </c>
     </row>
     <row r="106" ht="22" customHeight="1" s="32">
       <c r="A106" s="31" t="inlineStr">
@@ -23037,6 +23531,14 @@
         <is>
           <t>62</t>
         </is>
+      </c>
+      <c r="O106" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P106" t="n" s="31">
+        <v>0</v>
       </c>
     </row>
     <row r="107" ht="75" customHeight="1" s="32">
@@ -23110,6 +23612,14 @@
           <t>63</t>
         </is>
       </c>
+      <c r="O107" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P107" t="n" s="31">
+        <v>0</v>
+      </c>
     </row>
     <row r="108" ht="22" customHeight="1" s="32">
       <c r="A108" s="31" t="inlineStr">
@@ -23178,6 +23688,14 @@
           <t>64</t>
         </is>
       </c>
+      <c r="O108" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P108" t="n" s="31">
+        <v>0</v>
+      </c>
     </row>
     <row r="109" ht="22" customHeight="1" s="32">
       <c r="A109" s="31" t="inlineStr">
@@ -23246,6 +23764,14 @@
           <t>65</t>
         </is>
       </c>
+      <c r="O109" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P109" t="n" s="31">
+        <v>0</v>
+      </c>
     </row>
     <row r="110" ht="22" customHeight="1" s="32">
       <c r="A110" s="31" t="inlineStr">
@@ -23314,6 +23840,14 @@
           <t>66</t>
         </is>
       </c>
+      <c r="O110" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P110" t="n" s="31">
+        <v>0</v>
+      </c>
     </row>
     <row r="111" ht="22" customHeight="1" s="32">
       <c r="A111" s="31" t="inlineStr">
@@ -23382,6 +23916,14 @@
           <t>67</t>
         </is>
       </c>
+      <c r="O111" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P111" t="n" s="31">
+        <v>0</v>
+      </c>
     </row>
     <row r="112" ht="22" customHeight="1" s="32">
       <c r="A112" s="31" t="inlineStr">
@@ -23450,6 +23992,14 @@
           <t>68</t>
         </is>
       </c>
+      <c r="O112" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P112" t="n" s="31">
+        <v>0</v>
+      </c>
     </row>
     <row r="113" ht="22" customHeight="1" s="32">
       <c r="A113" s="31" t="inlineStr">
@@ -23518,6 +24068,14 @@
           <t>69</t>
         </is>
       </c>
+      <c r="O113" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P113" t="n" s="31">
+        <v>0</v>
+      </c>
     </row>
     <row r="114" ht="22" customHeight="1" s="32">
       <c r="A114" s="31" t="inlineStr">
@@ -23586,6 +24144,14 @@
           <t>70</t>
         </is>
       </c>
+      <c r="O114" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P114" t="n" s="31">
+        <v>0</v>
+      </c>
     </row>
     <row r="115" ht="22" customHeight="1" s="32">
       <c r="A115" s="31" t="inlineStr">
@@ -23654,6 +24220,14 @@
           <t>71</t>
         </is>
       </c>
+      <c r="O115" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P115" t="n" s="31">
+        <v>0</v>
+      </c>
     </row>
     <row r="116" ht="22" customHeight="1" s="32">
       <c r="A116" s="31" t="inlineStr">
@@ -23722,6 +24296,14 @@
           <t>72</t>
         </is>
       </c>
+      <c r="O116" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P116" t="n" s="31">
+        <v>0</v>
+      </c>
     </row>
     <row r="117" ht="22" customHeight="1" s="32">
       <c r="A117" s="31" t="inlineStr">
@@ -23790,6 +24372,14 @@
           <t>73</t>
         </is>
       </c>
+      <c r="O117" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P117" t="n" s="31">
+        <v>0</v>
+      </c>
     </row>
     <row r="118" ht="22" customHeight="1" s="32">
       <c r="A118" s="31" t="inlineStr">
@@ -23858,6 +24448,14 @@
           <t>74</t>
         </is>
       </c>
+      <c r="O118" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P118" t="n" s="31">
+        <v>0</v>
+      </c>
     </row>
     <row r="119" ht="22" customHeight="1" s="32">
       <c r="A119" s="31" t="inlineStr">
@@ -23926,6 +24524,14 @@
           <t>75</t>
         </is>
       </c>
+      <c r="O119" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P119" t="n" s="31">
+        <v>0</v>
+      </c>
     </row>
     <row r="120" ht="22" customHeight="1" s="32">
       <c r="A120" s="31" t="inlineStr">
@@ -23994,6 +24600,14 @@
           <t>76</t>
         </is>
       </c>
+      <c r="O120" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P120" t="n" s="31">
+        <v>0</v>
+      </c>
     </row>
     <row r="121" ht="22" customHeight="1" s="32">
       <c r="A121" s="31" t="inlineStr">
@@ -24062,6 +24676,14 @@
           <t>77</t>
         </is>
       </c>
+      <c r="O121" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P121" t="n" s="31">
+        <v>0</v>
+      </c>
     </row>
     <row r="122" ht="22" customHeight="1" s="32">
       <c r="A122" s="31" t="inlineStr">
@@ -24130,6 +24752,14 @@
           <t>78</t>
         </is>
       </c>
+      <c r="O122" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P122" t="n" s="31">
+        <v>0</v>
+      </c>
     </row>
     <row r="123" ht="22" customHeight="1" s="32">
       <c r="A123" s="31" t="inlineStr">
@@ -24197,6 +24827,14 @@
         <is>
           <t>79</t>
         </is>
+      </c>
+      <c r="O123" t="inlineStr" s="31">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P123" t="n" s="31">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -24208,7 +24846,7 @@
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A44:D44"/>
   </mergeCells>
-  <dataValidations count="23">
+  <dataValidations count="25">
     <dataValidation sqref="C4:C15" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
       <formula1>=DV_Logic_SlotTypes_Enabled</formula1>
     </dataValidation>
@@ -24245,46 +24883,53 @@
     <dataValidation sqref="K46:K123" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
       <formula1>=DV_Logic_Parts_ImplementationStatus</formula1>
     </dataValidation>
-    <dataValidation sqref="Q46:Q55" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
+    <dataValidation sqref="S46:S55" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
       <formula1>INDIRECT("tblParts[PartId]")</formula1>
     </dataValidation>
-    <dataValidation sqref="S46:S55" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
+    <dataValidation sqref="U46:U55" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
       <formula1>=DV_Logic_PartEffects_Trigger</formula1>
     </dataValidation>
-    <dataValidation sqref="T46:T55" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
+    <dataValidation sqref="V46:V55" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
       <formula1>=DV_Logic_PartEffects_EffectKind</formula1>
     </dataValidation>
-    <dataValidation sqref="U46:U55" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
+    <dataValidation sqref="W46:W55" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
       <formula1>=DV_Logic_PartEffects_Target</formula1>
     </dataValidation>
-    <dataValidation sqref="V46:V55" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
+    <dataValidation sqref="X46:X55" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
       <formula1>=DV_Logic_PartEffects_ValueOp</formula1>
     </dataValidation>
-    <dataValidation sqref="X46:X55" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
+    <dataValidation sqref="Z46:Z55" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
       <formula1>=DV_Logic_PartEffects_BehaviorId</formula1>
     </dataValidation>
-    <dataValidation sqref="Y46:Y55" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
+    <dataValidation sqref="AA46:AA55" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
       <formula1>=DV_Logic_PartEffects_FormulaId</formula1>
     </dataValidation>
-    <dataValidation sqref="Z46:Z55" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
+    <dataValidation sqref="AB46:AB55" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
       <formula1>=DV_Logic_PartEffects_AttackPatternId</formula1>
     </dataValidation>
-    <dataValidation sqref="AA46:AA55" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
+    <dataValidation sqref="AC46:AC55" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
       <formula1>=DV_Logic_PartEffects_ParamName</formula1>
     </dataValidation>
-    <dataValidation sqref="AE46:AE55" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
+    <dataValidation sqref="AG46:AG55" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
       <formula1>=DV_Logic_PartEffects_StackPolicy</formula1>
     </dataValidation>
-    <dataValidation sqref="AF46:AF55" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
+    <dataValidation sqref="AH46:AH55" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
       <formula1>=DV_Logic_PartEffects_Enabled</formula1>
+    </dataValidation>
+    <dataValidation sqref="O46:O123" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
+      <formula1>=DV_Logic_Parts_Enabled</formula1>
+    </dataValidation>
+    <dataValidation sqref="P46:P123" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" type="whole" operator="between" errorStyle="stop" errorTitle="无效数值" error="请输入 0 到 100000 之间的整数。" promptTitle="商店价格" prompt="未上架填 0；上架符文必须填写正整数价格。">
+      <formula1>0</formula1>
+      <formula2>100000</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="4">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
   </tableParts>
 </worksheet>
 </file>

--- a/Design/Data/ReEchoData.xlsx
+++ b/Design/Data/ReEchoData.xlsx
@@ -15,6 +15,7 @@
     <sheet name="_WorkbookMeta" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="_ExportMap" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="_SystemData" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="AttributeCatalog" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName name="DV_Logic_Elements_Id">'_SystemData'!$R$2:$R$5</definedName>
@@ -97,7 +98,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode=";;;"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <name val="等线"/>
       <color theme="1"/>
@@ -169,6 +170,9 @@
     </font>
     <font>
       <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="11">
@@ -247,7 +251,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -361,6 +365,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
@@ -576,7 +584,7 @@
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="tblExportMap" displayName="tblExportMap" ref="A1:E17" headerRowCount="1" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="tblExportMap" displayName="tblExportMap" ref="A1:E18" headerRowCount="1" totalsRowShown="0">
   <tableColumns count="5">
     <tableColumn id="1" name="SheetName"/>
     <tableColumn id="2" name="TableName"/>
@@ -616,6 +624,22 @@
     <tableColumn id="5" name="Value"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="tblAttributes" displayName="tblAttributes" ref="A1:G9" headerRowCount="1">
+  <autoFilter ref="A1:G9"/>
+  <tableColumns count="7">
+    <tableColumn id="1" name="Id"/>
+    <tableColumn id="2" name="DisplayName"/>
+    <tableColumn id="3" name="Tier"/>
+    <tableColumn id="4" name="IconName"/>
+    <tableColumn id="5" name="ValueKind"/>
+    <tableColumn id="6" name="DisplayOrder"/>
+    <tableColumn id="7" name="Explanation"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
 </file>
 
@@ -2620,7 +2644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <cols>
     <col width="13" customWidth="1" style="28" min="1" max="1"/>
@@ -3086,6 +3110,33 @@
       <c r="E17" s="31" t="inlineStr">
         <is>
           <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>AttributeCatalog</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>tblAttributes</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>attributes.csv</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
     </row>
@@ -5591,6 +5642,327 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00FFC000"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="39" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="B1" s="39" t="inlineStr">
+        <is>
+          <t>DisplayName</t>
+        </is>
+      </c>
+      <c r="C1" s="39" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="D1" s="39" t="inlineStr">
+        <is>
+          <t>IconName</t>
+        </is>
+      </c>
+      <c r="E1" s="39" t="inlineStr">
+        <is>
+          <t>ValueKind</t>
+        </is>
+      </c>
+      <c r="F1" s="39" t="inlineStr">
+        <is>
+          <t>DisplayOrder</t>
+        </is>
+      </c>
+      <c r="G1" s="39" t="inlineStr">
+        <is>
+          <t>Explanation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="40" t="inlineStr">
+        <is>
+          <t>S_HP</t>
+        </is>
+      </c>
+      <c r="B2" s="40" t="inlineStr">
+        <is>
+          <t>生命值</t>
+        </is>
+      </c>
+      <c r="C2" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="40" t="inlineStr">
+        <is>
+          <t>生命值</t>
+        </is>
+      </c>
+      <c r="E2" s="40" t="inlineStr">
+        <is>
+          <t>Absolute</t>
+        </is>
+      </c>
+      <c r="F2" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="40" t="inlineStr">
+        <is>
+          <t>角色受到伤害的承受上限</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="40" t="inlineStr">
+        <is>
+          <t>S_P_Attack_Power</t>
+        </is>
+      </c>
+      <c r="B3" s="40" t="inlineStr">
+        <is>
+          <t>物理攻击力</t>
+        </is>
+      </c>
+      <c r="C3" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="40" t="inlineStr">
+        <is>
+          <t>物理攻击力</t>
+        </is>
+      </c>
+      <c r="E3" s="40" t="inlineStr">
+        <is>
+          <t>Absolute</t>
+        </is>
+      </c>
+      <c r="F3" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" s="40" t="inlineStr">
+        <is>
+          <t>物理系攻击加值</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="40" t="inlineStr">
+        <is>
+          <t>S_E_Attack_Power</t>
+        </is>
+      </c>
+      <c r="B4" s="40" t="inlineStr">
+        <is>
+          <t>元素攻击力</t>
+        </is>
+      </c>
+      <c r="C4" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="40" t="inlineStr">
+        <is>
+          <t>元素攻击力</t>
+        </is>
+      </c>
+      <c r="E4" s="40" t="inlineStr">
+        <is>
+          <t>Absolute</t>
+        </is>
+      </c>
+      <c r="F4" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="G4" s="40" t="inlineStr">
+        <is>
+          <t>元素系攻击加值</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="40" t="inlineStr">
+        <is>
+          <t>S_Movement_Speed</t>
+        </is>
+      </c>
+      <c r="B5" s="40" t="inlineStr">
+        <is>
+          <t>移动速度</t>
+        </is>
+      </c>
+      <c r="C5" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="40" t="inlineStr">
+        <is>
+          <t>移动速度</t>
+        </is>
+      </c>
+      <c r="E5" s="40" t="inlineStr">
+        <is>
+          <t>Percent</t>
+        </is>
+      </c>
+      <c r="F5" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" s="40" t="inlineStr">
+        <is>
+          <t>角色移动速度（以百分比表示）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="40" t="inlineStr">
+        <is>
+          <t>S_Critical_Hit_Rate</t>
+        </is>
+      </c>
+      <c r="B6" s="40" t="inlineStr">
+        <is>
+          <t>暴击率</t>
+        </is>
+      </c>
+      <c r="C6" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="40" t="inlineStr">
+        <is>
+          <t>暴击率</t>
+        </is>
+      </c>
+      <c r="E6" s="40" t="inlineStr">
+        <is>
+          <t>Percent</t>
+        </is>
+      </c>
+      <c r="F6" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="G6" s="40" t="inlineStr">
+        <is>
+          <t>触发暴击的概率</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="40" t="inlineStr">
+        <is>
+          <t>S_Critical_Hit_Effect</t>
+        </is>
+      </c>
+      <c r="B7" s="40" t="inlineStr">
+        <is>
+          <t>暴击效果</t>
+        </is>
+      </c>
+      <c r="C7" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="40" t="inlineStr">
+        <is>
+          <t>暴击效果</t>
+        </is>
+      </c>
+      <c r="E7" s="40" t="inlineStr">
+        <is>
+          <t>Percent</t>
+        </is>
+      </c>
+      <c r="F7" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="G7" s="40" t="inlineStr">
+        <is>
+          <t>暴击造成的额外伤害比例</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="40" t="inlineStr">
+        <is>
+          <t>S_Echo_Efficiency</t>
+        </is>
+      </c>
+      <c r="B8" s="40" t="inlineStr">
+        <is>
+          <t>回响效能</t>
+        </is>
+      </c>
+      <c r="C8" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="40" t="inlineStr">
+        <is>
+          <t>回响效能</t>
+        </is>
+      </c>
+      <c r="E8" s="40" t="inlineStr">
+        <is>
+          <t>Percent</t>
+        </is>
+      </c>
+      <c r="F8" s="40" t="n">
+        <v>7</v>
+      </c>
+      <c r="G8" s="40" t="inlineStr">
+        <is>
+          <t>回响造成的伤害效率</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="40" t="inlineStr">
+        <is>
+          <t>S_Elemental_Reaction_Efficiency</t>
+        </is>
+      </c>
+      <c r="B9" s="40" t="inlineStr">
+        <is>
+          <t>元素反应效能</t>
+        </is>
+      </c>
+      <c r="C9" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" s="40" t="inlineStr">
+        <is>
+          <t>元素反应效能</t>
+        </is>
+      </c>
+      <c r="E9" s="40" t="inlineStr">
+        <is>
+          <t>Percent</t>
+        </is>
+      </c>
+      <c r="F9" s="40" t="n">
+        <v>8</v>
+      </c>
+      <c r="G9" s="40" t="inlineStr">
+        <is>
+          <t>元素反应造成的效率</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
+  </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="1" sort="0"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -5878,9 +6250,6 @@
       </c>
       <c r="J7" s="37" t="n"/>
     </row>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
     <row r="11" ht="25" customHeight="1" s="32">
       <c r="A11" s="34" t="inlineStr">
         <is>
@@ -9471,7 +9840,6 @@
       </c>
       <c r="N45" s="37" t="n"/>
     </row>
-    <row r="46"/>
     <row r="47" ht="25" customHeight="1" s="32">
       <c r="A47" s="34" t="inlineStr">
         <is>
@@ -13013,8 +13381,6 @@
       <c r="V8" s="31" t="n"/>
       <c r="W8" s="31" t="n"/>
     </row>
-    <row r="9"/>
-    <row r="10"/>
     <row r="11" ht="25" customHeight="1" s="32">
       <c r="A11" s="34" t="inlineStr">
         <is>
@@ -13912,8 +14278,6 @@
       </c>
       <c r="P10" s="37" t="n"/>
     </row>
-    <row r="11"/>
-    <row r="12"/>
     <row r="13" ht="25" customHeight="1" s="32">
       <c r="A13" s="34" t="inlineStr">
         <is>
@@ -14646,8 +15010,6 @@
       </c>
       <c r="U20" s="37" t="n"/>
     </row>
-    <row r="21"/>
-    <row r="22"/>
     <row r="23" ht="25" customHeight="1" s="32">
       <c r="A23" s="34" t="inlineStr">
         <is>
@@ -16625,7 +16987,6 @@
       </c>
       <c r="F15" s="37" t="n"/>
     </row>
-    <row r="16"/>
     <row r="17" ht="25" customHeight="1" s="32">
       <c r="A17" s="34" t="inlineStr">
         <is>
@@ -17583,10 +17944,6 @@
       </c>
       <c r="I39" s="37" t="n"/>
     </row>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
     <row r="44" ht="25" customHeight="1" s="32">
       <c r="A44" s="34" t="inlineStr">
         <is>
@@ -24852,8 +25209,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6"/>
     <row r="7">
       <c r="B7" s="1" t="inlineStr">
         <is>
@@ -25452,7 +25807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="L1:L1"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="13.81640625" defaultRowHeight="13"/>
   <sheetData>
     <row r="1" ht="39" customHeight="1" s="32">

--- a/Design/Data/ReEchoData.xlsx
+++ b/Design/Data/ReEchoData.xlsx
@@ -525,7 +525,7 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="tblPartEffects" displayName="tblPartEffects" ref="R45:AK51" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="tblPartEffects" displayName="tblPartEffects" ref="R45:AK82" headerRowCount="1">
   <autoFilter ref="R45:AK55"/>
   <tableColumns count="20">
     <tableColumn id="16" name="Id"/>
@@ -18635,26 +18635,90 @@
           <t>0</t>
         </is>
       </c>
-      <c r="R52" s="31" t="n"/>
-      <c r="S52" s="31" t="n"/>
-      <c r="T52" s="31" t="n"/>
-      <c r="U52" s="31" t="n"/>
-      <c r="V52" s="31" t="n"/>
-      <c r="W52" s="31" t="n"/>
-      <c r="X52" s="31" t="n"/>
-      <c r="Y52" s="31" t="n"/>
-      <c r="Z52" s="31" t="n"/>
-      <c r="AA52" s="31" t="n"/>
-      <c r="AB52" s="31" t="n"/>
-      <c r="AC52" s="31" t="n"/>
-      <c r="AD52" s="31" t="n"/>
-      <c r="AE52" s="31" t="n"/>
-      <c r="AF52" s="31" t="n"/>
-      <c r="AG52" s="31" t="n"/>
-      <c r="AH52" s="31" t="n"/>
-      <c r="AI52" s="31" t="n"/>
-      <c r="AJ52" s="31" t="n"/>
-      <c r="AK52" s="31" t="n"/>
+      <c r="R52" s="37" t="inlineStr">
+        <is>
+          <t>PE_BOW_HASTE_BOWSTRING_1</t>
+        </is>
+      </c>
+      <c r="S52" s="37" t="inlineStr">
+        <is>
+          <t>P_BOW_HASTE_BOWSTRING</t>
+        </is>
+      </c>
+      <c r="T52" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" s="37" t="inlineStr">
+        <is>
+          <t>OnEquip</t>
+        </is>
+      </c>
+      <c r="V52" s="37" t="inlineStr">
+        <is>
+          <t>StatModifier</t>
+        </is>
+      </c>
+      <c r="W52" s="37" t="inlineStr">
+        <is>
+          <t>AttackSpeed</t>
+        </is>
+      </c>
+      <c r="X52" s="37" t="inlineStr">
+        <is>
+          <t>Multiply</t>
+        </is>
+      </c>
+      <c r="Y52" s="37" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z52" s="37" t="inlineStr">
+        <is>
+          <t>Part.StatModifier</t>
+        </is>
+      </c>
+      <c r="AA52" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB52" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC52" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD52" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE52" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF52" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG52" s="37" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="AH52" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI52" s="37" t="n"/>
+      <c r="AJ52" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK52" s="37" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="53" ht="22" customHeight="1" s="32">
       <c r="A53" s="37" t="inlineStr">
@@ -18737,26 +18801,90 @@
           <t>0</t>
         </is>
       </c>
-      <c r="R53" s="31" t="n"/>
-      <c r="S53" s="31" t="n"/>
-      <c r="T53" s="31" t="n"/>
-      <c r="U53" s="31" t="n"/>
-      <c r="V53" s="31" t="n"/>
-      <c r="W53" s="31" t="n"/>
-      <c r="X53" s="31" t="n"/>
-      <c r="Y53" s="31" t="n"/>
-      <c r="Z53" s="31" t="n"/>
-      <c r="AA53" s="31" t="n"/>
-      <c r="AB53" s="31" t="n"/>
-      <c r="AC53" s="31" t="n"/>
-      <c r="AD53" s="31" t="n"/>
-      <c r="AE53" s="31" t="n"/>
-      <c r="AF53" s="31" t="n"/>
-      <c r="AG53" s="31" t="n"/>
-      <c r="AH53" s="31" t="n"/>
-      <c r="AI53" s="31" t="n"/>
-      <c r="AJ53" s="31" t="n"/>
-      <c r="AK53" s="31" t="n"/>
+      <c r="R53" s="37" t="inlineStr">
+        <is>
+          <t>PE_BOW_HASTE_BOWSTRING_2</t>
+        </is>
+      </c>
+      <c r="S53" s="37" t="inlineStr">
+        <is>
+          <t>P_BOW_HASTE_BOWSTRING</t>
+        </is>
+      </c>
+      <c r="T53" s="37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" s="37" t="inlineStr">
+        <is>
+          <t>OnEquip</t>
+        </is>
+      </c>
+      <c r="V53" s="37" t="inlineStr">
+        <is>
+          <t>StatModifier</t>
+        </is>
+      </c>
+      <c r="W53" s="37" t="inlineStr">
+        <is>
+          <t>PhysicalCoefficient</t>
+        </is>
+      </c>
+      <c r="X53" s="37" t="inlineStr">
+        <is>
+          <t>Multiply</t>
+        </is>
+      </c>
+      <c r="Y53" s="37" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Z53" s="37" t="inlineStr">
+        <is>
+          <t>Part.StatModifier</t>
+        </is>
+      </c>
+      <c r="AA53" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB53" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC53" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD53" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE53" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF53" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG53" s="37" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="AH53" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI53" s="37" t="n"/>
+      <c r="AJ53" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK53" s="37" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="54" ht="22" customHeight="1" s="32">
       <c r="A54" s="37" t="inlineStr">
@@ -18839,26 +18967,90 @@
           <t>0</t>
         </is>
       </c>
-      <c r="R54" s="31" t="n"/>
-      <c r="S54" s="31" t="n"/>
-      <c r="T54" s="31" t="n"/>
-      <c r="U54" s="31" t="n"/>
-      <c r="V54" s="31" t="n"/>
-      <c r="W54" s="31" t="n"/>
-      <c r="X54" s="31" t="n"/>
-      <c r="Y54" s="31" t="n"/>
-      <c r="Z54" s="31" t="n"/>
-      <c r="AA54" s="31" t="n"/>
-      <c r="AB54" s="31" t="n"/>
-      <c r="AC54" s="31" t="n"/>
-      <c r="AD54" s="31" t="n"/>
-      <c r="AE54" s="31" t="n"/>
-      <c r="AF54" s="31" t="n"/>
-      <c r="AG54" s="31" t="n"/>
-      <c r="AH54" s="31" t="n"/>
-      <c r="AI54" s="31" t="n"/>
-      <c r="AJ54" s="31" t="n"/>
-      <c r="AK54" s="31" t="n"/>
+      <c r="R54" s="37" t="inlineStr">
+        <is>
+          <t>PE_BOW_HASTE_BOWSTRING_3</t>
+        </is>
+      </c>
+      <c r="S54" s="37" t="inlineStr">
+        <is>
+          <t>P_BOW_HASTE_BOWSTRING</t>
+        </is>
+      </c>
+      <c r="T54" s="37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U54" s="37" t="inlineStr">
+        <is>
+          <t>OnEquip</t>
+        </is>
+      </c>
+      <c r="V54" s="37" t="inlineStr">
+        <is>
+          <t>StatModifier</t>
+        </is>
+      </c>
+      <c r="W54" s="37" t="inlineStr">
+        <is>
+          <t>ElementalCoefficient</t>
+        </is>
+      </c>
+      <c r="X54" s="37" t="inlineStr">
+        <is>
+          <t>Multiply</t>
+        </is>
+      </c>
+      <c r="Y54" s="37" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Z54" s="37" t="inlineStr">
+        <is>
+          <t>Part.StatModifier</t>
+        </is>
+      </c>
+      <c r="AA54" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB54" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC54" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD54" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE54" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF54" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG54" s="37" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="AH54" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI54" s="37" t="n"/>
+      <c r="AJ54" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK54" s="37" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="55" ht="22" customHeight="1" s="32">
       <c r="A55" s="37" t="inlineStr">
@@ -18937,26 +19129,90 @@
           <t>0</t>
         </is>
       </c>
-      <c r="R55" s="31" t="n"/>
-      <c r="S55" s="31" t="n"/>
-      <c r="T55" s="31" t="n"/>
-      <c r="U55" s="31" t="n"/>
-      <c r="V55" s="31" t="n"/>
-      <c r="W55" s="31" t="n"/>
-      <c r="X55" s="31" t="n"/>
-      <c r="Y55" s="31" t="n"/>
-      <c r="Z55" s="31" t="n"/>
-      <c r="AA55" s="31" t="n"/>
-      <c r="AB55" s="31" t="n"/>
-      <c r="AC55" s="31" t="n"/>
-      <c r="AD55" s="31" t="n"/>
-      <c r="AE55" s="31" t="n"/>
-      <c r="AF55" s="31" t="n"/>
-      <c r="AG55" s="31" t="n"/>
-      <c r="AH55" s="31" t="n"/>
-      <c r="AI55" s="31" t="n"/>
-      <c r="AJ55" s="31" t="n"/>
-      <c r="AK55" s="31" t="n"/>
+      <c r="R55" s="37" t="inlineStr">
+        <is>
+          <t>PE_BOW_HEAVY_BOWSTRING_1</t>
+        </is>
+      </c>
+      <c r="S55" s="37" t="inlineStr">
+        <is>
+          <t>P_BOW_HEAVY_BOWSTRING</t>
+        </is>
+      </c>
+      <c r="T55" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" s="37" t="inlineStr">
+        <is>
+          <t>OnEquip</t>
+        </is>
+      </c>
+      <c r="V55" s="37" t="inlineStr">
+        <is>
+          <t>StatModifier</t>
+        </is>
+      </c>
+      <c r="W55" s="37" t="inlineStr">
+        <is>
+          <t>AttackSpeed</t>
+        </is>
+      </c>
+      <c r="X55" s="37" t="inlineStr">
+        <is>
+          <t>Multiply</t>
+        </is>
+      </c>
+      <c r="Y55" s="37" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Z55" s="37" t="inlineStr">
+        <is>
+          <t>Part.StatModifier</t>
+        </is>
+      </c>
+      <c r="AA55" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB55" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC55" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD55" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE55" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF55" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG55" s="37" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="AH55" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI55" s="37" t="n"/>
+      <c r="AJ55" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK55" s="37" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="56" ht="22" customHeight="1" s="32">
       <c r="A56" s="37" t="inlineStr">
@@ -19039,6 +19295,90 @@
           <t>0</t>
         </is>
       </c>
+      <c r="R56" s="37" t="inlineStr">
+        <is>
+          <t>PE_BOW_HEAVY_BOWSTRING_2</t>
+        </is>
+      </c>
+      <c r="S56" s="37" t="inlineStr">
+        <is>
+          <t>P_BOW_HEAVY_BOWSTRING</t>
+        </is>
+      </c>
+      <c r="T56" s="37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" s="37" t="inlineStr">
+        <is>
+          <t>OnEquip</t>
+        </is>
+      </c>
+      <c r="V56" s="37" t="inlineStr">
+        <is>
+          <t>StatModifier</t>
+        </is>
+      </c>
+      <c r="W56" s="37" t="inlineStr">
+        <is>
+          <t>PhysicalCoefficient</t>
+        </is>
+      </c>
+      <c r="X56" s="37" t="inlineStr">
+        <is>
+          <t>Multiply</t>
+        </is>
+      </c>
+      <c r="Y56" s="37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z56" s="37" t="inlineStr">
+        <is>
+          <t>Part.StatModifier</t>
+        </is>
+      </c>
+      <c r="AA56" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB56" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC56" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD56" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE56" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF56" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG56" s="37" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="AH56" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI56" s="37" t="n"/>
+      <c r="AJ56" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK56" s="37" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="57" ht="22" customHeight="1" s="32">
       <c r="A57" s="37" t="inlineStr">
@@ -19117,16 +19457,100 @@
           <t>0</t>
         </is>
       </c>
+      <c r="R57" s="37" t="inlineStr">
+        <is>
+          <t>PE_BOW_HEAVY_BOWSTRING_3</t>
+        </is>
+      </c>
+      <c r="S57" s="37" t="inlineStr">
+        <is>
+          <t>P_BOW_HEAVY_BOWSTRING</t>
+        </is>
+      </c>
+      <c r="T57" s="37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U57" s="37" t="inlineStr">
+        <is>
+          <t>OnEquip</t>
+        </is>
+      </c>
+      <c r="V57" s="37" t="inlineStr">
+        <is>
+          <t>StatModifier</t>
+        </is>
+      </c>
+      <c r="W57" s="37" t="inlineStr">
+        <is>
+          <t>ElementalCoefficient</t>
+        </is>
+      </c>
+      <c r="X57" s="37" t="inlineStr">
+        <is>
+          <t>Multiply</t>
+        </is>
+      </c>
+      <c r="Y57" s="37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z57" s="37" t="inlineStr">
+        <is>
+          <t>Part.StatModifier</t>
+        </is>
+      </c>
+      <c r="AA57" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB57" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC57" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD57" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE57" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF57" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG57" s="37" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="AH57" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI57" s="37" t="n"/>
+      <c r="AJ57" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK57" s="37" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="58" ht="22" customHeight="1" s="32">
       <c r="A58" s="37" t="inlineStr">
         <is>
-          <t>AUDIT_WEAPON_SLOTS_C_22</t>
+          <t>P_BOW_HASTE_BOWSTRING</t>
         </is>
       </c>
       <c r="B58" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>P_BOW_HASTE_BOWSTRING</t>
         </is>
       </c>
       <c r="C58" s="37" t="inlineStr">
@@ -19139,7 +19563,11 @@
           <t>Bowstring</t>
         </is>
       </c>
-      <c r="E58" s="37" t="n"/>
+      <c r="E58" s="37" t="inlineStr">
+        <is>
+          <t>攻速弓弦</t>
+        </is>
+      </c>
       <c r="F58" s="37" t="inlineStr">
         <is>
           <t>效果：攻击速度+60%，伤害倍率-40%</t>
@@ -19147,34 +19575,30 @@
       </c>
       <c r="G58" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="H58" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Bowstring|Numeric</t>
         </is>
       </c>
       <c r="I58" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="J58" s="37" t="inlineStr">
         <is>
-          <t>Unimplemented</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K58" s="37" t="inlineStr">
         <is>
-          <t>Disabled</t>
-        </is>
-      </c>
-      <c r="L58" s="37" t="inlineStr">
-        <is>
-          <t>Unnamed workbook row; no stable PartId assigned.</t>
-        </is>
-      </c>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="L58" s="37" t="n"/>
       <c r="M58" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -19187,24 +19611,106 @@
       </c>
       <c r="O58" s="37" t="inlineStr">
         <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="P58" s="37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="P58" s="37" t="n">
+        <v>30</v>
+      </c>
+      <c r="R58" s="37" t="inlineStr">
+        <is>
+          <t>PE_SCYTHE_HASTE_ROTARYBLADE_1</t>
+        </is>
+      </c>
+      <c r="S58" s="37" t="inlineStr">
+        <is>
+          <t>P_SCYTHE_HASTE_ROTARYBLADE</t>
+        </is>
+      </c>
+      <c r="T58" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" s="37" t="inlineStr">
+        <is>
+          <t>OnEquip</t>
+        </is>
+      </c>
+      <c r="V58" s="37" t="inlineStr">
+        <is>
+          <t>StatModifier</t>
+        </is>
+      </c>
+      <c r="W58" s="37" t="inlineStr">
+        <is>
+          <t>AttackSpeed</t>
+        </is>
+      </c>
+      <c r="X58" s="37" t="inlineStr">
+        <is>
+          <t>Multiply</t>
+        </is>
+      </c>
+      <c r="Y58" s="37" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z58" s="37" t="inlineStr">
+        <is>
+          <t>Part.StatModifier</t>
+        </is>
+      </c>
+      <c r="AA58" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB58" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC58" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD58" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE58" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF58" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG58" s="37" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="AH58" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI58" s="37" t="n"/>
+      <c r="AJ58" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK58" s="37" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="59" ht="22" customHeight="1" s="32">
       <c r="A59" s="37" t="inlineStr">
         <is>
-          <t>AUDIT_WEAPON_SLOTS_C_23</t>
+          <t>P_BOW_HEAVY_BOWSTRING</t>
         </is>
       </c>
       <c r="B59" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>P_BOW_HEAVY_BOWSTRING</t>
         </is>
       </c>
       <c r="C59" s="37" t="inlineStr">
@@ -19217,7 +19723,11 @@
           <t>Bowstring</t>
         </is>
       </c>
-      <c r="E59" s="37" t="n"/>
+      <c r="E59" s="37" t="inlineStr">
+        <is>
+          <t>重击弓弦</t>
+        </is>
+      </c>
       <c r="F59" s="37" t="inlineStr">
         <is>
           <t>效果：攻击速度-30%，伤害倍率+50%</t>
@@ -19225,34 +19735,30 @@
       </c>
       <c r="G59" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="H59" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Bowstring|Numeric</t>
         </is>
       </c>
       <c r="I59" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="J59" s="37" t="inlineStr">
         <is>
-          <t>Unimplemented</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K59" s="37" t="inlineStr">
         <is>
-          <t>Disabled</t>
-        </is>
-      </c>
-      <c r="L59" s="37" t="inlineStr">
-        <is>
-          <t>Unnamed workbook row; no stable PartId assigned.</t>
-        </is>
-      </c>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="L59" s="37" t="n"/>
       <c r="M59" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -19265,13 +19771,95 @@
       </c>
       <c r="O59" s="37" t="inlineStr">
         <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="P59" s="37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="P59" s="37" t="n">
+        <v>30</v>
+      </c>
+      <c r="R59" s="37" t="inlineStr">
+        <is>
+          <t>PE_SCYTHE_HASTE_ROTARYBLADE_2</t>
+        </is>
+      </c>
+      <c r="S59" s="37" t="inlineStr">
+        <is>
+          <t>P_SCYTHE_HASTE_ROTARYBLADE</t>
+        </is>
+      </c>
+      <c r="T59" s="37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" s="37" t="inlineStr">
+        <is>
+          <t>OnEquip</t>
+        </is>
+      </c>
+      <c r="V59" s="37" t="inlineStr">
+        <is>
+          <t>StatModifier</t>
+        </is>
+      </c>
+      <c r="W59" s="37" t="inlineStr">
+        <is>
+          <t>AttackRange</t>
+        </is>
+      </c>
+      <c r="X59" s="37" t="inlineStr">
+        <is>
+          <t>Multiply</t>
+        </is>
+      </c>
+      <c r="Y59" s="37" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Z59" s="37" t="inlineStr">
+        <is>
+          <t>Part.StatModifier</t>
+        </is>
+      </c>
+      <c r="AA59" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB59" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC59" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD59" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE59" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF59" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG59" s="37" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="AH59" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI59" s="37" t="n"/>
+      <c r="AJ59" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK59" s="37" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="60" ht="30" customHeight="1" s="32">
@@ -19351,6 +19939,90 @@
           <t>0</t>
         </is>
       </c>
+      <c r="R60" s="37" t="inlineStr">
+        <is>
+          <t>PE_LONGSWORD_NARROWWIDE_SWORDBLADE_1</t>
+        </is>
+      </c>
+      <c r="S60" s="37" t="inlineStr">
+        <is>
+          <t>P_LONGSWORD_NARROWWIDE_SWORDBLADE</t>
+        </is>
+      </c>
+      <c r="T60" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" s="37" t="inlineStr">
+        <is>
+          <t>OnEquip</t>
+        </is>
+      </c>
+      <c r="V60" s="37" t="inlineStr">
+        <is>
+          <t>StatModifier</t>
+        </is>
+      </c>
+      <c r="W60" s="37" t="inlineStr">
+        <is>
+          <t>AttackArc</t>
+        </is>
+      </c>
+      <c r="X60" s="37" t="inlineStr">
+        <is>
+          <t>Override</t>
+        </is>
+      </c>
+      <c r="Y60" s="37" t="n">
+        <v>120</v>
+      </c>
+      <c r="Z60" s="37" t="inlineStr">
+        <is>
+          <t>Part.StatModifier</t>
+        </is>
+      </c>
+      <c r="AA60" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB60" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC60" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD60" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE60" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF60" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG60" s="37" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="AH60" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI60" s="37" t="n"/>
+      <c r="AJ60" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK60" s="37" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="61" ht="22" customHeight="1" s="32">
       <c r="A61" s="37" t="inlineStr">
@@ -19429,6 +20101,90 @@
           <t>0</t>
         </is>
       </c>
+      <c r="R61" s="37" t="inlineStr">
+        <is>
+          <t>PE_LONGSWORD_NARROWWIDE_SWORDBLADE_2</t>
+        </is>
+      </c>
+      <c r="S61" s="37" t="inlineStr">
+        <is>
+          <t>P_LONGSWORD_NARROWWIDE_SWORDBLADE</t>
+        </is>
+      </c>
+      <c r="T61" s="37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" s="37" t="inlineStr">
+        <is>
+          <t>OnEquip</t>
+        </is>
+      </c>
+      <c r="V61" s="37" t="inlineStr">
+        <is>
+          <t>StatModifier</t>
+        </is>
+      </c>
+      <c r="W61" s="37" t="inlineStr">
+        <is>
+          <t>AttackRange</t>
+        </is>
+      </c>
+      <c r="X61" s="37" t="inlineStr">
+        <is>
+          <t>Multiply</t>
+        </is>
+      </c>
+      <c r="Y61" s="37" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z61" s="37" t="inlineStr">
+        <is>
+          <t>Part.StatModifier</t>
+        </is>
+      </c>
+      <c r="AA61" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB61" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC61" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD61" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE61" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF61" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG61" s="37" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="AH61" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI61" s="37" t="n"/>
+      <c r="AJ61" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK61" s="37" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="62" ht="22" customHeight="1" s="32">
       <c r="A62" s="37" t="inlineStr">
@@ -19507,6 +20263,90 @@
           <t>0</t>
         </is>
       </c>
+      <c r="R62" s="37" t="inlineStr">
+        <is>
+          <t>PE_LONGSWORD_SLOWWIDE_SWORDBLADE_1</t>
+        </is>
+      </c>
+      <c r="S62" s="37" t="inlineStr">
+        <is>
+          <t>P_LONGSWORD_SLOWWIDE_SWORDBLADE</t>
+        </is>
+      </c>
+      <c r="T62" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" s="37" t="inlineStr">
+        <is>
+          <t>OnEquip</t>
+        </is>
+      </c>
+      <c r="V62" s="37" t="inlineStr">
+        <is>
+          <t>StatModifier</t>
+        </is>
+      </c>
+      <c r="W62" s="37" t="inlineStr">
+        <is>
+          <t>AttackSpeed</t>
+        </is>
+      </c>
+      <c r="X62" s="37" t="inlineStr">
+        <is>
+          <t>Multiply</t>
+        </is>
+      </c>
+      <c r="Y62" s="37" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Z62" s="37" t="inlineStr">
+        <is>
+          <t>Part.StatModifier</t>
+        </is>
+      </c>
+      <c r="AA62" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB62" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC62" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD62" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE62" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF62" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG62" s="37" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="AH62" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI62" s="37" t="n"/>
+      <c r="AJ62" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK62" s="37" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="63" ht="22" customHeight="1" s="32">
       <c r="A63" s="37" t="inlineStr">
@@ -19585,16 +20425,100 @@
           <t>0</t>
         </is>
       </c>
+      <c r="R63" s="37" t="inlineStr">
+        <is>
+          <t>PE_LONGSWORD_SLOWWIDE_SWORDBLADE_2</t>
+        </is>
+      </c>
+      <c r="S63" s="37" t="inlineStr">
+        <is>
+          <t>P_LONGSWORD_SLOWWIDE_SWORDBLADE</t>
+        </is>
+      </c>
+      <c r="T63" s="37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" s="37" t="inlineStr">
+        <is>
+          <t>OnEquip</t>
+        </is>
+      </c>
+      <c r="V63" s="37" t="inlineStr">
+        <is>
+          <t>StatModifier</t>
+        </is>
+      </c>
+      <c r="W63" s="37" t="inlineStr">
+        <is>
+          <t>AttackRange</t>
+        </is>
+      </c>
+      <c r="X63" s="37" t="inlineStr">
+        <is>
+          <t>Multiply</t>
+        </is>
+      </c>
+      <c r="Y63" s="37" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z63" s="37" t="inlineStr">
+        <is>
+          <t>Part.StatModifier</t>
+        </is>
+      </c>
+      <c r="AA63" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB63" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC63" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD63" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE63" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF63" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG63" s="37" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="AH63" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI63" s="37" t="n"/>
+      <c r="AJ63" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK63" s="37" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="64" ht="22" customHeight="1" s="32">
       <c r="A64" s="37" t="inlineStr">
         <is>
-          <t>AUDIT_WEAPON_SLOTS_C_28</t>
+          <t>P_SCYTHE_HASTE_ROTARYBLADE</t>
         </is>
       </c>
       <c r="B64" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>P_SCYTHE_HASTE_ROTARYBLADE</t>
         </is>
       </c>
       <c r="C64" s="37" t="inlineStr">
@@ -19607,7 +20531,11 @@
           <t>RotaryBlade</t>
         </is>
       </c>
-      <c r="E64" s="37" t="n"/>
+      <c r="E64" s="37" t="inlineStr">
+        <is>
+          <t>攻速减范围旋刃</t>
+        </is>
+      </c>
       <c r="F64" s="37" t="inlineStr">
         <is>
           <t>效果：攻击速度+40%，攻击范围-20%</t>
@@ -19615,34 +20543,30 @@
       </c>
       <c r="G64" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="H64" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>RotaryBlade|Numeric</t>
         </is>
       </c>
       <c r="I64" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="J64" s="37" t="inlineStr">
         <is>
-          <t>Unimplemented</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K64" s="37" t="inlineStr">
         <is>
-          <t>Disabled</t>
-        </is>
-      </c>
-      <c r="L64" s="37" t="inlineStr">
-        <is>
-          <t>Unnamed workbook row; no stable PartId assigned.</t>
-        </is>
-      </c>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="L64" s="37" t="n"/>
       <c r="M64" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -19655,13 +20579,95 @@
       </c>
       <c r="O64" s="37" t="inlineStr">
         <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="P64" s="37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="P64" s="37" t="n">
+        <v>30</v>
+      </c>
+      <c r="R64" s="37" t="inlineStr">
+        <is>
+          <t>PE_LONGSWORD_KILLHEAL_SWORDBLADE_1</t>
+        </is>
+      </c>
+      <c r="S64" s="37" t="inlineStr">
+        <is>
+          <t>P_LONGSWORD_KILLHEAL_SWORDBLADE</t>
+        </is>
+      </c>
+      <c r="T64" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" s="37" t="inlineStr">
+        <is>
+          <t>OnKill</t>
+        </is>
+      </c>
+      <c r="V64" s="37" t="inlineStr">
+        <is>
+          <t>UniqueBehavior</t>
+        </is>
+      </c>
+      <c r="W64" s="37" t="inlineStr">
+        <is>
+          <t>OnKill</t>
+        </is>
+      </c>
+      <c r="X64" s="37" t="inlineStr">
+        <is>
+          <t>Add</t>
+        </is>
+      </c>
+      <c r="Y64" s="37" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Z64" s="37" t="inlineStr">
+        <is>
+          <t>Part.OnKillHealPercent</t>
+        </is>
+      </c>
+      <c r="AA64" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB64" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC64" s="37" t="inlineStr">
+        <is>
+          <t>HealMaxHpPercent</t>
+        </is>
+      </c>
+      <c r="AD64" s="37" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AE64" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF64" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG64" s="37" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="AH64" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI64" s="37" t="n"/>
+      <c r="AJ64" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK64" s="37" t="n">
+        <v>39</v>
       </c>
     </row>
     <row r="65" ht="22" customHeight="1" s="32">
@@ -19741,6 +20747,90 @@
           <t>0</t>
         </is>
       </c>
+      <c r="R65" s="37" t="inlineStr">
+        <is>
+          <t>PE_LONGSWORD_HASTE_GRIP_1</t>
+        </is>
+      </c>
+      <c r="S65" s="37" t="inlineStr">
+        <is>
+          <t>P_LONGSWORD_HASTE_GRIP</t>
+        </is>
+      </c>
+      <c r="T65" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" s="37" t="inlineStr">
+        <is>
+          <t>OnEquip</t>
+        </is>
+      </c>
+      <c r="V65" s="37" t="inlineStr">
+        <is>
+          <t>StatModifier</t>
+        </is>
+      </c>
+      <c r="W65" s="37" t="inlineStr">
+        <is>
+          <t>AttackSpeed</t>
+        </is>
+      </c>
+      <c r="X65" s="37" t="inlineStr">
+        <is>
+          <t>Multiply</t>
+        </is>
+      </c>
+      <c r="Y65" s="37" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z65" s="37" t="inlineStr">
+        <is>
+          <t>Part.StatModifier</t>
+        </is>
+      </c>
+      <c r="AA65" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB65" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC65" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD65" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE65" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF65" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG65" s="37" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="AH65" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI65" s="37" t="n"/>
+      <c r="AJ65" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK65" s="37" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="66" ht="22" customHeight="1" s="32">
       <c r="A66" s="37" t="inlineStr">
@@ -19819,6 +20909,90 @@
           <t>0</t>
         </is>
       </c>
+      <c r="R66" s="37" t="inlineStr">
+        <is>
+          <t>PE_LONGSWORD_HEAVY_GRIP_1</t>
+        </is>
+      </c>
+      <c r="S66" s="37" t="inlineStr">
+        <is>
+          <t>P_LONGSWORD_HEAVY_GRIP</t>
+        </is>
+      </c>
+      <c r="T66" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" s="37" t="inlineStr">
+        <is>
+          <t>OnEquip</t>
+        </is>
+      </c>
+      <c r="V66" s="37" t="inlineStr">
+        <is>
+          <t>StatModifier</t>
+        </is>
+      </c>
+      <c r="W66" s="37" t="inlineStr">
+        <is>
+          <t>AttackSpeed</t>
+        </is>
+      </c>
+      <c r="X66" s="37" t="inlineStr">
+        <is>
+          <t>Multiply</t>
+        </is>
+      </c>
+      <c r="Y66" s="37" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Z66" s="37" t="inlineStr">
+        <is>
+          <t>Part.StatModifier</t>
+        </is>
+      </c>
+      <c r="AA66" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB66" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC66" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD66" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE66" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF66" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG66" s="37" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="AH66" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI66" s="37" t="n"/>
+      <c r="AJ66" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK66" s="37" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="67" ht="22" customHeight="1" s="32">
       <c r="A67" s="37" t="inlineStr">
@@ -19897,6 +21071,90 @@
           <t>0</t>
         </is>
       </c>
+      <c r="R67" s="37" t="inlineStr">
+        <is>
+          <t>PE_LONGSWORD_HEAVY_GRIP_2</t>
+        </is>
+      </c>
+      <c r="S67" s="37" t="inlineStr">
+        <is>
+          <t>P_LONGSWORD_HEAVY_GRIP</t>
+        </is>
+      </c>
+      <c r="T67" s="37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" s="37" t="inlineStr">
+        <is>
+          <t>OnEquip</t>
+        </is>
+      </c>
+      <c r="V67" s="37" t="inlineStr">
+        <is>
+          <t>StatModifier</t>
+        </is>
+      </c>
+      <c r="W67" s="37" t="inlineStr">
+        <is>
+          <t>PhysicalCoefficient</t>
+        </is>
+      </c>
+      <c r="X67" s="37" t="inlineStr">
+        <is>
+          <t>Multiply</t>
+        </is>
+      </c>
+      <c r="Y67" s="37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z67" s="37" t="inlineStr">
+        <is>
+          <t>Part.StatModifier</t>
+        </is>
+      </c>
+      <c r="AA67" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB67" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC67" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD67" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE67" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF67" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG67" s="37" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="AH67" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI67" s="37" t="n"/>
+      <c r="AJ67" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK67" s="37" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="68" ht="22" customHeight="1" s="32">
       <c r="A68" s="37" t="inlineStr">
@@ -19975,6 +21233,90 @@
           <t>0</t>
         </is>
       </c>
+      <c r="R68" s="37" t="inlineStr">
+        <is>
+          <t>PE_LONGSWORD_HEAVY_GRIP_3</t>
+        </is>
+      </c>
+      <c r="S68" s="37" t="inlineStr">
+        <is>
+          <t>P_LONGSWORD_HEAVY_GRIP</t>
+        </is>
+      </c>
+      <c r="T68" s="37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U68" s="37" t="inlineStr">
+        <is>
+          <t>OnEquip</t>
+        </is>
+      </c>
+      <c r="V68" s="37" t="inlineStr">
+        <is>
+          <t>StatModifier</t>
+        </is>
+      </c>
+      <c r="W68" s="37" t="inlineStr">
+        <is>
+          <t>ElementalCoefficient</t>
+        </is>
+      </c>
+      <c r="X68" s="37" t="inlineStr">
+        <is>
+          <t>Multiply</t>
+        </is>
+      </c>
+      <c r="Y68" s="37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z68" s="37" t="inlineStr">
+        <is>
+          <t>Part.StatModifier</t>
+        </is>
+      </c>
+      <c r="AA68" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB68" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC68" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD68" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE68" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF68" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG68" s="37" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="AH68" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI68" s="37" t="n"/>
+      <c r="AJ68" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK68" s="37" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="69" ht="22" customHeight="1" s="32">
       <c r="A69" s="37" t="inlineStr">
@@ -20053,6 +21395,90 @@
           <t>0</t>
         </is>
       </c>
+      <c r="R69" s="37" t="inlineStr">
+        <is>
+          <t>PE_GUN_TRIPLESPREAD_MUZZLE_1</t>
+        </is>
+      </c>
+      <c r="S69" s="37" t="inlineStr">
+        <is>
+          <t>P_GUN_TRIPLESPREAD_MUZZLE</t>
+        </is>
+      </c>
+      <c r="T69" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U69" s="37" t="inlineStr">
+        <is>
+          <t>OnEquip</t>
+        </is>
+      </c>
+      <c r="V69" s="37" t="inlineStr">
+        <is>
+          <t>StatModifier</t>
+        </is>
+      </c>
+      <c r="W69" s="37" t="inlineStr">
+        <is>
+          <t>ProjectileCount</t>
+        </is>
+      </c>
+      <c r="X69" s="37" t="inlineStr">
+        <is>
+          <t>Override</t>
+        </is>
+      </c>
+      <c r="Y69" s="37" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z69" s="37" t="inlineStr">
+        <is>
+          <t>Part.StatModifier</t>
+        </is>
+      </c>
+      <c r="AA69" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB69" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC69" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD69" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE69" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF69" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG69" s="37" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="AH69" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI69" s="37" t="n"/>
+      <c r="AJ69" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK69" s="37" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="70" ht="22" customHeight="1" s="32">
       <c r="A70" s="37" t="inlineStr">
@@ -20130,6 +21556,90 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="R70" s="37" t="inlineStr">
+        <is>
+          <t>PE_GUN_TRIPLESPREAD_MUZZLE_2</t>
+        </is>
+      </c>
+      <c r="S70" s="37" t="inlineStr">
+        <is>
+          <t>P_GUN_TRIPLESPREAD_MUZZLE</t>
+        </is>
+      </c>
+      <c r="T70" s="37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U70" s="37" t="inlineStr">
+        <is>
+          <t>OnEquip</t>
+        </is>
+      </c>
+      <c r="V70" s="37" t="inlineStr">
+        <is>
+          <t>StatModifier</t>
+        </is>
+      </c>
+      <c r="W70" s="37" t="inlineStr">
+        <is>
+          <t>ConcentrationDegrees</t>
+        </is>
+      </c>
+      <c r="X70" s="37" t="inlineStr">
+        <is>
+          <t>Override</t>
+        </is>
+      </c>
+      <c r="Y70" s="37" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z70" s="37" t="inlineStr">
+        <is>
+          <t>Part.StatModifier</t>
+        </is>
+      </c>
+      <c r="AA70" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB70" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC70" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD70" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE70" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF70" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="37" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="AH70" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI70" s="37" t="n"/>
+      <c r="AJ70" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK70" s="37" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="71" ht="22" customHeight="1" s="32">
@@ -20213,16 +21723,100 @@
           <t>0</t>
         </is>
       </c>
+      <c r="R71" s="37" t="inlineStr">
+        <is>
+          <t>PE_STAFF_DUALSPREAD_STAFFBODY_1</t>
+        </is>
+      </c>
+      <c r="S71" s="37" t="inlineStr">
+        <is>
+          <t>P_STAFF_DUALSPREAD_STAFFBODY</t>
+        </is>
+      </c>
+      <c r="T71" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U71" s="37" t="inlineStr">
+        <is>
+          <t>OnEquip</t>
+        </is>
+      </c>
+      <c r="V71" s="37" t="inlineStr">
+        <is>
+          <t>StatModifier</t>
+        </is>
+      </c>
+      <c r="W71" s="37" t="inlineStr">
+        <is>
+          <t>ProjectileCount</t>
+        </is>
+      </c>
+      <c r="X71" s="37" t="inlineStr">
+        <is>
+          <t>Override</t>
+        </is>
+      </c>
+      <c r="Y71" s="37" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z71" s="37" t="inlineStr">
+        <is>
+          <t>Part.StatModifier</t>
+        </is>
+      </c>
+      <c r="AA71" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB71" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC71" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD71" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE71" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF71" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG71" s="37" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="AH71" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI71" s="37" t="n"/>
+      <c r="AJ71" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK71" s="37" t="n">
+        <v>59</v>
+      </c>
     </row>
     <row r="72" ht="22" customHeight="1" s="32">
       <c r="A72" s="37" t="inlineStr">
         <is>
-          <t>AUDIT_WEAPON_SLOTS_C_36</t>
+          <t>P_LONGSWORD_NARROWWIDE_SWORDBLADE</t>
         </is>
       </c>
       <c r="B72" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>P_LONGSWORD_NARROWWIDE_SWORDBLADE</t>
         </is>
       </c>
       <c r="C72" s="37" t="inlineStr">
@@ -20235,7 +21829,11 @@
           <t>SwordBlade</t>
         </is>
       </c>
-      <c r="E72" s="37" t="n"/>
+      <c r="E72" s="37" t="inlineStr">
+        <is>
+          <t>窄角广域剑刃</t>
+        </is>
+      </c>
       <c r="F72" s="37" t="inlineStr">
         <is>
           <t>效果：攻击角度降为120°；攻击范围+30%</t>
@@ -20243,34 +21841,30 @@
       </c>
       <c r="G72" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="H72" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>SwordBlade|Numeric</t>
         </is>
       </c>
       <c r="I72" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="J72" s="37" t="inlineStr">
         <is>
-          <t>Unimplemented</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K72" s="37" t="inlineStr">
         <is>
-          <t>Disabled</t>
-        </is>
-      </c>
-      <c r="L72" s="37" t="inlineStr">
-        <is>
-          <t>Unnamed workbook row; no stable PartId assigned.</t>
-        </is>
-      </c>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="L72" s="37" t="n"/>
       <c r="M72" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -20283,24 +21877,106 @@
       </c>
       <c r="O72" s="37" t="inlineStr">
         <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="P72" s="37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="P72" s="37" t="n">
+        <v>30</v>
+      </c>
+      <c r="R72" s="37" t="inlineStr">
+        <is>
+          <t>PE_STAFF_DUALSPREAD_STAFFBODY_2</t>
+        </is>
+      </c>
+      <c r="S72" s="37" t="inlineStr">
+        <is>
+          <t>P_STAFF_DUALSPREAD_STAFFBODY</t>
+        </is>
+      </c>
+      <c r="T72" s="37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U72" s="37" t="inlineStr">
+        <is>
+          <t>OnEquip</t>
+        </is>
+      </c>
+      <c r="V72" s="37" t="inlineStr">
+        <is>
+          <t>StatModifier</t>
+        </is>
+      </c>
+      <c r="W72" s="37" t="inlineStr">
+        <is>
+          <t>ConcentrationDegrees</t>
+        </is>
+      </c>
+      <c r="X72" s="37" t="inlineStr">
+        <is>
+          <t>Override</t>
+        </is>
+      </c>
+      <c r="Y72" s="37" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z72" s="37" t="inlineStr">
+        <is>
+          <t>Part.StatModifier</t>
+        </is>
+      </c>
+      <c r="AA72" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB72" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC72" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD72" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE72" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF72" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG72" s="37" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="AH72" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI72" s="37" t="n"/>
+      <c r="AJ72" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK72" s="37" t="n">
+        <v>59</v>
       </c>
     </row>
     <row r="73" ht="22" customHeight="1" s="32">
       <c r="A73" s="37" t="inlineStr">
         <is>
-          <t>AUDIT_WEAPON_SLOTS_C_37</t>
+          <t>P_LONGSWORD_SLOWWIDE_SWORDBLADE</t>
         </is>
       </c>
       <c r="B73" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>P_LONGSWORD_SLOWWIDE_SWORDBLADE</t>
         </is>
       </c>
       <c r="C73" s="37" t="inlineStr">
@@ -20313,7 +21989,11 @@
           <t>SwordBlade</t>
         </is>
       </c>
-      <c r="E73" s="37" t="n"/>
+      <c r="E73" s="37" t="inlineStr">
+        <is>
+          <t>减攻速广域剑刃</t>
+        </is>
+      </c>
       <c r="F73" s="37" t="inlineStr">
         <is>
           <t>效果：攻击速度-20%，攻击范围+30%</t>
@@ -20321,34 +22001,30 @@
       </c>
       <c r="G73" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="H73" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>SwordBlade|Numeric</t>
         </is>
       </c>
       <c r="I73" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="J73" s="37" t="inlineStr">
         <is>
-          <t>Unimplemented</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K73" s="37" t="inlineStr">
         <is>
-          <t>Disabled</t>
-        </is>
-      </c>
-      <c r="L73" s="37" t="inlineStr">
-        <is>
-          <t>Unnamed workbook row; no stable PartId assigned.</t>
-        </is>
-      </c>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="L73" s="37" t="n"/>
       <c r="M73" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -20361,13 +22037,95 @@
       </c>
       <c r="O73" s="37" t="inlineStr">
         <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="P73" s="37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="P73" s="37" t="n">
+        <v>30</v>
+      </c>
+      <c r="R73" s="37" t="inlineStr">
+        <is>
+          <t>PE_STAFF_WIDEWEAK_STAFFCRYSTAL_1</t>
+        </is>
+      </c>
+      <c r="S73" s="37" t="inlineStr">
+        <is>
+          <t>P_STAFF_WIDEWEAK_STAFFCRYSTAL</t>
+        </is>
+      </c>
+      <c r="T73" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U73" s="37" t="inlineStr">
+        <is>
+          <t>OnEquip</t>
+        </is>
+      </c>
+      <c r="V73" s="37" t="inlineStr">
+        <is>
+          <t>StatModifier</t>
+        </is>
+      </c>
+      <c r="W73" s="37" t="inlineStr">
+        <is>
+          <t>PhysicalCoefficient</t>
+        </is>
+      </c>
+      <c r="X73" s="37" t="inlineStr">
+        <is>
+          <t>Multiply</t>
+        </is>
+      </c>
+      <c r="Y73" s="37" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Z73" s="37" t="inlineStr">
+        <is>
+          <t>Part.StatModifier</t>
+        </is>
+      </c>
+      <c r="AA73" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB73" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC73" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD73" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE73" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF73" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG73" s="37" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="AH73" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI73" s="37" t="n"/>
+      <c r="AJ73" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK73" s="37" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="74" ht="22" customHeight="1" s="32">
@@ -20447,16 +22205,100 @@
           <t>0</t>
         </is>
       </c>
+      <c r="R74" s="37" t="inlineStr">
+        <is>
+          <t>PE_STAFF_WIDEWEAK_STAFFCRYSTAL_2</t>
+        </is>
+      </c>
+      <c r="S74" s="37" t="inlineStr">
+        <is>
+          <t>P_STAFF_WIDEWEAK_STAFFCRYSTAL</t>
+        </is>
+      </c>
+      <c r="T74" s="37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U74" s="37" t="inlineStr">
+        <is>
+          <t>OnEquip</t>
+        </is>
+      </c>
+      <c r="V74" s="37" t="inlineStr">
+        <is>
+          <t>StatModifier</t>
+        </is>
+      </c>
+      <c r="W74" s="37" t="inlineStr">
+        <is>
+          <t>ElementalCoefficient</t>
+        </is>
+      </c>
+      <c r="X74" s="37" t="inlineStr">
+        <is>
+          <t>Multiply</t>
+        </is>
+      </c>
+      <c r="Y74" s="37" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Z74" s="37" t="inlineStr">
+        <is>
+          <t>Part.StatModifier</t>
+        </is>
+      </c>
+      <c r="AA74" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB74" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC74" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD74" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE74" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF74" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG74" s="37" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="AH74" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI74" s="37" t="n"/>
+      <c r="AJ74" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK74" s="37" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="75" ht="22" customHeight="1" s="32">
       <c r="A75" s="37" t="inlineStr">
         <is>
-          <t>AUDIT_WEAPON_SLOTS_C_39</t>
+          <t>P_LONGSWORD_KILLHEAL_SWORDBLADE</t>
         </is>
       </c>
       <c r="B75" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>P_LONGSWORD_KILLHEAL_SWORDBLADE</t>
         </is>
       </c>
       <c r="C75" s="37" t="inlineStr">
@@ -20469,7 +22311,11 @@
           <t>SwordBlade</t>
         </is>
       </c>
-      <c r="E75" s="37" t="n"/>
+      <c r="E75" s="37" t="inlineStr">
+        <is>
+          <t>击杀吸血剑刃</t>
+        </is>
+      </c>
       <c r="F75" s="37" t="inlineStr">
         <is>
           <t>效果：每击杀一名敌方单位，回复5%最大生命值</t>
@@ -20477,34 +22323,30 @@
       </c>
       <c r="G75" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="H75" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>SwordBlade|UniqueBehavior</t>
         </is>
       </c>
       <c r="I75" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="J75" s="37" t="inlineStr">
         <is>
-          <t>Unimplemented</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K75" s="37" t="inlineStr">
         <is>
-          <t>Disabled</t>
-        </is>
-      </c>
-      <c r="L75" s="37" t="inlineStr">
-        <is>
-          <t>Unnamed workbook row; no stable PartId assigned.</t>
-        </is>
-      </c>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="L75" s="37" t="n"/>
       <c r="M75" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -20517,13 +22359,95 @@
       </c>
       <c r="O75" s="37" t="inlineStr">
         <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="P75" s="37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="P75" s="37" t="n">
+        <v>45</v>
+      </c>
+      <c r="R75" s="37" t="inlineStr">
+        <is>
+          <t>PE_STAFF_WIDEWEAK_STAFFCRYSTAL_3</t>
+        </is>
+      </c>
+      <c r="S75" s="37" t="inlineStr">
+        <is>
+          <t>P_STAFF_WIDEWEAK_STAFFCRYSTAL</t>
+        </is>
+      </c>
+      <c r="T75" s="37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U75" s="37" t="inlineStr">
+        <is>
+          <t>OnEquip</t>
+        </is>
+      </c>
+      <c r="V75" s="37" t="inlineStr">
+        <is>
+          <t>StatModifier</t>
+        </is>
+      </c>
+      <c r="W75" s="37" t="inlineStr">
+        <is>
+          <t>ExplosionRadius</t>
+        </is>
+      </c>
+      <c r="X75" s="37" t="inlineStr">
+        <is>
+          <t>Multiply</t>
+        </is>
+      </c>
+      <c r="Y75" s="37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z75" s="37" t="inlineStr">
+        <is>
+          <t>Part.StatModifier</t>
+        </is>
+      </c>
+      <c r="AA75" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB75" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC75" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD75" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE75" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="37" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="AH75" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI75" s="37" t="n"/>
+      <c r="AJ75" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK75" s="37" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="76" ht="22" customHeight="1" s="32">
@@ -20603,6 +22527,90 @@
           <t>0</t>
         </is>
       </c>
+      <c r="R76" s="37" t="inlineStr">
+        <is>
+          <t>PE_STAFF_NARROWSTRONG_STAFFCRYSTAL_1</t>
+        </is>
+      </c>
+      <c r="S76" s="37" t="inlineStr">
+        <is>
+          <t>P_STAFF_NARROWSTRONG_STAFFCRYSTAL</t>
+        </is>
+      </c>
+      <c r="T76" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U76" s="37" t="inlineStr">
+        <is>
+          <t>OnEquip</t>
+        </is>
+      </c>
+      <c r="V76" s="37" t="inlineStr">
+        <is>
+          <t>StatModifier</t>
+        </is>
+      </c>
+      <c r="W76" s="37" t="inlineStr">
+        <is>
+          <t>PhysicalCoefficient</t>
+        </is>
+      </c>
+      <c r="X76" s="37" t="inlineStr">
+        <is>
+          <t>Multiply</t>
+        </is>
+      </c>
+      <c r="Y76" s="37" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z76" s="37" t="inlineStr">
+        <is>
+          <t>Part.StatModifier</t>
+        </is>
+      </c>
+      <c r="AA76" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB76" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC76" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD76" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE76" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF76" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG76" s="37" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="AH76" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI76" s="37" t="n"/>
+      <c r="AJ76" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK76" s="37" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="77" ht="22" customHeight="1" s="32">
       <c r="A77" s="37" t="inlineStr">
@@ -20680,6 +22688,90 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="R77" s="37" t="inlineStr">
+        <is>
+          <t>PE_STAFF_NARROWSTRONG_STAFFCRYSTAL_2</t>
+        </is>
+      </c>
+      <c r="S77" s="37" t="inlineStr">
+        <is>
+          <t>P_STAFF_NARROWSTRONG_STAFFCRYSTAL</t>
+        </is>
+      </c>
+      <c r="T77" s="37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U77" s="37" t="inlineStr">
+        <is>
+          <t>OnEquip</t>
+        </is>
+      </c>
+      <c r="V77" s="37" t="inlineStr">
+        <is>
+          <t>StatModifier</t>
+        </is>
+      </c>
+      <c r="W77" s="37" t="inlineStr">
+        <is>
+          <t>ElementalCoefficient</t>
+        </is>
+      </c>
+      <c r="X77" s="37" t="inlineStr">
+        <is>
+          <t>Multiply</t>
+        </is>
+      </c>
+      <c r="Y77" s="37" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z77" s="37" t="inlineStr">
+        <is>
+          <t>Part.StatModifier</t>
+        </is>
+      </c>
+      <c r="AA77" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB77" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC77" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD77" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE77" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF77" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG77" s="37" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="AH77" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI77" s="37" t="n"/>
+      <c r="AJ77" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK77" s="37" t="n">
+        <v>65</v>
       </c>
     </row>
     <row r="78" ht="22" customHeight="1" s="32">
@@ -20761,16 +22853,100 @@
           <t>0</t>
         </is>
       </c>
+      <c r="R78" s="37" t="inlineStr">
+        <is>
+          <t>PE_STAFF_NARROWSTRONG_STAFFCRYSTAL_3</t>
+        </is>
+      </c>
+      <c r="S78" s="37" t="inlineStr">
+        <is>
+          <t>P_STAFF_NARROWSTRONG_STAFFCRYSTAL</t>
+        </is>
+      </c>
+      <c r="T78" s="37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U78" s="37" t="inlineStr">
+        <is>
+          <t>OnEquip</t>
+        </is>
+      </c>
+      <c r="V78" s="37" t="inlineStr">
+        <is>
+          <t>StatModifier</t>
+        </is>
+      </c>
+      <c r="W78" s="37" t="inlineStr">
+        <is>
+          <t>ExplosionRadius</t>
+        </is>
+      </c>
+      <c r="X78" s="37" t="inlineStr">
+        <is>
+          <t>Multiply</t>
+        </is>
+      </c>
+      <c r="Y78" s="37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z78" s="37" t="inlineStr">
+        <is>
+          <t>Part.StatModifier</t>
+        </is>
+      </c>
+      <c r="AA78" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB78" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC78" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD78" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE78" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF78" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG78" s="37" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="AH78" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI78" s="37" t="n"/>
+      <c r="AJ78" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK78" s="37" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="79" ht="75" customHeight="1" s="32">
       <c r="A79" s="37" t="inlineStr">
         <is>
-          <t>AUDIT_WEAPON_SLOTS_C_43</t>
+          <t>P_LONGSWORD_HASTE_GRIP</t>
         </is>
       </c>
       <c r="B79" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>P_LONGSWORD_HASTE_GRIP</t>
         </is>
       </c>
       <c r="C79" s="37" t="inlineStr">
@@ -20783,7 +22959,11 @@
           <t>Grip</t>
         </is>
       </c>
-      <c r="E79" s="37" t="n"/>
+      <c r="E79" s="37" t="inlineStr">
+        <is>
+          <t>攻速剑柄</t>
+        </is>
+      </c>
       <c r="F79" s="37" t="inlineStr">
         <is>
           <t>效果：攻击速度+20%</t>
@@ -20791,34 +22971,30 @@
       </c>
       <c r="G79" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="H79" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Grip|Numeric</t>
         </is>
       </c>
       <c r="I79" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="J79" s="37" t="inlineStr">
         <is>
-          <t>Unimplemented</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K79" s="37" t="inlineStr">
         <is>
-          <t>Disabled</t>
-        </is>
-      </c>
-      <c r="L79" s="37" t="inlineStr">
-        <is>
-          <t>Unnamed workbook row; no stable PartId assigned.</t>
-        </is>
-      </c>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="L79" s="37" t="n"/>
       <c r="M79" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -20831,13 +23007,95 @@
       </c>
       <c r="O79" s="37" t="inlineStr">
         <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="P79" s="37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="P79" s="37" t="n">
+        <v>30</v>
+      </c>
+      <c r="R79" s="37" t="inlineStr">
+        <is>
+          <t>PE_STAFF_SLOWWIDE_STAFFCRYSTAL_1</t>
+        </is>
+      </c>
+      <c r="S79" s="37" t="inlineStr">
+        <is>
+          <t>P_STAFF_SLOWWIDE_STAFFCRYSTAL</t>
+        </is>
+      </c>
+      <c r="T79" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U79" s="37" t="inlineStr">
+        <is>
+          <t>OnEquip</t>
+        </is>
+      </c>
+      <c r="V79" s="37" t="inlineStr">
+        <is>
+          <t>StatModifier</t>
+        </is>
+      </c>
+      <c r="W79" s="37" t="inlineStr">
+        <is>
+          <t>AttackSpeed</t>
+        </is>
+      </c>
+      <c r="X79" s="37" t="inlineStr">
+        <is>
+          <t>Multiply</t>
+        </is>
+      </c>
+      <c r="Y79" s="37" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Z79" s="37" t="inlineStr">
+        <is>
+          <t>Part.StatModifier</t>
+        </is>
+      </c>
+      <c r="AA79" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB79" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC79" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD79" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE79" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF79" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG79" s="37" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="AH79" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI79" s="37" t="n"/>
+      <c r="AJ79" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK79" s="37" t="n">
+        <v>67</v>
       </c>
     </row>
     <row r="80" ht="22" customHeight="1" s="32">
@@ -20917,6 +23175,90 @@
           <t>0</t>
         </is>
       </c>
+      <c r="R80" s="37" t="inlineStr">
+        <is>
+          <t>PE_STAFF_SLOWWIDE_STAFFCRYSTAL_2</t>
+        </is>
+      </c>
+      <c r="S80" s="37" t="inlineStr">
+        <is>
+          <t>P_STAFF_SLOWWIDE_STAFFCRYSTAL</t>
+        </is>
+      </c>
+      <c r="T80" s="37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U80" s="37" t="inlineStr">
+        <is>
+          <t>OnEquip</t>
+        </is>
+      </c>
+      <c r="V80" s="37" t="inlineStr">
+        <is>
+          <t>StatModifier</t>
+        </is>
+      </c>
+      <c r="W80" s="37" t="inlineStr">
+        <is>
+          <t>ExplosionRadius</t>
+        </is>
+      </c>
+      <c r="X80" s="37" t="inlineStr">
+        <is>
+          <t>Multiply</t>
+        </is>
+      </c>
+      <c r="Y80" s="37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z80" s="37" t="inlineStr">
+        <is>
+          <t>Part.StatModifier</t>
+        </is>
+      </c>
+      <c r="AA80" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB80" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC80" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD80" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE80" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF80" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG80" s="37" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="AH80" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI80" s="37" t="n"/>
+      <c r="AJ80" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK80" s="37" t="n">
+        <v>67</v>
+      </c>
     </row>
     <row r="81" ht="22" customHeight="1" s="32">
       <c r="A81" s="37" t="inlineStr">
@@ -20995,6 +23337,90 @@
           <t>0</t>
         </is>
       </c>
+      <c r="R81" s="37" t="inlineStr">
+        <is>
+          <t>PE_WHIP_HASTE_WHIPBODY_1</t>
+        </is>
+      </c>
+      <c r="S81" s="37" t="inlineStr">
+        <is>
+          <t>P_WHIP_HASTE_WHIPBODY</t>
+        </is>
+      </c>
+      <c r="T81" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U81" s="37" t="inlineStr">
+        <is>
+          <t>OnEquip</t>
+        </is>
+      </c>
+      <c r="V81" s="37" t="inlineStr">
+        <is>
+          <t>StatModifier</t>
+        </is>
+      </c>
+      <c r="W81" s="37" t="inlineStr">
+        <is>
+          <t>AttackSpeed</t>
+        </is>
+      </c>
+      <c r="X81" s="37" t="inlineStr">
+        <is>
+          <t>Multiply</t>
+        </is>
+      </c>
+      <c r="Y81" s="37" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z81" s="37" t="inlineStr">
+        <is>
+          <t>Part.StatModifier</t>
+        </is>
+      </c>
+      <c r="AA81" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB81" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC81" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD81" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE81" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF81" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG81" s="37" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="AH81" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI81" s="37" t="n"/>
+      <c r="AJ81" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK81" s="37" t="n">
+        <v>73</v>
+      </c>
     </row>
     <row r="82" ht="22" customHeight="1" s="32">
       <c r="A82" s="37" t="inlineStr">
@@ -21073,16 +23499,100 @@
           <t>0</t>
         </is>
       </c>
+      <c r="R82" s="37" t="inlineStr">
+        <is>
+          <t>PE_WHIP_KILLHEAL_WHIPBODY_1</t>
+        </is>
+      </c>
+      <c r="S82" s="37" t="inlineStr">
+        <is>
+          <t>P_WHIP_KILLHEAL_WHIPBODY</t>
+        </is>
+      </c>
+      <c r="T82" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U82" s="37" t="inlineStr">
+        <is>
+          <t>OnKill</t>
+        </is>
+      </c>
+      <c r="V82" s="37" t="inlineStr">
+        <is>
+          <t>UniqueBehavior</t>
+        </is>
+      </c>
+      <c r="W82" s="37" t="inlineStr">
+        <is>
+          <t>OnKill</t>
+        </is>
+      </c>
+      <c r="X82" s="37" t="inlineStr">
+        <is>
+          <t>Add</t>
+        </is>
+      </c>
+      <c r="Y82" s="37" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Z82" s="37" t="inlineStr">
+        <is>
+          <t>Part.OnKillHealPercent</t>
+        </is>
+      </c>
+      <c r="AA82" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB82" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC82" s="37" t="inlineStr">
+        <is>
+          <t>HealMaxHpPercent</t>
+        </is>
+      </c>
+      <c r="AD82" s="37" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AE82" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF82" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG82" s="37" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="AH82" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI82" s="37" t="n"/>
+      <c r="AJ82" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK82" s="37" t="n">
+        <v>74</v>
+      </c>
     </row>
     <row r="83" ht="22" customHeight="1" s="32">
       <c r="A83" s="37" t="inlineStr">
         <is>
-          <t>AUDIT_WEAPON_SLOTS_C_47</t>
+          <t>P_LONGSWORD_HEAVY_GRIP</t>
         </is>
       </c>
       <c r="B83" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>P_LONGSWORD_HEAVY_GRIP</t>
         </is>
       </c>
       <c r="C83" s="37" t="inlineStr">
@@ -21095,7 +23605,11 @@
           <t>Grip</t>
         </is>
       </c>
-      <c r="E83" s="37" t="n"/>
+      <c r="E83" s="37" t="inlineStr">
+        <is>
+          <t>重击剑柄</t>
+        </is>
+      </c>
       <c r="F83" s="37" t="inlineStr">
         <is>
           <t>效果：攻击速度-30%，伤害倍率+50%</t>
@@ -21103,34 +23617,30 @@
       </c>
       <c r="G83" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="H83" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Grip|Numeric</t>
         </is>
       </c>
       <c r="I83" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="J83" s="37" t="inlineStr">
         <is>
-          <t>Unimplemented</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K83" s="37" t="inlineStr">
         <is>
-          <t>Disabled</t>
-        </is>
-      </c>
-      <c r="L83" s="37" t="inlineStr">
-        <is>
-          <t>Unnamed workbook row; no stable PartId assigned.</t>
-        </is>
-      </c>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="L83" s="37" t="n"/>
       <c r="M83" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -21143,24 +23653,22 @@
       </c>
       <c r="O83" s="37" t="inlineStr">
         <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="P83" s="37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="P83" s="37" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="84" ht="22" customHeight="1" s="32">
       <c r="A84" s="37" t="inlineStr">
         <is>
-          <t>AUDIT_WEAPON_SLOTS_C_48</t>
+          <t>P_GUN_TRIPLESPREAD_MUZZLE</t>
         </is>
       </c>
       <c r="B84" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>P_GUN_TRIPLESPREAD_MUZZLE</t>
         </is>
       </c>
       <c r="C84" s="37" t="inlineStr">
@@ -21173,7 +23681,11 @@
           <t>Muzzle</t>
         </is>
       </c>
-      <c r="E84" s="37" t="n"/>
+      <c r="E84" s="37" t="inlineStr">
+        <is>
+          <t>三发散射枪口</t>
+        </is>
+      </c>
       <c r="F84" s="37" t="inlineStr">
         <is>
           <t>效果：弹道固定为3，武器集中性固定为60°</t>
@@ -21181,34 +23693,30 @@
       </c>
       <c r="G84" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="H84" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Muzzle|Numeric</t>
         </is>
       </c>
       <c r="I84" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="J84" s="37" t="inlineStr">
         <is>
-          <t>Unimplemented</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K84" s="37" t="inlineStr">
         <is>
-          <t>Disabled</t>
-        </is>
-      </c>
-      <c r="L84" s="37" t="inlineStr">
-        <is>
-          <t>Unnamed workbook row; no stable PartId assigned.</t>
-        </is>
-      </c>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="L84" s="37" t="n"/>
       <c r="M84" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -21221,13 +23729,11 @@
       </c>
       <c r="O84" s="37" t="inlineStr">
         <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="P84" s="37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="P84" s="37" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="85" ht="22" customHeight="1" s="32">
@@ -22013,12 +24519,12 @@
     <row r="95" ht="22" customHeight="1" s="32">
       <c r="A95" s="37" t="inlineStr">
         <is>
-          <t>AUDIT_WEAPON_SLOTS_C_59</t>
+          <t>P_STAFF_DUALSPREAD_STAFFBODY</t>
         </is>
       </c>
       <c r="B95" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>P_STAFF_DUALSPREAD_STAFFBODY</t>
         </is>
       </c>
       <c r="C95" s="37" t="inlineStr">
@@ -22031,7 +24537,11 @@
           <t>StaffBody</t>
         </is>
       </c>
-      <c r="E95" s="37" t="n"/>
+      <c r="E95" s="37" t="inlineStr">
+        <is>
+          <t>双发散射杖体</t>
+        </is>
+      </c>
       <c r="F95" s="37" t="inlineStr">
         <is>
           <t>效果：弹道固定为2，武器集中性固定为60°</t>
@@ -22039,34 +24549,30 @@
       </c>
       <c r="G95" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="H95" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>StaffBody|Numeric</t>
         </is>
       </c>
       <c r="I95" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="J95" s="37" t="inlineStr">
         <is>
-          <t>Unimplemented</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K95" s="37" t="inlineStr">
         <is>
-          <t>Disabled</t>
-        </is>
-      </c>
-      <c r="L95" s="37" t="inlineStr">
-        <is>
-          <t>Unnamed workbook row; no stable PartId assigned.</t>
-        </is>
-      </c>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="L95" s="37" t="n"/>
       <c r="M95" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -22079,13 +24585,11 @@
       </c>
       <c r="O95" s="37" t="inlineStr">
         <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="P95" s="37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="P95" s="37" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="96" ht="22" customHeight="1" s="32">
@@ -22407,12 +24911,12 @@
     <row r="100" ht="22" customHeight="1" s="32">
       <c r="A100" s="37" t="inlineStr">
         <is>
-          <t>AUDIT_WEAPON_SLOTS_C_64</t>
+          <t>P_STAFF_WIDEWEAK_STAFFCRYSTAL</t>
         </is>
       </c>
       <c r="B100" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>P_STAFF_WIDEWEAK_STAFFCRYSTAL</t>
         </is>
       </c>
       <c r="C100" s="37" t="inlineStr">
@@ -22425,7 +24929,11 @@
           <t>StaffCrystal</t>
         </is>
       </c>
-      <c r="E100" s="37" t="n"/>
+      <c r="E100" s="37" t="inlineStr">
+        <is>
+          <t>大范围减伤杖晶</t>
+        </is>
+      </c>
       <c r="F100" s="37" t="inlineStr">
         <is>
           <t>效果：伤害倍率-30%，爆炸范围+50%</t>
@@ -22433,34 +24941,30 @@
       </c>
       <c r="G100" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="H100" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>StaffCrystal|Numeric</t>
         </is>
       </c>
       <c r="I100" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="J100" s="37" t="inlineStr">
         <is>
-          <t>Unimplemented</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K100" s="37" t="inlineStr">
         <is>
-          <t>Disabled</t>
-        </is>
-      </c>
-      <c r="L100" s="37" t="inlineStr">
-        <is>
-          <t>Unnamed workbook row; no stable PartId assigned.</t>
-        </is>
-      </c>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="L100" s="37" t="n"/>
       <c r="M100" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -22473,24 +24977,22 @@
       </c>
       <c r="O100" s="37" t="inlineStr">
         <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="P100" s="37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="P100" s="37" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="101" ht="22" customHeight="1" s="32">
       <c r="A101" s="37" t="inlineStr">
         <is>
-          <t>AUDIT_WEAPON_SLOTS_C_65</t>
+          <t>P_STAFF_NARROWSTRONG_STAFFCRYSTAL</t>
         </is>
       </c>
       <c r="B101" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>P_STAFF_NARROWSTRONG_STAFFCRYSTAL</t>
         </is>
       </c>
       <c r="C101" s="37" t="inlineStr">
@@ -22503,7 +25005,11 @@
           <t>StaffCrystal</t>
         </is>
       </c>
-      <c r="E101" s="37" t="n"/>
+      <c r="E101" s="37" t="inlineStr">
+        <is>
+          <t>高伤小范围杖晶</t>
+        </is>
+      </c>
       <c r="F101" s="37" t="inlineStr">
         <is>
           <t>效果：伤害倍率+70%，爆炸范围-50%</t>
@@ -22511,34 +25017,30 @@
       </c>
       <c r="G101" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="H101" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>StaffCrystal|Numeric</t>
         </is>
       </c>
       <c r="I101" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="J101" s="37" t="inlineStr">
         <is>
-          <t>Unimplemented</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K101" s="37" t="inlineStr">
         <is>
-          <t>Disabled</t>
-        </is>
-      </c>
-      <c r="L101" s="37" t="inlineStr">
-        <is>
-          <t>Unnamed workbook row; no stable PartId assigned.</t>
-        </is>
-      </c>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="L101" s="37" t="n"/>
       <c r="M101" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -22551,13 +25053,11 @@
       </c>
       <c r="O101" s="37" t="inlineStr">
         <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="P101" s="37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="P101" s="37" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="102" ht="22" customHeight="1" s="32">
@@ -22641,12 +25141,12 @@
     <row r="103" ht="22" customHeight="1" s="32">
       <c r="A103" s="37" t="inlineStr">
         <is>
-          <t>AUDIT_WEAPON_SLOTS_C_67</t>
+          <t>P_STAFF_SLOWWIDE_STAFFCRYSTAL</t>
         </is>
       </c>
       <c r="B103" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>P_STAFF_SLOWWIDE_STAFFCRYSTAL</t>
         </is>
       </c>
       <c r="C103" s="37" t="inlineStr">
@@ -22659,7 +25159,11 @@
           <t>StaffCrystal</t>
         </is>
       </c>
-      <c r="E103" s="37" t="n"/>
+      <c r="E103" s="37" t="inlineStr">
+        <is>
+          <t>减攻速大范围杖晶</t>
+        </is>
+      </c>
       <c r="F103" s="37" t="inlineStr">
         <is>
           <t>效果：攻击速度-30%，爆炸范围+50%</t>
@@ -22667,34 +25171,30 @@
       </c>
       <c r="G103" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="H103" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>StaffCrystal|Numeric</t>
         </is>
       </c>
       <c r="I103" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="J103" s="37" t="inlineStr">
         <is>
-          <t>Unimplemented</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K103" s="37" t="inlineStr">
         <is>
-          <t>Disabled</t>
-        </is>
-      </c>
-      <c r="L103" s="37" t="inlineStr">
-        <is>
-          <t>Unnamed workbook row; no stable PartId assigned.</t>
-        </is>
-      </c>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="L103" s="37" t="n"/>
       <c r="M103" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -22707,13 +25207,11 @@
       </c>
       <c r="O103" s="37" t="inlineStr">
         <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="P103" s="37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="P103" s="37" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="104" ht="22" customHeight="1" s="32">
@@ -23109,12 +25607,12 @@
     <row r="109" ht="22" customHeight="1" s="32">
       <c r="A109" s="37" t="inlineStr">
         <is>
-          <t>AUDIT_WEAPON_SLOTS_C_73</t>
+          <t>P_WHIP_HASTE_WHIPBODY</t>
         </is>
       </c>
       <c r="B109" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>P_WHIP_HASTE_WHIPBODY</t>
         </is>
       </c>
       <c r="C109" s="37" t="inlineStr">
@@ -23127,7 +25625,11 @@
           <t>WhipBody</t>
         </is>
       </c>
-      <c r="E109" s="37" t="n"/>
+      <c r="E109" s="37" t="inlineStr">
+        <is>
+          <t>攻速鞭体</t>
+        </is>
+      </c>
       <c r="F109" s="37" t="inlineStr">
         <is>
           <t>效果：攻击速度+20%</t>
@@ -23135,34 +25637,30 @@
       </c>
       <c r="G109" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="H109" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>WhipBody|Numeric</t>
         </is>
       </c>
       <c r="I109" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="J109" s="37" t="inlineStr">
         <is>
-          <t>Unimplemented</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K109" s="37" t="inlineStr">
         <is>
-          <t>Disabled</t>
-        </is>
-      </c>
-      <c r="L109" s="37" t="inlineStr">
-        <is>
-          <t>Unnamed workbook row; no stable PartId assigned.</t>
-        </is>
-      </c>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="L109" s="37" t="n"/>
       <c r="M109" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -23175,24 +25673,22 @@
       </c>
       <c r="O109" s="37" t="inlineStr">
         <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="P109" s="37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="P109" s="37" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="110" ht="22" customHeight="1" s="32">
       <c r="A110" s="37" t="inlineStr">
         <is>
-          <t>AUDIT_WEAPON_SLOTS_C_74</t>
+          <t>P_WHIP_KILLHEAL_WHIPBODY</t>
         </is>
       </c>
       <c r="B110" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>P_WHIP_KILLHEAL_WHIPBODY</t>
         </is>
       </c>
       <c r="C110" s="37" t="inlineStr">
@@ -23205,7 +25701,11 @@
           <t>WhipBody</t>
         </is>
       </c>
-      <c r="E110" s="37" t="n"/>
+      <c r="E110" s="37" t="inlineStr">
+        <is>
+          <t>击杀吸血鞭体</t>
+        </is>
+      </c>
       <c r="F110" s="37" t="inlineStr">
         <is>
           <t>效果：每击杀一名敌方单位，回复5%最大生命值</t>
@@ -23213,34 +25713,30 @@
       </c>
       <c r="G110" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="H110" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>WhipBody|UniqueBehavior</t>
         </is>
       </c>
       <c r="I110" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="J110" s="37" t="inlineStr">
         <is>
-          <t>Unimplemented</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K110" s="37" t="inlineStr">
         <is>
-          <t>Disabled</t>
-        </is>
-      </c>
-      <c r="L110" s="37" t="inlineStr">
-        <is>
-          <t>Unnamed workbook row; no stable PartId assigned.</t>
-        </is>
-      </c>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="L110" s="37" t="n"/>
       <c r="M110" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -23253,13 +25749,11 @@
       </c>
       <c r="O110" s="37" t="inlineStr">
         <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="P110" s="37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="P110" s="37" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="111" ht="22" customHeight="1" s="32">
@@ -23842,37 +26336,37 @@
     <dataValidation sqref="K46:K123" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
       <formula1>=DV_Logic_Parts_ImplementationStatus</formula1>
     </dataValidation>
-    <dataValidation sqref="S46:S55" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
+    <dataValidation sqref="S46:S82" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
       <formula1>INDIRECT("tblParts[PartId]")</formula1>
     </dataValidation>
-    <dataValidation sqref="U46:U55" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
+    <dataValidation sqref="U46:U82" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
       <formula1>=DV_Logic_PartEffects_Trigger</formula1>
     </dataValidation>
-    <dataValidation sqref="V46:V55" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
+    <dataValidation sqref="V46:V82" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
       <formula1>=DV_Logic_PartEffects_EffectKind</formula1>
     </dataValidation>
-    <dataValidation sqref="W46:W55" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
+    <dataValidation sqref="W46:W82" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
       <formula1>=DV_Logic_PartEffects_Target</formula1>
     </dataValidation>
-    <dataValidation sqref="X46:X55" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
+    <dataValidation sqref="X46:X82" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
       <formula1>=DV_Logic_PartEffects_ValueOp</formula1>
     </dataValidation>
-    <dataValidation sqref="Z46:Z55" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
+    <dataValidation sqref="Z46:Z82" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
       <formula1>=DV_Logic_PartEffects_BehaviorId</formula1>
     </dataValidation>
-    <dataValidation sqref="AA46:AA55" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
+    <dataValidation sqref="AA46:AA82" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
       <formula1>=DV_Logic_PartEffects_FormulaId</formula1>
     </dataValidation>
-    <dataValidation sqref="AB46:AB55" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
+    <dataValidation sqref="AB46:AB82" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
       <formula1>=DV_Logic_PartEffects_AttackPatternId</formula1>
     </dataValidation>
-    <dataValidation sqref="AC46:AC55" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
+    <dataValidation sqref="AC46:AC82" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
       <formula1>=DV_Logic_PartEffects_ParamName</formula1>
     </dataValidation>
-    <dataValidation sqref="AG46:AG55" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
+    <dataValidation sqref="AG46:AG82" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
       <formula1>=DV_Logic_PartEffects_StackPolicy</formula1>
     </dataValidation>
-    <dataValidation sqref="AH46:AH55" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
+    <dataValidation sqref="AH46:AH82" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
       <formula1>=DV_Logic_PartEffects_Enabled</formula1>
     </dataValidation>
     <dataValidation sqref="O46:O123" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">

--- a/Design/Data/ReEchoData.xlsx
+++ b/Design/Data/ReEchoData.xlsx
@@ -18909,7 +18909,7 @@
       </c>
       <c r="E54" s="37" t="inlineStr">
         <is>
-          <t>穿刺箭头</t>
+          <t>暴击穿透箭头</t>
         </is>
       </c>
       <c r="F54" s="37" t="inlineStr">
@@ -19060,7 +19060,7 @@
       </c>
       <c r="B55" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>P_AUDIT_C_19</t>
         </is>
       </c>
       <c r="C55" s="37" t="inlineStr">
@@ -19073,7 +19073,11 @@
           <t>Arrowhead</t>
         </is>
       </c>
-      <c r="E55" s="37" t="n"/>
+      <c r="E55" s="37" t="inlineStr">
+        <is>
+          <t>暴击流血箭头</t>
+        </is>
+      </c>
       <c r="F55" s="37" t="inlineStr">
         <is>
           <t>效果：箭命中敌人且暴击后，敌人获得【流血】，持续3秒，可以叠加</t>
@@ -19106,7 +19110,7 @@
       </c>
       <c r="L55" s="37" t="inlineStr">
         <is>
-          <t>Unnamed workbook row; no stable PartId assigned.</t>
+          <t>Disabled placeholder; part effect not yet implemented.</t>
         </is>
       </c>
       <c r="M55" s="37" t="inlineStr">
@@ -19237,7 +19241,7 @@
       </c>
       <c r="E56" s="37" t="inlineStr">
         <is>
-          <t>多发箭头</t>
+          <t>三连箭头</t>
         </is>
       </c>
       <c r="F56" s="37" t="inlineStr">
@@ -19388,7 +19392,7 @@
       </c>
       <c r="B57" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>P_AUDIT_C_21</t>
         </is>
       </c>
       <c r="C57" s="37" t="inlineStr">
@@ -19401,7 +19405,11 @@
           <t>Arrowhead</t>
         </is>
       </c>
-      <c r="E57" s="37" t="n"/>
+      <c r="E57" s="37" t="inlineStr">
+        <is>
+          <t>碎片掉落箭头</t>
+        </is>
+      </c>
       <c r="F57" s="37" t="inlineStr">
         <is>
           <t>效果：击杀一名敌方单位后，额外掉落1时间碎片</t>
@@ -19434,7 +19442,7 @@
       </c>
       <c r="L57" s="37" t="inlineStr">
         <is>
-          <t>Unnamed workbook row; no stable PartId assigned.</t>
+          <t>Disabled placeholder; part effect not yet implemented.</t>
         </is>
       </c>
       <c r="M57" s="37" t="inlineStr">
@@ -19870,7 +19878,7 @@
       </c>
       <c r="B60" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>P_AUDIT_C_24</t>
         </is>
       </c>
       <c r="C60" s="37" t="inlineStr">
@@ -19883,7 +19891,11 @@
           <t>Bowstring</t>
         </is>
       </c>
-      <c r="E60" s="37" t="n"/>
+      <c r="E60" s="37" t="inlineStr">
+        <is>
+          <t>击杀移速弓弦</t>
+        </is>
+      </c>
       <c r="F60" s="37" t="inlineStr">
         <is>
           <t>效果：击杀一名敌方单位后，移动速度+20%，持续5s。不可叠加</t>
@@ -19916,7 +19928,7 @@
       </c>
       <c r="L60" s="37" t="inlineStr">
         <is>
-          <t>Unnamed workbook row; no stable PartId assigned.</t>
+          <t>Disabled placeholder; part effect not yet implemented.</t>
         </is>
       </c>
       <c r="M60" s="37" t="inlineStr">
@@ -20032,7 +20044,7 @@
       </c>
       <c r="B61" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>P_AUDIT_C_25</t>
         </is>
       </c>
       <c r="C61" s="37" t="inlineStr">
@@ -20045,7 +20057,11 @@
           <t>Bowstring</t>
         </is>
       </c>
-      <c r="E61" s="37" t="n"/>
+      <c r="E61" s="37" t="inlineStr">
+        <is>
+          <t>连击双速弓弦</t>
+        </is>
+      </c>
       <c r="F61" s="37" t="inlineStr">
         <is>
           <t>效果：每次攻击后，攻击速度和移动速度+4%。这个效果最多叠加5层，持续5s，若1秒内没有攻击行为，层数自然流失。</t>
@@ -20078,7 +20094,7 @@
       </c>
       <c r="L61" s="37" t="inlineStr">
         <is>
-          <t>Unnamed workbook row; no stable PartId assigned.</t>
+          <t>Disabled placeholder; part effect not yet implemented.</t>
         </is>
       </c>
       <c r="M61" s="37" t="inlineStr">
@@ -20194,7 +20210,7 @@
       </c>
       <c r="B62" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>P_AUDIT_C_26</t>
         </is>
       </c>
       <c r="C62" s="37" t="inlineStr">
@@ -20207,7 +20223,11 @@
           <t>RotaryBlade</t>
         </is>
       </c>
-      <c r="E62" s="37" t="n"/>
+      <c r="E62" s="37" t="inlineStr">
+        <is>
+          <t>群攻成长旋刃</t>
+        </is>
+      </c>
       <c r="F62" s="37" t="inlineStr">
         <is>
           <t>效果：每次攻击同时命中4名敌人后，攻击范围+2%，持续5s。这个效果可以叠加。</t>
@@ -20240,7 +20260,7 @@
       </c>
       <c r="L62" s="37" t="inlineStr">
         <is>
-          <t>Unnamed workbook row; no stable PartId assigned.</t>
+          <t>Disabled placeholder; part effect not yet implemented.</t>
         </is>
       </c>
       <c r="M62" s="37" t="inlineStr">
@@ -20356,7 +20376,7 @@
       </c>
       <c r="B63" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>P_AUDIT_C_27</t>
         </is>
       </c>
       <c r="C63" s="37" t="inlineStr">
@@ -20369,7 +20389,11 @@
           <t>RotaryBlade</t>
         </is>
       </c>
-      <c r="E63" s="37" t="n"/>
+      <c r="E63" s="37" t="inlineStr">
+        <is>
+          <t>命中吸血旋刃</t>
+        </is>
+      </c>
       <c r="F63" s="37" t="inlineStr">
         <is>
           <t>效果：每次攻击，每命中一名敌方单位，回复自身1%最大生命值</t>
@@ -20402,7 +20426,7 @@
       </c>
       <c r="L63" s="37" t="inlineStr">
         <is>
-          <t>Unnamed workbook row; no stable PartId assigned.</t>
+          <t>Disabled placeholder; part effect not yet implemented.</t>
         </is>
       </c>
       <c r="M63" s="37" t="inlineStr">
@@ -20678,7 +20702,7 @@
       </c>
       <c r="B65" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>P_AUDIT_C_29</t>
         </is>
       </c>
       <c r="C65" s="37" t="inlineStr">
@@ -20691,7 +20715,11 @@
           <t>RotaryBlade</t>
         </is>
       </c>
-      <c r="E65" s="37" t="n"/>
+      <c r="E65" s="37" t="inlineStr">
+        <is>
+          <t>晕眩旋刃</t>
+        </is>
+      </c>
       <c r="F65" s="37" t="inlineStr">
         <is>
           <t>效果：每次攻击有20%概率将敌人【晕眩】，持续1s</t>
@@ -20724,7 +20752,7 @@
       </c>
       <c r="L65" s="37" t="inlineStr">
         <is>
-          <t>Unnamed workbook row; no stable PartId assigned.</t>
+          <t>Disabled placeholder; part effect not yet implemented.</t>
         </is>
       </c>
       <c r="M65" s="37" t="inlineStr">
@@ -20840,7 +20868,7 @@
       </c>
       <c r="B66" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>P_AUDIT_C_30</t>
         </is>
       </c>
       <c r="C66" s="37" t="inlineStr">
@@ -20853,7 +20881,11 @@
           <t>RotaryBlade</t>
         </is>
       </c>
-      <c r="E66" s="37" t="n"/>
+      <c r="E66" s="37" t="inlineStr">
+        <is>
+          <t>流血旋刃</t>
+        </is>
+      </c>
       <c r="F66" s="37" t="inlineStr">
         <is>
           <t>效果：敌方单位被命中3次后，获得【流血】，持续3s，可以叠加</t>
@@ -20886,7 +20918,7 @@
       </c>
       <c r="L66" s="37" t="inlineStr">
         <is>
-          <t>Unnamed workbook row; no stable PartId assigned.</t>
+          <t>Disabled placeholder; part effect not yet implemented.</t>
         </is>
       </c>
       <c r="M66" s="37" t="inlineStr">
@@ -21002,7 +21034,7 @@
       </c>
       <c r="B67" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>P_AUDIT_C_31</t>
         </is>
       </c>
       <c r="C67" s="37" t="inlineStr">
@@ -21015,7 +21047,11 @@
           <t>RotaryBlade</t>
         </is>
       </c>
-      <c r="E67" s="37" t="n"/>
+      <c r="E67" s="37" t="inlineStr">
+        <is>
+          <t>外圈增伤旋刃</t>
+        </is>
+      </c>
       <c r="F67" s="37" t="inlineStr">
         <is>
           <t>效果：外圈敌人受到的额外伤害倍率+40%</t>
@@ -21048,7 +21084,7 @@
       </c>
       <c r="L67" s="37" t="inlineStr">
         <is>
-          <t>Unnamed workbook row; no stable PartId assigned.</t>
+          <t>Disabled placeholder; part effect not yet implemented.</t>
         </is>
       </c>
       <c r="M67" s="37" t="inlineStr">
@@ -21164,7 +21200,7 @@
       </c>
       <c r="B68" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>P_AUDIT_C_32</t>
         </is>
       </c>
       <c r="C68" s="37" t="inlineStr">
@@ -21177,7 +21213,11 @@
           <t>Grip</t>
         </is>
       </c>
-      <c r="E68" s="37" t="n"/>
+      <c r="E68" s="37" t="inlineStr">
+        <is>
+          <t>镰刃命中移速握柄</t>
+        </is>
+      </c>
       <c r="F68" s="37" t="inlineStr">
         <is>
           <t>效果：每次攻击，每命中一名敌方单位，获得1%移动速度，持续5s。这个效果最多叠加30层</t>
@@ -21210,7 +21250,7 @@
       </c>
       <c r="L68" s="37" t="inlineStr">
         <is>
-          <t>Unnamed workbook row; no stable PartId assigned.</t>
+          <t>Disabled placeholder; part effect not yet implemented.</t>
         </is>
       </c>
       <c r="M68" s="37" t="inlineStr">
@@ -21326,7 +21366,7 @@
       </c>
       <c r="B69" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>P_AUDIT_C_33</t>
         </is>
       </c>
       <c r="C69" s="37" t="inlineStr">
@@ -21339,7 +21379,11 @@
           <t>Grip</t>
         </is>
       </c>
-      <c r="E69" s="37" t="n"/>
+      <c r="E69" s="37" t="inlineStr">
+        <is>
+          <t>群攻无敌握柄</t>
+        </is>
+      </c>
       <c r="F69" s="37" t="inlineStr">
         <is>
           <t>效果：攻击速度-50%。每次攻击，同时命中4名敌方单位时，获得【无敌】，持续0.5秒</t>
@@ -21372,7 +21416,7 @@
       </c>
       <c r="L69" s="37" t="inlineStr">
         <is>
-          <t>Unnamed workbook row; no stable PartId assigned.</t>
+          <t>Disabled placeholder; part effect not yet implemented.</t>
         </is>
       </c>
       <c r="M69" s="37" t="inlineStr">
@@ -21488,7 +21532,7 @@
       </c>
       <c r="B70" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>P_AUDIT_C_34</t>
         </is>
       </c>
       <c r="C70" s="37" t="inlineStr">
@@ -21501,7 +21545,11 @@
           <t>Grip</t>
         </is>
       </c>
-      <c r="E70" s="37" t="n"/>
+      <c r="E70" s="37" t="inlineStr">
+        <is>
+          <t>镰刃命中攻速握柄</t>
+        </is>
+      </c>
       <c r="F70" s="37" t="inlineStr">
         <is>
           <t>效果：每次攻击，每命中一名敌方单位，获得1%攻击速度，持续5s。这个效果最多叠加30层</t>
@@ -21534,7 +21582,7 @@
       </c>
       <c r="L70" s="37" t="inlineStr">
         <is>
-          <t>Unnamed workbook row; no stable PartId assigned.</t>
+          <t>Disabled placeholder; part effect not yet implemented.</t>
         </is>
       </c>
       <c r="M70" s="37" t="inlineStr">
@@ -21650,7 +21698,7 @@
       </c>
       <c r="B71" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>P_AUDIT_C_35</t>
         </is>
       </c>
       <c r="C71" s="37" t="inlineStr">
@@ -21663,7 +21711,11 @@
           <t>Grip</t>
         </is>
       </c>
-      <c r="E71" s="37" t="n"/>
+      <c r="E71" s="37" t="inlineStr">
+        <is>
+          <t>投掷召回链</t>
+        </is>
+      </c>
       <c r="F71" s="37" t="inlineStr">
         <is>
           <t>效果：你现在点击右键可以向前掷出镰刀并停留在其目标出。再次点击右键后，可将其召回
@@ -21700,7 +21752,7 @@
       </c>
       <c r="L71" s="37" t="inlineStr">
         <is>
-          <t>Unnamed workbook row; no stable PartId assigned.</t>
+          <t>Disabled placeholder; part effect not yet implemented.</t>
         </is>
       </c>
       <c r="M71" s="37" t="inlineStr">
@@ -22136,7 +22188,7 @@
       </c>
       <c r="B74" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>P_AUDIT_C_38</t>
         </is>
       </c>
       <c r="C74" s="37" t="inlineStr">
@@ -22149,7 +22201,11 @@
           <t>SwordBlade</t>
         </is>
       </c>
-      <c r="E74" s="37" t="n"/>
+      <c r="E74" s="37" t="inlineStr">
+        <is>
+          <t>群攻成长剑刃</t>
+        </is>
+      </c>
       <c r="F74" s="37" t="inlineStr">
         <is>
           <t>效果：每次攻击同时命中4名敌人后，攻击范围+2%，持续5s。这个效果可以叠加。</t>
@@ -22182,7 +22238,7 @@
       </c>
       <c r="L74" s="37" t="inlineStr">
         <is>
-          <t>Unnamed workbook row; no stable PartId assigned.</t>
+          <t>Disabled placeholder; part effect not yet implemented.</t>
         </is>
       </c>
       <c r="M74" s="37" t="inlineStr">
@@ -22458,7 +22514,7 @@
       </c>
       <c r="B76" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>P_AUDIT_C_40</t>
         </is>
       </c>
       <c r="C76" s="37" t="inlineStr">
@@ -22471,7 +22527,11 @@
           <t>SwordBlade</t>
         </is>
       </c>
-      <c r="E76" s="37" t="n"/>
+      <c r="E76" s="37" t="inlineStr">
+        <is>
+          <t>命中碎片剑刃</t>
+        </is>
+      </c>
       <c r="F76" s="37" t="inlineStr">
         <is>
           <t>效果：每命中5名敌方单位，掉落1时间碎片</t>
@@ -22504,7 +22564,7 @@
       </c>
       <c r="L76" s="37" t="inlineStr">
         <is>
-          <t>Unnamed workbook row; no stable PartId assigned.</t>
+          <t>Disabled placeholder; part effect not yet implemented.</t>
         </is>
       </c>
       <c r="M76" s="37" t="inlineStr">
@@ -22620,7 +22680,7 @@
       </c>
       <c r="B77" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>P_AUDIT_C_41</t>
         </is>
       </c>
       <c r="C77" s="37" t="inlineStr">
@@ -22633,7 +22693,11 @@
           <t>SwordBlade</t>
         </is>
       </c>
-      <c r="E77" s="37" t="n"/>
+      <c r="E77" s="37" t="inlineStr">
+        <is>
+          <t>暴击流血剑刃</t>
+        </is>
+      </c>
       <c r="F77" s="37" t="inlineStr">
         <is>
           <t>效果：命中敌方且暴击时，敌方单位获得【流血】，持续3s，可以叠加</t>
@@ -22666,7 +22730,7 @@
       </c>
       <c r="L77" s="37" t="inlineStr">
         <is>
-          <t>Unnamed workbook row; no stable PartId assigned.</t>
+          <t>Disabled placeholder; part effect not yet implemented.</t>
         </is>
       </c>
       <c r="M77" s="37" t="inlineStr">
@@ -22782,7 +22846,7 @@
       </c>
       <c r="B78" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>P_AUDIT_C_42</t>
         </is>
       </c>
       <c r="C78" s="37" t="inlineStr">
@@ -22795,7 +22859,11 @@
           <t>SwordBlade</t>
         </is>
       </c>
-      <c r="E78" s="37" t="n"/>
+      <c r="E78" s="37" t="inlineStr">
+        <is>
+          <t>群攻陨星剑刃</t>
+        </is>
+      </c>
       <c r="F78" s="37" t="inlineStr">
         <is>
           <t>效果：当你单次命中超过6名敌方单位时，在距离你最近的敌方单位处坠落一颗流星，造成爆炸
@@ -22830,7 +22898,7 @@
       </c>
       <c r="L78" s="37" t="inlineStr">
         <is>
-          <t>Unnamed workbook row; no stable PartId assigned.</t>
+          <t>Disabled placeholder; part effect not yet implemented.</t>
         </is>
       </c>
       <c r="M78" s="37" t="inlineStr">
@@ -23106,7 +23174,7 @@
       </c>
       <c r="B80" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>P_AUDIT_C_44</t>
         </is>
       </c>
       <c r="C80" s="37" t="inlineStr">
@@ -23119,7 +23187,11 @@
           <t>Grip</t>
         </is>
       </c>
-      <c r="E80" s="37" t="n"/>
+      <c r="E80" s="37" t="inlineStr">
+        <is>
+          <t>命中移速剑柄</t>
+        </is>
+      </c>
       <c r="F80" s="37" t="inlineStr">
         <is>
           <t>效果：每次攻击，每命中一名敌方单位，获得1%移动速度，持续5s。这个效果最多叠加30层</t>
@@ -23152,7 +23224,7 @@
       </c>
       <c r="L80" s="37" t="inlineStr">
         <is>
-          <t>Unnamed workbook row; no stable PartId assigned.</t>
+          <t>Disabled placeholder; part effect not yet implemented.</t>
         </is>
       </c>
       <c r="M80" s="37" t="inlineStr">
@@ -23268,7 +23340,7 @@
       </c>
       <c r="B81" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>P_AUDIT_C_45</t>
         </is>
       </c>
       <c r="C81" s="37" t="inlineStr">
@@ -23281,7 +23353,11 @@
           <t>Grip</t>
         </is>
       </c>
-      <c r="E81" s="37" t="n"/>
+      <c r="E81" s="37" t="inlineStr">
+        <is>
+          <t>命中攻速剑柄</t>
+        </is>
+      </c>
       <c r="F81" s="37" t="inlineStr">
         <is>
           <t>效果：每次攻击，每命中一名敌方单位，获得1%攻击速度，持续5s。这个效果最多叠加30层</t>
@@ -23314,7 +23390,7 @@
       </c>
       <c r="L81" s="37" t="inlineStr">
         <is>
-          <t>Unnamed workbook row; no stable PartId assigned.</t>
+          <t>Disabled placeholder; part effect not yet implemented.</t>
         </is>
       </c>
       <c r="M81" s="37" t="inlineStr">
@@ -23430,7 +23506,7 @@
       </c>
       <c r="B82" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>P_AUDIT_C_46</t>
         </is>
       </c>
       <c r="C82" s="37" t="inlineStr">
@@ -23443,7 +23519,11 @@
           <t>Grip</t>
         </is>
       </c>
-      <c r="E82" s="37" t="n"/>
+      <c r="E82" s="37" t="inlineStr">
+        <is>
+          <t>晕眩剑柄</t>
+        </is>
+      </c>
       <c r="F82" s="37" t="inlineStr">
         <is>
           <t>效果：每次攻击，有20%概率将敌人【晕眩】，持续1s</t>
@@ -23476,7 +23556,7 @@
       </c>
       <c r="L82" s="37" t="inlineStr">
         <is>
-          <t>Unnamed workbook row; no stable PartId assigned.</t>
+          <t>Disabled placeholder; part effect not yet implemented.</t>
         </is>
       </c>
       <c r="M82" s="37" t="inlineStr">
@@ -23744,7 +23824,7 @@
       </c>
       <c r="B85" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>P_AUDIT_C_49</t>
         </is>
       </c>
       <c r="C85" s="37" t="inlineStr">
@@ -23757,7 +23837,11 @@
           <t>Muzzle</t>
         </is>
       </c>
-      <c r="E85" s="37" t="n"/>
+      <c r="E85" s="37" t="inlineStr">
+        <is>
+          <t>极限蓄能枪口</t>
+        </is>
+      </c>
       <c r="F85" s="37" t="inlineStr">
         <is>
           <t>效果：攻击速度-500%，伤害倍率+180%</t>
@@ -23790,7 +23874,7 @@
       </c>
       <c r="L85" s="37" t="inlineStr">
         <is>
-          <t>Unnamed workbook row; no stable PartId assigned.</t>
+          <t>Disabled placeholder; part effect not yet implemented.</t>
         </is>
       </c>
       <c r="M85" s="37" t="inlineStr">
@@ -23822,7 +23906,7 @@
       </c>
       <c r="B86" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>P_AUDIT_C_50</t>
         </is>
       </c>
       <c r="C86" s="37" t="inlineStr">
@@ -23835,7 +23919,11 @@
           <t>Muzzle</t>
         </is>
       </c>
-      <c r="E86" s="37" t="n"/>
+      <c r="E86" s="37" t="inlineStr">
+        <is>
+          <t>连发枪口</t>
+        </is>
+      </c>
       <c r="F86" s="37" t="inlineStr">
         <is>
           <t>效果：攻击速度+50%</t>
@@ -23868,7 +23956,7 @@
       </c>
       <c r="L86" s="37" t="inlineStr">
         <is>
-          <t>Unnamed workbook row; no stable PartId assigned.</t>
+          <t>Disabled placeholder; part effect not yet implemented.</t>
         </is>
       </c>
       <c r="M86" s="37" t="inlineStr">
@@ -23900,7 +23988,7 @@
       </c>
       <c r="B87" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>P_AUDIT_C_51</t>
         </is>
       </c>
       <c r="C87" s="37" t="inlineStr">
@@ -23913,7 +24001,11 @@
           <t>Muzzle</t>
         </is>
       </c>
-      <c r="E87" s="37" t="n"/>
+      <c r="E87" s="37" t="inlineStr">
+        <is>
+          <t>爆炸枪口</t>
+        </is>
+      </c>
       <c r="F87" s="37" t="inlineStr">
         <is>
           <t>效果：子弹变为爆炸物。爆炸范围1m</t>
@@ -23946,7 +24038,7 @@
       </c>
       <c r="L87" s="37" t="inlineStr">
         <is>
-          <t>Unnamed workbook row; no stable PartId assigned.</t>
+          <t>Disabled placeholder; part effect not yet implemented.</t>
         </is>
       </c>
       <c r="M87" s="37" t="inlineStr">
@@ -23978,7 +24070,7 @@
       </c>
       <c r="B88" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>P_AUDIT_C_52</t>
         </is>
       </c>
       <c r="C88" s="37" t="inlineStr">
@@ -23991,7 +24083,11 @@
           <t>Muzzle</t>
         </is>
       </c>
-      <c r="E88" s="37" t="n"/>
+      <c r="E88" s="37" t="inlineStr">
+        <is>
+          <t>暴击穿透枪口</t>
+        </is>
+      </c>
       <c r="F88" s="37" t="inlineStr">
         <is>
           <t>效果：子弹命中敌人且暴击后，会穿透该敌人</t>
@@ -24024,7 +24120,7 @@
       </c>
       <c r="L88" s="37" t="inlineStr">
         <is>
-          <t>Unnamed workbook row; no stable PartId assigned.</t>
+          <t>Disabled placeholder; part effect not yet implemented.</t>
         </is>
       </c>
       <c r="M88" s="37" t="inlineStr">
@@ -24056,7 +24152,7 @@
       </c>
       <c r="B89" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>P_AUDIT_C_53</t>
         </is>
       </c>
       <c r="C89" s="37" t="inlineStr">
@@ -24069,7 +24165,11 @@
           <t>Muzzle</t>
         </is>
       </c>
-      <c r="E89" s="37" t="n"/>
+      <c r="E89" s="37" t="inlineStr">
+        <is>
+          <t>命中流血枪口</t>
+        </is>
+      </c>
       <c r="F89" s="37" t="inlineStr">
         <is>
           <t>效果：每次命中敌方单位时，敌方单位有30%概率获得【流血】，持续3s，可以叠加</t>
@@ -24102,7 +24202,7 @@
       </c>
       <c r="L89" s="37" t="inlineStr">
         <is>
-          <t>Unnamed workbook row; no stable PartId assigned.</t>
+          <t>Disabled placeholder; part effect not yet implemented.</t>
         </is>
       </c>
       <c r="M89" s="37" t="inlineStr">
@@ -24134,7 +24234,7 @@
       </c>
       <c r="B90" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>P_AUDIT_C_54</t>
         </is>
       </c>
       <c r="C90" s="37" t="inlineStr">
@@ -24147,7 +24247,11 @@
           <t>GunAction</t>
         </is>
       </c>
-      <c r="E90" s="37" t="n"/>
+      <c r="E90" s="37" t="inlineStr">
+        <is>
+          <t>命中吸血枪机</t>
+        </is>
+      </c>
       <c r="F90" s="37" t="inlineStr">
         <is>
           <t>效果：每次命中敌方单位，回复1%最大生命值</t>
@@ -24180,7 +24284,7 @@
       </c>
       <c r="L90" s="37" t="inlineStr">
         <is>
-          <t>Unnamed workbook row; no stable PartId assigned.</t>
+          <t>Disabled placeholder; part effect not yet implemented.</t>
         </is>
       </c>
       <c r="M90" s="37" t="inlineStr">
@@ -24212,7 +24316,7 @@
       </c>
       <c r="B91" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>P_AUDIT_C_55</t>
         </is>
       </c>
       <c r="C91" s="37" t="inlineStr">
@@ -24225,7 +24329,11 @@
           <t>GunAction</t>
         </is>
       </c>
-      <c r="E91" s="37" t="n"/>
+      <c r="E91" s="37" t="inlineStr">
+        <is>
+          <t>命中碎片枪机</t>
+        </is>
+      </c>
       <c r="F91" s="37" t="inlineStr">
         <is>
           <t>效果：每命中5名敌方单位，掉落1时间碎片</t>
@@ -24258,7 +24366,7 @@
       </c>
       <c r="L91" s="37" t="inlineStr">
         <is>
-          <t>Unnamed workbook row; no stable PartId assigned.</t>
+          <t>Disabled placeholder; part effect not yet implemented.</t>
         </is>
       </c>
       <c r="M91" s="37" t="inlineStr">
@@ -24290,7 +24398,7 @@
       </c>
       <c r="B92" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>P_AUDIT_C_56</t>
         </is>
       </c>
       <c r="C92" s="37" t="inlineStr">
@@ -24303,7 +24411,11 @@
           <t>GunAction</t>
         </is>
       </c>
-      <c r="E92" s="37" t="n"/>
+      <c r="E92" s="37" t="inlineStr">
+        <is>
+          <t>连射攻速枪机</t>
+        </is>
+      </c>
       <c r="F92" s="37" t="inlineStr">
         <is>
           <t>效果：每次攻击，获得1%攻击速度，持续5s。这个效果最多叠加30层</t>
@@ -24336,7 +24448,7 @@
       </c>
       <c r="L92" s="37" t="inlineStr">
         <is>
-          <t>Unnamed workbook row; no stable PartId assigned.</t>
+          <t>Disabled placeholder; part effect not yet implemented.</t>
         </is>
       </c>
       <c r="M92" s="37" t="inlineStr">
@@ -24368,7 +24480,7 @@
       </c>
       <c r="B93" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>P_AUDIT_C_57</t>
         </is>
       </c>
       <c r="C93" s="37" t="inlineStr">
@@ -24381,7 +24493,11 @@
           <t>GunAction</t>
         </is>
       </c>
-      <c r="E93" s="37" t="n"/>
+      <c r="E93" s="37" t="inlineStr">
+        <is>
+          <t>连射移速枪机</t>
+        </is>
+      </c>
       <c r="F93" s="37" t="inlineStr">
         <is>
           <t>效果：每次攻击，获得1%移动速度，持续5s。这个效果最多叠加30层</t>
@@ -24414,7 +24530,7 @@
       </c>
       <c r="L93" s="37" t="inlineStr">
         <is>
-          <t>Unnamed workbook row; no stable PartId assigned.</t>
+          <t>Disabled placeholder; part effect not yet implemented.</t>
         </is>
       </c>
       <c r="M93" s="37" t="inlineStr">
@@ -24446,7 +24562,7 @@
       </c>
       <c r="B94" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>P_AUDIT_C_58</t>
         </is>
       </c>
       <c r="C94" s="37" t="inlineStr">
@@ -24459,7 +24575,11 @@
           <t>StaffBody</t>
         </is>
       </c>
-      <c r="E94" s="37" t="n"/>
+      <c r="E94" s="37" t="inlineStr">
+        <is>
+          <t>命中吸血杖体</t>
+        </is>
+      </c>
       <c r="F94" s="37" t="inlineStr">
         <is>
           <t>效果：每次攻击，每命中一名敌方单位，回复自身1%最大生命值</t>
@@ -24492,7 +24612,7 @@
       </c>
       <c r="L94" s="37" t="inlineStr">
         <is>
-          <t>Unnamed workbook row; no stable PartId assigned.</t>
+          <t>Disabled placeholder; part effect not yet implemented.</t>
         </is>
       </c>
       <c r="M94" s="37" t="inlineStr">
@@ -24600,7 +24720,7 @@
       </c>
       <c r="B96" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>P_AUDIT_C_60</t>
         </is>
       </c>
       <c r="C96" s="37" t="inlineStr">
@@ -24613,7 +24733,11 @@
           <t>StaffBody</t>
         </is>
       </c>
-      <c r="E96" s="37" t="n"/>
+      <c r="E96" s="37" t="inlineStr">
+        <is>
+          <t>命中移速杖体</t>
+        </is>
+      </c>
       <c r="F96" s="37" t="inlineStr">
         <is>
           <t>效果：每次攻击，每命中一名敌方单位，获得1%移动速度，持续5s。这个效果最多叠加30层</t>
@@ -24646,7 +24770,7 @@
       </c>
       <c r="L96" s="37" t="inlineStr">
         <is>
-          <t>Unnamed workbook row; no stable PartId assigned.</t>
+          <t>Disabled placeholder; part effect not yet implemented.</t>
         </is>
       </c>
       <c r="M96" s="37" t="inlineStr">
@@ -24678,7 +24802,7 @@
       </c>
       <c r="B97" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>P_AUDIT_C_61</t>
         </is>
       </c>
       <c r="C97" s="37" t="inlineStr">
@@ -24691,7 +24815,11 @@
           <t>StaffBody</t>
         </is>
       </c>
-      <c r="E97" s="37" t="n"/>
+      <c r="E97" s="37" t="inlineStr">
+        <is>
+          <t>命中攻速杖体</t>
+        </is>
+      </c>
       <c r="F97" s="37" t="inlineStr">
         <is>
           <t>效果：每次攻击，每命中一名敌方单位，获得1%攻击速度，持续5s。这个效果最多叠加30层</t>
@@ -24724,7 +24852,7 @@
       </c>
       <c r="L97" s="37" t="inlineStr">
         <is>
-          <t>Unnamed workbook row; no stable PartId assigned.</t>
+          <t>Disabled placeholder; part effect not yet implemented.</t>
         </is>
       </c>
       <c r="M97" s="37" t="inlineStr">
@@ -24756,7 +24884,7 @@
       </c>
       <c r="B98" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>P_AUDIT_C_62</t>
         </is>
       </c>
       <c r="C98" s="37" t="inlineStr">
@@ -24769,7 +24897,11 @@
           <t>StaffBody</t>
         </is>
       </c>
-      <c r="E98" s="37" t="n"/>
+      <c r="E98" s="37" t="inlineStr">
+        <is>
+          <t>群攻爆炸成长杖体</t>
+        </is>
+      </c>
       <c r="F98" s="37" t="inlineStr">
         <is>
           <t>效果：每次攻击同时命中4名敌人后，爆炸范围+2%，持续5s。这个效果可以叠加。</t>
@@ -24802,7 +24934,7 @@
       </c>
       <c r="L98" s="37" t="inlineStr">
         <is>
-          <t>Unnamed workbook row; no stable PartId assigned.</t>
+          <t>Disabled placeholder; part effect not yet implemented.</t>
         </is>
       </c>
       <c r="M98" s="37" t="inlineStr">
@@ -24834,7 +24966,7 @@
       </c>
       <c r="B99" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>P_AUDIT_C_63</t>
         </is>
       </c>
       <c r="C99" s="37" t="inlineStr">
@@ -24847,7 +24979,11 @@
           <t>StaffBody</t>
         </is>
       </c>
-      <c r="E99" s="37" t="n"/>
+      <c r="E99" s="37" t="inlineStr">
+        <is>
+          <t>近战副手杖体</t>
+        </is>
+      </c>
       <c r="F99" s="37" t="inlineStr">
         <is>
           <t>效果：你现在点击右键，可以挥动法杖进行近战攻击
@@ -24884,7 +25020,7 @@
       </c>
       <c r="L99" s="37" t="inlineStr">
         <is>
-          <t>Unnamed workbook row; no stable PartId assigned.</t>
+          <t>Disabled placeholder; part effect not yet implemented.</t>
         </is>
       </c>
       <c r="M99" s="37" t="inlineStr">
@@ -25068,7 +25204,7 @@
       </c>
       <c r="B102" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>P_AUDIT_C_66</t>
         </is>
       </c>
       <c r="C102" s="37" t="inlineStr">
@@ -25081,7 +25217,11 @@
           <t>StaffCrystal</t>
         </is>
       </c>
-      <c r="E102" s="37" t="n"/>
+      <c r="E102" s="37" t="inlineStr">
+        <is>
+          <t>命中碎片杖晶</t>
+        </is>
+      </c>
       <c r="F102" s="37" t="inlineStr">
         <is>
           <t>效果：每命中5名敌方单位，掉落1时间碎片</t>
@@ -25114,7 +25254,7 @@
       </c>
       <c r="L102" s="37" t="inlineStr">
         <is>
-          <t>Unnamed workbook row; no stable PartId assigned.</t>
+          <t>Disabled placeholder; part effect not yet implemented.</t>
         </is>
       </c>
       <c r="M102" s="37" t="inlineStr">
@@ -25222,7 +25362,7 @@
       </c>
       <c r="B104" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>P_AUDIT_C_68</t>
         </is>
       </c>
       <c r="C104" s="37" t="inlineStr">
@@ -25235,7 +25375,11 @@
           <t>StaffCrystal</t>
         </is>
       </c>
-      <c r="E104" s="37" t="n"/>
+      <c r="E104" s="37" t="inlineStr">
+        <is>
+          <t>中心晕眩杖晶</t>
+        </is>
+      </c>
       <c r="F104" s="37" t="inlineStr">
         <is>
           <t>效果：爆炸范围中心1m的敌人被【眩晕】，持续1s</t>
@@ -25268,7 +25412,7 @@
       </c>
       <c r="L104" s="37" t="inlineStr">
         <is>
-          <t>Unnamed workbook row; no stable PartId assigned.</t>
+          <t>Disabled placeholder; part effect not yet implemented.</t>
         </is>
       </c>
       <c r="M104" s="37" t="inlineStr">
@@ -25300,7 +25444,7 @@
       </c>
       <c r="B105" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>P_AUDIT_C_69</t>
         </is>
       </c>
       <c r="C105" s="37" t="inlineStr">
@@ -25313,7 +25457,11 @@
           <t>StaffCrystal</t>
         </is>
       </c>
-      <c r="E105" s="37" t="n"/>
+      <c r="E105" s="37" t="inlineStr">
+        <is>
+          <t>单体高伤杖晶</t>
+        </is>
+      </c>
       <c r="F105" s="37" t="inlineStr">
         <is>
           <t>效果：炮弹不会爆炸。伤害倍率+70%</t>
@@ -25346,7 +25494,7 @@
       </c>
       <c r="L105" s="37" t="inlineStr">
         <is>
-          <t>Unnamed workbook row; no stable PartId assigned.</t>
+          <t>Disabled placeholder; part effect not yet implemented.</t>
         </is>
       </c>
       <c r="M105" s="37" t="inlineStr">
@@ -25378,7 +25526,7 @@
       </c>
       <c r="B106" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>P_AUDIT_C_70</t>
         </is>
       </c>
       <c r="C106" s="37" t="inlineStr">
@@ -25391,7 +25539,11 @@
           <t>WhipBody</t>
         </is>
       </c>
-      <c r="E106" s="37" t="n"/>
+      <c r="E106" s="37" t="inlineStr">
+        <is>
+          <t>暴击流血鞭体</t>
+        </is>
+      </c>
       <c r="F106" s="37" t="inlineStr">
         <is>
           <t>效果：命中敌人且暴击后，敌人获得【流血】，持续3秒，可以叠加</t>
@@ -25424,7 +25576,7 @@
       </c>
       <c r="L106" s="37" t="inlineStr">
         <is>
-          <t>Unnamed workbook row; no stable PartId assigned.</t>
+          <t>Disabled placeholder; part effect not yet implemented.</t>
         </is>
       </c>
       <c r="M106" s="37" t="inlineStr">
@@ -25456,7 +25608,7 @@
       </c>
       <c r="B107" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>P_AUDIT_C_71</t>
         </is>
       </c>
       <c r="C107" s="37" t="inlineStr">
@@ -25469,7 +25621,11 @@
           <t>WhipBody</t>
         </is>
       </c>
-      <c r="E107" s="37" t="n"/>
+      <c r="E107" s="37" t="inlineStr">
+        <is>
+          <t>慢攻重击鞭体</t>
+        </is>
+      </c>
       <c r="F107" s="37" t="inlineStr">
         <is>
           <t>效果：攻击速度-30%，伤害倍率+40%（第二段+80%）</t>
@@ -25502,7 +25658,7 @@
       </c>
       <c r="L107" s="37" t="inlineStr">
         <is>
-          <t>Unnamed workbook row; no stable PartId assigned.</t>
+          <t>Disabled placeholder; part effect not yet implemented.</t>
         </is>
       </c>
       <c r="M107" s="37" t="inlineStr">
@@ -25534,7 +25690,7 @@
       </c>
       <c r="B108" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>P_AUDIT_C_72</t>
         </is>
       </c>
       <c r="C108" s="37" t="inlineStr">
@@ -25547,7 +25703,11 @@
           <t>WhipBody</t>
         </is>
       </c>
-      <c r="E108" s="37" t="n"/>
+      <c r="E108" s="37" t="inlineStr">
+        <is>
+          <t>去击退重击鞭体</t>
+        </is>
+      </c>
       <c r="F108" s="37" t="inlineStr">
         <is>
           <t>效果：第一段攻击不再附带【击退】效果，伤害倍率+40%（第二段+80%）</t>
@@ -25580,7 +25740,7 @@
       </c>
       <c r="L108" s="37" t="inlineStr">
         <is>
-          <t>Unnamed workbook row; no stable PartId assigned.</t>
+          <t>Disabled placeholder; part effect not yet implemented.</t>
         </is>
       </c>
       <c r="M108" s="37" t="inlineStr">
@@ -25764,7 +25924,7 @@
       </c>
       <c r="B111" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>P_AUDIT_C_75</t>
         </is>
       </c>
       <c r="C111" s="37" t="inlineStr">
@@ -25777,7 +25937,11 @@
           <t>Grip</t>
         </is>
       </c>
-      <c r="E111" s="37" t="n"/>
+      <c r="E111" s="37" t="inlineStr">
+        <is>
+          <t>第一段横扫握柄</t>
+        </is>
+      </c>
       <c r="F111" s="37" t="inlineStr">
         <is>
           <t>效果：只触发第一段攻击，并且第一段攻击外圈敌人也会受到额外伤害</t>
@@ -25810,7 +25974,7 @@
       </c>
       <c r="L111" s="37" t="inlineStr">
         <is>
-          <t>Unnamed workbook row; no stable PartId assigned.</t>
+          <t>Disabled placeholder; part effect not yet implemented.</t>
         </is>
       </c>
       <c r="M111" s="37" t="inlineStr">
@@ -25842,7 +26006,7 @@
       </c>
       <c r="B112" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>P_AUDIT_C_76</t>
         </is>
       </c>
       <c r="C112" s="37" t="inlineStr">
@@ -25855,7 +26019,11 @@
           <t>Grip</t>
         </is>
       </c>
-      <c r="E112" s="37" t="n"/>
+      <c r="E112" s="37" t="inlineStr">
+        <is>
+          <t>第二段刺击握柄</t>
+        </is>
+      </c>
       <c r="F112" s="37" t="inlineStr">
         <is>
           <t>效果：只触发第二段攻击，第二段攻击角度为60°</t>
@@ -25888,7 +26056,7 @@
       </c>
       <c r="L112" s="37" t="inlineStr">
         <is>
-          <t>Unnamed workbook row; no stable PartId assigned.</t>
+          <t>Disabled placeholder; part effect not yet implemented.</t>
         </is>
       </c>
       <c r="M112" s="37" t="inlineStr">
@@ -25920,7 +26088,7 @@
       </c>
       <c r="B113" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>P_AUDIT_C_77</t>
         </is>
       </c>
       <c r="C113" s="37" t="inlineStr">
@@ -25933,7 +26101,11 @@
           <t>Grip</t>
         </is>
       </c>
-      <c r="E113" s="37" t="n"/>
+      <c r="E113" s="37" t="inlineStr">
+        <is>
+          <t>鞭术命中移速握柄</t>
+        </is>
+      </c>
       <c r="F113" s="37" t="inlineStr">
         <is>
           <t>效果：每次攻击，每命中一名敌方单位，获得1%移动速度，持续5s。这个效果最多叠加30层</t>
@@ -25966,7 +26138,7 @@
       </c>
       <c r="L113" s="37" t="inlineStr">
         <is>
-          <t>Unnamed workbook row; no stable PartId assigned.</t>
+          <t>Disabled placeholder; part effect not yet implemented.</t>
         </is>
       </c>
       <c r="M113" s="37" t="inlineStr">
@@ -25998,7 +26170,7 @@
       </c>
       <c r="B114" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>P_AUDIT_C_78</t>
         </is>
       </c>
       <c r="C114" s="37" t="inlineStr">
@@ -26011,7 +26183,11 @@
           <t>Grip</t>
         </is>
       </c>
-      <c r="E114" s="37" t="n"/>
+      <c r="E114" s="37" t="inlineStr">
+        <is>
+          <t>鞭术命中攻速握柄</t>
+        </is>
+      </c>
       <c r="F114" s="37" t="inlineStr">
         <is>
           <t>效果：每次攻击，每命中一名敌方单位，获得1%攻击速度，持续5s。这个效果最多叠加30层</t>
@@ -26044,7 +26220,7 @@
       </c>
       <c r="L114" s="37" t="inlineStr">
         <is>
-          <t>Unnamed workbook row; no stable PartId assigned.</t>
+          <t>Disabled placeholder; part effect not yet implemented.</t>
         </is>
       </c>
       <c r="M114" s="37" t="inlineStr">
@@ -26076,7 +26252,7 @@
       </c>
       <c r="B115" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>P_AUDIT_C_79</t>
         </is>
       </c>
       <c r="C115" s="37" t="inlineStr">
@@ -26089,7 +26265,11 @@
           <t>Grip</t>
         </is>
       </c>
-      <c r="E115" s="37" t="n"/>
+      <c r="E115" s="37" t="inlineStr">
+        <is>
+          <t>群攻延伸握柄</t>
+        </is>
+      </c>
       <c r="F115" s="37" t="inlineStr">
         <is>
           <t>效果：每次攻击同时命中4名敌人后，攻击范围+2%，持续5s。这个效果可以叠加。</t>
@@ -26122,7 +26302,7 @@
       </c>
       <c r="L115" s="37" t="inlineStr">
         <is>
-          <t>Unnamed workbook row; no stable PartId assigned.</t>
+          <t>Disabled placeholder; part effect not yet implemented.</t>
         </is>
       </c>
       <c r="M115" s="37" t="inlineStr">

--- a/Design/Data/ReEchoData.xlsx
+++ b/Design/Data/ReEchoData.xlsx
@@ -9418,12 +9418,12 @@
       </c>
       <c r="I39" s="37" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="J39" s="37" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="K39" s="37" t="inlineStr">
@@ -9438,10 +9438,14 @@
       </c>
       <c r="M39" s="37" t="inlineStr">
         <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="N39" s="37" t="n"/>
+          <t>Disabled</t>
+        </is>
+      </c>
+      <c r="N39" s="37" t="inlineStr">
+        <is>
+          <t>已废弃-设计数值稿最新版移除-保留数据与Shard机制测试</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="22" customHeight="1" s="32">
       <c r="A40" s="37" t="inlineStr">
@@ -9484,12 +9488,12 @@
       </c>
       <c r="I40" s="37" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="J40" s="37" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="K40" s="37" t="inlineStr">
@@ -9504,10 +9508,14 @@
       </c>
       <c r="M40" s="37" t="inlineStr">
         <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="N40" s="37" t="n"/>
+          <t>Disabled</t>
+        </is>
+      </c>
+      <c r="N40" s="37" t="inlineStr">
+        <is>
+          <t>已废弃-设计数值稿最新版移除-保留数据与Shard机制测试</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="22" customHeight="1" s="32">
       <c r="A41" s="37" t="inlineStr">

--- a/Design/Data/ReEchoData.xlsx
+++ b/Design/Data/ReEchoData.xlsx
@@ -574,7 +574,31 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="tblWorkbookMeta" displayName="tblWorkbookMeta" ref="A1:B8" headerRowCount="1" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="tblShopPriceRanges" displayName="tblShopPriceRanges" ref="A1:C9" headerRowCount="1">
+  <autoFilter ref="A1:C9"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="PriceCategory"/>
+    <tableColumn id="2" name="MinPrice"/>
+    <tableColumn id="3" name="MaxPrice"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="tblShopDropLevels" displayName="tblShopDropLevels" ref="A12:C20" headerRowCount="1">
+  <autoFilter ref="A12:C20"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="EncounterIndex"/>
+    <tableColumn id="2" name="FreeTier"/>
+    <tableColumn id="3" name="ShopTiers"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="tblWorkbookMeta" displayName="tblWorkbookMeta" ref="A1:B8" headerRowCount="1" totalsRowShown="0">
   <tableColumns count="2">
     <tableColumn id="1" name="Key"/>
     <tableColumn id="2" name="Value"/>
@@ -583,8 +607,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="tblExportMap" displayName="tblExportMap" ref="A1:E18" headerRowCount="1" totalsRowShown="0">
+<file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="tblExportMap" displayName="tblExportMap" ref="A1:E20" headerRowCount="1" totalsRowShown="0">
   <tableColumns count="5">
     <tableColumn id="1" name="SheetName"/>
     <tableColumn id="2" name="TableName"/>
@@ -596,8 +620,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="tblRuntimeSmoke" displayName="tblRuntimeSmoke" ref="A3:J4" headerRowCount="1" totalsRowShown="0">
+<file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="tblRuntimeSmoke" displayName="tblRuntimeSmoke" ref="A3:J4" headerRowCount="1" totalsRowShown="0">
   <tableColumns count="10">
     <tableColumn id="1" name="Id"/>
     <tableColumn id="2" name="DisplayNameKey"/>
@@ -611,35 +635,6 @@
     <tableColumn id="10" name="ModifierOp"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="tblRuntimeSmokeEffects" displayName="tblRuntimeSmokeEffects" ref="L3:P4" headerRowCount="1" totalsRowShown="0">
-  <tableColumns count="5">
-    <tableColumn id="1" name="Id"/>
-    <tableColumn id="2" name="RuntimeRowId"/>
-    <tableColumn id="3" name="ParamName"/>
-    <tableColumn id="4" name="ValueOp"/>
-    <tableColumn id="5" name="Value"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="tblAttributes" displayName="tblAttributes" ref="A1:G9" headerRowCount="1">
-  <autoFilter ref="A1:G9"/>
-  <tableColumns count="7">
-    <tableColumn id="1" name="Id"/>
-    <tableColumn id="2" name="DisplayName"/>
-    <tableColumn id="3" name="Tier"/>
-    <tableColumn id="4" name="IconName"/>
-    <tableColumn id="5" name="ValueKind"/>
-    <tableColumn id="6" name="DisplayOrder"/>
-    <tableColumn id="7" name="Explanation"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
 </file>
 
@@ -667,6 +662,35 @@
     <tableColumn id="18" name="DisabledReason"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="tblRuntimeSmokeEffects" displayName="tblRuntimeSmokeEffects" ref="L3:P4" headerRowCount="1" totalsRowShown="0">
+  <tableColumns count="5">
+    <tableColumn id="1" name="Id"/>
+    <tableColumn id="2" name="RuntimeRowId"/>
+    <tableColumn id="3" name="ParamName"/>
+    <tableColumn id="4" name="ValueOp"/>
+    <tableColumn id="5" name="Value"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="21" name="tblAttributes" displayName="tblAttributes" ref="A1:G9" headerRowCount="1">
+  <autoFilter ref="A1:G9"/>
+  <tableColumns count="7">
+    <tableColumn id="1" name="Id"/>
+    <tableColumn id="2" name="DisplayName"/>
+    <tableColumn id="3" name="Tier"/>
+    <tableColumn id="4" name="IconName"/>
+    <tableColumn id="5" name="ValueKind"/>
+    <tableColumn id="6" name="DisplayOrder"/>
+    <tableColumn id="7" name="Explanation"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
 </file>
 
@@ -2644,7 +2668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <cols>
     <col width="13" customWidth="1" style="28" min="1" max="1"/>
@@ -3137,6 +3161,60 @@
       <c r="E18" s="0" t="inlineStr">
         <is>
           <t>100</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0" t="inlineStr">
+        <is>
+          <t>经济系统</t>
+        </is>
+      </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>tblShopPriceRanges</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t>shop_price_ranges.csv</t>
+        </is>
+      </c>
+      <c r="E19" s="0" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="0" t="inlineStr">
+        <is>
+          <t>经济系统</t>
+        </is>
+      </c>
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t>tblShopDropLevels</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D20" s="0" t="inlineStr">
+        <is>
+          <t>shop_drop_levels.csv</t>
+        </is>
+      </c>
+      <c r="E20" s="0" t="inlineStr">
+        <is>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -27220,18 +27298,246 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="L1:L1"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="13.81640625" defaultRowHeight="13"/>
   <sheetData>
     <row r="1" ht="39" customHeight="1" s="32">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>PriceCategory</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>MinPrice</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>MaxPrice</t>
+        </is>
+      </c>
       <c r="L1" s="26" t="inlineStr">
         <is>
           <t>ReferenceOnly：经济系统尚未迁移为生产 Table，本 Sheet 仅作说明。</t>
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="38" t="inlineStr">
+        <is>
+          <t>Core_Primordial</t>
+        </is>
+      </c>
+      <c r="B2" s="38" t="n">
+        <v>10</v>
+      </c>
+      <c r="C2" s="38" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="38" t="inlineStr">
+        <is>
+          <t>Core_Element</t>
+        </is>
+      </c>
+      <c r="B3" s="38" t="n">
+        <v>20</v>
+      </c>
+      <c r="C3" s="38" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="38" t="inlineStr">
+        <is>
+          <t>Rune</t>
+        </is>
+      </c>
+      <c r="B4" s="38" t="n">
+        <v>30</v>
+      </c>
+      <c r="C4" s="38" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="38" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+      <c r="B5" s="38" t="n">
+        <v>10</v>
+      </c>
+      <c r="C5" s="38" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="38" t="inlineStr">
+        <is>
+          <t>Card_T1</t>
+        </is>
+      </c>
+      <c r="B6" s="38" t="n">
+        <v>30</v>
+      </c>
+      <c r="C6" s="38" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="38" t="inlineStr">
+        <is>
+          <t>Card_T2</t>
+        </is>
+      </c>
+      <c r="B7" s="38" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" s="38" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="38" t="inlineStr">
+        <is>
+          <t>Card_T3</t>
+        </is>
+      </c>
+      <c r="B8" s="38" t="n">
+        <v>150</v>
+      </c>
+      <c r="C8" s="38" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="38" t="inlineStr">
+        <is>
+          <t>PrismCrystal</t>
+        </is>
+      </c>
+      <c r="B9" s="38" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" s="38" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="inlineStr">
+        <is>
+          <t>EncounterIndex</t>
+        </is>
+      </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>FreeTier</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>ShopTiers</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" s="40" t="n"/>
+      <c r="C13" s="40" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="38" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" s="38" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" s="38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="38" t="n">
+        <v>3</v>
+      </c>
+      <c r="B15" s="38" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" s="38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="38" t="n">
+        <v>4</v>
+      </c>
+      <c r="B16" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="38" t="inlineStr">
+        <is>
+          <t>2|3</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="38" t="n">
+        <v>5</v>
+      </c>
+      <c r="B17" s="38" t="n">
+        <v>2</v>
+      </c>
+      <c r="C17" s="40" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="38" t="n">
+        <v>6</v>
+      </c>
+      <c r="B18" s="38" t="n">
+        <v>3</v>
+      </c>
+      <c r="C18" s="38" t="inlineStr">
+        <is>
+          <t>1|2</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="38" t="n">
+        <v>7</v>
+      </c>
+      <c r="B19" s="38" t="n">
+        <v>2</v>
+      </c>
+      <c r="C19" s="38" t="inlineStr">
+        <is>
+          <t>1|3</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="38" t="n">
+        <v>8</v>
+      </c>
+      <c r="B20" s="40" t="n"/>
+      <c r="C20" s="40" t="n"/>
+    </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="2">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/Design/Data/ReEchoData.xlsx
+++ b/Design/Data/ReEchoData.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet name="属性S" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="元素体系Y" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="构筑体系G" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="角色体系J" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="武器体系W" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="武器插槽C" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="怪物体系M" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="状态Z" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="经济系统" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="_WorkbookMeta" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="_ExportMap" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="_SystemData" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="AttributeCatalog" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="属性S" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="元素体系Y" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="构筑体系G" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色体系J" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="武器体系W" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="武器插槽C" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="怪物体系M" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="状态Z" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经济系统" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_WorkbookMeta" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_ExportMap" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_SystemData" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AttributeCatalog" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName name="DV_Logic_Elements_Id">'_SystemData'!$R$2:$R$5</definedName>
@@ -73,22 +73,22 @@
     <definedName name="DV_Logic_Parts_Enabled">'_SystemData'!$BR$2:$BR$3</definedName>
     <definedName name="DV_Logic_Parts_ReviewStatus">'_SystemData'!$BS$2:$BS$3</definedName>
     <definedName name="DV_Logic_Parts_ImplementationStatus">'_SystemData'!$BT$2:$BT$3</definedName>
-    <definedName name="DV_Logic_PartEffects_Trigger">'_SystemData'!$BU$2:$BU$3</definedName>
     <definedName name="DV_Logic_PartEffects_EffectKind">'_SystemData'!$BV$2:$BV$5</definedName>
-    <definedName name="DV_Logic_PartEffects_Target">'_SystemData'!$BW$2:$BW$8</definedName>
     <definedName name="DV_Logic_PartEffects_ValueOp">'_SystemData'!$BX$2:$BX$4</definedName>
-    <definedName name="DV_Logic_PartEffects_BehaviorId">'_SystemData'!$BY$2:$BY$5</definedName>
     <definedName name="DV_Logic_PartEffects_FormulaId">'_SystemData'!$BZ$2:$BZ$2</definedName>
     <definedName name="DV_Logic_PartEffects_AttackPatternId">'_SystemData'!$CA$2:$CA$3</definedName>
-    <definedName name="DV_Logic_PartEffects_ParamName">'_SystemData'!$CB$2:$CB$9</definedName>
-    <definedName name="DV_Logic_PartEffects_StackPolicy">'_SystemData'!$CC$2:$CC$3</definedName>
     <definedName name="DV_Logic_PartEffects_Enabled">'_SystemData'!$CD$2:$CD$3</definedName>
-    <definedName name="DV_Logic_Statuses_BehaviorId">'_SystemData'!$CE$2:$CE$4</definedName>
     <definedName name="DV_Logic_Statuses_StackPolicy">'_SystemData'!$CF$2:$CF$4</definedName>
-    <definedName name="DV_Logic_Statuses_RefreshPolicy">'_SystemData'!$CG$2:$CG$3</definedName>
     <definedName name="DV_Logic_Statuses_MutexGroup">'_SystemData'!$CH$2:$CH$8</definedName>
     <definedName name="DV_Logic_Statuses_Tags">'_SystemData'!$CI$2:$CI$9</definedName>
     <definedName name="DV_Logic_Statuses_Enabled">'_SystemData'!$CJ$2:$CJ$3</definedName>
+    <definedName name="DV_Logic_PartEffects_Trigger">'_SystemData'!$BU$2:$BU$8</definedName>
+    <definedName name="DV_Logic_PartEffects_Target">'_SystemData'!$BW$2:$BW$14</definedName>
+    <definedName name="DV_Logic_PartEffects_BehaviorId">'_SystemData'!$BY$2:$BY$24</definedName>
+    <definedName name="DV_Logic_PartEffects_ParamName">'_SystemData'!$CB$2:$CB$19</definedName>
+    <definedName name="DV_Logic_PartEffects_StackPolicy">'_SystemData'!$CC$2:$CC$5</definedName>
+    <definedName name="DV_Logic_Statuses_BehaviorId">'_SystemData'!$CE$2:$CE$6</definedName>
+    <definedName name="DV_Logic_Statuses_RefreshPolicy">'_SystemData'!$CG$2:$CG$4</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -525,7 +525,7 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="tblPartEffects" displayName="tblPartEffects" ref="R45:AK82" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="tblPartEffects" displayName="tblPartEffects" ref="R45:AK120" headerRowCount="1">
   <autoFilter ref="R45:AK55"/>
   <tableColumns count="20">
     <tableColumn id="16" name="Id"/>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="BU3" s="36" t="inlineStr">
         <is>
-          <t>OnKill</t>
+          <t>OnAttack</t>
         </is>
       </c>
       <c r="BV3" s="36" t="inlineStr">
@@ -4695,6 +4695,11 @@
           <t>Core|DamageChannel|Grass</t>
         </is>
       </c>
+      <c r="BU4" s="0" t="inlineStr">
+        <is>
+          <t>OnActiveAttack</t>
+        </is>
+      </c>
       <c r="BV4" s="36" t="inlineStr">
         <is>
           <t>AttackPatternReplacement</t>
@@ -4720,6 +4725,11 @@
           <t>Grass</t>
         </is>
       </c>
+      <c r="CC4" s="0" t="inlineStr">
+        <is>
+          <t>NoStack</t>
+        </is>
+      </c>
       <c r="CE4" s="36" t="inlineStr">
         <is>
           <t>Status.Burn</t>
@@ -4728,6 +4738,11 @@
       <c r="CF4" s="36" t="inlineStr">
         <is>
           <t>Stackable</t>
+        </is>
+      </c>
+      <c r="CG4" s="0" t="inlineStr">
+        <is>
+          <t>Independent</t>
         </is>
       </c>
       <c r="CH4" s="36" t="inlineStr">
@@ -4862,6 +4877,11 @@
           <t>Core|DamageChannel|Flame</t>
         </is>
       </c>
+      <c r="BU5" s="0" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
       <c r="BV5" s="36" t="inlineStr">
         <is>
           <t>UniqueBehavior</t>
@@ -4880,6 +4900,16 @@
       <c r="CB5" s="36" t="inlineStr">
         <is>
           <t>Flame</t>
+        </is>
+      </c>
+      <c r="CC5" s="0" t="inlineStr">
+        <is>
+          <t>IndependentTimed</t>
+        </is>
+      </c>
+      <c r="CE5" s="0" t="inlineStr">
+        <is>
+          <t>Status.Stun</t>
         </is>
       </c>
       <c r="CH5" s="36" t="inlineStr">
@@ -4984,14 +5014,29 @@
           <t>Core|DamageChannel|Lightning</t>
         </is>
       </c>
+      <c r="BU6" s="0" t="inlineStr">
+        <is>
+          <t>OnCriticalHit</t>
+        </is>
+      </c>
       <c r="BW6" s="36" t="inlineStr">
         <is>
           <t>ElementalCoefficient</t>
         </is>
       </c>
+      <c r="BY6" s="0" t="inlineStr">
+        <is>
+          <t>Part.ProjectileSplitOnHit</t>
+        </is>
+      </c>
       <c r="CB6" s="36" t="inlineStr">
         <is>
           <t>Lightning</t>
+        </is>
+      </c>
+      <c r="CE6" s="0" t="inlineStr">
+        <is>
+          <t>Status.Bleeding</t>
         </is>
       </c>
       <c r="CH6" s="36" t="inlineStr">
@@ -5071,9 +5116,19 @@
           <t>Core|DamageChannel|RandomElement</t>
         </is>
       </c>
+      <c r="BU7" s="0" t="inlineStr">
+        <is>
+          <t>OnAttackResolved</t>
+        </is>
+      </c>
       <c r="BW7" s="36" t="inlineStr">
         <is>
           <t>AttackPattern</t>
+        </is>
+      </c>
+      <c r="BY7" s="0" t="inlineStr">
+        <is>
+          <t>Part.ProjectilePierceOnCritical</t>
         </is>
       </c>
       <c r="CB7" s="36" t="inlineStr">
@@ -5158,9 +5213,19 @@
           <t>Grip|AttackPatternReplacement</t>
         </is>
       </c>
+      <c r="BU8" s="0" t="inlineStr">
+        <is>
+          <t>OnKill</t>
+        </is>
+      </c>
       <c r="BW8" s="36" t="inlineStr">
         <is>
           <t>OnKill</t>
+        </is>
+      </c>
+      <c r="BY8" s="0" t="inlineStr">
+        <is>
+          <t>Part.ApplyBleedOnCritical</t>
         </is>
       </c>
       <c r="CB8" s="36" t="inlineStr">
@@ -5235,6 +5300,16 @@
           <t>Grip|Numeric</t>
         </is>
       </c>
+      <c r="BW9" s="0" t="inlineStr">
+        <is>
+          <t>AttackRange</t>
+        </is>
+      </c>
+      <c r="BY9" s="0" t="inlineStr">
+        <is>
+          <t>Part.DropShardOnKill</t>
+        </is>
+      </c>
       <c r="CB9" s="36" t="inlineStr">
         <is>
           <t>HealMaxHpPercent</t>
@@ -5292,6 +5367,21 @@
           <t>None</t>
         </is>
       </c>
+      <c r="BW10" s="0" t="inlineStr">
+        <is>
+          <t>AttackArc</t>
+        </is>
+      </c>
+      <c r="BY10" s="0" t="inlineStr">
+        <is>
+          <t>Part.MoveSpeedOnKill</t>
+        </is>
+      </c>
+      <c r="CB10" s="0" t="inlineStr">
+        <is>
+          <t>MaxChildren</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="AD11" s="36" t="inlineStr">
@@ -5334,6 +5424,21 @@
           <t>Blade|UniqueBehavior</t>
         </is>
       </c>
+      <c r="BW11" s="0" t="inlineStr">
+        <is>
+          <t>ProjectileCount</t>
+        </is>
+      </c>
+      <c r="BY11" s="0" t="inlineStr">
+        <is>
+          <t>Part.AttackMoveSpeedOnAttack</t>
+        </is>
+      </c>
+      <c r="CB11" s="0" t="inlineStr">
+        <is>
+          <t>ShardCount</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="AD12" s="36" t="inlineStr">
@@ -5376,6 +5481,21 @@
           <t>Arrowhead|UniqueBehavior</t>
         </is>
       </c>
+      <c r="BW12" s="0" t="inlineStr">
+        <is>
+          <t>ConcentrationDegrees</t>
+        </is>
+      </c>
+      <c r="BY12" s="0" t="inlineStr">
+        <is>
+          <t>Part.RangeOnGroupHit</t>
+        </is>
+      </c>
+      <c r="CB12" s="0" t="inlineStr">
+        <is>
+          <t>MaxStacks</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="AD13" s="36" t="inlineStr">
@@ -5408,6 +5528,21 @@
           <t>Arrowhead|AttackPatternReplacement</t>
         </is>
       </c>
+      <c r="BW13" s="0" t="inlineStr">
+        <is>
+          <t>ExplosionRadius</t>
+        </is>
+      </c>
+      <c r="BY13" s="0" t="inlineStr">
+        <is>
+          <t>Part.HealOnHit</t>
+        </is>
+      </c>
+      <c r="CB13" s="0" t="inlineStr">
+        <is>
+          <t>GroupThreshold</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="AD14" s="36" t="inlineStr">
@@ -5435,6 +5570,21 @@
           <t>KillThreshold</t>
         </is>
       </c>
+      <c r="BW14" s="0" t="inlineStr">
+        <is>
+          <t>RuntimeBehavior</t>
+        </is>
+      </c>
+      <c r="BY14" s="0" t="inlineStr">
+        <is>
+          <t>Part.StunOnHit</t>
+        </is>
+      </c>
+      <c r="CB14" s="0" t="inlineStr">
+        <is>
+          <t>Chance</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="AD15" s="36" t="inlineStr">
@@ -5457,6 +5607,16 @@
           <t>PenaltyChoices</t>
         </is>
       </c>
+      <c r="BY15" s="0" t="inlineStr">
+        <is>
+          <t>Part.BleedEveryTargetHits</t>
+        </is>
+      </c>
+      <c r="CB15" s="0" t="inlineStr">
+        <is>
+          <t>HitThreshold</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="AD16" s="36" t="inlineStr">
@@ -5479,6 +5639,16 @@
           <t>ShardCost</t>
         </is>
       </c>
+      <c r="BY16" s="0" t="inlineStr">
+        <is>
+          <t>Part.OuterRingDamage</t>
+        </is>
+      </c>
+      <c r="CB16" s="0" t="inlineStr">
+        <is>
+          <t>OuterRingFraction</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="AD17" s="36" t="inlineStr">
@@ -5501,6 +5671,16 @@
           <t>DistinctCount</t>
         </is>
       </c>
+      <c r="BY17" s="0" t="inlineStr">
+        <is>
+          <t>Part.MoveSpeedPerHit</t>
+        </is>
+      </c>
+      <c r="CB17" s="0" t="inlineStr">
+        <is>
+          <t>MaxRangeCm</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="AD18" s="36" t="inlineStr">
@@ -5518,6 +5698,16 @@
           <t>Card.SoloBody</t>
         </is>
       </c>
+      <c r="BY18" s="0" t="inlineStr">
+        <is>
+          <t>Part.InvulnerableOnGroupHit</t>
+        </is>
+      </c>
+      <c r="CB18" s="0" t="inlineStr">
+        <is>
+          <t>StationaryDamageMultiplier</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="AD19" s="36" t="inlineStr">
@@ -5535,6 +5725,16 @@
           <t>Card.TauntEcho</t>
         </is>
       </c>
+      <c r="BY19" s="0" t="inlineStr">
+        <is>
+          <t>Part.AttackSpeedPerHit</t>
+        </is>
+      </c>
+      <c r="CB19" s="0" t="inlineStr">
+        <is>
+          <t>ExplosionRadiusCm</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="AD20" s="36" t="inlineStr">
@@ -5552,6 +5752,11 @@
           <t>Card.SoulResonance</t>
         </is>
       </c>
+      <c r="BY20" s="0" t="inlineStr">
+        <is>
+          <t>Part.ScytheThrowRecall</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="AD21" s="36" t="inlineStr">
@@ -5569,6 +5774,11 @@
           <t>Card.EnemyImmunity</t>
         </is>
       </c>
+      <c r="BY21" s="0" t="inlineStr">
+        <is>
+          <t>Part.DropShardEveryHits</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="AD22" s="36" t="inlineStr">
@@ -5586,6 +5796,11 @@
           <t>Card.CriticalElement</t>
         </is>
       </c>
+      <c r="BY22" s="0" t="inlineStr">
+        <is>
+          <t>Part.MeteorOnGroupHit</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="AN23" s="36" t="inlineStr">
@@ -5598,6 +5813,11 @@
           <t>Card.ElementCanCrit</t>
         </is>
       </c>
+      <c r="BY23" s="0" t="inlineStr">
+        <is>
+          <t>Part.ApplyBleedOnHitChance</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="AN24" s="36" t="inlineStr">
@@ -5608,6 +5828,11 @@
       <c r="AP24" s="36" t="inlineStr">
         <is>
           <t>Card.DistanceDamage</t>
+        </is>
+      </c>
+      <c r="BY24" s="0" t="inlineStr">
+        <is>
+          <t>Part.AttackSpeedOnAttack</t>
         </is>
       </c>
     </row>
@@ -14414,7 +14639,7 @@
       </c>
       <c r="C15" s="37" t="inlineStr">
         <is>
-          <t>Staff</t>
+          <t>法杖</t>
         </is>
       </c>
       <c r="D15" s="37" t="inlineStr">
@@ -14517,7 +14742,7 @@
       </c>
       <c r="C16" s="37" t="inlineStr">
         <is>
-          <t>Crescent Blade</t>
+          <t>长剑</t>
         </is>
       </c>
       <c r="D16" s="37" t="inlineStr">
@@ -14620,7 +14845,7 @@
       </c>
       <c r="C17" s="37" t="inlineStr">
         <is>
-          <t>Harvest Scythe</t>
+          <t>镰刀</t>
         </is>
       </c>
       <c r="D17" s="37" t="inlineStr">
@@ -14723,7 +14948,7 @@
       </c>
       <c r="C18" s="37" t="inlineStr">
         <is>
-          <t>Whip</t>
+          <t>鞭</t>
         </is>
       </c>
       <c r="D18" s="37" t="inlineStr">
@@ -14826,7 +15051,7 @@
       </c>
       <c r="C19" s="37" t="inlineStr">
         <is>
-          <t>Bow</t>
+          <t>弓</t>
         </is>
       </c>
       <c r="D19" s="37" t="inlineStr">
@@ -14929,7 +15154,7 @@
       </c>
       <c r="C20" s="37" t="inlineStr">
         <is>
-          <t>Gun</t>
+          <t>枪</t>
         </is>
       </c>
       <c r="D20" s="37" t="inlineStr">
@@ -18683,24 +18908,20 @@
       </c>
       <c r="I52" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="J52" s="37" t="inlineStr">
         <is>
-          <t>Unimplemented</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K52" s="37" t="inlineStr">
         <is>
-          <t>Disabled</t>
-        </is>
-      </c>
-      <c r="L52" s="37" t="inlineStr">
-        <is>
-          <t>Split projectile handler is not implemented.</t>
-        </is>
-      </c>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="L52" s="37" t="n"/>
       <c r="M52" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -18713,12 +18934,12 @@
       </c>
       <c r="O52" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="P52" s="37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45</t>
         </is>
       </c>
       <c r="R52" s="37" t="inlineStr">
@@ -18844,29 +19065,25 @@
       </c>
       <c r="H53" s="37" t="inlineStr">
         <is>
-          <t>Arrowhead|AttackPatternReplacement</t>
+          <t>Arrowhead|Numeric</t>
         </is>
       </c>
       <c r="I53" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="J53" s="37" t="inlineStr">
         <is>
-          <t>Unimplemented</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K53" s="37" t="inlineStr">
         <is>
-          <t>Disabled</t>
-        </is>
-      </c>
-      <c r="L53" s="37" t="inlineStr">
-        <is>
-          <t>Projectile explosion handler is not implemented.</t>
-        </is>
-      </c>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="L53" s="37" t="n"/>
       <c r="M53" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -18879,12 +19096,12 @@
       </c>
       <c r="O53" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="P53" s="37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45</t>
         </is>
       </c>
       <c r="R53" s="37" t="inlineStr">
@@ -19015,24 +19232,20 @@
       </c>
       <c r="I54" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="J54" s="37" t="inlineStr">
         <is>
-          <t>Unimplemented</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K54" s="37" t="inlineStr">
         <is>
-          <t>Disabled</t>
-        </is>
-      </c>
-      <c r="L54" s="37" t="inlineStr">
-        <is>
-          <t>Pierce-on-crit handler is not implemented.</t>
-        </is>
-      </c>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="L54" s="37" t="n"/>
       <c r="M54" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -19045,12 +19258,12 @@
       </c>
       <c r="O54" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="P54" s="37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45</t>
         </is>
       </c>
       <c r="R54" s="37" t="inlineStr">
@@ -19141,12 +19354,12 @@
     <row r="55" ht="22" customHeight="1" s="32">
       <c r="A55" s="37" t="inlineStr">
         <is>
-          <t>AUDIT_WEAPON_SLOTS_C_19</t>
+          <t>P_BOW_CRITBLEED_ARROWHEAD</t>
         </is>
       </c>
       <c r="B55" s="37" t="inlineStr">
         <is>
-          <t>P_AUDIT_C_19</t>
+          <t>P_BOW_CRITBLEED_ARROWHEAD</t>
         </is>
       </c>
       <c r="C55" s="37" t="inlineStr">
@@ -19171,34 +19384,30 @@
       </c>
       <c r="G55" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="H55" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Arrowhead|UniqueBehavior|Bleeding</t>
         </is>
       </c>
       <c r="I55" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="J55" s="37" t="inlineStr">
         <is>
-          <t>Unimplemented</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K55" s="37" t="inlineStr">
         <is>
-          <t>Disabled</t>
-        </is>
-      </c>
-      <c r="L55" s="37" t="inlineStr">
-        <is>
-          <t>Disabled placeholder; part effect not yet implemented.</t>
-        </is>
-      </c>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="L55" s="37" t="n"/>
       <c r="M55" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -19211,12 +19420,12 @@
       </c>
       <c r="O55" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="P55" s="37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45</t>
         </is>
       </c>
       <c r="R55" s="37" t="inlineStr">
@@ -19342,29 +19551,25 @@
       </c>
       <c r="H56" s="37" t="inlineStr">
         <is>
-          <t>Arrowhead|AttackPatternReplacement</t>
+          <t>Arrowhead|Numeric</t>
         </is>
       </c>
       <c r="I56" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="J56" s="37" t="inlineStr">
         <is>
-          <t>Unimplemented</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K56" s="37" t="inlineStr">
         <is>
-          <t>Disabled</t>
-        </is>
-      </c>
-      <c r="L56" s="37" t="inlineStr">
-        <is>
-          <t>Multi-projectile spread handler is not implemented.</t>
-        </is>
-      </c>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="L56" s="37" t="n"/>
       <c r="M56" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -19377,12 +19582,12 @@
       </c>
       <c r="O56" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="P56" s="37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45</t>
         </is>
       </c>
       <c r="R56" s="37" t="inlineStr">
@@ -19473,12 +19678,12 @@
     <row r="57" ht="22" customHeight="1" s="32">
       <c r="A57" s="37" t="inlineStr">
         <is>
-          <t>AUDIT_WEAPON_SLOTS_C_21</t>
+          <t>P_BOW_KILLSHARD_ARROWHEAD</t>
         </is>
       </c>
       <c r="B57" s="37" t="inlineStr">
         <is>
-          <t>P_AUDIT_C_21</t>
+          <t>P_BOW_KILLSHARD_ARROWHEAD</t>
         </is>
       </c>
       <c r="C57" s="37" t="inlineStr">
@@ -19503,34 +19708,30 @@
       </c>
       <c r="G57" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="H57" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Arrowhead|UniqueBehavior|TimeShard</t>
         </is>
       </c>
       <c r="I57" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="J57" s="37" t="inlineStr">
         <is>
-          <t>Unimplemented</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K57" s="37" t="inlineStr">
         <is>
-          <t>Disabled</t>
-        </is>
-      </c>
-      <c r="L57" s="37" t="inlineStr">
-        <is>
-          <t>Disabled placeholder; part effect not yet implemented.</t>
-        </is>
-      </c>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="L57" s="37" t="n"/>
       <c r="M57" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -19543,12 +19744,12 @@
       </c>
       <c r="O57" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="P57" s="37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45</t>
         </is>
       </c>
       <c r="R57" s="37" t="inlineStr">
@@ -19959,12 +20160,12 @@
     <row r="60" ht="30" customHeight="1" s="32">
       <c r="A60" s="37" t="inlineStr">
         <is>
-          <t>AUDIT_WEAPON_SLOTS_C_24</t>
+          <t>P_BOW_KILLHASTE_BOWSTRING</t>
         </is>
       </c>
       <c r="B60" s="37" t="inlineStr">
         <is>
-          <t>P_AUDIT_C_24</t>
+          <t>P_BOW_KILLHASTE_BOWSTRING</t>
         </is>
       </c>
       <c r="C60" s="37" t="inlineStr">
@@ -19984,39 +20185,35 @@
       </c>
       <c r="F60" s="37" t="inlineStr">
         <is>
-          <t>效果：击杀一名敌方单位后，移动速度+20%，持续5s。不可叠加</t>
+          <t>效果：击杀一名敌方单位后，移动速度+20%，持续5s。可以叠加</t>
         </is>
       </c>
       <c r="G60" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="H60" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Bowstring|UniqueBehavior|MoveSpeed</t>
         </is>
       </c>
       <c r="I60" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="J60" s="37" t="inlineStr">
         <is>
-          <t>Unimplemented</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K60" s="37" t="inlineStr">
         <is>
-          <t>Disabled</t>
-        </is>
-      </c>
-      <c r="L60" s="37" t="inlineStr">
-        <is>
-          <t>Disabled placeholder; part effect not yet implemented.</t>
-        </is>
-      </c>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="L60" s="37" t="n"/>
       <c r="M60" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -20029,12 +20226,12 @@
       </c>
       <c r="O60" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="P60" s="37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45</t>
         </is>
       </c>
       <c r="R60" s="37" t="inlineStr">
@@ -20125,12 +20322,12 @@
     <row r="61" ht="22" customHeight="1" s="32">
       <c r="A61" s="37" t="inlineStr">
         <is>
-          <t>AUDIT_WEAPON_SLOTS_C_25</t>
+          <t>P_BOW_COMBOHASTE_BOWSTRING</t>
         </is>
       </c>
       <c r="B61" s="37" t="inlineStr">
         <is>
-          <t>P_AUDIT_C_25</t>
+          <t>P_BOW_COMBOHASTE_BOWSTRING</t>
         </is>
       </c>
       <c r="C61" s="37" t="inlineStr">
@@ -20155,34 +20352,30 @@
       </c>
       <c r="G61" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="H61" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Bowstring|UniqueBehavior|AttackSpeed|MoveSpeed</t>
         </is>
       </c>
       <c r="I61" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="J61" s="37" t="inlineStr">
         <is>
-          <t>Unimplemented</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K61" s="37" t="inlineStr">
         <is>
-          <t>Disabled</t>
-        </is>
-      </c>
-      <c r="L61" s="37" t="inlineStr">
-        <is>
-          <t>Disabled placeholder; part effect not yet implemented.</t>
-        </is>
-      </c>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="L61" s="37" t="n"/>
       <c r="M61" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -20195,12 +20388,12 @@
       </c>
       <c r="O61" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="P61" s="37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45</t>
         </is>
       </c>
       <c r="R61" s="37" t="inlineStr">
@@ -20291,12 +20484,12 @@
     <row r="62" ht="22" customHeight="1" s="32">
       <c r="A62" s="37" t="inlineStr">
         <is>
-          <t>AUDIT_WEAPON_SLOTS_C_26</t>
+          <t>P_SCYTHE_GROUPGROWTH_ROTARYBLADE</t>
         </is>
       </c>
       <c r="B62" s="37" t="inlineStr">
         <is>
-          <t>P_AUDIT_C_26</t>
+          <t>P_SCYTHE_GROUPGROWTH_ROTARYBLADE</t>
         </is>
       </c>
       <c r="C62" s="37" t="inlineStr">
@@ -20321,34 +20514,30 @@
       </c>
       <c r="G62" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="H62" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>RotaryBlade|UniqueBehavior|AttackRange</t>
         </is>
       </c>
       <c r="I62" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="J62" s="37" t="inlineStr">
         <is>
-          <t>Unimplemented</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K62" s="37" t="inlineStr">
         <is>
-          <t>Disabled</t>
-        </is>
-      </c>
-      <c r="L62" s="37" t="inlineStr">
-        <is>
-          <t>Disabled placeholder; part effect not yet implemented.</t>
-        </is>
-      </c>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="L62" s="37" t="n"/>
       <c r="M62" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -20361,12 +20550,12 @@
       </c>
       <c r="O62" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="P62" s="37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45</t>
         </is>
       </c>
       <c r="R62" s="37" t="inlineStr">
@@ -20457,12 +20646,12 @@
     <row r="63" ht="22" customHeight="1" s="32">
       <c r="A63" s="37" t="inlineStr">
         <is>
-          <t>AUDIT_WEAPON_SLOTS_C_27</t>
+          <t>P_SCYTHE_LIFESTEAL_ROTARYBLADE</t>
         </is>
       </c>
       <c r="B63" s="37" t="inlineStr">
         <is>
-          <t>P_AUDIT_C_27</t>
+          <t>P_SCYTHE_LIFESTEAL_ROTARYBLADE</t>
         </is>
       </c>
       <c r="C63" s="37" t="inlineStr">
@@ -20487,34 +20676,30 @@
       </c>
       <c r="G63" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="H63" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>RotaryBlade|UniqueBehavior|Healing</t>
         </is>
       </c>
       <c r="I63" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="J63" s="37" t="inlineStr">
         <is>
-          <t>Unimplemented</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K63" s="37" t="inlineStr">
         <is>
-          <t>Disabled</t>
-        </is>
-      </c>
-      <c r="L63" s="37" t="inlineStr">
-        <is>
-          <t>Disabled placeholder; part effect not yet implemented.</t>
-        </is>
-      </c>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="L63" s="37" t="n"/>
       <c r="M63" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -20527,12 +20712,12 @@
       </c>
       <c r="O63" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="P63" s="37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45</t>
         </is>
       </c>
       <c r="R63" s="37" t="inlineStr">
@@ -20783,12 +20968,12 @@
     <row r="65" ht="22" customHeight="1" s="32">
       <c r="A65" s="37" t="inlineStr">
         <is>
-          <t>AUDIT_WEAPON_SLOTS_C_29</t>
+          <t>P_SCYTHE_STUN_ROTARYBLADE</t>
         </is>
       </c>
       <c r="B65" s="37" t="inlineStr">
         <is>
-          <t>P_AUDIT_C_29</t>
+          <t>P_SCYTHE_STUN_ROTARYBLADE</t>
         </is>
       </c>
       <c r="C65" s="37" t="inlineStr">
@@ -20813,34 +20998,30 @@
       </c>
       <c r="G65" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="H65" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>RotaryBlade|UniqueBehavior|Stun</t>
         </is>
       </c>
       <c r="I65" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="J65" s="37" t="inlineStr">
         <is>
-          <t>Unimplemented</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K65" s="37" t="inlineStr">
         <is>
-          <t>Disabled</t>
-        </is>
-      </c>
-      <c r="L65" s="37" t="inlineStr">
-        <is>
-          <t>Disabled placeholder; part effect not yet implemented.</t>
-        </is>
-      </c>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="L65" s="37" t="n"/>
       <c r="M65" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -20853,12 +21034,12 @@
       </c>
       <c r="O65" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="P65" s="37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45</t>
         </is>
       </c>
       <c r="R65" s="37" t="inlineStr">
@@ -20949,12 +21130,12 @@
     <row r="66" ht="22" customHeight="1" s="32">
       <c r="A66" s="37" t="inlineStr">
         <is>
-          <t>AUDIT_WEAPON_SLOTS_C_30</t>
+          <t>P_SCYTHE_BLEED_ROTARYBLADE</t>
         </is>
       </c>
       <c r="B66" s="37" t="inlineStr">
         <is>
-          <t>P_AUDIT_C_30</t>
+          <t>P_SCYTHE_BLEED_ROTARYBLADE</t>
         </is>
       </c>
       <c r="C66" s="37" t="inlineStr">
@@ -20979,34 +21160,30 @@
       </c>
       <c r="G66" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="H66" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>RotaryBlade|UniqueBehavior|Bleeding</t>
         </is>
       </c>
       <c r="I66" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="J66" s="37" t="inlineStr">
         <is>
-          <t>Unimplemented</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K66" s="37" t="inlineStr">
         <is>
-          <t>Disabled</t>
-        </is>
-      </c>
-      <c r="L66" s="37" t="inlineStr">
-        <is>
-          <t>Disabled placeholder; part effect not yet implemented.</t>
-        </is>
-      </c>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="L66" s="37" t="n"/>
       <c r="M66" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -21019,12 +21196,12 @@
       </c>
       <c r="O66" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="P66" s="37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45</t>
         </is>
       </c>
       <c r="R66" s="37" t="inlineStr">
@@ -21115,12 +21292,12 @@
     <row r="67" ht="22" customHeight="1" s="32">
       <c r="A67" s="37" t="inlineStr">
         <is>
-          <t>AUDIT_WEAPON_SLOTS_C_31</t>
+          <t>P_SCYTHE_OUTERRING_ROTARYBLADE</t>
         </is>
       </c>
       <c r="B67" s="37" t="inlineStr">
         <is>
-          <t>P_AUDIT_C_31</t>
+          <t>P_SCYTHE_OUTERRING_ROTARYBLADE</t>
         </is>
       </c>
       <c r="C67" s="37" t="inlineStr">
@@ -21145,34 +21322,30 @@
       </c>
       <c r="G67" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="H67" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>RotaryBlade|UniqueBehavior|Damage</t>
         </is>
       </c>
       <c r="I67" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="J67" s="37" t="inlineStr">
         <is>
-          <t>Unimplemented</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K67" s="37" t="inlineStr">
         <is>
-          <t>Disabled</t>
-        </is>
-      </c>
-      <c r="L67" s="37" t="inlineStr">
-        <is>
-          <t>Disabled placeholder; part effect not yet implemented.</t>
-        </is>
-      </c>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="L67" s="37" t="n"/>
       <c r="M67" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -21185,12 +21358,12 @@
       </c>
       <c r="O67" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="P67" s="37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45</t>
         </is>
       </c>
       <c r="R67" s="37" t="inlineStr">
@@ -21281,12 +21454,12 @@
     <row r="68" ht="22" customHeight="1" s="32">
       <c r="A68" s="37" t="inlineStr">
         <is>
-          <t>AUDIT_WEAPON_SLOTS_C_32</t>
+          <t>P_SCYTHE_MOVESTACK_GRIP</t>
         </is>
       </c>
       <c r="B68" s="37" t="inlineStr">
         <is>
-          <t>P_AUDIT_C_32</t>
+          <t>P_SCYTHE_MOVESTACK_GRIP</t>
         </is>
       </c>
       <c r="C68" s="37" t="inlineStr">
@@ -21311,34 +21484,30 @@
       </c>
       <c r="G68" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="H68" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Grip|UniqueBehavior|MoveSpeed</t>
         </is>
       </c>
       <c r="I68" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="J68" s="37" t="inlineStr">
         <is>
-          <t>Unimplemented</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K68" s="37" t="inlineStr">
         <is>
-          <t>Disabled</t>
-        </is>
-      </c>
-      <c r="L68" s="37" t="inlineStr">
-        <is>
-          <t>Disabled placeholder; part effect not yet implemented.</t>
-        </is>
-      </c>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="L68" s="37" t="n"/>
       <c r="M68" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -21351,12 +21520,12 @@
       </c>
       <c r="O68" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="P68" s="37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45</t>
         </is>
       </c>
       <c r="R68" s="37" t="inlineStr">
@@ -21447,12 +21616,12 @@
     <row r="69" ht="22" customHeight="1" s="32">
       <c r="A69" s="37" t="inlineStr">
         <is>
-          <t>AUDIT_WEAPON_SLOTS_C_33</t>
+          <t>P_SCYTHE_GROUPINVULN_GRIP</t>
         </is>
       </c>
       <c r="B69" s="37" t="inlineStr">
         <is>
-          <t>P_AUDIT_C_33</t>
+          <t>P_SCYTHE_GROUPINVULN_GRIP</t>
         </is>
       </c>
       <c r="C69" s="37" t="inlineStr">
@@ -21477,34 +21646,30 @@
       </c>
       <c r="G69" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="H69" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Grip|UniqueBehavior|Invulnerable</t>
         </is>
       </c>
       <c r="I69" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="J69" s="37" t="inlineStr">
         <is>
-          <t>Unimplemented</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K69" s="37" t="inlineStr">
         <is>
-          <t>Disabled</t>
-        </is>
-      </c>
-      <c r="L69" s="37" t="inlineStr">
-        <is>
-          <t>Disabled placeholder; part effect not yet implemented.</t>
-        </is>
-      </c>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="L69" s="37" t="n"/>
       <c r="M69" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -21517,12 +21682,12 @@
       </c>
       <c r="O69" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="P69" s="37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45</t>
         </is>
       </c>
       <c r="R69" s="37" t="inlineStr">
@@ -21613,12 +21778,12 @@
     <row r="70" ht="22" customHeight="1" s="32">
       <c r="A70" s="37" t="inlineStr">
         <is>
-          <t>AUDIT_WEAPON_SLOTS_C_34</t>
+          <t>P_SCYTHE_ATTACKSTACK_GRIP</t>
         </is>
       </c>
       <c r="B70" s="37" t="inlineStr">
         <is>
-          <t>P_AUDIT_C_34</t>
+          <t>P_SCYTHE_ATTACKSTACK_GRIP</t>
         </is>
       </c>
       <c r="C70" s="37" t="inlineStr">
@@ -21643,34 +21808,30 @@
       </c>
       <c r="G70" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="H70" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Grip|UniqueBehavior|AttackSpeed</t>
         </is>
       </c>
       <c r="I70" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="J70" s="37" t="inlineStr">
         <is>
-          <t>Unimplemented</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K70" s="37" t="inlineStr">
         <is>
-          <t>Disabled</t>
-        </is>
-      </c>
-      <c r="L70" s="37" t="inlineStr">
-        <is>
-          <t>Disabled placeholder; part effect not yet implemented.</t>
-        </is>
-      </c>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="L70" s="37" t="n"/>
       <c r="M70" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -21683,12 +21844,12 @@
       </c>
       <c r="O70" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="P70" s="37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45</t>
         </is>
       </c>
       <c r="R70" s="37" t="inlineStr">
@@ -21779,12 +21940,12 @@
     <row r="71" ht="22" customHeight="1" s="32">
       <c r="A71" s="37" t="inlineStr">
         <is>
-          <t>AUDIT_WEAPON_SLOTS_C_35</t>
+          <t>P_SCYTHE_THROWRECALL_GRIP</t>
         </is>
       </c>
       <c r="B71" s="37" t="inlineStr">
         <is>
-          <t>P_AUDIT_C_35</t>
+          <t>P_SCYTHE_THROWRECALL_GRIP</t>
         </is>
       </c>
       <c r="C71" s="37" t="inlineStr">
@@ -21813,34 +21974,30 @@
       </c>
       <c r="G71" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="H71" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Grip|UniqueBehavior|ActiveAttack</t>
         </is>
       </c>
       <c r="I71" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="J71" s="37" t="inlineStr">
         <is>
-          <t>Unimplemented</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K71" s="37" t="inlineStr">
         <is>
-          <t>Disabled</t>
-        </is>
-      </c>
-      <c r="L71" s="37" t="inlineStr">
-        <is>
-          <t>Disabled placeholder; part effect not yet implemented.</t>
-        </is>
-      </c>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="L71" s="37" t="n"/>
       <c r="M71" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -21853,12 +22010,12 @@
       </c>
       <c r="O71" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="P71" s="37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45</t>
         </is>
       </c>
       <c r="R71" s="37" t="inlineStr">
@@ -21933,10 +22090,14 @@
       </c>
       <c r="AH71" s="37" t="inlineStr">
         <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="AI71" s="37" t="n"/>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AI71" s="37" t="inlineStr">
+        <is>
+          <t>Retired: staff/whip weapon runes disabled on request</t>
+        </is>
+      </c>
       <c r="AJ71" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -22093,10 +22254,14 @@
       </c>
       <c r="AH72" s="37" t="inlineStr">
         <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="AI72" s="37" t="n"/>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AI72" s="37" t="inlineStr">
+        <is>
+          <t>Retired: staff/whip weapon runes disabled on request</t>
+        </is>
+      </c>
       <c r="AJ72" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -22253,10 +22418,14 @@
       </c>
       <c r="AH73" s="37" t="inlineStr">
         <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="AI73" s="37" t="n"/>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AI73" s="37" t="inlineStr">
+        <is>
+          <t>Retired: staff/whip weapon runes disabled on request</t>
+        </is>
+      </c>
       <c r="AJ73" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -22269,12 +22438,12 @@
     <row r="74" ht="22" customHeight="1" s="32">
       <c r="A74" s="37" t="inlineStr">
         <is>
-          <t>AUDIT_WEAPON_SLOTS_C_38</t>
+          <t>P_LONGSWORD_GROUPGROWTH_SWORDBLADE</t>
         </is>
       </c>
       <c r="B74" s="37" t="inlineStr">
         <is>
-          <t>P_AUDIT_C_38</t>
+          <t>P_LONGSWORD_GROUPGROWTH_SWORDBLADE</t>
         </is>
       </c>
       <c r="C74" s="37" t="inlineStr">
@@ -22299,34 +22468,30 @@
       </c>
       <c r="G74" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="H74" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>SwordBlade|UniqueBehavior|AttackRange</t>
         </is>
       </c>
       <c r="I74" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="J74" s="37" t="inlineStr">
         <is>
-          <t>Unimplemented</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K74" s="37" t="inlineStr">
         <is>
-          <t>Disabled</t>
-        </is>
-      </c>
-      <c r="L74" s="37" t="inlineStr">
-        <is>
-          <t>Disabled placeholder; part effect not yet implemented.</t>
-        </is>
-      </c>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="L74" s="37" t="n"/>
       <c r="M74" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -22339,12 +22504,12 @@
       </c>
       <c r="O74" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="P74" s="37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45</t>
         </is>
       </c>
       <c r="R74" s="37" t="inlineStr">
@@ -22419,10 +22584,14 @@
       </c>
       <c r="AH74" s="37" t="inlineStr">
         <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="AI74" s="37" t="n"/>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AI74" s="37" t="inlineStr">
+        <is>
+          <t>Retired: staff/whip weapon runes disabled on request</t>
+        </is>
+      </c>
       <c r="AJ74" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -22579,10 +22748,14 @@
       </c>
       <c r="AH75" s="37" t="inlineStr">
         <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="AI75" s="37" t="n"/>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AI75" s="37" t="inlineStr">
+        <is>
+          <t>Retired: staff/whip weapon runes disabled on request</t>
+        </is>
+      </c>
       <c r="AJ75" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -22595,12 +22768,12 @@
     <row r="76" ht="22" customHeight="1" s="32">
       <c r="A76" s="37" t="inlineStr">
         <is>
-          <t>AUDIT_WEAPON_SLOTS_C_40</t>
+          <t>P_LONGSWORD_HITSHARD_SWORDBLADE</t>
         </is>
       </c>
       <c r="B76" s="37" t="inlineStr">
         <is>
-          <t>P_AUDIT_C_40</t>
+          <t>P_LONGSWORD_HITSHARD_SWORDBLADE</t>
         </is>
       </c>
       <c r="C76" s="37" t="inlineStr">
@@ -22625,34 +22798,30 @@
       </c>
       <c r="G76" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="H76" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>SwordBlade|UniqueBehavior|TimeShard</t>
         </is>
       </c>
       <c r="I76" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="J76" s="37" t="inlineStr">
         <is>
-          <t>Unimplemented</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K76" s="37" t="inlineStr">
         <is>
-          <t>Disabled</t>
-        </is>
-      </c>
-      <c r="L76" s="37" t="inlineStr">
-        <is>
-          <t>Disabled placeholder; part effect not yet implemented.</t>
-        </is>
-      </c>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="L76" s="37" t="n"/>
       <c r="M76" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -22665,12 +22834,12 @@
       </c>
       <c r="O76" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="P76" s="37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45</t>
         </is>
       </c>
       <c r="R76" s="37" t="inlineStr">
@@ -22745,10 +22914,14 @@
       </c>
       <c r="AH76" s="37" t="inlineStr">
         <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="AI76" s="37" t="n"/>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AI76" s="37" t="inlineStr">
+        <is>
+          <t>Retired: staff/whip weapon runes disabled on request</t>
+        </is>
+      </c>
       <c r="AJ76" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -22761,12 +22934,12 @@
     <row r="77" ht="22" customHeight="1" s="32">
       <c r="A77" s="37" t="inlineStr">
         <is>
-          <t>AUDIT_WEAPON_SLOTS_C_41</t>
+          <t>P_LONGSWORD_CRITBLEED_SWORDBLADE</t>
         </is>
       </c>
       <c r="B77" s="37" t="inlineStr">
         <is>
-          <t>P_AUDIT_C_41</t>
+          <t>P_LONGSWORD_CRITBLEED_SWORDBLADE</t>
         </is>
       </c>
       <c r="C77" s="37" t="inlineStr">
@@ -22791,34 +22964,30 @@
       </c>
       <c r="G77" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="H77" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>SwordBlade|UniqueBehavior|Bleeding</t>
         </is>
       </c>
       <c r="I77" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="J77" s="37" t="inlineStr">
         <is>
-          <t>Unimplemented</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K77" s="37" t="inlineStr">
         <is>
-          <t>Disabled</t>
-        </is>
-      </c>
-      <c r="L77" s="37" t="inlineStr">
-        <is>
-          <t>Disabled placeholder; part effect not yet implemented.</t>
-        </is>
-      </c>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="L77" s="37" t="n"/>
       <c r="M77" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -22831,12 +23000,12 @@
       </c>
       <c r="O77" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="P77" s="37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45</t>
         </is>
       </c>
       <c r="R77" s="37" t="inlineStr">
@@ -22911,10 +23080,14 @@
       </c>
       <c r="AH77" s="37" t="inlineStr">
         <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="AI77" s="37" t="n"/>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AI77" s="37" t="inlineStr">
+        <is>
+          <t>Retired: staff/whip weapon runes disabled on request</t>
+        </is>
+      </c>
       <c r="AJ77" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -22927,12 +23100,12 @@
     <row r="78" ht="22" customHeight="1" s="32">
       <c r="A78" s="37" t="inlineStr">
         <is>
-          <t>AUDIT_WEAPON_SLOTS_C_42</t>
+          <t>P_LONGSWORD_METEOR_SWORDBLADE</t>
         </is>
       </c>
       <c r="B78" s="37" t="inlineStr">
         <is>
-          <t>P_AUDIT_C_42</t>
+          <t>P_LONGSWORD_METEOR_SWORDBLADE</t>
         </is>
       </c>
       <c r="C78" s="37" t="inlineStr">
@@ -22959,34 +23132,30 @@
       </c>
       <c r="G78" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="H78" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>SwordBlade|UniqueBehavior|Meteor</t>
         </is>
       </c>
       <c r="I78" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="J78" s="37" t="inlineStr">
         <is>
-          <t>Unimplemented</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K78" s="37" t="inlineStr">
         <is>
-          <t>Disabled</t>
-        </is>
-      </c>
-      <c r="L78" s="37" t="inlineStr">
-        <is>
-          <t>Disabled placeholder; part effect not yet implemented.</t>
-        </is>
-      </c>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="L78" s="37" t="n"/>
       <c r="M78" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -22999,12 +23168,12 @@
       </c>
       <c r="O78" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="P78" s="37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45</t>
         </is>
       </c>
       <c r="R78" s="37" t="inlineStr">
@@ -23079,10 +23248,14 @@
       </c>
       <c r="AH78" s="37" t="inlineStr">
         <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="AI78" s="37" t="n"/>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AI78" s="37" t="inlineStr">
+        <is>
+          <t>Retired: staff/whip weapon runes disabled on request</t>
+        </is>
+      </c>
       <c r="AJ78" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -23239,10 +23412,14 @@
       </c>
       <c r="AH79" s="37" t="inlineStr">
         <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="AI79" s="37" t="n"/>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AI79" s="37" t="inlineStr">
+        <is>
+          <t>Retired: staff/whip weapon runes disabled on request</t>
+        </is>
+      </c>
       <c r="AJ79" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -23255,12 +23432,12 @@
     <row r="80" ht="22" customHeight="1" s="32">
       <c r="A80" s="37" t="inlineStr">
         <is>
-          <t>AUDIT_WEAPON_SLOTS_C_44</t>
+          <t>P_LONGSWORD_MOVESTACK_GRIP</t>
         </is>
       </c>
       <c r="B80" s="37" t="inlineStr">
         <is>
-          <t>P_AUDIT_C_44</t>
+          <t>P_LONGSWORD_MOVESTACK_GRIP</t>
         </is>
       </c>
       <c r="C80" s="37" t="inlineStr">
@@ -23285,34 +23462,30 @@
       </c>
       <c r="G80" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="H80" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Grip|UniqueBehavior|MoveSpeed</t>
         </is>
       </c>
       <c r="I80" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="J80" s="37" t="inlineStr">
         <is>
-          <t>Unimplemented</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K80" s="37" t="inlineStr">
         <is>
-          <t>Disabled</t>
-        </is>
-      </c>
-      <c r="L80" s="37" t="inlineStr">
-        <is>
-          <t>Disabled placeholder; part effect not yet implemented.</t>
-        </is>
-      </c>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="L80" s="37" t="n"/>
       <c r="M80" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -23325,12 +23498,12 @@
       </c>
       <c r="O80" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="P80" s="37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45</t>
         </is>
       </c>
       <c r="R80" s="37" t="inlineStr">
@@ -23405,10 +23578,14 @@
       </c>
       <c r="AH80" s="37" t="inlineStr">
         <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="AI80" s="37" t="n"/>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AI80" s="37" t="inlineStr">
+        <is>
+          <t>Retired: staff/whip weapon runes disabled on request</t>
+        </is>
+      </c>
       <c r="AJ80" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -23421,12 +23598,12 @@
     <row r="81" ht="22" customHeight="1" s="32">
       <c r="A81" s="37" t="inlineStr">
         <is>
-          <t>AUDIT_WEAPON_SLOTS_C_45</t>
+          <t>P_LONGSWORD_ATTACKSTACK_GRIP</t>
         </is>
       </c>
       <c r="B81" s="37" t="inlineStr">
         <is>
-          <t>P_AUDIT_C_45</t>
+          <t>P_LONGSWORD_ATTACKSTACK_GRIP</t>
         </is>
       </c>
       <c r="C81" s="37" t="inlineStr">
@@ -23451,34 +23628,30 @@
       </c>
       <c r="G81" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="H81" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Grip|UniqueBehavior|AttackSpeed</t>
         </is>
       </c>
       <c r="I81" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="J81" s="37" t="inlineStr">
         <is>
-          <t>Unimplemented</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K81" s="37" t="inlineStr">
         <is>
-          <t>Disabled</t>
-        </is>
-      </c>
-      <c r="L81" s="37" t="inlineStr">
-        <is>
-          <t>Disabled placeholder; part effect not yet implemented.</t>
-        </is>
-      </c>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="L81" s="37" t="n"/>
       <c r="M81" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -23491,12 +23664,12 @@
       </c>
       <c r="O81" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="P81" s="37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45</t>
         </is>
       </c>
       <c r="R81" s="37" t="inlineStr">
@@ -23571,10 +23744,14 @@
       </c>
       <c r="AH81" s="37" t="inlineStr">
         <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="AI81" s="37" t="n"/>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AI81" s="37" t="inlineStr">
+        <is>
+          <t>Retired: staff/whip weapon runes disabled on request</t>
+        </is>
+      </c>
       <c r="AJ81" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -23587,12 +23764,12 @@
     <row r="82" ht="22" customHeight="1" s="32">
       <c r="A82" s="37" t="inlineStr">
         <is>
-          <t>AUDIT_WEAPON_SLOTS_C_46</t>
+          <t>P_LONGSWORD_STUN_GRIP</t>
         </is>
       </c>
       <c r="B82" s="37" t="inlineStr">
         <is>
-          <t>P_AUDIT_C_46</t>
+          <t>P_LONGSWORD_STUN_GRIP</t>
         </is>
       </c>
       <c r="C82" s="37" t="inlineStr">
@@ -23617,34 +23794,30 @@
       </c>
       <c r="G82" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="H82" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Grip|UniqueBehavior|Stun</t>
         </is>
       </c>
       <c r="I82" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="J82" s="37" t="inlineStr">
         <is>
-          <t>Unimplemented</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K82" s="37" t="inlineStr">
         <is>
-          <t>Disabled</t>
-        </is>
-      </c>
-      <c r="L82" s="37" t="inlineStr">
-        <is>
-          <t>Disabled placeholder; part effect not yet implemented.</t>
-        </is>
-      </c>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="L82" s="37" t="n"/>
       <c r="M82" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -23657,12 +23830,12 @@
       </c>
       <c r="O82" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="P82" s="37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45</t>
         </is>
       </c>
       <c r="R82" s="37" t="inlineStr">
@@ -23737,10 +23910,14 @@
       </c>
       <c r="AH82" s="37" t="inlineStr">
         <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="AI82" s="37" t="n"/>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AI82" s="37" t="inlineStr">
+        <is>
+          <t>Retired: staff/whip weapon runes disabled on request</t>
+        </is>
+      </c>
       <c r="AJ82" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -23825,6 +24002,102 @@
       <c r="P83" s="37" t="n">
         <v>30</v>
       </c>
+      <c r="R83" s="37" t="inlineStr">
+        <is>
+          <t>PE_BOW_SPLIT_ARROWHEAD_1</t>
+        </is>
+      </c>
+      <c r="S83" s="37" t="inlineStr">
+        <is>
+          <t>P_BOW_SPLIT_ARROWHEAD</t>
+        </is>
+      </c>
+      <c r="T83" s="37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U83" s="37" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="V83" s="37" t="inlineStr">
+        <is>
+          <t>UniqueBehavior</t>
+        </is>
+      </c>
+      <c r="W83" s="37" t="inlineStr">
+        <is>
+          <t>RuntimeBehavior</t>
+        </is>
+      </c>
+      <c r="X83" s="37" t="inlineStr">
+        <is>
+          <t>Multiply</t>
+        </is>
+      </c>
+      <c r="Y83" s="37" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="Z83" s="37" t="inlineStr">
+        <is>
+          <t>Part.ProjectileSplitOnHit</t>
+        </is>
+      </c>
+      <c r="AA83" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB83" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC83" s="37" t="inlineStr">
+        <is>
+          <t>MaxChildren</t>
+        </is>
+      </c>
+      <c r="AD83" s="37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE83" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF83" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG83" s="37" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="AH83" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI83" s="37" t="n"/>
+      <c r="AJ83" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK83" s="37" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="22" customHeight="1" s="32">
       <c r="A84" s="37" t="inlineStr">
@@ -23901,16 +24174,112 @@
       <c r="P84" s="37" t="n">
         <v>45</v>
       </c>
+      <c r="R84" s="37" t="inlineStr">
+        <is>
+          <t>PE_BOW_EXPLOSIVE_ARROWHEAD_1</t>
+        </is>
+      </c>
+      <c r="S84" s="37" t="inlineStr">
+        <is>
+          <t>P_BOW_EXPLOSIVE_ARROWHEAD</t>
+        </is>
+      </c>
+      <c r="T84" s="37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U84" s="37" t="inlineStr">
+        <is>
+          <t>OnEquip</t>
+        </is>
+      </c>
+      <c r="V84" s="37" t="inlineStr">
+        <is>
+          <t>StatModifier</t>
+        </is>
+      </c>
+      <c r="W84" s="37" t="inlineStr">
+        <is>
+          <t>ExplosionRadius</t>
+        </is>
+      </c>
+      <c r="X84" s="37" t="inlineStr">
+        <is>
+          <t>Override</t>
+        </is>
+      </c>
+      <c r="Y84" s="37" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="Z84" s="37" t="inlineStr">
+        <is>
+          <t>Part.StatModifier</t>
+        </is>
+      </c>
+      <c r="AA84" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB84" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC84" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD84" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE84" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF84" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG84" s="37" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="AH84" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI84" s="37" t="n"/>
+      <c r="AJ84" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK84" s="37" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="22" customHeight="1" s="32">
       <c r="A85" s="37" t="inlineStr">
         <is>
-          <t>AUDIT_WEAPON_SLOTS_C_49</t>
+          <t>P_GUN_CHARGED_MUZZLE</t>
         </is>
       </c>
       <c r="B85" s="37" t="inlineStr">
         <is>
-          <t>P_AUDIT_C_49</t>
+          <t>P_GUN_CHARGED_MUZZLE</t>
         </is>
       </c>
       <c r="C85" s="37" t="inlineStr">
@@ -23935,34 +24304,30 @@
       </c>
       <c r="G85" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="H85" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Muzzle|Numeric</t>
         </is>
       </c>
       <c r="I85" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="J85" s="37" t="inlineStr">
         <is>
-          <t>Unimplemented</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K85" s="37" t="inlineStr">
         <is>
-          <t>Disabled</t>
-        </is>
-      </c>
-      <c r="L85" s="37" t="inlineStr">
-        <is>
-          <t>Disabled placeholder; part effect not yet implemented.</t>
-        </is>
-      </c>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="L85" s="37" t="n"/>
       <c r="M85" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -23975,24 +24340,120 @@
       </c>
       <c r="O85" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="P85" s="37" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="R85" s="37" t="inlineStr">
+        <is>
+          <t>PE_BOW_PIERCING_ARROWHEAD_1</t>
+        </is>
+      </c>
+      <c r="S85" s="37" t="inlineStr">
+        <is>
+          <t>P_BOW_PIERCING_ARROWHEAD</t>
+        </is>
+      </c>
+      <c r="T85" s="37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U85" s="37" t="inlineStr">
+        <is>
+          <t>OnCriticalHit</t>
+        </is>
+      </c>
+      <c r="V85" s="37" t="inlineStr">
+        <is>
+          <t>UniqueBehavior</t>
+        </is>
+      </c>
+      <c r="W85" s="37" t="inlineStr">
+        <is>
+          <t>RuntimeBehavior</t>
+        </is>
+      </c>
+      <c r="X85" s="37" t="inlineStr">
+        <is>
+          <t>Override</t>
+        </is>
+      </c>
+      <c r="Y85" s="37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z85" s="37" t="inlineStr">
+        <is>
+          <t>Part.ProjectilePierceOnCritical</t>
+        </is>
+      </c>
+      <c r="AA85" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB85" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC85" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD85" s="37" t="inlineStr">
+        <is>
           <t>0</t>
+        </is>
+      </c>
+      <c r="AE85" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF85" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG85" s="37" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="AH85" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI85" s="37" t="n"/>
+      <c r="AJ85" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK85" s="37" t="inlineStr">
+        <is>
+          <t>18</t>
         </is>
       </c>
     </row>
     <row r="86" ht="45" customHeight="1" s="32">
       <c r="A86" s="37" t="inlineStr">
         <is>
-          <t>AUDIT_WEAPON_SLOTS_C_50</t>
+          <t>P_GUN_RAPID_MUZZLE</t>
         </is>
       </c>
       <c r="B86" s="37" t="inlineStr">
         <is>
-          <t>P_AUDIT_C_50</t>
+          <t>P_GUN_RAPID_MUZZLE</t>
         </is>
       </c>
       <c r="C86" s="37" t="inlineStr">
@@ -24017,34 +24478,30 @@
       </c>
       <c r="G86" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="H86" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Muzzle|Numeric</t>
         </is>
       </c>
       <c r="I86" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="J86" s="37" t="inlineStr">
         <is>
-          <t>Unimplemented</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K86" s="37" t="inlineStr">
         <is>
-          <t>Disabled</t>
-        </is>
-      </c>
-      <c r="L86" s="37" t="inlineStr">
-        <is>
-          <t>Disabled placeholder; part effect not yet implemented.</t>
-        </is>
-      </c>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="L86" s="37" t="n"/>
       <c r="M86" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -24057,24 +24514,120 @@
       </c>
       <c r="O86" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="P86" s="37" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="R86" s="37" t="inlineStr">
+        <is>
+          <t>PE_BOW_CRITBLEED_ARROWHEAD_1</t>
+        </is>
+      </c>
+      <c r="S86" s="37" t="inlineStr">
+        <is>
+          <t>P_BOW_CRITBLEED_ARROWHEAD</t>
+        </is>
+      </c>
+      <c r="T86" s="37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U86" s="37" t="inlineStr">
+        <is>
+          <t>OnCriticalHit</t>
+        </is>
+      </c>
+      <c r="V86" s="37" t="inlineStr">
+        <is>
+          <t>UniqueBehavior</t>
+        </is>
+      </c>
+      <c r="W86" s="37" t="inlineStr">
+        <is>
+          <t>RuntimeBehavior</t>
+        </is>
+      </c>
+      <c r="X86" s="37" t="inlineStr">
+        <is>
+          <t>Add</t>
+        </is>
+      </c>
+      <c r="Y86" s="37" t="inlineStr">
+        <is>
+          <t>0.005</t>
+        </is>
+      </c>
+      <c r="Z86" s="37" t="inlineStr">
+        <is>
+          <t>Part.ApplyBleedOnCritical</t>
+        </is>
+      </c>
+      <c r="AA86" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB86" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC86" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD86" s="37" t="inlineStr">
+        <is>
           <t>0</t>
+        </is>
+      </c>
+      <c r="AE86" s="37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF86" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG86" s="37" t="inlineStr">
+        <is>
+          <t>Stackable</t>
+        </is>
+      </c>
+      <c r="AH86" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI86" s="37" t="n"/>
+      <c r="AJ86" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK86" s="37" t="inlineStr">
+        <is>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="87" ht="22" customHeight="1" s="32">
       <c r="A87" s="37" t="inlineStr">
         <is>
-          <t>AUDIT_WEAPON_SLOTS_C_51</t>
+          <t>P_GUN_EXPLOSIVE_MUZZLE</t>
         </is>
       </c>
       <c r="B87" s="37" t="inlineStr">
         <is>
-          <t>P_AUDIT_C_51</t>
+          <t>P_GUN_EXPLOSIVE_MUZZLE</t>
         </is>
       </c>
       <c r="C87" s="37" t="inlineStr">
@@ -24099,34 +24652,30 @@
       </c>
       <c r="G87" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="H87" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Muzzle|Numeric</t>
         </is>
       </c>
       <c r="I87" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="J87" s="37" t="inlineStr">
         <is>
-          <t>Unimplemented</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K87" s="37" t="inlineStr">
         <is>
-          <t>Disabled</t>
-        </is>
-      </c>
-      <c r="L87" s="37" t="inlineStr">
-        <is>
-          <t>Disabled placeholder; part effect not yet implemented.</t>
-        </is>
-      </c>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="L87" s="37" t="n"/>
       <c r="M87" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -24139,24 +24688,120 @@
       </c>
       <c r="O87" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="P87" s="37" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="R87" s="37" t="inlineStr">
+        <is>
+          <t>PE_BOW_MULTISHOT_ARROWHEAD_1</t>
+        </is>
+      </c>
+      <c r="S87" s="37" t="inlineStr">
+        <is>
+          <t>P_BOW_MULTISHOT_ARROWHEAD</t>
+        </is>
+      </c>
+      <c r="T87" s="37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U87" s="37" t="inlineStr">
+        <is>
+          <t>OnEquip</t>
+        </is>
+      </c>
+      <c r="V87" s="37" t="inlineStr">
+        <is>
+          <t>StatModifier</t>
+        </is>
+      </c>
+      <c r="W87" s="37" t="inlineStr">
+        <is>
+          <t>ProjectileCount</t>
+        </is>
+      </c>
+      <c r="X87" s="37" t="inlineStr">
+        <is>
+          <t>Override</t>
+        </is>
+      </c>
+      <c r="Y87" s="37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z87" s="37" t="inlineStr">
+        <is>
+          <t>Part.StatModifier</t>
+        </is>
+      </c>
+      <c r="AA87" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB87" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC87" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD87" s="37" t="inlineStr">
+        <is>
           <t>0</t>
+        </is>
+      </c>
+      <c r="AE87" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF87" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG87" s="37" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="AH87" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI87" s="37" t="n"/>
+      <c r="AJ87" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK87" s="37" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="88" ht="22" customHeight="1" s="32">
       <c r="A88" s="37" t="inlineStr">
         <is>
-          <t>AUDIT_WEAPON_SLOTS_C_52</t>
+          <t>P_GUN_PIERCING_MUZZLE</t>
         </is>
       </c>
       <c r="B88" s="37" t="inlineStr">
         <is>
-          <t>P_AUDIT_C_52</t>
+          <t>P_GUN_PIERCING_MUZZLE</t>
         </is>
       </c>
       <c r="C88" s="37" t="inlineStr">
@@ -24181,34 +24826,30 @@
       </c>
       <c r="G88" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="H88" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Muzzle|UniqueBehavior</t>
         </is>
       </c>
       <c r="I88" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="J88" s="37" t="inlineStr">
         <is>
-          <t>Unimplemented</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K88" s="37" t="inlineStr">
         <is>
-          <t>Disabled</t>
-        </is>
-      </c>
-      <c r="L88" s="37" t="inlineStr">
-        <is>
-          <t>Disabled placeholder; part effect not yet implemented.</t>
-        </is>
-      </c>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="L88" s="37" t="n"/>
       <c r="M88" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -24221,24 +24862,120 @@
       </c>
       <c r="O88" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="P88" s="37" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="R88" s="37" t="inlineStr">
+        <is>
+          <t>PE_BOW_MULTISHOT_ARROWHEAD_2</t>
+        </is>
+      </c>
+      <c r="S88" s="37" t="inlineStr">
+        <is>
+          <t>P_BOW_MULTISHOT_ARROWHEAD</t>
+        </is>
+      </c>
+      <c r="T88" s="37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U88" s="37" t="inlineStr">
+        <is>
+          <t>OnEquip</t>
+        </is>
+      </c>
+      <c r="V88" s="37" t="inlineStr">
+        <is>
+          <t>StatModifier</t>
+        </is>
+      </c>
+      <c r="W88" s="37" t="inlineStr">
+        <is>
+          <t>ConcentrationDegrees</t>
+        </is>
+      </c>
+      <c r="X88" s="37" t="inlineStr">
+        <is>
+          <t>Override</t>
+        </is>
+      </c>
+      <c r="Y88" s="37" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="Z88" s="37" t="inlineStr">
+        <is>
+          <t>Part.StatModifier</t>
+        </is>
+      </c>
+      <c r="AA88" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB88" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC88" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD88" s="37" t="inlineStr">
+        <is>
           <t>0</t>
+        </is>
+      </c>
+      <c r="AE88" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF88" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG88" s="37" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="AH88" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI88" s="37" t="n"/>
+      <c r="AJ88" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK88" s="37" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="89" ht="22" customHeight="1" s="32">
       <c r="A89" s="37" t="inlineStr">
         <is>
-          <t>AUDIT_WEAPON_SLOTS_C_53</t>
+          <t>P_GUN_BLEED_MUZZLE</t>
         </is>
       </c>
       <c r="B89" s="37" t="inlineStr">
         <is>
-          <t>P_AUDIT_C_53</t>
+          <t>P_GUN_BLEED_MUZZLE</t>
         </is>
       </c>
       <c r="C89" s="37" t="inlineStr">
@@ -24263,34 +25000,30 @@
       </c>
       <c r="G89" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="H89" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Muzzle|UniqueBehavior|Bleeding</t>
         </is>
       </c>
       <c r="I89" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="J89" s="37" t="inlineStr">
         <is>
-          <t>Unimplemented</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K89" s="37" t="inlineStr">
         <is>
-          <t>Disabled</t>
-        </is>
-      </c>
-      <c r="L89" s="37" t="inlineStr">
-        <is>
-          <t>Disabled placeholder; part effect not yet implemented.</t>
-        </is>
-      </c>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="L89" s="37" t="n"/>
       <c r="M89" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -24303,24 +25036,120 @@
       </c>
       <c r="O89" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="P89" s="37" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="R89" s="37" t="inlineStr">
+        <is>
+          <t>PE_BOW_KILLSHARD_ARROWHEAD_1</t>
+        </is>
+      </c>
+      <c r="S89" s="37" t="inlineStr">
+        <is>
+          <t>P_BOW_KILLSHARD_ARROWHEAD</t>
+        </is>
+      </c>
+      <c r="T89" s="37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U89" s="37" t="inlineStr">
+        <is>
+          <t>OnKill</t>
+        </is>
+      </c>
+      <c r="V89" s="37" t="inlineStr">
+        <is>
+          <t>UniqueBehavior</t>
+        </is>
+      </c>
+      <c r="W89" s="37" t="inlineStr">
+        <is>
+          <t>RuntimeBehavior</t>
+        </is>
+      </c>
+      <c r="X89" s="37" t="inlineStr">
+        <is>
+          <t>Add</t>
+        </is>
+      </c>
+      <c r="Y89" s="37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z89" s="37" t="inlineStr">
+        <is>
+          <t>Part.DropShardOnKill</t>
+        </is>
+      </c>
+      <c r="AA89" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB89" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC89" s="37" t="inlineStr">
+        <is>
+          <t>ShardCount</t>
+        </is>
+      </c>
+      <c r="AD89" s="37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE89" s="37" t="inlineStr">
+        <is>
           <t>0</t>
+        </is>
+      </c>
+      <c r="AF89" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG89" s="37" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="AH89" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI89" s="37" t="n"/>
+      <c r="AJ89" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK89" s="37" t="inlineStr">
+        <is>
+          <t>21</t>
         </is>
       </c>
     </row>
     <row r="90" ht="22" customHeight="1" s="32">
       <c r="A90" s="37" t="inlineStr">
         <is>
-          <t>AUDIT_WEAPON_SLOTS_C_54</t>
+          <t>P_GUN_LIFESTEAL_GUNACTION</t>
         </is>
       </c>
       <c r="B90" s="37" t="inlineStr">
         <is>
-          <t>P_AUDIT_C_54</t>
+          <t>P_GUN_LIFESTEAL_GUNACTION</t>
         </is>
       </c>
       <c r="C90" s="37" t="inlineStr">
@@ -24345,34 +25174,30 @@
       </c>
       <c r="G90" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="H90" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>GunAction|UniqueBehavior|Healing</t>
         </is>
       </c>
       <c r="I90" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="J90" s="37" t="inlineStr">
         <is>
-          <t>Unimplemented</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K90" s="37" t="inlineStr">
         <is>
-          <t>Disabled</t>
-        </is>
-      </c>
-      <c r="L90" s="37" t="inlineStr">
-        <is>
-          <t>Disabled placeholder; part effect not yet implemented.</t>
-        </is>
-      </c>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="L90" s="37" t="n"/>
       <c r="M90" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -24385,24 +25210,120 @@
       </c>
       <c r="O90" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="P90" s="37" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="R90" s="37" t="inlineStr">
+        <is>
+          <t>PE_BOW_KILLHASTE_BOWSTRING_1</t>
+        </is>
+      </c>
+      <c r="S90" s="37" t="inlineStr">
+        <is>
+          <t>P_BOW_KILLHASTE_BOWSTRING</t>
+        </is>
+      </c>
+      <c r="T90" s="37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U90" s="37" t="inlineStr">
+        <is>
+          <t>OnKill</t>
+        </is>
+      </c>
+      <c r="V90" s="37" t="inlineStr">
+        <is>
+          <t>UniqueBehavior</t>
+        </is>
+      </c>
+      <c r="W90" s="37" t="inlineStr">
+        <is>
+          <t>RuntimeBehavior</t>
+        </is>
+      </c>
+      <c r="X90" s="37" t="inlineStr">
+        <is>
+          <t>Add</t>
+        </is>
+      </c>
+      <c r="Y90" s="37" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="Z90" s="37" t="inlineStr">
+        <is>
+          <t>Part.MoveSpeedOnKill</t>
+        </is>
+      </c>
+      <c r="AA90" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB90" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC90" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD90" s="37" t="inlineStr">
+        <is>
           <t>0</t>
+        </is>
+      </c>
+      <c r="AE90" s="37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AF90" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG90" s="37" t="inlineStr">
+        <is>
+          <t>IndependentTimed</t>
+        </is>
+      </c>
+      <c r="AH90" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI90" s="37" t="n"/>
+      <c r="AJ90" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK90" s="37" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="91" ht="22" customHeight="1" s="32">
       <c r="A91" s="37" t="inlineStr">
         <is>
-          <t>AUDIT_WEAPON_SLOTS_C_55</t>
+          <t>P_GUN_HITSHARD_GUNACTION</t>
         </is>
       </c>
       <c r="B91" s="37" t="inlineStr">
         <is>
-          <t>P_AUDIT_C_55</t>
+          <t>P_GUN_HITSHARD_GUNACTION</t>
         </is>
       </c>
       <c r="C91" s="37" t="inlineStr">
@@ -24427,34 +25348,30 @@
       </c>
       <c r="G91" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="H91" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>GunAction|UniqueBehavior|TimeShard</t>
         </is>
       </c>
       <c r="I91" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="J91" s="37" t="inlineStr">
         <is>
-          <t>Unimplemented</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K91" s="37" t="inlineStr">
         <is>
-          <t>Disabled</t>
-        </is>
-      </c>
-      <c r="L91" s="37" t="inlineStr">
-        <is>
-          <t>Disabled placeholder; part effect not yet implemented.</t>
-        </is>
-      </c>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="L91" s="37" t="n"/>
       <c r="M91" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -24467,24 +25384,120 @@
       </c>
       <c r="O91" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="P91" s="37" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="R91" s="37" t="inlineStr">
+        <is>
+          <t>PE_BOW_COMBOHASTE_BOWSTRING_1</t>
+        </is>
+      </c>
+      <c r="S91" s="37" t="inlineStr">
+        <is>
+          <t>P_BOW_COMBOHASTE_BOWSTRING</t>
+        </is>
+      </c>
+      <c r="T91" s="37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U91" s="37" t="inlineStr">
+        <is>
+          <t>OnAttack</t>
+        </is>
+      </c>
+      <c r="V91" s="37" t="inlineStr">
+        <is>
+          <t>UniqueBehavior</t>
+        </is>
+      </c>
+      <c r="W91" s="37" t="inlineStr">
+        <is>
+          <t>RuntimeBehavior</t>
+        </is>
+      </c>
+      <c r="X91" s="37" t="inlineStr">
+        <is>
+          <t>Add</t>
+        </is>
+      </c>
+      <c r="Y91" s="37" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="Z91" s="37" t="inlineStr">
+        <is>
+          <t>Part.AttackMoveSpeedOnAttack</t>
+        </is>
+      </c>
+      <c r="AA91" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB91" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC91" s="37" t="inlineStr">
+        <is>
+          <t>MaxStacks</t>
+        </is>
+      </c>
+      <c r="AD91" s="37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE91" s="37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AF91" s="37" t="inlineStr">
+        <is>
           <t>0</t>
+        </is>
+      </c>
+      <c r="AG91" s="37" t="inlineStr">
+        <is>
+          <t>IndependentTimed</t>
+        </is>
+      </c>
+      <c r="AH91" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI91" s="37" t="n"/>
+      <c r="AJ91" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK91" s="37" t="inlineStr">
+        <is>
+          <t>25</t>
         </is>
       </c>
     </row>
     <row r="92" ht="22" customHeight="1" s="32">
       <c r="A92" s="37" t="inlineStr">
         <is>
-          <t>AUDIT_WEAPON_SLOTS_C_56</t>
+          <t>P_GUN_ATTACKSTACK_GUNACTION</t>
         </is>
       </c>
       <c r="B92" s="37" t="inlineStr">
         <is>
-          <t>P_AUDIT_C_56</t>
+          <t>P_GUN_ATTACKSTACK_GUNACTION</t>
         </is>
       </c>
       <c r="C92" s="37" t="inlineStr">
@@ -24509,34 +25522,30 @@
       </c>
       <c r="G92" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="H92" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>GunAction|UniqueBehavior|AttackSpeed</t>
         </is>
       </c>
       <c r="I92" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="J92" s="37" t="inlineStr">
         <is>
-          <t>Unimplemented</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K92" s="37" t="inlineStr">
         <is>
-          <t>Disabled</t>
-        </is>
-      </c>
-      <c r="L92" s="37" t="inlineStr">
-        <is>
-          <t>Disabled placeholder; part effect not yet implemented.</t>
-        </is>
-      </c>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="L92" s="37" t="n"/>
       <c r="M92" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -24549,12 +25558,108 @@
       </c>
       <c r="O92" s="37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="P92" s="37" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="R92" s="37" t="inlineStr">
+        <is>
+          <t>PE_SCYTHE_GROUPGROWTH_ROTARYBLADE_1</t>
+        </is>
+      </c>
+      <c r="S92" s="37" t="inlineStr">
+        <is>
+          <t>P_SCYTHE_GROUPGROWTH_ROTARYBLADE</t>
+        </is>
+      </c>
+      <c r="T92" s="37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U92" s="37" t="inlineStr">
+        <is>
+          <t>OnAttackResolved</t>
+        </is>
+      </c>
+      <c r="V92" s="37" t="inlineStr">
+        <is>
+          <t>UniqueBehavior</t>
+        </is>
+      </c>
+      <c r="W92" s="37" t="inlineStr">
+        <is>
+          <t>RuntimeBehavior</t>
+        </is>
+      </c>
+      <c r="X92" s="37" t="inlineStr">
+        <is>
+          <t>Add</t>
+        </is>
+      </c>
+      <c r="Y92" s="37" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="Z92" s="37" t="inlineStr">
+        <is>
+          <t>Part.RangeOnGroupHit</t>
+        </is>
+      </c>
+      <c r="AA92" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB92" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC92" s="37" t="inlineStr">
+        <is>
+          <t>GroupThreshold</t>
+        </is>
+      </c>
+      <c r="AD92" s="37" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE92" s="37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AF92" s="37" t="inlineStr">
+        <is>
           <t>0</t>
+        </is>
+      </c>
+      <c r="AG92" s="37" t="inlineStr">
+        <is>
+          <t>IndependentTimed</t>
+        </is>
+      </c>
+      <c r="AH92" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI92" s="37" t="n"/>
+      <c r="AJ92" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK92" s="37" t="inlineStr">
+        <is>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -24639,6 +25744,102 @@
           <t>0</t>
         </is>
       </c>
+      <c r="R93" s="37" t="inlineStr">
+        <is>
+          <t>PE_SCYTHE_LIFESTEAL_ROTARYBLADE_1</t>
+        </is>
+      </c>
+      <c r="S93" s="37" t="inlineStr">
+        <is>
+          <t>P_SCYTHE_LIFESTEAL_ROTARYBLADE</t>
+        </is>
+      </c>
+      <c r="T93" s="37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U93" s="37" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="V93" s="37" t="inlineStr">
+        <is>
+          <t>UniqueBehavior</t>
+        </is>
+      </c>
+      <c r="W93" s="37" t="inlineStr">
+        <is>
+          <t>RuntimeBehavior</t>
+        </is>
+      </c>
+      <c r="X93" s="37" t="inlineStr">
+        <is>
+          <t>Add</t>
+        </is>
+      </c>
+      <c r="Y93" s="37" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="Z93" s="37" t="inlineStr">
+        <is>
+          <t>Part.HealOnHit</t>
+        </is>
+      </c>
+      <c r="AA93" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB93" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC93" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD93" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE93" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF93" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG93" s="37" t="inlineStr">
+        <is>
+          <t>Stackable</t>
+        </is>
+      </c>
+      <c r="AH93" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI93" s="37" t="n"/>
+      <c r="AJ93" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK93" s="37" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="22" customHeight="1" s="32">
       <c r="A94" s="37" t="inlineStr">
@@ -24698,7 +25899,7 @@
       </c>
       <c r="L94" s="37" t="inlineStr">
         <is>
-          <t>Disabled placeholder; part effect not yet implemented.</t>
+          <t>Retired: staff/whip weapon runes disabled on request</t>
         </is>
       </c>
       <c r="M94" s="37" t="inlineStr">
@@ -24719,6 +25920,102 @@
       <c r="P94" s="37" t="inlineStr">
         <is>
           <t>0</t>
+        </is>
+      </c>
+      <c r="R94" s="37" t="inlineStr">
+        <is>
+          <t>PE_SCYTHE_STUN_ROTARYBLADE_1</t>
+        </is>
+      </c>
+      <c r="S94" s="37" t="inlineStr">
+        <is>
+          <t>P_SCYTHE_STUN_ROTARYBLADE</t>
+        </is>
+      </c>
+      <c r="T94" s="37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U94" s="37" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="V94" s="37" t="inlineStr">
+        <is>
+          <t>UniqueBehavior</t>
+        </is>
+      </c>
+      <c r="W94" s="37" t="inlineStr">
+        <is>
+          <t>RuntimeBehavior</t>
+        </is>
+      </c>
+      <c r="X94" s="37" t="inlineStr">
+        <is>
+          <t>Add</t>
+        </is>
+      </c>
+      <c r="Y94" s="37" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="Z94" s="37" t="inlineStr">
+        <is>
+          <t>Part.StunOnHit</t>
+        </is>
+      </c>
+      <c r="AA94" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB94" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC94" s="37" t="inlineStr">
+        <is>
+          <t>Chance</t>
+        </is>
+      </c>
+      <c r="AD94" s="37" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="AE94" s="37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF94" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG94" s="37" t="inlineStr">
+        <is>
+          <t>NoStack</t>
+        </is>
+      </c>
+      <c r="AH94" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI94" s="37" t="n"/>
+      <c r="AJ94" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK94" s="37" t="inlineStr">
+        <is>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -24765,7 +26062,7 @@
       </c>
       <c r="I95" s="37" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="J95" s="37" t="inlineStr">
@@ -24775,10 +26072,14 @@
       </c>
       <c r="K95" s="37" t="inlineStr">
         <is>
-          <t>Implemented</t>
-        </is>
-      </c>
-      <c r="L95" s="37" t="n"/>
+          <t>Disabled</t>
+        </is>
+      </c>
+      <c r="L95" s="37" t="inlineStr">
+        <is>
+          <t>Retired: staff/whip weapon runes disabled on request</t>
+        </is>
+      </c>
       <c r="M95" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -24791,11 +26092,109 @@
       </c>
       <c r="O95" s="37" t="inlineStr">
         <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="P95" s="37" t="n">
-        <v>45</v>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P95" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R95" s="37" t="inlineStr">
+        <is>
+          <t>PE_SCYTHE_BLEED_ROTARYBLADE_1</t>
+        </is>
+      </c>
+      <c r="S95" s="37" t="inlineStr">
+        <is>
+          <t>P_SCYTHE_BLEED_ROTARYBLADE</t>
+        </is>
+      </c>
+      <c r="T95" s="37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U95" s="37" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="V95" s="37" t="inlineStr">
+        <is>
+          <t>UniqueBehavior</t>
+        </is>
+      </c>
+      <c r="W95" s="37" t="inlineStr">
+        <is>
+          <t>RuntimeBehavior</t>
+        </is>
+      </c>
+      <c r="X95" s="37" t="inlineStr">
+        <is>
+          <t>Add</t>
+        </is>
+      </c>
+      <c r="Y95" s="37" t="inlineStr">
+        <is>
+          <t>0.005</t>
+        </is>
+      </c>
+      <c r="Z95" s="37" t="inlineStr">
+        <is>
+          <t>Part.BleedEveryTargetHits</t>
+        </is>
+      </c>
+      <c r="AA95" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB95" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC95" s="37" t="inlineStr">
+        <is>
+          <t>HitThreshold</t>
+        </is>
+      </c>
+      <c r="AD95" s="37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE95" s="37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF95" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG95" s="37" t="inlineStr">
+        <is>
+          <t>Stackable</t>
+        </is>
+      </c>
+      <c r="AH95" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI95" s="37" t="n"/>
+      <c r="AJ95" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK95" s="37" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
     </row>
     <row r="96" ht="22" customHeight="1" s="32">
@@ -24856,7 +26255,7 @@
       </c>
       <c r="L96" s="37" t="inlineStr">
         <is>
-          <t>Disabled placeholder; part effect not yet implemented.</t>
+          <t>Retired: staff/whip weapon runes disabled on request</t>
         </is>
       </c>
       <c r="M96" s="37" t="inlineStr">
@@ -24877,6 +26276,102 @@
       <c r="P96" s="37" t="inlineStr">
         <is>
           <t>0</t>
+        </is>
+      </c>
+      <c r="R96" s="37" t="inlineStr">
+        <is>
+          <t>PE_SCYTHE_OUTERRING_ROTARYBLADE_1</t>
+        </is>
+      </c>
+      <c r="S96" s="37" t="inlineStr">
+        <is>
+          <t>P_SCYTHE_OUTERRING_ROTARYBLADE</t>
+        </is>
+      </c>
+      <c r="T96" s="37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U96" s="37" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="V96" s="37" t="inlineStr">
+        <is>
+          <t>UniqueBehavior</t>
+        </is>
+      </c>
+      <c r="W96" s="37" t="inlineStr">
+        <is>
+          <t>RuntimeBehavior</t>
+        </is>
+      </c>
+      <c r="X96" s="37" t="inlineStr">
+        <is>
+          <t>Add</t>
+        </is>
+      </c>
+      <c r="Y96" s="37" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="Z96" s="37" t="inlineStr">
+        <is>
+          <t>Part.OuterRingDamage</t>
+        </is>
+      </c>
+      <c r="AA96" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB96" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC96" s="37" t="inlineStr">
+        <is>
+          <t>OuterRingFraction</t>
+        </is>
+      </c>
+      <c r="AD96" s="37" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="AE96" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF96" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG96" s="37" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="AH96" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI96" s="37" t="n"/>
+      <c r="AJ96" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK96" s="37" t="inlineStr">
+        <is>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -24938,7 +26433,7 @@
       </c>
       <c r="L97" s="37" t="inlineStr">
         <is>
-          <t>Disabled placeholder; part effect not yet implemented.</t>
+          <t>Retired: staff/whip weapon runes disabled on request</t>
         </is>
       </c>
       <c r="M97" s="37" t="inlineStr">
@@ -24959,6 +26454,102 @@
       <c r="P97" s="37" t="inlineStr">
         <is>
           <t>0</t>
+        </is>
+      </c>
+      <c r="R97" s="37" t="inlineStr">
+        <is>
+          <t>PE_SCYTHE_MOVESTACK_GRIP_1</t>
+        </is>
+      </c>
+      <c r="S97" s="37" t="inlineStr">
+        <is>
+          <t>P_SCYTHE_MOVESTACK_GRIP</t>
+        </is>
+      </c>
+      <c r="T97" s="37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U97" s="37" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="V97" s="37" t="inlineStr">
+        <is>
+          <t>UniqueBehavior</t>
+        </is>
+      </c>
+      <c r="W97" s="37" t="inlineStr">
+        <is>
+          <t>RuntimeBehavior</t>
+        </is>
+      </c>
+      <c r="X97" s="37" t="inlineStr">
+        <is>
+          <t>Add</t>
+        </is>
+      </c>
+      <c r="Y97" s="37" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="Z97" s="37" t="inlineStr">
+        <is>
+          <t>Part.MoveSpeedPerHit</t>
+        </is>
+      </c>
+      <c r="AA97" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB97" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC97" s="37" t="inlineStr">
+        <is>
+          <t>MaxStacks</t>
+        </is>
+      </c>
+      <c r="AD97" s="37" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AE97" s="37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AF97" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG97" s="37" t="inlineStr">
+        <is>
+          <t>IndependentTimed</t>
+        </is>
+      </c>
+      <c r="AH97" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI97" s="37" t="n"/>
+      <c r="AJ97" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK97" s="37" t="inlineStr">
+        <is>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -25020,7 +26611,7 @@
       </c>
       <c r="L98" s="37" t="inlineStr">
         <is>
-          <t>Disabled placeholder; part effect not yet implemented.</t>
+          <t>Retired: staff/whip weapon runes disabled on request</t>
         </is>
       </c>
       <c r="M98" s="37" t="inlineStr">
@@ -25041,6 +26632,102 @@
       <c r="P98" s="37" t="inlineStr">
         <is>
           <t>0</t>
+        </is>
+      </c>
+      <c r="R98" s="37" t="inlineStr">
+        <is>
+          <t>PE_SCYTHE_GROUPINVULN_GRIP_1</t>
+        </is>
+      </c>
+      <c r="S98" s="37" t="inlineStr">
+        <is>
+          <t>P_SCYTHE_GROUPINVULN_GRIP</t>
+        </is>
+      </c>
+      <c r="T98" s="37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U98" s="37" t="inlineStr">
+        <is>
+          <t>OnEquip</t>
+        </is>
+      </c>
+      <c r="V98" s="37" t="inlineStr">
+        <is>
+          <t>StatModifier</t>
+        </is>
+      </c>
+      <c r="W98" s="37" t="inlineStr">
+        <is>
+          <t>AttackSpeed</t>
+        </is>
+      </c>
+      <c r="X98" s="37" t="inlineStr">
+        <is>
+          <t>Multiply</t>
+        </is>
+      </c>
+      <c r="Y98" s="37" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="Z98" s="37" t="inlineStr">
+        <is>
+          <t>Part.StatModifier</t>
+        </is>
+      </c>
+      <c r="AA98" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB98" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC98" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD98" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE98" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF98" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG98" s="37" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="AH98" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI98" s="37" t="n"/>
+      <c r="AJ98" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK98" s="37" t="inlineStr">
+        <is>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -25106,7 +26793,7 @@
       </c>
       <c r="L99" s="37" t="inlineStr">
         <is>
-          <t>Disabled placeholder; part effect not yet implemented.</t>
+          <t>Retired: staff/whip weapon runes disabled on request</t>
         </is>
       </c>
       <c r="M99" s="37" t="inlineStr">
@@ -25127,6 +26814,102 @@
       <c r="P99" s="37" t="inlineStr">
         <is>
           <t>0</t>
+        </is>
+      </c>
+      <c r="R99" s="37" t="inlineStr">
+        <is>
+          <t>PE_SCYTHE_GROUPINVULN_GRIP_2</t>
+        </is>
+      </c>
+      <c r="S99" s="37" t="inlineStr">
+        <is>
+          <t>P_SCYTHE_GROUPINVULN_GRIP</t>
+        </is>
+      </c>
+      <c r="T99" s="37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U99" s="37" t="inlineStr">
+        <is>
+          <t>OnAttackResolved</t>
+        </is>
+      </c>
+      <c r="V99" s="37" t="inlineStr">
+        <is>
+          <t>UniqueBehavior</t>
+        </is>
+      </c>
+      <c r="W99" s="37" t="inlineStr">
+        <is>
+          <t>RuntimeBehavior</t>
+        </is>
+      </c>
+      <c r="X99" s="37" t="inlineStr">
+        <is>
+          <t>Override</t>
+        </is>
+      </c>
+      <c r="Y99" s="37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z99" s="37" t="inlineStr">
+        <is>
+          <t>Part.InvulnerableOnGroupHit</t>
+        </is>
+      </c>
+      <c r="AA99" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB99" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC99" s="37" t="inlineStr">
+        <is>
+          <t>GroupThreshold</t>
+        </is>
+      </c>
+      <c r="AD99" s="37" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE99" s="37" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="AF99" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG99" s="37" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="AH99" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI99" s="37" t="n"/>
+      <c r="AJ99" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK99" s="37" t="inlineStr">
+        <is>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -25173,7 +26956,7 @@
       </c>
       <c r="I100" s="37" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="J100" s="37" t="inlineStr">
@@ -25183,10 +26966,14 @@
       </c>
       <c r="K100" s="37" t="inlineStr">
         <is>
-          <t>Implemented</t>
-        </is>
-      </c>
-      <c r="L100" s="37" t="n"/>
+          <t>Disabled</t>
+        </is>
+      </c>
+      <c r="L100" s="37" t="inlineStr">
+        <is>
+          <t>Retired: staff/whip weapon runes disabled on request</t>
+        </is>
+      </c>
       <c r="M100" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -25199,11 +26986,109 @@
       </c>
       <c r="O100" s="37" t="inlineStr">
         <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="P100" s="37" t="n">
-        <v>30</v>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P100" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R100" s="37" t="inlineStr">
+        <is>
+          <t>PE_SCYTHE_ATTACKSTACK_GRIP_1</t>
+        </is>
+      </c>
+      <c r="S100" s="37" t="inlineStr">
+        <is>
+          <t>P_SCYTHE_ATTACKSTACK_GRIP</t>
+        </is>
+      </c>
+      <c r="T100" s="37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U100" s="37" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="V100" s="37" t="inlineStr">
+        <is>
+          <t>UniqueBehavior</t>
+        </is>
+      </c>
+      <c r="W100" s="37" t="inlineStr">
+        <is>
+          <t>RuntimeBehavior</t>
+        </is>
+      </c>
+      <c r="X100" s="37" t="inlineStr">
+        <is>
+          <t>Add</t>
+        </is>
+      </c>
+      <c r="Y100" s="37" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="Z100" s="37" t="inlineStr">
+        <is>
+          <t>Part.AttackSpeedPerHit</t>
+        </is>
+      </c>
+      <c r="AA100" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB100" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC100" s="37" t="inlineStr">
+        <is>
+          <t>MaxStacks</t>
+        </is>
+      </c>
+      <c r="AD100" s="37" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AE100" s="37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AF100" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG100" s="37" t="inlineStr">
+        <is>
+          <t>IndependentTimed</t>
+        </is>
+      </c>
+      <c r="AH100" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI100" s="37" t="n"/>
+      <c r="AJ100" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK100" s="37" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
       </c>
     </row>
     <row r="101" ht="22" customHeight="1" s="32">
@@ -25249,7 +27134,7 @@
       </c>
       <c r="I101" s="37" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="J101" s="37" t="inlineStr">
@@ -25259,10 +27144,14 @@
       </c>
       <c r="K101" s="37" t="inlineStr">
         <is>
-          <t>Implemented</t>
-        </is>
-      </c>
-      <c r="L101" s="37" t="n"/>
+          <t>Disabled</t>
+        </is>
+      </c>
+      <c r="L101" s="37" t="inlineStr">
+        <is>
+          <t>Retired: staff/whip weapon runes disabled on request</t>
+        </is>
+      </c>
       <c r="M101" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -25275,11 +27164,109 @@
       </c>
       <c r="O101" s="37" t="inlineStr">
         <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="P101" s="37" t="n">
-        <v>30</v>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P101" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R101" s="37" t="inlineStr">
+        <is>
+          <t>PE_SCYTHE_THROWRECALL_GRIP_1</t>
+        </is>
+      </c>
+      <c r="S101" s="37" t="inlineStr">
+        <is>
+          <t>P_SCYTHE_THROWRECALL_GRIP</t>
+        </is>
+      </c>
+      <c r="T101" s="37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U101" s="37" t="inlineStr">
+        <is>
+          <t>OnActiveAttack</t>
+        </is>
+      </c>
+      <c r="V101" s="37" t="inlineStr">
+        <is>
+          <t>UniqueBehavior</t>
+        </is>
+      </c>
+      <c r="W101" s="37" t="inlineStr">
+        <is>
+          <t>RuntimeBehavior</t>
+        </is>
+      </c>
+      <c r="X101" s="37" t="inlineStr">
+        <is>
+          <t>Multiply</t>
+        </is>
+      </c>
+      <c r="Y101" s="37" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="Z101" s="37" t="inlineStr">
+        <is>
+          <t>Part.ScytheThrowRecall</t>
+        </is>
+      </c>
+      <c r="AA101" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB101" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC101" s="37" t="inlineStr">
+        <is>
+          <t>MaxRangeCm</t>
+        </is>
+      </c>
+      <c r="AD101" s="37" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="AE101" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF101" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG101" s="37" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="AH101" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI101" s="37" t="n"/>
+      <c r="AJ101" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK101" s="37" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
       </c>
     </row>
     <row r="102" ht="22" customHeight="1" s="32">
@@ -25340,7 +27327,7 @@
       </c>
       <c r="L102" s="37" t="inlineStr">
         <is>
-          <t>Disabled placeholder; part effect not yet implemented.</t>
+          <t>Retired: staff/whip weapon runes disabled on request</t>
         </is>
       </c>
       <c r="M102" s="37" t="inlineStr">
@@ -25361,6 +27348,102 @@
       <c r="P102" s="37" t="inlineStr">
         <is>
           <t>0</t>
+        </is>
+      </c>
+      <c r="R102" s="37" t="inlineStr">
+        <is>
+          <t>PE_SCYTHE_THROWRECALL_GRIP_2</t>
+        </is>
+      </c>
+      <c r="S102" s="37" t="inlineStr">
+        <is>
+          <t>P_SCYTHE_THROWRECALL_GRIP</t>
+        </is>
+      </c>
+      <c r="T102" s="37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U102" s="37" t="inlineStr">
+        <is>
+          <t>OnActiveAttack</t>
+        </is>
+      </c>
+      <c r="V102" s="37" t="inlineStr">
+        <is>
+          <t>UniqueBehavior</t>
+        </is>
+      </c>
+      <c r="W102" s="37" t="inlineStr">
+        <is>
+          <t>RuntimeBehavior</t>
+        </is>
+      </c>
+      <c r="X102" s="37" t="inlineStr">
+        <is>
+          <t>Multiply</t>
+        </is>
+      </c>
+      <c r="Y102" s="37" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="Z102" s="37" t="inlineStr">
+        <is>
+          <t>Part.ScytheThrowRecall</t>
+        </is>
+      </c>
+      <c r="AA102" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB102" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC102" s="37" t="inlineStr">
+        <is>
+          <t>StationaryDamageMultiplier</t>
+        </is>
+      </c>
+      <c r="AD102" s="37" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="AE102" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF102" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG102" s="37" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="AH102" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI102" s="37" t="n"/>
+      <c r="AJ102" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK102" s="37" t="inlineStr">
+        <is>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -25407,7 +27490,7 @@
       </c>
       <c r="I103" s="37" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="J103" s="37" t="inlineStr">
@@ -25417,10 +27500,14 @@
       </c>
       <c r="K103" s="37" t="inlineStr">
         <is>
-          <t>Implemented</t>
-        </is>
-      </c>
-      <c r="L103" s="37" t="n"/>
+          <t>Disabled</t>
+        </is>
+      </c>
+      <c r="L103" s="37" t="inlineStr">
+        <is>
+          <t>Retired: staff/whip weapon runes disabled on request</t>
+        </is>
+      </c>
       <c r="M103" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -25433,11 +27520,109 @@
       </c>
       <c r="O103" s="37" t="inlineStr">
         <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="P103" s="37" t="n">
-        <v>30</v>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P103" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R103" s="37" t="inlineStr">
+        <is>
+          <t>PE_LONGSWORD_GROUPGROWTH_SWORDBLADE_1</t>
+        </is>
+      </c>
+      <c r="S103" s="37" t="inlineStr">
+        <is>
+          <t>P_LONGSWORD_GROUPGROWTH_SWORDBLADE</t>
+        </is>
+      </c>
+      <c r="T103" s="37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U103" s="37" t="inlineStr">
+        <is>
+          <t>OnAttackResolved</t>
+        </is>
+      </c>
+      <c r="V103" s="37" t="inlineStr">
+        <is>
+          <t>UniqueBehavior</t>
+        </is>
+      </c>
+      <c r="W103" s="37" t="inlineStr">
+        <is>
+          <t>RuntimeBehavior</t>
+        </is>
+      </c>
+      <c r="X103" s="37" t="inlineStr">
+        <is>
+          <t>Add</t>
+        </is>
+      </c>
+      <c r="Y103" s="37" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="Z103" s="37" t="inlineStr">
+        <is>
+          <t>Part.RangeOnGroupHit</t>
+        </is>
+      </c>
+      <c r="AA103" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB103" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC103" s="37" t="inlineStr">
+        <is>
+          <t>GroupThreshold</t>
+        </is>
+      </c>
+      <c r="AD103" s="37" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE103" s="37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AF103" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG103" s="37" t="inlineStr">
+        <is>
+          <t>IndependentTimed</t>
+        </is>
+      </c>
+      <c r="AH103" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI103" s="37" t="n"/>
+      <c r="AJ103" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK103" s="37" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
       </c>
     </row>
     <row r="104" ht="22" customHeight="1" s="32">
@@ -25498,7 +27683,7 @@
       </c>
       <c r="L104" s="37" t="inlineStr">
         <is>
-          <t>Disabled placeholder; part effect not yet implemented.</t>
+          <t>Retired: staff/whip weapon runes disabled on request</t>
         </is>
       </c>
       <c r="M104" s="37" t="inlineStr">
@@ -25519,6 +27704,102 @@
       <c r="P104" s="37" t="inlineStr">
         <is>
           <t>0</t>
+        </is>
+      </c>
+      <c r="R104" s="37" t="inlineStr">
+        <is>
+          <t>PE_LONGSWORD_HITSHARD_SWORDBLADE_1</t>
+        </is>
+      </c>
+      <c r="S104" s="37" t="inlineStr">
+        <is>
+          <t>P_LONGSWORD_HITSHARD_SWORDBLADE</t>
+        </is>
+      </c>
+      <c r="T104" s="37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U104" s="37" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="V104" s="37" t="inlineStr">
+        <is>
+          <t>UniqueBehavior</t>
+        </is>
+      </c>
+      <c r="W104" s="37" t="inlineStr">
+        <is>
+          <t>RuntimeBehavior</t>
+        </is>
+      </c>
+      <c r="X104" s="37" t="inlineStr">
+        <is>
+          <t>Add</t>
+        </is>
+      </c>
+      <c r="Y104" s="37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z104" s="37" t="inlineStr">
+        <is>
+          <t>Part.DropShardEveryHits</t>
+        </is>
+      </c>
+      <c r="AA104" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB104" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC104" s="37" t="inlineStr">
+        <is>
+          <t>HitThreshold</t>
+        </is>
+      </c>
+      <c r="AD104" s="37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE104" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF104" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG104" s="37" t="inlineStr">
+        <is>
+          <t>Stackable</t>
+        </is>
+      </c>
+      <c r="AH104" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI104" s="37" t="n"/>
+      <c r="AJ104" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK104" s="37" t="inlineStr">
+        <is>
+          <t>40</t>
         </is>
       </c>
     </row>
@@ -25580,7 +27861,7 @@
       </c>
       <c r="L105" s="37" t="inlineStr">
         <is>
-          <t>Disabled placeholder; part effect not yet implemented.</t>
+          <t>Retired: staff/whip weapon runes disabled on request</t>
         </is>
       </c>
       <c r="M105" s="37" t="inlineStr">
@@ -25601,6 +27882,102 @@
       <c r="P105" s="37" t="inlineStr">
         <is>
           <t>0</t>
+        </is>
+      </c>
+      <c r="R105" s="37" t="inlineStr">
+        <is>
+          <t>PE_LONGSWORD_CRITBLEED_SWORDBLADE_1</t>
+        </is>
+      </c>
+      <c r="S105" s="37" t="inlineStr">
+        <is>
+          <t>P_LONGSWORD_CRITBLEED_SWORDBLADE</t>
+        </is>
+      </c>
+      <c r="T105" s="37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U105" s="37" t="inlineStr">
+        <is>
+          <t>OnCriticalHit</t>
+        </is>
+      </c>
+      <c r="V105" s="37" t="inlineStr">
+        <is>
+          <t>UniqueBehavior</t>
+        </is>
+      </c>
+      <c r="W105" s="37" t="inlineStr">
+        <is>
+          <t>RuntimeBehavior</t>
+        </is>
+      </c>
+      <c r="X105" s="37" t="inlineStr">
+        <is>
+          <t>Add</t>
+        </is>
+      </c>
+      <c r="Y105" s="37" t="inlineStr">
+        <is>
+          <t>0.005</t>
+        </is>
+      </c>
+      <c r="Z105" s="37" t="inlineStr">
+        <is>
+          <t>Part.ApplyBleedOnCritical</t>
+        </is>
+      </c>
+      <c r="AA105" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB105" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC105" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD105" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE105" s="37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF105" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG105" s="37" t="inlineStr">
+        <is>
+          <t>Stackable</t>
+        </is>
+      </c>
+      <c r="AH105" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI105" s="37" t="n"/>
+      <c r="AJ105" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK105" s="37" t="inlineStr">
+        <is>
+          <t>41</t>
         </is>
       </c>
     </row>
@@ -25662,7 +28039,7 @@
       </c>
       <c r="L106" s="37" t="inlineStr">
         <is>
-          <t>Disabled placeholder; part effect not yet implemented.</t>
+          <t>Retired: staff/whip weapon runes disabled on request</t>
         </is>
       </c>
       <c r="M106" s="37" t="inlineStr">
@@ -25683,6 +28060,102 @@
       <c r="P106" s="37" t="inlineStr">
         <is>
           <t>0</t>
+        </is>
+      </c>
+      <c r="R106" s="37" t="inlineStr">
+        <is>
+          <t>PE_LONGSWORD_METEOR_SWORDBLADE_1</t>
+        </is>
+      </c>
+      <c r="S106" s="37" t="inlineStr">
+        <is>
+          <t>P_LONGSWORD_METEOR_SWORDBLADE</t>
+        </is>
+      </c>
+      <c r="T106" s="37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U106" s="37" t="inlineStr">
+        <is>
+          <t>OnAttackResolved</t>
+        </is>
+      </c>
+      <c r="V106" s="37" t="inlineStr">
+        <is>
+          <t>UniqueBehavior</t>
+        </is>
+      </c>
+      <c r="W106" s="37" t="inlineStr">
+        <is>
+          <t>RuntimeBehavior</t>
+        </is>
+      </c>
+      <c r="X106" s="37" t="inlineStr">
+        <is>
+          <t>Multiply</t>
+        </is>
+      </c>
+      <c r="Y106" s="37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z106" s="37" t="inlineStr">
+        <is>
+          <t>Part.MeteorOnGroupHit</t>
+        </is>
+      </c>
+      <c r="AA106" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB106" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC106" s="37" t="inlineStr">
+        <is>
+          <t>GroupThreshold</t>
+        </is>
+      </c>
+      <c r="AD106" s="37" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AE106" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF106" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG106" s="37" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="AH106" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI106" s="37" t="n"/>
+      <c r="AJ106" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK106" s="37" t="inlineStr">
+        <is>
+          <t>42</t>
         </is>
       </c>
     </row>
@@ -25744,7 +28217,7 @@
       </c>
       <c r="L107" s="37" t="inlineStr">
         <is>
-          <t>Disabled placeholder; part effect not yet implemented.</t>
+          <t>Retired: staff/whip weapon runes disabled on request</t>
         </is>
       </c>
       <c r="M107" s="37" t="inlineStr">
@@ -25765,6 +28238,102 @@
       <c r="P107" s="37" t="inlineStr">
         <is>
           <t>0</t>
+        </is>
+      </c>
+      <c r="R107" s="37" t="inlineStr">
+        <is>
+          <t>PE_LONGSWORD_METEOR_SWORDBLADE_2</t>
+        </is>
+      </c>
+      <c r="S107" s="37" t="inlineStr">
+        <is>
+          <t>P_LONGSWORD_METEOR_SWORDBLADE</t>
+        </is>
+      </c>
+      <c r="T107" s="37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U107" s="37" t="inlineStr">
+        <is>
+          <t>OnAttackResolved</t>
+        </is>
+      </c>
+      <c r="V107" s="37" t="inlineStr">
+        <is>
+          <t>UniqueBehavior</t>
+        </is>
+      </c>
+      <c r="W107" s="37" t="inlineStr">
+        <is>
+          <t>RuntimeBehavior</t>
+        </is>
+      </c>
+      <c r="X107" s="37" t="inlineStr">
+        <is>
+          <t>Override</t>
+        </is>
+      </c>
+      <c r="Y107" s="37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z107" s="37" t="inlineStr">
+        <is>
+          <t>Part.MeteorOnGroupHit</t>
+        </is>
+      </c>
+      <c r="AA107" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB107" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC107" s="37" t="inlineStr">
+        <is>
+          <t>ExplosionRadiusCm</t>
+        </is>
+      </c>
+      <c r="AD107" s="37" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="AE107" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF107" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG107" s="37" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="AH107" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI107" s="37" t="n"/>
+      <c r="AJ107" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK107" s="37" t="inlineStr">
+        <is>
+          <t>42</t>
         </is>
       </c>
     </row>
@@ -25826,7 +28395,7 @@
       </c>
       <c r="L108" s="37" t="inlineStr">
         <is>
-          <t>Disabled placeholder; part effect not yet implemented.</t>
+          <t>Retired: staff/whip weapon runes disabled on request</t>
         </is>
       </c>
       <c r="M108" s="37" t="inlineStr">
@@ -25847,6 +28416,102 @@
       <c r="P108" s="37" t="inlineStr">
         <is>
           <t>0</t>
+        </is>
+      </c>
+      <c r="R108" s="37" t="inlineStr">
+        <is>
+          <t>PE_LONGSWORD_MOVESTACK_GRIP_1</t>
+        </is>
+      </c>
+      <c r="S108" s="37" t="inlineStr">
+        <is>
+          <t>P_LONGSWORD_MOVESTACK_GRIP</t>
+        </is>
+      </c>
+      <c r="T108" s="37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U108" s="37" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="V108" s="37" t="inlineStr">
+        <is>
+          <t>UniqueBehavior</t>
+        </is>
+      </c>
+      <c r="W108" s="37" t="inlineStr">
+        <is>
+          <t>RuntimeBehavior</t>
+        </is>
+      </c>
+      <c r="X108" s="37" t="inlineStr">
+        <is>
+          <t>Add</t>
+        </is>
+      </c>
+      <c r="Y108" s="37" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="Z108" s="37" t="inlineStr">
+        <is>
+          <t>Part.MoveSpeedPerHit</t>
+        </is>
+      </c>
+      <c r="AA108" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB108" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC108" s="37" t="inlineStr">
+        <is>
+          <t>MaxStacks</t>
+        </is>
+      </c>
+      <c r="AD108" s="37" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AE108" s="37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AF108" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG108" s="37" t="inlineStr">
+        <is>
+          <t>IndependentTimed</t>
+        </is>
+      </c>
+      <c r="AH108" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI108" s="37" t="n"/>
+      <c r="AJ108" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK108" s="37" t="inlineStr">
+        <is>
+          <t>44</t>
         </is>
       </c>
     </row>
@@ -25893,7 +28558,7 @@
       </c>
       <c r="I109" s="37" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="J109" s="37" t="inlineStr">
@@ -25903,10 +28568,14 @@
       </c>
       <c r="K109" s="37" t="inlineStr">
         <is>
-          <t>Implemented</t>
-        </is>
-      </c>
-      <c r="L109" s="37" t="n"/>
+          <t>Disabled</t>
+        </is>
+      </c>
+      <c r="L109" s="37" t="inlineStr">
+        <is>
+          <t>Retired: staff/whip weapon runes disabled on request</t>
+        </is>
+      </c>
       <c r="M109" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -25919,11 +28588,109 @@
       </c>
       <c r="O109" s="37" t="inlineStr">
         <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="P109" s="37" t="n">
-        <v>30</v>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P109" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R109" s="37" t="inlineStr">
+        <is>
+          <t>PE_LONGSWORD_ATTACKSTACK_GRIP_1</t>
+        </is>
+      </c>
+      <c r="S109" s="37" t="inlineStr">
+        <is>
+          <t>P_LONGSWORD_ATTACKSTACK_GRIP</t>
+        </is>
+      </c>
+      <c r="T109" s="37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U109" s="37" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="V109" s="37" t="inlineStr">
+        <is>
+          <t>UniqueBehavior</t>
+        </is>
+      </c>
+      <c r="W109" s="37" t="inlineStr">
+        <is>
+          <t>RuntimeBehavior</t>
+        </is>
+      </c>
+      <c r="X109" s="37" t="inlineStr">
+        <is>
+          <t>Add</t>
+        </is>
+      </c>
+      <c r="Y109" s="37" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="Z109" s="37" t="inlineStr">
+        <is>
+          <t>Part.AttackSpeedPerHit</t>
+        </is>
+      </c>
+      <c r="AA109" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB109" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC109" s="37" t="inlineStr">
+        <is>
+          <t>MaxStacks</t>
+        </is>
+      </c>
+      <c r="AD109" s="37" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AE109" s="37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AF109" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG109" s="37" t="inlineStr">
+        <is>
+          <t>IndependentTimed</t>
+        </is>
+      </c>
+      <c r="AH109" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI109" s="37" t="n"/>
+      <c r="AJ109" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK109" s="37" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
       </c>
     </row>
     <row r="110" ht="22" customHeight="1" s="32">
@@ -25969,7 +28736,7 @@
       </c>
       <c r="I110" s="37" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="J110" s="37" t="inlineStr">
@@ -25979,10 +28746,14 @@
       </c>
       <c r="K110" s="37" t="inlineStr">
         <is>
-          <t>Implemented</t>
-        </is>
-      </c>
-      <c r="L110" s="37" t="n"/>
+          <t>Disabled</t>
+        </is>
+      </c>
+      <c r="L110" s="37" t="inlineStr">
+        <is>
+          <t>Retired: staff/whip weapon runes disabled on request</t>
+        </is>
+      </c>
       <c r="M110" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -25995,11 +28766,109 @@
       </c>
       <c r="O110" s="37" t="inlineStr">
         <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="P110" s="37" t="n">
-        <v>45</v>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P110" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R110" s="37" t="inlineStr">
+        <is>
+          <t>PE_LONGSWORD_STUN_GRIP_1</t>
+        </is>
+      </c>
+      <c r="S110" s="37" t="inlineStr">
+        <is>
+          <t>P_LONGSWORD_STUN_GRIP</t>
+        </is>
+      </c>
+      <c r="T110" s="37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U110" s="37" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="V110" s="37" t="inlineStr">
+        <is>
+          <t>UniqueBehavior</t>
+        </is>
+      </c>
+      <c r="W110" s="37" t="inlineStr">
+        <is>
+          <t>RuntimeBehavior</t>
+        </is>
+      </c>
+      <c r="X110" s="37" t="inlineStr">
+        <is>
+          <t>Add</t>
+        </is>
+      </c>
+      <c r="Y110" s="37" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="Z110" s="37" t="inlineStr">
+        <is>
+          <t>Part.StunOnHit</t>
+        </is>
+      </c>
+      <c r="AA110" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB110" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC110" s="37" t="inlineStr">
+        <is>
+          <t>Chance</t>
+        </is>
+      </c>
+      <c r="AD110" s="37" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="AE110" s="37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF110" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG110" s="37" t="inlineStr">
+        <is>
+          <t>NoStack</t>
+        </is>
+      </c>
+      <c r="AH110" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI110" s="37" t="n"/>
+      <c r="AJ110" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK110" s="37" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
       </c>
     </row>
     <row r="111" ht="22" customHeight="1" s="32">
@@ -26060,7 +28929,7 @@
       </c>
       <c r="L111" s="37" t="inlineStr">
         <is>
-          <t>Disabled placeholder; part effect not yet implemented.</t>
+          <t>Retired: staff/whip weapon runes disabled on request</t>
         </is>
       </c>
       <c r="M111" s="37" t="inlineStr">
@@ -26081,6 +28950,102 @@
       <c r="P111" s="37" t="inlineStr">
         <is>
           <t>0</t>
+        </is>
+      </c>
+      <c r="R111" s="37" t="inlineStr">
+        <is>
+          <t>PE_GUN_CHARGED_MUZZLE_1</t>
+        </is>
+      </c>
+      <c r="S111" s="37" t="inlineStr">
+        <is>
+          <t>P_GUN_CHARGED_MUZZLE</t>
+        </is>
+      </c>
+      <c r="T111" s="37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U111" s="37" t="inlineStr">
+        <is>
+          <t>OnEquip</t>
+        </is>
+      </c>
+      <c r="V111" s="37" t="inlineStr">
+        <is>
+          <t>StatModifier</t>
+        </is>
+      </c>
+      <c r="W111" s="37" t="inlineStr">
+        <is>
+          <t>AttackSpeed</t>
+        </is>
+      </c>
+      <c r="X111" s="37" t="inlineStr">
+        <is>
+          <t>Multiply</t>
+        </is>
+      </c>
+      <c r="Y111" s="37" t="inlineStr">
+        <is>
+          <t>0.166666667</t>
+        </is>
+      </c>
+      <c r="Z111" s="37" t="inlineStr">
+        <is>
+          <t>Part.StatModifier</t>
+        </is>
+      </c>
+      <c r="AA111" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB111" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC111" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD111" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE111" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF111" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG111" s="37" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="AH111" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI111" s="37" t="n"/>
+      <c r="AJ111" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK111" s="37" t="inlineStr">
+        <is>
+          <t>49</t>
         </is>
       </c>
     </row>
@@ -26142,7 +29107,7 @@
       </c>
       <c r="L112" s="37" t="inlineStr">
         <is>
-          <t>Disabled placeholder; part effect not yet implemented.</t>
+          <t>Retired: staff/whip weapon runes disabled on request</t>
         </is>
       </c>
       <c r="M112" s="37" t="inlineStr">
@@ -26163,6 +29128,102 @@
       <c r="P112" s="37" t="inlineStr">
         <is>
           <t>0</t>
+        </is>
+      </c>
+      <c r="R112" s="37" t="inlineStr">
+        <is>
+          <t>PE_GUN_CHARGED_MUZZLE_2</t>
+        </is>
+      </c>
+      <c r="S112" s="37" t="inlineStr">
+        <is>
+          <t>P_GUN_CHARGED_MUZZLE</t>
+        </is>
+      </c>
+      <c r="T112" s="37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U112" s="37" t="inlineStr">
+        <is>
+          <t>OnEquip</t>
+        </is>
+      </c>
+      <c r="V112" s="37" t="inlineStr">
+        <is>
+          <t>StatModifier</t>
+        </is>
+      </c>
+      <c r="W112" s="37" t="inlineStr">
+        <is>
+          <t>PhysicalCoefficient</t>
+        </is>
+      </c>
+      <c r="X112" s="37" t="inlineStr">
+        <is>
+          <t>Multiply</t>
+        </is>
+      </c>
+      <c r="Y112" s="37" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="Z112" s="37" t="inlineStr">
+        <is>
+          <t>Part.StatModifier</t>
+        </is>
+      </c>
+      <c r="AA112" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB112" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC112" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD112" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE112" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF112" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG112" s="37" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="AH112" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI112" s="37" t="n"/>
+      <c r="AJ112" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK112" s="37" t="inlineStr">
+        <is>
+          <t>49</t>
         </is>
       </c>
     </row>
@@ -26224,7 +29285,7 @@
       </c>
       <c r="L113" s="37" t="inlineStr">
         <is>
-          <t>Disabled placeholder; part effect not yet implemented.</t>
+          <t>Retired: staff/whip weapon runes disabled on request</t>
         </is>
       </c>
       <c r="M113" s="37" t="inlineStr">
@@ -26245,6 +29306,102 @@
       <c r="P113" s="37" t="inlineStr">
         <is>
           <t>0</t>
+        </is>
+      </c>
+      <c r="R113" s="37" t="inlineStr">
+        <is>
+          <t>PE_GUN_CHARGED_MUZZLE_3</t>
+        </is>
+      </c>
+      <c r="S113" s="37" t="inlineStr">
+        <is>
+          <t>P_GUN_CHARGED_MUZZLE</t>
+        </is>
+      </c>
+      <c r="T113" s="37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U113" s="37" t="inlineStr">
+        <is>
+          <t>OnEquip</t>
+        </is>
+      </c>
+      <c r="V113" s="37" t="inlineStr">
+        <is>
+          <t>StatModifier</t>
+        </is>
+      </c>
+      <c r="W113" s="37" t="inlineStr">
+        <is>
+          <t>ElementalCoefficient</t>
+        </is>
+      </c>
+      <c r="X113" s="37" t="inlineStr">
+        <is>
+          <t>Multiply</t>
+        </is>
+      </c>
+      <c r="Y113" s="37" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="Z113" s="37" t="inlineStr">
+        <is>
+          <t>Part.StatModifier</t>
+        </is>
+      </c>
+      <c r="AA113" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB113" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC113" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD113" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE113" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF113" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG113" s="37" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="AH113" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI113" s="37" t="n"/>
+      <c r="AJ113" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK113" s="37" t="inlineStr">
+        <is>
+          <t>49</t>
         </is>
       </c>
     </row>
@@ -26306,7 +29463,7 @@
       </c>
       <c r="L114" s="37" t="inlineStr">
         <is>
-          <t>Disabled placeholder; part effect not yet implemented.</t>
+          <t>Retired: staff/whip weapon runes disabled on request</t>
         </is>
       </c>
       <c r="M114" s="37" t="inlineStr">
@@ -26327,6 +29484,102 @@
       <c r="P114" s="37" t="inlineStr">
         <is>
           <t>0</t>
+        </is>
+      </c>
+      <c r="R114" s="37" t="inlineStr">
+        <is>
+          <t>PE_GUN_RAPID_MUZZLE_1</t>
+        </is>
+      </c>
+      <c r="S114" s="37" t="inlineStr">
+        <is>
+          <t>P_GUN_RAPID_MUZZLE</t>
+        </is>
+      </c>
+      <c r="T114" s="37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U114" s="37" t="inlineStr">
+        <is>
+          <t>OnEquip</t>
+        </is>
+      </c>
+      <c r="V114" s="37" t="inlineStr">
+        <is>
+          <t>StatModifier</t>
+        </is>
+      </c>
+      <c r="W114" s="37" t="inlineStr">
+        <is>
+          <t>AttackSpeed</t>
+        </is>
+      </c>
+      <c r="X114" s="37" t="inlineStr">
+        <is>
+          <t>Multiply</t>
+        </is>
+      </c>
+      <c r="Y114" s="37" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="Z114" s="37" t="inlineStr">
+        <is>
+          <t>Part.StatModifier</t>
+        </is>
+      </c>
+      <c r="AA114" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB114" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC114" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD114" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE114" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF114" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG114" s="37" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="AH114" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI114" s="37" t="n"/>
+      <c r="AJ114" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK114" s="37" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
     </row>
@@ -26388,7 +29641,7 @@
       </c>
       <c r="L115" s="37" t="inlineStr">
         <is>
-          <t>Disabled placeholder; part effect not yet implemented.</t>
+          <t>Retired: staff/whip weapon runes disabled on request</t>
         </is>
       </c>
       <c r="M115" s="37" t="inlineStr">
@@ -26409,6 +29662,102 @@
       <c r="P115" s="37" t="inlineStr">
         <is>
           <t>0</t>
+        </is>
+      </c>
+      <c r="R115" s="37" t="inlineStr">
+        <is>
+          <t>PE_GUN_EXPLOSIVE_MUZZLE_1</t>
+        </is>
+      </c>
+      <c r="S115" s="37" t="inlineStr">
+        <is>
+          <t>P_GUN_EXPLOSIVE_MUZZLE</t>
+        </is>
+      </c>
+      <c r="T115" s="37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U115" s="37" t="inlineStr">
+        <is>
+          <t>OnEquip</t>
+        </is>
+      </c>
+      <c r="V115" s="37" t="inlineStr">
+        <is>
+          <t>StatModifier</t>
+        </is>
+      </c>
+      <c r="W115" s="37" t="inlineStr">
+        <is>
+          <t>ExplosionRadius</t>
+        </is>
+      </c>
+      <c r="X115" s="37" t="inlineStr">
+        <is>
+          <t>Override</t>
+        </is>
+      </c>
+      <c r="Y115" s="37" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="Z115" s="37" t="inlineStr">
+        <is>
+          <t>Part.StatModifier</t>
+        </is>
+      </c>
+      <c r="AA115" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB115" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC115" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD115" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE115" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF115" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG115" s="37" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="AH115" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI115" s="37" t="n"/>
+      <c r="AJ115" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK115" s="37" t="inlineStr">
+        <is>
+          <t>51</t>
         </is>
       </c>
     </row>
@@ -26429,6 +29778,102 @@
       <c r="N116" s="31" t="n"/>
       <c r="O116" s="31" t="n"/>
       <c r="P116" s="31" t="n"/>
+      <c r="R116" s="37" t="inlineStr">
+        <is>
+          <t>PE_GUN_PIERCING_MUZZLE_1</t>
+        </is>
+      </c>
+      <c r="S116" s="37" t="inlineStr">
+        <is>
+          <t>P_GUN_PIERCING_MUZZLE</t>
+        </is>
+      </c>
+      <c r="T116" s="37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U116" s="37" t="inlineStr">
+        <is>
+          <t>OnCriticalHit</t>
+        </is>
+      </c>
+      <c r="V116" s="37" t="inlineStr">
+        <is>
+          <t>UniqueBehavior</t>
+        </is>
+      </c>
+      <c r="W116" s="37" t="inlineStr">
+        <is>
+          <t>RuntimeBehavior</t>
+        </is>
+      </c>
+      <c r="X116" s="37" t="inlineStr">
+        <is>
+          <t>Override</t>
+        </is>
+      </c>
+      <c r="Y116" s="37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z116" s="37" t="inlineStr">
+        <is>
+          <t>Part.ProjectilePierceOnCritical</t>
+        </is>
+      </c>
+      <c r="AA116" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB116" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC116" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD116" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE116" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF116" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG116" s="37" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="AH116" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI116" s="37" t="n"/>
+      <c r="AJ116" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK116" s="37" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="22" customHeight="1" s="32">
       <c r="A117" s="31" t="n"/>
@@ -26447,6 +29892,102 @@
       <c r="N117" s="31" t="n"/>
       <c r="O117" s="31" t="n"/>
       <c r="P117" s="31" t="n"/>
+      <c r="R117" s="37" t="inlineStr">
+        <is>
+          <t>PE_GUN_BLEED_MUZZLE_1</t>
+        </is>
+      </c>
+      <c r="S117" s="37" t="inlineStr">
+        <is>
+          <t>P_GUN_BLEED_MUZZLE</t>
+        </is>
+      </c>
+      <c r="T117" s="37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U117" s="37" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="V117" s="37" t="inlineStr">
+        <is>
+          <t>UniqueBehavior</t>
+        </is>
+      </c>
+      <c r="W117" s="37" t="inlineStr">
+        <is>
+          <t>RuntimeBehavior</t>
+        </is>
+      </c>
+      <c r="X117" s="37" t="inlineStr">
+        <is>
+          <t>Add</t>
+        </is>
+      </c>
+      <c r="Y117" s="37" t="inlineStr">
+        <is>
+          <t>0.005</t>
+        </is>
+      </c>
+      <c r="Z117" s="37" t="inlineStr">
+        <is>
+          <t>Part.ApplyBleedOnHitChance</t>
+        </is>
+      </c>
+      <c r="AA117" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB117" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC117" s="37" t="inlineStr">
+        <is>
+          <t>Chance</t>
+        </is>
+      </c>
+      <c r="AD117" s="37" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="AE117" s="37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF117" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG117" s="37" t="inlineStr">
+        <is>
+          <t>Stackable</t>
+        </is>
+      </c>
+      <c r="AH117" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI117" s="37" t="n"/>
+      <c r="AJ117" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK117" s="37" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="22" customHeight="1" s="32">
       <c r="A118" s="31" t="n"/>
@@ -26465,6 +30006,102 @@
       <c r="N118" s="31" t="n"/>
       <c r="O118" s="31" t="n"/>
       <c r="P118" s="31" t="n"/>
+      <c r="R118" s="37" t="inlineStr">
+        <is>
+          <t>PE_GUN_LIFESTEAL_GUNACTION_1</t>
+        </is>
+      </c>
+      <c r="S118" s="37" t="inlineStr">
+        <is>
+          <t>P_GUN_LIFESTEAL_GUNACTION</t>
+        </is>
+      </c>
+      <c r="T118" s="37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U118" s="37" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="V118" s="37" t="inlineStr">
+        <is>
+          <t>UniqueBehavior</t>
+        </is>
+      </c>
+      <c r="W118" s="37" t="inlineStr">
+        <is>
+          <t>RuntimeBehavior</t>
+        </is>
+      </c>
+      <c r="X118" s="37" t="inlineStr">
+        <is>
+          <t>Add</t>
+        </is>
+      </c>
+      <c r="Y118" s="37" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="Z118" s="37" t="inlineStr">
+        <is>
+          <t>Part.HealOnHit</t>
+        </is>
+      </c>
+      <c r="AA118" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB118" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC118" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD118" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE118" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF118" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG118" s="37" t="inlineStr">
+        <is>
+          <t>Stackable</t>
+        </is>
+      </c>
+      <c r="AH118" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI118" s="37" t="n"/>
+      <c r="AJ118" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK118" s="37" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="22" customHeight="1" s="32">
       <c r="A119" s="31" t="n"/>
@@ -26483,6 +30120,102 @@
       <c r="N119" s="31" t="n"/>
       <c r="O119" s="31" t="n"/>
       <c r="P119" s="31" t="n"/>
+      <c r="R119" s="37" t="inlineStr">
+        <is>
+          <t>PE_GUN_HITSHARD_GUNACTION_1</t>
+        </is>
+      </c>
+      <c r="S119" s="37" t="inlineStr">
+        <is>
+          <t>P_GUN_HITSHARD_GUNACTION</t>
+        </is>
+      </c>
+      <c r="T119" s="37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U119" s="37" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="V119" s="37" t="inlineStr">
+        <is>
+          <t>UniqueBehavior</t>
+        </is>
+      </c>
+      <c r="W119" s="37" t="inlineStr">
+        <is>
+          <t>RuntimeBehavior</t>
+        </is>
+      </c>
+      <c r="X119" s="37" t="inlineStr">
+        <is>
+          <t>Add</t>
+        </is>
+      </c>
+      <c r="Y119" s="37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z119" s="37" t="inlineStr">
+        <is>
+          <t>Part.DropShardEveryHits</t>
+        </is>
+      </c>
+      <c r="AA119" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB119" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC119" s="37" t="inlineStr">
+        <is>
+          <t>HitThreshold</t>
+        </is>
+      </c>
+      <c r="AD119" s="37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE119" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF119" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG119" s="37" t="inlineStr">
+        <is>
+          <t>Stackable</t>
+        </is>
+      </c>
+      <c r="AH119" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI119" s="37" t="n"/>
+      <c r="AJ119" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK119" s="37" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="22" customHeight="1" s="32">
       <c r="A120" s="31" t="n"/>
@@ -26501,6 +30234,102 @@
       <c r="N120" s="31" t="n"/>
       <c r="O120" s="31" t="n"/>
       <c r="P120" s="31" t="n"/>
+      <c r="R120" s="37" t="inlineStr">
+        <is>
+          <t>PE_GUN_ATTACKSTACK_GUNACTION_1</t>
+        </is>
+      </c>
+      <c r="S120" s="37" t="inlineStr">
+        <is>
+          <t>P_GUN_ATTACKSTACK_GUNACTION</t>
+        </is>
+      </c>
+      <c r="T120" s="37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U120" s="37" t="inlineStr">
+        <is>
+          <t>OnAttack</t>
+        </is>
+      </c>
+      <c r="V120" s="37" t="inlineStr">
+        <is>
+          <t>UniqueBehavior</t>
+        </is>
+      </c>
+      <c r="W120" s="37" t="inlineStr">
+        <is>
+          <t>RuntimeBehavior</t>
+        </is>
+      </c>
+      <c r="X120" s="37" t="inlineStr">
+        <is>
+          <t>Add</t>
+        </is>
+      </c>
+      <c r="Y120" s="37" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="Z120" s="37" t="inlineStr">
+        <is>
+          <t>Part.AttackSpeedOnAttack</t>
+        </is>
+      </c>
+      <c r="AA120" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AB120" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC120" s="37" t="inlineStr">
+        <is>
+          <t>MaxStacks</t>
+        </is>
+      </c>
+      <c r="AD120" s="37" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AE120" s="37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AF120" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG120" s="37" t="inlineStr">
+        <is>
+          <t>IndependentTimed</t>
+        </is>
+      </c>
+      <c r="AH120" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI120" s="37" t="n"/>
+      <c r="AJ120" s="37" t="inlineStr">
+        <is>
+          <t>武器插槽C</t>
+        </is>
+      </c>
+      <c r="AK120" s="37" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="22" customHeight="1" s="32">
       <c r="A121" s="31" t="n"/>
@@ -26602,37 +30431,37 @@
     <dataValidation sqref="K46:K123" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
       <formula1>=DV_Logic_Parts_ImplementationStatus</formula1>
     </dataValidation>
-    <dataValidation sqref="S46:S82" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
+    <dataValidation sqref="S46:S120" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
       <formula1>INDIRECT("tblParts[PartId]")</formula1>
     </dataValidation>
-    <dataValidation sqref="U46:U82" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
+    <dataValidation sqref="U46:U120" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
       <formula1>=DV_Logic_PartEffects_Trigger</formula1>
     </dataValidation>
-    <dataValidation sqref="V46:V82" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
+    <dataValidation sqref="V46:V120" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
       <formula1>=DV_Logic_PartEffects_EffectKind</formula1>
     </dataValidation>
-    <dataValidation sqref="W46:W82" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
+    <dataValidation sqref="W46:W120" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
       <formula1>=DV_Logic_PartEffects_Target</formula1>
     </dataValidation>
-    <dataValidation sqref="X46:X82" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
+    <dataValidation sqref="X46:X120" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
       <formula1>=DV_Logic_PartEffects_ValueOp</formula1>
     </dataValidation>
-    <dataValidation sqref="Z46:Z82" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
+    <dataValidation sqref="Z46:Z120" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
       <formula1>=DV_Logic_PartEffects_BehaviorId</formula1>
     </dataValidation>
-    <dataValidation sqref="AA46:AA82" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
+    <dataValidation sqref="AA46:AA120" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
       <formula1>=DV_Logic_PartEffects_FormulaId</formula1>
     </dataValidation>
-    <dataValidation sqref="AB46:AB82" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
+    <dataValidation sqref="AB46:AB120" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
       <formula1>=DV_Logic_PartEffects_AttackPatternId</formula1>
     </dataValidation>
-    <dataValidation sqref="AC46:AC82" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
+    <dataValidation sqref="AC46:AC120" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
       <formula1>=DV_Logic_PartEffects_ParamName</formula1>
     </dataValidation>
-    <dataValidation sqref="AG46:AG82" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
+    <dataValidation sqref="AG46:AG120" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
       <formula1>=DV_Logic_PartEffects_StackPolicy</formula1>
     </dataValidation>
-    <dataValidation sqref="AH46:AH82" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
+    <dataValidation sqref="AH46:AH120" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
       <formula1>=DV_Logic_PartEffects_Enabled</formula1>
     </dataValidation>
     <dataValidation sqref="O46:O123" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
@@ -26991,12 +30820,12 @@
       </c>
       <c r="D7" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Status.Stun</t>
         </is>
       </c>
       <c r="E7" s="37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F7" s="37" t="inlineStr">
@@ -27021,14 +30850,10 @@
       </c>
       <c r="J7" s="37" t="inlineStr">
         <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="K7" s="37" t="inlineStr">
-        <is>
-          <t>No current reaction or build handler in Plan 20</t>
-        </is>
-      </c>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="K7" s="37" t="n"/>
     </row>
     <row r="8" ht="30" customHeight="1" s="32">
       <c r="A8" s="37" t="inlineStr">
@@ -27220,12 +31045,12 @@
       </c>
       <c r="D11" s="37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Status.Bleeding</t>
         </is>
       </c>
       <c r="E11" s="37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F11" s="37" t="inlineStr">
@@ -27235,7 +31060,7 @@
       </c>
       <c r="G11" s="37" t="inlineStr">
         <is>
-          <t>Refresh</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="H11" s="37" t="inlineStr">
@@ -27250,14 +31075,10 @@
       </c>
       <c r="J11" s="37" t="inlineStr">
         <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="K11" s="37" t="inlineStr">
-        <is>
-          <t>No current reaction or build handler in Plan 20</t>
-        </is>
-      </c>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="K11" s="37" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="0" sort="0"/>

--- a/Design/Data/ReEchoData.xlsx
+++ b/Design/Data/ReEchoData.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="属性S" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="元素体系Y" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="构筑体系G" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色体系J" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="武器体系W" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="武器插槽C" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="怪物体系M" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="状态Z" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经济系统" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_WorkbookMeta" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_ExportMap" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_SystemData" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AttributeCatalog" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="属性S" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="元素体系Y" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="构筑体系G" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="角色体系J" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="武器体系W" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="武器插槽C" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="怪物体系M" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="状态Z" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="经济系统" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="_WorkbookMeta" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="_ExportMap" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="_SystemData" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="AttributeCatalog" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName name="DV_Logic_Elements_Id">'_SystemData'!$R$2:$R$5</definedName>
@@ -24488,7 +24488,7 @@
       </c>
       <c r="I86" s="37" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="J86" s="37" t="inlineStr">
@@ -24498,10 +24498,14 @@
       </c>
       <c r="K86" s="37" t="inlineStr">
         <is>
-          <t>Implemented</t>
-        </is>
-      </c>
-      <c r="L86" s="37" t="n"/>
+          <t>Disabled</t>
+        </is>
+      </c>
+      <c r="L86" s="37" t="inlineStr">
+        <is>
+          <t>策划确认不想要</t>
+        </is>
+      </c>
       <c r="M86" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -24514,12 +24518,12 @@
       </c>
       <c r="O86" s="37" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="P86" s="37" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R86" s="37" t="inlineStr">
@@ -24604,10 +24608,14 @@
       </c>
       <c r="AH86" s="37" t="inlineStr">
         <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="AI86" s="37" t="n"/>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AI86" s="37" t="inlineStr">
+        <is>
+          <t>策划确认不想要</t>
+        </is>
+      </c>
       <c r="AJ86" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>
@@ -29568,10 +29576,14 @@
       </c>
       <c r="AH114" s="37" t="inlineStr">
         <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="AI114" s="37" t="n"/>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AI114" s="37" t="inlineStr">
+        <is>
+          <t>策划确认不想要</t>
+        </is>
+      </c>
       <c r="AJ114" s="37" t="inlineStr">
         <is>
           <t>武器插槽C</t>

--- a/Design/Data/ReEchoData.xlsx
+++ b/Design/Data/ReEchoData.xlsx
@@ -2,20 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="属性S" sheetId="1" r:id="R7a5b0cdc7aa84fe4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="元素体系Y" sheetId="2" r:id="R1bc7404443534c88"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="构筑体系G" sheetId="3" r:id="R407445188ec24609"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色体系J" sheetId="4" r:id="R9a15102f2ec94e54"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="武器体系W" sheetId="5" r:id="Rf2e352088efe4efe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="武器插槽C" sheetId="6" r:id="Rd4cf6e8d18d340e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="怪物体系M" sheetId="7" r:id="R27c178e542634a0a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="状态Z" sheetId="8" r:id="R984f885cbae44552"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经济系统" sheetId="9" r:id="R067796afa7e248d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_WorkbookMeta" sheetId="10" r:id="R1d3398b9fa1a4362"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_ExportMap" sheetId="11" r:id="Rec6a22445b4c496c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_SystemData" sheetId="12" r:id="Rc1250bd3e0374e00"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AttributeCatalog" sheetId="13" r:id="Rd4aab6433a464bf4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色能力A" sheetId="14" r:id="Rc18e4728588b4f91"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="属性S" sheetId="1" r:id="Rcba2f3e8b3a14084"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="元素体系Y" sheetId="2" r:id="Re8edb6112fcc4d69"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="构筑体系G" sheetId="3" r:id="R7b17187d927e4b1b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色体系J" sheetId="4" r:id="R01b017a3af024bfa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="武器体系W" sheetId="5" r:id="Re4810378a66f4195"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="武器插槽C" sheetId="6" r:id="R4ba95ac7ff8d4043"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="怪物体系M" sheetId="7" r:id="R204c8ffb67ed4f42"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="状态Z" sheetId="8" r:id="Rb1d18962f9344212"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经济系统" sheetId="9" r:id="R63f5957737214167"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_WorkbookMeta" sheetId="10" r:id="Rf7c19e732f254aa3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_ExportMap" sheetId="11" r:id="Re6616ae2d3fa4b0d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_SystemData" sheetId="12" r:id="R22c02b0f44274321"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AttributeCatalog" sheetId="13" r:id="Rd0273ff98f9d4486"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色能力A" sheetId="14" r:id="Rbc1c4d54239b468b"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="DV_Logic_Elements_Id">'_SystemData'!$R$2:$R$5</x:definedName>
@@ -663,7 +663,8 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="32" name="tblPartEffects" displayName="tblPartEffects" ref="R45:AK108" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="35" name="tblPartEffects" displayName="tblPartEffects" ref="R45:AK104" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="R45:AK104"/>
   <x:tableColumns count="20">
     <x:tableColumn id="1" name="Id"/>
     <x:tableColumn id="2" name="PartId"/>
@@ -988,8 +989,9 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="26" name="tblWeapons" displayName="tblWeapons" ref="A14:U18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="21">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="33" name="tblWeapons" displayName="tblWeapons" ref="A14:T18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A14:T18"/>
+  <x:tableColumns count="20">
     <x:tableColumn id="1" name="Id"/>
     <x:tableColumn id="2" name="WeaponTypeId"/>
     <x:tableColumn id="3" name="DisplayName"/>
@@ -999,48 +1001,47 @@
     <x:tableColumn id="7" name="LoadoutOrder"/>
     <x:tableColumn id="8" name="AttackPatternId"/>
     <x:tableColumn id="9" name="AttackIntervalSeconds"/>
-    <x:tableColumn id="10" name="PhysicalCoefficient"/>
-    <x:tableColumn id="11" name="ElementalCoefficient"/>
-    <x:tableColumn id="12" name="RangeCm"/>
-    <x:tableColumn id="13" name="ArcDegrees"/>
-    <x:tableColumn id="14" name="ProjectileCount"/>
-    <x:tableColumn id="15" name="ConcentrationDegrees"/>
-    <x:tableColumn id="16" name="ExplosionRadiusCm"/>
-    <x:tableColumn id="17" name="DataRevision"/>
-    <x:tableColumn id="18" name="Enabled"/>
-    <x:tableColumn id="19" name="SourceSheet"/>
-    <x:tableColumn id="20" name="SourceRow"/>
-    <x:tableColumn id="21" name="DisabledReason"/>
+    <x:tableColumn id="10" name="DamageCoefficient"/>
+    <x:tableColumn id="11" name="RangeCm"/>
+    <x:tableColumn id="12" name="ArcDegrees"/>
+    <x:tableColumn id="13" name="ProjectileCount"/>
+    <x:tableColumn id="14" name="ConcentrationDegrees"/>
+    <x:tableColumn id="15" name="ExplosionRadiusCm"/>
+    <x:tableColumn id="16" name="DataRevision"/>
+    <x:tableColumn id="17" name="Enabled"/>
+    <x:tableColumn id="18" name="SourceSheet"/>
+    <x:tableColumn id="19" name="SourceRow"/>
+    <x:tableColumn id="20" name="DisabledReason"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="27" name="tblAttackSteps" displayName="tblAttackSteps" ref="A24:V29" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="22">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="34" name="tblAttackSteps" displayName="tblAttackSteps" ref="A24:U29" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A24:U29"/>
+  <x:tableColumns count="21">
     <x:tableColumn id="1" name="Id"/>
     <x:tableColumn id="2" name="AttackPatternId"/>
     <x:tableColumn id="3" name="StepIndex"/>
     <x:tableColumn id="4" name="DurationSeconds"/>
-    <x:tableColumn id="5" name="PhysicalCoefficient"/>
-    <x:tableColumn id="6" name="ElementalCoefficient"/>
-    <x:tableColumn id="7" name="RangeCm"/>
-    <x:tableColumn id="8" name="ArcDegrees"/>
-    <x:tableColumn id="9" name="ProjectileCount"/>
-    <x:tableColumn id="10" name="ConcentrationDegrees"/>
-    <x:tableColumn id="11" name="ExplosionRadiusCm"/>
-    <x:tableColumn id="12" name="MovementCm"/>
-    <x:tableColumn id="13" name="Invulnerable"/>
-    <x:tableColumn id="14" name="BehaviorId"/>
-    <x:tableColumn id="15" name="FormulaId"/>
-    <x:tableColumn id="16" name="ConditionId"/>
-    <x:tableColumn id="17" name="Enabled"/>
-    <x:tableColumn id="18" name="SourceSheet"/>
-    <x:tableColumn id="19" name="SourceRow"/>
-    <x:tableColumn id="20" name="DisabledReason"/>
-    <x:tableColumn id="21" name="OuterRingStartFraction"/>
-    <x:tableColumn id="22" name="OuterRingBonusMultiplier"/>
+    <x:tableColumn id="5" name="DamageCoefficient"/>
+    <x:tableColumn id="6" name="RangeCm"/>
+    <x:tableColumn id="7" name="ArcDegrees"/>
+    <x:tableColumn id="8" name="ProjectileCount"/>
+    <x:tableColumn id="9" name="ConcentrationDegrees"/>
+    <x:tableColumn id="10" name="ExplosionRadiusCm"/>
+    <x:tableColumn id="11" name="MovementCm"/>
+    <x:tableColumn id="12" name="Invulnerable"/>
+    <x:tableColumn id="13" name="BehaviorId"/>
+    <x:tableColumn id="14" name="FormulaId"/>
+    <x:tableColumn id="15" name="ConditionId"/>
+    <x:tableColumn id="16" name="Enabled"/>
+    <x:tableColumn id="17" name="SourceSheet"/>
+    <x:tableColumn id="18" name="SourceRow"/>
+    <x:tableColumn id="19" name="DisabledReason"/>
+    <x:tableColumn id="20" name="OuterRingStartFraction"/>
+    <x:tableColumn id="21" name="OuterRingBonusMultiplier"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -3506,7 +3507,7 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <sheetProtection xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
+  <x:sheetProtection xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <x:dataValidations count="1">
     <x:dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="A2:A1048576">
       <x:formula1>"角色一级属性,角色二级属性,武器自有属性,卡牌影响属性,"</x:formula1>
@@ -3621,10 +3622,10 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <sheetProtection xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
+  <x:sheetProtection xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raa20dcf8b43e4865"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1c346f1253344e5a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4250,10 +4251,10 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <sheetProtection xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
+  <x:sheetProtection xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R98ae1a0899e5479d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re7dced820b7c4ca0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6906,7 +6907,7 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <sheetProtection xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
+  <x:sheetProtection xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <x:dataValidations count="2">
     <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="C4">
       <x:formula1>"true,false"</x:formula1>
@@ -6917,8 +6918,8 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2590e87fa8ff44a8"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc68c1a6cca904b46"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a2b98d812874406"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad8a0add7c2d416d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7232,10 +7233,10 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <sheetProtection xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="1" sort="0"/>
+  <x:sheetProtection xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="1" sort="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5adf7858677c4680"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf52bbfcf0d094bff"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7700,7 +7701,7 @@
       <x:c r="L11" s="79" t="n"/>
     </x:row>
   </x:sheetData>
-  <sheetProtection xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="0" sort="0"/>
+  <x:sheetProtection xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="0" sort="0"/>
   <x:mergeCells>
     <x:mergeCell ref="A2:L2"/>
     <x:mergeCell ref="A1:L1"/>
@@ -7730,7 +7731,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R495d35b4716b428b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9b1ed20b23194e2d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8666,7 +8667,7 @@
       <x:c r="R18" s="78" t="n"/>
     </x:row>
   </x:sheetData>
-  <sheetProtection xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="0" sort="0"/>
+  <x:sheetProtection xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="0" sort="0"/>
   <x:mergeCells>
     <x:mergeCell ref="A1:R1"/>
     <x:mergeCell ref="A2:D2"/>
@@ -8718,8 +8719,8 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R49831d63389a47e9"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0c9015df32e74192"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf52cf794010d4a88"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6fd6c645fcbe4f83"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13941,7 +13942,7 @@
       <x:c r="K102" s="68" t="n"/>
     </x:row>
   </x:sheetData>
-  <sheetProtection xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="0" sort="0"/>
+  <x:sheetProtection xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="0" sort="0"/>
   <x:mergeCells>
     <x:mergeCell ref="A47:D47"/>
     <x:mergeCell ref="A2:D2"/>
@@ -13999,8 +14000,8 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra2e042214ab340f0"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R80407cc0a4f54b4f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb153232f8aa642f9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R37168bbc4f014768"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14512,7 +14513,7 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <sheetProtection xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="0" sort="0"/>
+  <x:sheetProtection xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="0" sort="0"/>
   <x:mergeCells>
     <x:mergeCell ref="A1:W1"/>
     <x:mergeCell ref="A11:C11"/>
@@ -14543,8 +14544,8 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra07e3ba34a1b4b76"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R40ebeb8f7cdf434d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra2dbea913eee4413"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raf152b9802bc4524"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14950,41 +14951,39 @@
         <x:v>AttackIntervalSeconds</x:v>
       </x:c>
       <x:c r="J14" s="29" t="str">
-        <x:v>PhysicalCoefficient</x:v>
+        <x:v>DamageCoefficient</x:v>
       </x:c>
       <x:c r="K14" s="29" t="str">
-        <x:v>ElementalCoefficient</x:v>
+        <x:v>RangeCm</x:v>
       </x:c>
       <x:c r="L14" s="29" t="str">
-        <x:v>RangeCm</x:v>
+        <x:v>ArcDegrees</x:v>
       </x:c>
       <x:c r="M14" s="29" t="str">
-        <x:v>ArcDegrees</x:v>
+        <x:v>ProjectileCount</x:v>
       </x:c>
       <x:c r="N14" s="29" t="str">
-        <x:v>ProjectileCount</x:v>
+        <x:v>ConcentrationDegrees</x:v>
       </x:c>
       <x:c r="O14" s="29" t="str">
-        <x:v>ConcentrationDegrees</x:v>
+        <x:v>ExplosionRadiusCm</x:v>
       </x:c>
       <x:c r="P14" s="29" t="str">
-        <x:v>ExplosionRadiusCm</x:v>
+        <x:v>DataRevision</x:v>
       </x:c>
       <x:c r="Q14" s="29" t="str">
-        <x:v>DataRevision</x:v>
+        <x:v>Enabled</x:v>
       </x:c>
       <x:c r="R14" s="29" t="str">
-        <x:v>Enabled</x:v>
+        <x:v>SourceSheet</x:v>
       </x:c>
       <x:c r="S14" s="29" t="str">
-        <x:v>SourceSheet</x:v>
+        <x:v>SourceRow</x:v>
       </x:c>
       <x:c r="T14" s="29" t="str">
-        <x:v>SourceRow</x:v>
-      </x:c>
-      <x:c r="U14" s="29" t="str">
         <x:v>DisabledReason</x:v>
       </x:c>
+      <x:c r="U14"/>
     </x:row>
     <x:row r="15" s="71" customFormat="1" ht="22" customHeight="1">
       <x:c r="A15" s="78" t="str">
@@ -15018,13 +15017,13 @@
         <x:v>0.60</x:v>
       </x:c>
       <x:c r="K15" s="78" t="str">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="L15" s="78" t="str">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="M15" s="78" t="str">
         <x:v>0</x:v>
-      </x:c>
-      <x:c r="L15" s="78" t="str">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="M15" s="78" t="str">
-        <x:v>360</x:v>
       </x:c>
       <x:c r="N15" s="78" t="str">
         <x:v>0</x:v>
@@ -15033,21 +15032,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="P15" s="78" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="Q15" s="78" t="str">
-        <x:v>1</x:v>
+        <x:v>true</x:v>
       </x:c>
       <x:c r="R15" s="78" t="str">
-        <x:v>true</x:v>
+        <x:v>武器体系W</x:v>
       </x:c>
       <x:c r="S15" s="78" t="str">
-        <x:v>武器体系W</x:v>
-      </x:c>
-      <x:c r="T15" s="78" t="str">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="U15" s="78"/>
+      <x:c r="T15" s="78"/>
+      <x:c r="U15"/>
     </x:row>
     <x:row r="16" s="71" customFormat="1" ht="22" customHeight="1">
       <x:c r="A16" s="78" t="str">
@@ -15081,13 +15078,13 @@
         <x:v>1.20</x:v>
       </x:c>
       <x:c r="K16" s="78" t="str">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="L16" s="78" t="str">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="M16" s="78" t="str">
         <x:v>0</x:v>
-      </x:c>
-      <x:c r="L16" s="78" t="str">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="M16" s="78" t="str">
-        <x:v>100</x:v>
       </x:c>
       <x:c r="N16" s="78" t="str">
         <x:v>0</x:v>
@@ -15096,21 +15093,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="P16" s="78" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="Q16" s="78" t="str">
-        <x:v>1</x:v>
+        <x:v>true</x:v>
       </x:c>
       <x:c r="R16" s="78" t="str">
-        <x:v>true</x:v>
+        <x:v>RuntimeCompatibility</x:v>
       </x:c>
       <x:c r="S16" s="78" t="str">
-        <x:v>RuntimeCompatibility</x:v>
-      </x:c>
-      <x:c r="T16" s="78" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="U16" s="78"/>
+      <x:c r="T16" s="78"/>
+      <x:c r="U16"/>
     </x:row>
     <x:row r="17" s="71" customFormat="1" ht="22" customHeight="1">
       <x:c r="A17" s="78" t="str">
@@ -15144,36 +15139,34 @@
         <x:v>1.00</x:v>
       </x:c>
       <x:c r="K17" s="78" t="str">
-        <x:v>1.00</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="L17" s="78" t="str">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="M17" s="78" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N17" s="78" t="str">
         <x:v>0</x:v>
-      </x:c>
-      <x:c r="N17" s="78" t="str">
-        <x:v>1</x:v>
       </x:c>
       <x:c r="O17" s="78" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="P17" s="78" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="Q17" s="78" t="str">
-        <x:v>1</x:v>
+        <x:v>true</x:v>
       </x:c>
       <x:c r="R17" s="78" t="str">
-        <x:v>true</x:v>
+        <x:v>RuntimeCompatibility</x:v>
       </x:c>
       <x:c r="S17" s="78" t="str">
-        <x:v>RuntimeCompatibility</x:v>
-      </x:c>
-      <x:c r="T17" s="78" t="str">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="U17" s="78"/>
+      <x:c r="T17" s="78"/>
+      <x:c r="U17"/>
     </x:row>
     <x:row r="18" s="71" customFormat="1" ht="22" customHeight="1">
       <x:c r="A18" s="78" t="str">
@@ -15207,36 +15200,34 @@
         <x:v>0.20</x:v>
       </x:c>
       <x:c r="K18" s="78" t="str">
-        <x:v>0.20</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="L18" s="78" t="str">
-        <x:v>1500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="M18" s="78" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N18" s="78" t="str">
         <x:v>0</x:v>
-      </x:c>
-      <x:c r="N18" s="78" t="str">
-        <x:v>1</x:v>
       </x:c>
       <x:c r="O18" s="78" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="P18" s="78" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="Q18" s="78" t="str">
-        <x:v>1</x:v>
+        <x:v>true</x:v>
       </x:c>
       <x:c r="R18" s="78" t="str">
-        <x:v>true</x:v>
+        <x:v>RuntimeCompatibility</x:v>
       </x:c>
       <x:c r="S18" s="78" t="str">
-        <x:v>RuntimeCompatibility</x:v>
-      </x:c>
-      <x:c r="T18" s="78" t="str">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="U18" s="78"/>
+      <x:c r="T18" s="78"/>
+      <x:c r="U18"/>
     </x:row>
     <x:row r="19" s="71" customFormat="1" ht="22" customHeight="1">
       <x:c r="A19" s="74"/>
@@ -15307,59 +15298,57 @@
         <x:v>DurationSeconds</x:v>
       </x:c>
       <x:c r="E24" s="29" t="str">
-        <x:v>PhysicalCoefficient</x:v>
+        <x:v>DamageCoefficient</x:v>
       </x:c>
       <x:c r="F24" s="29" t="str">
-        <x:v>ElementalCoefficient</x:v>
+        <x:v>RangeCm</x:v>
       </x:c>
       <x:c r="G24" s="29" t="str">
-        <x:v>RangeCm</x:v>
+        <x:v>ArcDegrees</x:v>
       </x:c>
       <x:c r="H24" s="29" t="str">
-        <x:v>ArcDegrees</x:v>
+        <x:v>ProjectileCount</x:v>
       </x:c>
       <x:c r="I24" s="29" t="str">
-        <x:v>ProjectileCount</x:v>
+        <x:v>ConcentrationDegrees</x:v>
       </x:c>
       <x:c r="J24" s="29" t="str">
-        <x:v>ConcentrationDegrees</x:v>
+        <x:v>ExplosionRadiusCm</x:v>
       </x:c>
       <x:c r="K24" s="29" t="str">
-        <x:v>ExplosionRadiusCm</x:v>
+        <x:v>MovementCm</x:v>
       </x:c>
       <x:c r="L24" s="29" t="str">
-        <x:v>MovementCm</x:v>
+        <x:v>Invulnerable</x:v>
       </x:c>
       <x:c r="M24" s="29" t="str">
-        <x:v>Invulnerable</x:v>
+        <x:v>BehaviorId</x:v>
       </x:c>
       <x:c r="N24" s="29" t="str">
-        <x:v>BehaviorId</x:v>
+        <x:v>FormulaId</x:v>
       </x:c>
       <x:c r="O24" s="29" t="str">
-        <x:v>FormulaId</x:v>
+        <x:v>ConditionId</x:v>
       </x:c>
       <x:c r="P24" s="29" t="str">
-        <x:v>ConditionId</x:v>
+        <x:v>Enabled</x:v>
       </x:c>
       <x:c r="Q24" s="29" t="str">
-        <x:v>Enabled</x:v>
+        <x:v>SourceSheet</x:v>
       </x:c>
       <x:c r="R24" s="29" t="str">
-        <x:v>SourceSheet</x:v>
+        <x:v>SourceRow</x:v>
       </x:c>
       <x:c r="S24" s="29" t="str">
-        <x:v>SourceRow</x:v>
+        <x:v>DisabledReason</x:v>
       </x:c>
       <x:c r="T24" s="29" t="str">
-        <x:v>DisabledReason</x:v>
+        <x:v>OuterRingStartFraction</x:v>
       </x:c>
       <x:c r="U24" t="str">
-        <x:v>OuterRingStartFraction</x:v>
-      </x:c>
-      <x:c r="V24" t="str">
         <x:v>OuterRingBonusMultiplier</x:v>
       </x:c>
+      <x:c r="V24"/>
     </x:row>
     <x:row r="25" s="71" customFormat="1" ht="22" customHeight="1">
       <x:c r="A25" s="78" t="str">
@@ -15378,13 +15367,13 @@
         <x:v>1.00</x:v>
       </x:c>
       <x:c r="F25" s="78" t="str">
-        <x:v>1.00</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G25" s="78" t="str">
-        <x:v>250</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="H25" s="78" t="str">
-        <x:v>180</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I25" s="78" t="str">
         <x:v>0</x:v>
@@ -15396,36 +15385,34 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L25" s="78" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="M25" s="78" t="str">
+        <x:v>Weapon.AttackStep</x:v>
+      </x:c>
+      <x:c r="N25" s="78" t="str">
+        <x:v>Weapon.DamageCoefficient</x:v>
+      </x:c>
+      <x:c r="O25" s="78" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="P25" s="78" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="Q25" s="78" t="str">
+        <x:v>武器体系W</x:v>
+      </x:c>
+      <x:c r="R25" s="78" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S25" s="78"/>
+      <x:c r="T25" s="78" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M25" s="78" t="str">
-        <x:v>false</x:v>
-      </x:c>
-      <x:c r="N25" s="78" t="str">
-        <x:v>Weapon.AttackStep</x:v>
-      </x:c>
-      <x:c r="O25" s="78" t="str">
-        <x:v>Weapon.PhysicalOrElementalCoefficient</x:v>
-      </x:c>
-      <x:c r="P25" s="78" t="str">
-        <x:v>None</x:v>
-      </x:c>
-      <x:c r="Q25" s="78" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="R25" s="78" t="str">
-        <x:v>武器体系W</x:v>
-      </x:c>
-      <x:c r="S25" s="78" t="str">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="T25" s="78"/>
-      <x:c r="U25" t="str" s="81">
+      <x:c r="U25" s="81" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="V25" t="str" s="81">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="V25"/>
     </x:row>
     <x:row r="26" s="71" customFormat="1" ht="22" customHeight="1">
       <x:c r="A26" s="78" t="str">
@@ -15444,13 +15431,13 @@
         <x:v>1.00</x:v>
       </x:c>
       <x:c r="F26" s="78" t="str">
-        <x:v>1.00</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G26" s="78" t="str">
-        <x:v>250</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="H26" s="78" t="str">
-        <x:v>180</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I26" s="78" t="str">
         <x:v>0</x:v>
@@ -15462,36 +15449,34 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L26" s="78" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="M26" s="78" t="str">
+        <x:v>Weapon.AttackStep</x:v>
+      </x:c>
+      <x:c r="N26" s="78" t="str">
+        <x:v>Weapon.DamageCoefficient</x:v>
+      </x:c>
+      <x:c r="O26" s="78" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="P26" s="78" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="Q26" s="78" t="str">
+        <x:v>武器体系W</x:v>
+      </x:c>
+      <x:c r="R26" s="78" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S26" s="78"/>
+      <x:c r="T26" s="78" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M26" s="78" t="str">
-        <x:v>false</x:v>
-      </x:c>
-      <x:c r="N26" s="78" t="str">
-        <x:v>Weapon.AttackStep</x:v>
-      </x:c>
-      <x:c r="O26" s="78" t="str">
-        <x:v>Weapon.PhysicalOrElementalCoefficient</x:v>
-      </x:c>
-      <x:c r="P26" s="78" t="str">
-        <x:v>None</x:v>
-      </x:c>
-      <x:c r="Q26" s="78" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="R26" s="78" t="str">
-        <x:v>武器体系W</x:v>
-      </x:c>
-      <x:c r="S26" s="78" t="str">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="T26" s="78"/>
-      <x:c r="U26" t="str" s="81">
+      <x:c r="U26" s="81" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="V26" t="str" s="81">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="V26"/>
     </x:row>
     <x:row r="27" s="71" customFormat="1" ht="22" customHeight="1">
       <x:c r="A27" s="78" t="str">
@@ -15510,13 +15495,13 @@
         <x:v>0.60</x:v>
       </x:c>
       <x:c r="F27" s="78" t="str">
-        <x:v>0.60</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="G27" s="78" t="str">
-        <x:v>150</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="H27" s="78" t="str">
-        <x:v>360</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I27" s="78" t="str">
         <x:v>0</x:v>
@@ -15528,36 +15513,34 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L27" s="78" t="str">
-        <x:v>0</x:v>
+        <x:v>false</x:v>
       </x:c>
       <x:c r="M27" s="78" t="str">
-        <x:v>false</x:v>
+        <x:v>Weapon.AttackStep</x:v>
       </x:c>
       <x:c r="N27" s="78" t="str">
-        <x:v>Weapon.AttackStep</x:v>
+        <x:v>Weapon.DamageCoefficient</x:v>
       </x:c>
       <x:c r="O27" s="78" t="str">
-        <x:v>Weapon.PhysicalOrElementalCoefficient</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="P27" s="78" t="str">
-        <x:v>None</x:v>
+        <x:v>true</x:v>
       </x:c>
       <x:c r="Q27" s="78" t="str">
-        <x:v>true</x:v>
+        <x:v>武器体系W</x:v>
       </x:c>
       <x:c r="R27" s="78" t="str">
-        <x:v>武器体系W</x:v>
-      </x:c>
-      <x:c r="S27" s="78" t="str">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="T27" s="78"/>
-      <x:c r="U27" t="str" s="81">
+      <x:c r="S27" s="78"/>
+      <x:c r="T27" s="78" t="str">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="V27" t="str" s="81">
+      <x:c r="U27" s="81" t="str">
         <x:v>0.4</x:v>
       </x:c>
+      <x:c r="V27"/>
     </x:row>
     <x:row r="28" s="71" customFormat="1" ht="22" customHeight="1">
       <x:c r="A28" s="78" t="str">
@@ -15576,16 +15559,16 @@
         <x:v>1.00</x:v>
       </x:c>
       <x:c r="F28" s="78" t="str">
-        <x:v>1.00</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G28" s="78" t="str">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H28" s="78" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I28" s="78" t="str">
         <x:v>0</x:v>
-      </x:c>
-      <x:c r="I28" s="78" t="str">
-        <x:v>1</x:v>
       </x:c>
       <x:c r="J28" s="78" t="str">
         <x:v>0</x:v>
@@ -15594,36 +15577,34 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L28" s="78" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="M28" s="78" t="str">
+        <x:v>Weapon.AttackStep</x:v>
+      </x:c>
+      <x:c r="N28" s="78" t="str">
+        <x:v>Weapon.DamageCoefficient</x:v>
+      </x:c>
+      <x:c r="O28" s="78" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="P28" s="78" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="Q28" s="78" t="str">
+        <x:v>武器体系W</x:v>
+      </x:c>
+      <x:c r="R28" s="78" t="str">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="S28" s="78"/>
+      <x:c r="T28" s="78" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M28" s="78" t="str">
-        <x:v>false</x:v>
-      </x:c>
-      <x:c r="N28" s="78" t="str">
-        <x:v>Weapon.AttackStep</x:v>
-      </x:c>
-      <x:c r="O28" s="78" t="str">
-        <x:v>Weapon.PhysicalOrElementalCoefficient</x:v>
-      </x:c>
-      <x:c r="P28" s="78" t="str">
-        <x:v>None</x:v>
-      </x:c>
-      <x:c r="Q28" s="78" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="R28" s="78" t="str">
-        <x:v>武器体系W</x:v>
-      </x:c>
-      <x:c r="S28" s="78" t="str">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="T28" s="78"/>
-      <x:c r="U28" t="str" s="81">
+      <x:c r="U28" s="81" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="V28" t="str" s="81">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="V28"/>
     </x:row>
     <x:row r="29" s="71" customFormat="1" ht="22" customHeight="1">
       <x:c r="A29" s="78" t="str">
@@ -15642,16 +15623,16 @@
         <x:v>0.20</x:v>
       </x:c>
       <x:c r="F29" s="78" t="str">
-        <x:v>0.20</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G29" s="78" t="str">
-        <x:v>1500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H29" s="78" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I29" s="78" t="str">
         <x:v>0</x:v>
-      </x:c>
-      <x:c r="I29" s="78" t="str">
-        <x:v>1</x:v>
       </x:c>
       <x:c r="J29" s="78" t="str">
         <x:v>0</x:v>
@@ -15660,36 +15641,34 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L29" s="78" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="M29" s="78" t="str">
+        <x:v>Weapon.AttackStep</x:v>
+      </x:c>
+      <x:c r="N29" s="78" t="str">
+        <x:v>Weapon.DamageCoefficient</x:v>
+      </x:c>
+      <x:c r="O29" s="78" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="P29" s="78" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="Q29" s="78" t="str">
+        <x:v>武器体系W</x:v>
+      </x:c>
+      <x:c r="R29" s="78" t="str">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="S29" s="78"/>
+      <x:c r="T29" s="78" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M29" s="78" t="str">
-        <x:v>false</x:v>
-      </x:c>
-      <x:c r="N29" s="78" t="str">
-        <x:v>Weapon.AttackStep</x:v>
-      </x:c>
-      <x:c r="O29" s="78" t="str">
-        <x:v>Weapon.PhysicalOrElementalCoefficient</x:v>
-      </x:c>
-      <x:c r="P29" s="78" t="str">
-        <x:v>None</x:v>
-      </x:c>
-      <x:c r="Q29" s="78" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="R29" s="78" t="str">
-        <x:v>武器体系W</x:v>
-      </x:c>
-      <x:c r="S29" s="78" t="str">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="T29" s="78"/>
-      <x:c r="U29" t="str" s="81">
+      <x:c r="U29" s="81" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="V29" t="str" s="81">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="V29"/>
     </x:row>
     <x:row r="30" s="71" customFormat="1" ht="22" customHeight="1">
       <x:c r="A30" s="74"/>
@@ -15890,7 +15869,7 @@
       <x:c r="T38" s="68" t="n"/>
     </x:row>
   </x:sheetData>
-  <sheetProtection xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="0" sort="0"/>
+  <x:sheetProtection xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="0" sort="0"/>
   <x:mergeCells>
     <x:mergeCell ref="A1:U1"/>
     <x:mergeCell ref="A23:D23"/>
@@ -15925,33 +15904,33 @@
     <x:dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="H15:H20">
       <x:formula1>=DV_Logic_Weapons_AttackPatternId</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="R15:R20">
-      <x:formula1>=DV_Logic_Weapons_Enabled</x:formula1>
-    </x:dataValidation>
     <x:dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="B25:B38">
       <x:formula1>=DV_Logic_AttackSteps_AttackPatternId</x:formula1>
     </x:dataValidation>
+    <x:dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="Q15:Q20">
+      <x:formula1>DV_Logic_Weapons_Enabled</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="L25:L38">
+      <x:formula1>DV_Logic_AttackSteps_Invulnerable</x:formula1>
+    </x:dataValidation>
     <x:dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="M25:M38">
-      <x:formula1>=DV_Logic_AttackSteps_Invulnerable</x:formula1>
+      <x:formula1>DV_Logic_AttackSteps_BehaviorId</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="N25:N38">
-      <x:formula1>=DV_Logic_AttackSteps_BehaviorId</x:formula1>
+      <x:formula1>DV_Logic_AttackSteps_FormulaId</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="O25:O38">
-      <x:formula1>=DV_Logic_AttackSteps_FormulaId</x:formula1>
+      <x:formula1>DV_Logic_AttackSteps_ConditionId</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="P25:P38">
-      <x:formula1>=DV_Logic_AttackSteps_ConditionId</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="Q25:Q38">
-      <x:formula1>=DV_Logic_AttackSteps_Enabled</x:formula1>
+      <x:formula1>DV_Logic_AttackSteps_Enabled</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="3">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R61ec9af47c1a43ea"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reabcc7b4d6a14fb7"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8c296967190c4860"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d465ecbf8f64326"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R172dea53d22843c5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb52f3166f6894dc8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17610,7 +17589,7 @@
         <x:v>StatModifier</x:v>
       </x:c>
       <x:c r="W53" s="78" t="str">
-        <x:v>PhysicalCoefficient</x:v>
+        <x:v>DamageCoefficient</x:v>
       </x:c>
       <x:c r="X53" s="78" t="str">
         <x:v>Multiply</x:v>
@@ -17701,13 +17680,13 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="R54" s="78" t="str">
-        <x:v>PE_BOW_HASTE_BOWSTRING_3</x:v>
+        <x:v>PE_BOW_HEAVY_BOWSTRING_1</x:v>
       </x:c>
       <x:c r="S54" s="78" t="str">
-        <x:v>P_BOW_HASTE_BOWSTRING</x:v>
+        <x:v>P_BOW_HEAVY_BOWSTRING</x:v>
       </x:c>
       <x:c r="T54" s="78" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="U54" s="78" t="str">
         <x:v>OnEquip</x:v>
@@ -17716,13 +17695,13 @@
         <x:v>StatModifier</x:v>
       </x:c>
       <x:c r="W54" s="78" t="str">
-        <x:v>ElementalCoefficient</x:v>
+        <x:v>AttackSpeed</x:v>
       </x:c>
       <x:c r="X54" s="78" t="str">
         <x:v>Multiply</x:v>
       </x:c>
       <x:c r="Y54" s="78" t="n">
-        <x:v>0.6</x:v>
+        <x:v>0.7</x:v>
       </x:c>
       <x:c r="Z54" s="78" t="str">
         <x:v>Part.StatModifier</x:v>
@@ -17756,7 +17735,7 @@
         <x:v>武器插槽C</x:v>
       </x:c>
       <x:c r="AK54" s="78" t="n">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="55" s="71" customFormat="1" ht="22" customHeight="1">
@@ -17807,13 +17786,13 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="R55" s="78" t="str">
-        <x:v>PE_BOW_HEAVY_BOWSTRING_1</x:v>
+        <x:v>PE_BOW_HEAVY_BOWSTRING_2</x:v>
       </x:c>
       <x:c r="S55" s="78" t="str">
         <x:v>P_BOW_HEAVY_BOWSTRING</x:v>
       </x:c>
       <x:c r="T55" s="78" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="U55" s="78" t="str">
         <x:v>OnEquip</x:v>
@@ -17822,13 +17801,13 @@
         <x:v>StatModifier</x:v>
       </x:c>
       <x:c r="W55" s="78" t="str">
-        <x:v>AttackSpeed</x:v>
+        <x:v>DamageCoefficient</x:v>
       </x:c>
       <x:c r="X55" s="78" t="str">
         <x:v>Multiply</x:v>
       </x:c>
       <x:c r="Y55" s="78" t="n">
-        <x:v>0.7</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="Z55" s="78" t="str">
         <x:v>Part.StatModifier</x:v>
@@ -17913,13 +17892,13 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="R56" s="78" t="str">
-        <x:v>PE_BOW_HEAVY_BOWSTRING_2</x:v>
+        <x:v>PE_SCYTHE_HASTE_ROTARYBLADE_1</x:v>
       </x:c>
       <x:c r="S56" s="78" t="str">
-        <x:v>P_BOW_HEAVY_BOWSTRING</x:v>
+        <x:v>P_SCYTHE_HASTE_ROTARYBLADE</x:v>
       </x:c>
       <x:c r="T56" s="78" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="U56" s="78" t="str">
         <x:v>OnEquip</x:v>
@@ -17928,13 +17907,13 @@
         <x:v>StatModifier</x:v>
       </x:c>
       <x:c r="W56" s="78" t="str">
-        <x:v>PhysicalCoefficient</x:v>
+        <x:v>AttackSpeed</x:v>
       </x:c>
       <x:c r="X56" s="78" t="str">
         <x:v>Multiply</x:v>
       </x:c>
       <x:c r="Y56" s="78" t="n">
-        <x:v>1.5</x:v>
+        <x:v>1.4</x:v>
       </x:c>
       <x:c r="Z56" s="78" t="str">
         <x:v>Part.StatModifier</x:v>
@@ -17968,7 +17947,7 @@
         <x:v>武器插槽C</x:v>
       </x:c>
       <x:c r="AK56" s="78" t="n">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="57" s="71" customFormat="1" ht="22" customHeight="1">
@@ -18019,13 +17998,13 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="R57" s="78" t="str">
-        <x:v>PE_BOW_HEAVY_BOWSTRING_3</x:v>
+        <x:v>PE_SCYTHE_HASTE_ROTARYBLADE_2</x:v>
       </x:c>
       <x:c r="S57" s="78" t="str">
-        <x:v>P_BOW_HEAVY_BOWSTRING</x:v>
+        <x:v>P_SCYTHE_HASTE_ROTARYBLADE</x:v>
       </x:c>
       <x:c r="T57" s="78" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="U57" s="78" t="str">
         <x:v>OnEquip</x:v>
@@ -18034,13 +18013,13 @@
         <x:v>StatModifier</x:v>
       </x:c>
       <x:c r="W57" s="78" t="str">
-        <x:v>ElementalCoefficient</x:v>
+        <x:v>AttackRange</x:v>
       </x:c>
       <x:c r="X57" s="78" t="str">
         <x:v>Multiply</x:v>
       </x:c>
       <x:c r="Y57" s="78" t="n">
-        <x:v>1.5</x:v>
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="Z57" s="78" t="str">
         <x:v>Part.StatModifier</x:v>
@@ -18074,7 +18053,7 @@
         <x:v>武器插槽C</x:v>
       </x:c>
       <x:c r="AK57" s="78" t="n">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="58" s="71" customFormat="1" ht="22" customHeight="1">
@@ -18125,10 +18104,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="R58" s="78" t="str">
-        <x:v>PE_SCYTHE_HASTE_ROTARYBLADE_1</x:v>
+        <x:v>PE_LONGSWORD_NARROWWIDE_SWORDBLADE_1</x:v>
       </x:c>
       <x:c r="S58" s="78" t="str">
-        <x:v>P_SCYTHE_HASTE_ROTARYBLADE</x:v>
+        <x:v>P_LONGSWORD_NARROWWIDE_SWORDBLADE</x:v>
       </x:c>
       <x:c r="T58" s="78" t="n">
         <x:v>1</x:v>
@@ -18140,13 +18119,13 @@
         <x:v>StatModifier</x:v>
       </x:c>
       <x:c r="W58" s="78" t="str">
-        <x:v>AttackSpeed</x:v>
+        <x:v>AttackArc</x:v>
       </x:c>
       <x:c r="X58" s="78" t="str">
-        <x:v>Multiply</x:v>
+        <x:v>Override</x:v>
       </x:c>
       <x:c r="Y58" s="78" t="n">
-        <x:v>1.4</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="Z58" s="78" t="str">
         <x:v>Part.StatModifier</x:v>
@@ -18180,7 +18159,7 @@
         <x:v>武器插槽C</x:v>
       </x:c>
       <x:c r="AK58" s="78" t="n">
-        <x:v>28</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="59" s="71" customFormat="1" ht="22" customHeight="1">
@@ -18231,10 +18210,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="R59" s="78" t="str">
-        <x:v>PE_SCYTHE_HASTE_ROTARYBLADE_2</x:v>
+        <x:v>PE_LONGSWORD_NARROWWIDE_SWORDBLADE_2</x:v>
       </x:c>
       <x:c r="S59" s="78" t="str">
-        <x:v>P_SCYTHE_HASTE_ROTARYBLADE</x:v>
+        <x:v>P_LONGSWORD_NARROWWIDE_SWORDBLADE</x:v>
       </x:c>
       <x:c r="T59" s="78" t="n">
         <x:v>2</x:v>
@@ -18252,7 +18231,7 @@
         <x:v>Multiply</x:v>
       </x:c>
       <x:c r="Y59" s="78" t="n">
-        <x:v>0.8</x:v>
+        <x:v>1.3</x:v>
       </x:c>
       <x:c r="Z59" s="78" t="str">
         <x:v>Part.StatModifier</x:v>
@@ -18286,7 +18265,7 @@
         <x:v>武器插槽C</x:v>
       </x:c>
       <x:c r="AK59" s="78" t="n">
-        <x:v>28</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="60" s="71" customFormat="1" ht="30" customHeight="1">
@@ -18337,10 +18316,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="R60" s="78" t="str">
-        <x:v>PE_LONGSWORD_NARROWWIDE_SWORDBLADE_1</x:v>
+        <x:v>PE_LONGSWORD_SLOWWIDE_SWORDBLADE_1</x:v>
       </x:c>
       <x:c r="S60" s="78" t="str">
-        <x:v>P_LONGSWORD_NARROWWIDE_SWORDBLADE</x:v>
+        <x:v>P_LONGSWORD_SLOWWIDE_SWORDBLADE</x:v>
       </x:c>
       <x:c r="T60" s="78" t="n">
         <x:v>1</x:v>
@@ -18352,13 +18331,13 @@
         <x:v>StatModifier</x:v>
       </x:c>
       <x:c r="W60" s="78" t="str">
-        <x:v>AttackArc</x:v>
+        <x:v>AttackSpeed</x:v>
       </x:c>
       <x:c r="X60" s="78" t="str">
-        <x:v>Override</x:v>
+        <x:v>Multiply</x:v>
       </x:c>
       <x:c r="Y60" s="78" t="n">
-        <x:v>120</x:v>
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="Z60" s="78" t="str">
         <x:v>Part.StatModifier</x:v>
@@ -18392,7 +18371,7 @@
         <x:v>武器插槽C</x:v>
       </x:c>
       <x:c r="AK60" s="78" t="n">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="61" s="71" customFormat="1" ht="22" customHeight="1">
@@ -18443,10 +18422,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="R61" s="78" t="str">
-        <x:v>PE_LONGSWORD_NARROWWIDE_SWORDBLADE_2</x:v>
+        <x:v>PE_LONGSWORD_SLOWWIDE_SWORDBLADE_2</x:v>
       </x:c>
       <x:c r="S61" s="78" t="str">
-        <x:v>P_LONGSWORD_NARROWWIDE_SWORDBLADE</x:v>
+        <x:v>P_LONGSWORD_SLOWWIDE_SWORDBLADE</x:v>
       </x:c>
       <x:c r="T61" s="78" t="n">
         <x:v>2</x:v>
@@ -18498,7 +18477,7 @@
         <x:v>武器插槽C</x:v>
       </x:c>
       <x:c r="AK61" s="78" t="n">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="62" s="71" customFormat="1" ht="22" customHeight="1">
@@ -18549,31 +18528,31 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="R62" s="78" t="str">
-        <x:v>PE_LONGSWORD_SLOWWIDE_SWORDBLADE_1</x:v>
+        <x:v>PE_LONGSWORD_KILLHEAL_SWORDBLADE_1</x:v>
       </x:c>
       <x:c r="S62" s="78" t="str">
-        <x:v>P_LONGSWORD_SLOWWIDE_SWORDBLADE</x:v>
+        <x:v>P_LONGSWORD_KILLHEAL_SWORDBLADE</x:v>
       </x:c>
       <x:c r="T62" s="78" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U62" s="78" t="str">
-        <x:v>OnEquip</x:v>
+        <x:v>OnKill</x:v>
       </x:c>
       <x:c r="V62" s="78" t="str">
-        <x:v>StatModifier</x:v>
+        <x:v>UniqueBehavior</x:v>
       </x:c>
       <x:c r="W62" s="78" t="str">
-        <x:v>AttackSpeed</x:v>
+        <x:v>OnKill</x:v>
       </x:c>
       <x:c r="X62" s="78" t="str">
-        <x:v>Multiply</x:v>
+        <x:v>Add</x:v>
       </x:c>
       <x:c r="Y62" s="78" t="n">
-        <x:v>0.8</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="Z62" s="78" t="str">
-        <x:v>Part.StatModifier</x:v>
+        <x:v>Part.OnKillHealPercent</x:v>
       </x:c>
       <x:c r="AA62" s="78" t="str">
         <x:v>None</x:v>
@@ -18582,10 +18561,10 @@
         <x:v>None</x:v>
       </x:c>
       <x:c r="AC62" s="78" t="str">
-        <x:v>None</x:v>
+        <x:v>HealMaxHpPercent</x:v>
       </x:c>
       <x:c r="AD62" s="78" t="n">
-        <x:v>0</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="AE62" s="78" t="n">
         <x:v>0</x:v>
@@ -18604,7 +18583,7 @@
         <x:v>武器插槽C</x:v>
       </x:c>
       <x:c r="AK62" s="78" t="n">
-        <x:v>37</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="63" s="71" customFormat="1" ht="22" customHeight="1">
@@ -18655,13 +18634,13 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="R63" s="78" t="str">
-        <x:v>PE_LONGSWORD_SLOWWIDE_SWORDBLADE_2</x:v>
+        <x:v>PE_LONGSWORD_HASTE_GRIP_1</x:v>
       </x:c>
       <x:c r="S63" s="78" t="str">
-        <x:v>P_LONGSWORD_SLOWWIDE_SWORDBLADE</x:v>
+        <x:v>P_LONGSWORD_HASTE_GRIP</x:v>
       </x:c>
       <x:c r="T63" s="78" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="U63" s="78" t="str">
         <x:v>OnEquip</x:v>
@@ -18670,13 +18649,13 @@
         <x:v>StatModifier</x:v>
       </x:c>
       <x:c r="W63" s="78" t="str">
-        <x:v>AttackRange</x:v>
+        <x:v>AttackSpeed</x:v>
       </x:c>
       <x:c r="X63" s="78" t="str">
         <x:v>Multiply</x:v>
       </x:c>
       <x:c r="Y63" s="78" t="n">
-        <x:v>1.3</x:v>
+        <x:v>1.2</x:v>
       </x:c>
       <x:c r="Z63" s="78" t="str">
         <x:v>Part.StatModifier</x:v>
@@ -18710,7 +18689,7 @@
         <x:v>武器插槽C</x:v>
       </x:c>
       <x:c r="AK63" s="78" t="n">
-        <x:v>37</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="64" s="71" customFormat="1" ht="22" customHeight="1">
@@ -18761,31 +18740,31 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="R64" s="78" t="str">
-        <x:v>PE_LONGSWORD_KILLHEAL_SWORDBLADE_1</x:v>
+        <x:v>PE_LONGSWORD_HEAVY_GRIP_1</x:v>
       </x:c>
       <x:c r="S64" s="78" t="str">
-        <x:v>P_LONGSWORD_KILLHEAL_SWORDBLADE</x:v>
+        <x:v>P_LONGSWORD_HEAVY_GRIP</x:v>
       </x:c>
       <x:c r="T64" s="78" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U64" s="78" t="str">
-        <x:v>OnKill</x:v>
+        <x:v>OnEquip</x:v>
       </x:c>
       <x:c r="V64" s="78" t="str">
-        <x:v>UniqueBehavior</x:v>
+        <x:v>StatModifier</x:v>
       </x:c>
       <x:c r="W64" s="78" t="str">
-        <x:v>OnKill</x:v>
+        <x:v>AttackSpeed</x:v>
       </x:c>
       <x:c r="X64" s="78" t="str">
-        <x:v>Add</x:v>
+        <x:v>Multiply</x:v>
       </x:c>
       <x:c r="Y64" s="78" t="n">
-        <x:v>0.05</x:v>
+        <x:v>0.7</x:v>
       </x:c>
       <x:c r="Z64" s="78" t="str">
-        <x:v>Part.OnKillHealPercent</x:v>
+        <x:v>Part.StatModifier</x:v>
       </x:c>
       <x:c r="AA64" s="78" t="str">
         <x:v>None</x:v>
@@ -18794,10 +18773,10 @@
         <x:v>None</x:v>
       </x:c>
       <x:c r="AC64" s="78" t="str">
-        <x:v>HealMaxHpPercent</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="AD64" s="78" t="n">
-        <x:v>0.05</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AE64" s="78" t="n">
         <x:v>0</x:v>
@@ -18816,7 +18795,7 @@
         <x:v>武器插槽C</x:v>
       </x:c>
       <x:c r="AK64" s="78" t="n">
-        <x:v>39</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="65" s="71" customFormat="1" ht="22" customHeight="1">
@@ -18867,13 +18846,13 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="R65" s="78" t="str">
-        <x:v>PE_LONGSWORD_HASTE_GRIP_1</x:v>
+        <x:v>PE_LONGSWORD_HEAVY_GRIP_2</x:v>
       </x:c>
       <x:c r="S65" s="78" t="str">
-        <x:v>P_LONGSWORD_HASTE_GRIP</x:v>
+        <x:v>P_LONGSWORD_HEAVY_GRIP</x:v>
       </x:c>
       <x:c r="T65" s="78" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="U65" s="78" t="str">
         <x:v>OnEquip</x:v>
@@ -18882,13 +18861,13 @@
         <x:v>StatModifier</x:v>
       </x:c>
       <x:c r="W65" s="78" t="str">
-        <x:v>AttackSpeed</x:v>
+        <x:v>DamageCoefficient</x:v>
       </x:c>
       <x:c r="X65" s="78" t="str">
         <x:v>Multiply</x:v>
       </x:c>
       <x:c r="Y65" s="78" t="n">
-        <x:v>1.2</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="Z65" s="78" t="str">
         <x:v>Part.StatModifier</x:v>
@@ -18922,7 +18901,7 @@
         <x:v>武器插槽C</x:v>
       </x:c>
       <x:c r="AK65" s="78" t="n">
-        <x:v>43</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="66" s="71" customFormat="1" ht="22" customHeight="1">
@@ -18973,10 +18952,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="R66" s="78" t="str">
-        <x:v>PE_LONGSWORD_HEAVY_GRIP_1</x:v>
+        <x:v>PE_GUN_TRIPLESPREAD_MUZZLE_1</x:v>
       </x:c>
       <x:c r="S66" s="78" t="str">
-        <x:v>P_LONGSWORD_HEAVY_GRIP</x:v>
+        <x:v>P_GUN_TRIPLESPREAD_MUZZLE</x:v>
       </x:c>
       <x:c r="T66" s="78" t="n">
         <x:v>1</x:v>
@@ -18988,13 +18967,13 @@
         <x:v>StatModifier</x:v>
       </x:c>
       <x:c r="W66" s="78" t="str">
-        <x:v>AttackSpeed</x:v>
+        <x:v>ProjectileCount</x:v>
       </x:c>
       <x:c r="X66" s="78" t="str">
-        <x:v>Multiply</x:v>
+        <x:v>Override</x:v>
       </x:c>
       <x:c r="Y66" s="78" t="n">
-        <x:v>0.7</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="Z66" s="78" t="str">
         <x:v>Part.StatModifier</x:v>
@@ -19028,7 +19007,7 @@
         <x:v>武器插槽C</x:v>
       </x:c>
       <x:c r="AK66" s="78" t="n">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="67" s="71" customFormat="1" ht="22" customHeight="1">
@@ -19079,10 +19058,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="R67" s="78" t="str">
-        <x:v>PE_LONGSWORD_HEAVY_GRIP_2</x:v>
+        <x:v>PE_GUN_TRIPLESPREAD_MUZZLE_2</x:v>
       </x:c>
       <x:c r="S67" s="78" t="str">
-        <x:v>P_LONGSWORD_HEAVY_GRIP</x:v>
+        <x:v>P_GUN_TRIPLESPREAD_MUZZLE</x:v>
       </x:c>
       <x:c r="T67" s="78" t="n">
         <x:v>2</x:v>
@@ -19094,13 +19073,13 @@
         <x:v>StatModifier</x:v>
       </x:c>
       <x:c r="W67" s="78" t="str">
-        <x:v>PhysicalCoefficient</x:v>
+        <x:v>ConcentrationDegrees</x:v>
       </x:c>
       <x:c r="X67" s="78" t="str">
-        <x:v>Multiply</x:v>
+        <x:v>Override</x:v>
       </x:c>
       <x:c r="Y67" s="78" t="n">
-        <x:v>1.5</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="Z67" s="78" t="str">
         <x:v>Part.StatModifier</x:v>
@@ -19134,7 +19113,7 @@
         <x:v>武器插槽C</x:v>
       </x:c>
       <x:c r="AK67" s="78" t="n">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="68" s="71" customFormat="1" ht="22" customHeight="1">
@@ -19185,31 +19164,31 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="R68" s="78" t="str">
-        <x:v>PE_LONGSWORD_HEAVY_GRIP_3</x:v>
+        <x:v>PE_BOW_SPLIT_ARROWHEAD_1</x:v>
       </x:c>
       <x:c r="S68" s="78" t="str">
-        <x:v>P_LONGSWORD_HEAVY_GRIP</x:v>
-      </x:c>
-      <x:c r="T68" s="78" t="n">
-        <x:v>3</x:v>
+        <x:v>P_BOW_SPLIT_ARROWHEAD</x:v>
+      </x:c>
+      <x:c r="T68" s="78" t="str">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="U68" s="78" t="str">
-        <x:v>OnEquip</x:v>
+        <x:v>OnHit</x:v>
       </x:c>
       <x:c r="V68" s="78" t="str">
-        <x:v>StatModifier</x:v>
+        <x:v>UniqueBehavior</x:v>
       </x:c>
       <x:c r="W68" s="78" t="str">
-        <x:v>ElementalCoefficient</x:v>
+        <x:v>RuntimeBehavior</x:v>
       </x:c>
       <x:c r="X68" s="78" t="str">
         <x:v>Multiply</x:v>
       </x:c>
-      <x:c r="Y68" s="78" t="n">
-        <x:v>1.5</x:v>
+      <x:c r="Y68" s="78" t="str">
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="Z68" s="78" t="str">
-        <x:v>Part.StatModifier</x:v>
+        <x:v>Part.ProjectileSplitOnHit</x:v>
       </x:c>
       <x:c r="AA68" s="78" t="str">
         <x:v>None</x:v>
@@ -19218,15 +19197,15 @@
         <x:v>None</x:v>
       </x:c>
       <x:c r="AC68" s="78" t="str">
-        <x:v>None</x:v>
-      </x:c>
-      <x:c r="AD68" s="78" t="n">
+        <x:v>MaxChildren</x:v>
+      </x:c>
+      <x:c r="AD68" s="78" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AE68" s="78" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AE68" s="78" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AF68" s="78" t="n">
+      <x:c r="AF68" s="78" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AG68" s="78" t="str">
@@ -19239,8 +19218,8 @@
       <x:c r="AJ68" s="78" t="str">
         <x:v>武器插槽C</x:v>
       </x:c>
-      <x:c r="AK68" s="78" t="n">
-        <x:v>47</x:v>
+      <x:c r="AK68" s="78" t="str">
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="69" s="71" customFormat="1" ht="22" customHeight="1">
@@ -19291,12 +19270,12 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="R69" s="78" t="str">
-        <x:v>PE_GUN_TRIPLESPREAD_MUZZLE_1</x:v>
+        <x:v>PE_BOW_EXPLOSIVE_ARROWHEAD_1</x:v>
       </x:c>
       <x:c r="S69" s="78" t="str">
-        <x:v>P_GUN_TRIPLESPREAD_MUZZLE</x:v>
-      </x:c>
-      <x:c r="T69" s="78" t="n">
+        <x:v>P_BOW_EXPLOSIVE_ARROWHEAD</x:v>
+      </x:c>
+      <x:c r="T69" s="78" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U69" s="78" t="str">
@@ -19306,13 +19285,13 @@
         <x:v>StatModifier</x:v>
       </x:c>
       <x:c r="W69" s="78" t="str">
-        <x:v>ProjectileCount</x:v>
+        <x:v>ExplosionRadius</x:v>
       </x:c>
       <x:c r="X69" s="78" t="str">
         <x:v>Override</x:v>
       </x:c>
-      <x:c r="Y69" s="78" t="n">
-        <x:v>3</x:v>
+      <x:c r="Y69" s="78" t="str">
+        <x:v>100</x:v>
       </x:c>
       <x:c r="Z69" s="78" t="str">
         <x:v>Part.StatModifier</x:v>
@@ -19326,13 +19305,13 @@
       <x:c r="AC69" s="78" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="AD69" s="78" t="n">
+      <x:c r="AD69" s="78" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AE69" s="78" t="n">
+      <x:c r="AE69" s="78" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AF69" s="78" t="n">
+      <x:c r="AF69" s="78" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AG69" s="78" t="str">
@@ -19345,8 +19324,8 @@
       <x:c r="AJ69" s="78" t="str">
         <x:v>武器插槽C</x:v>
       </x:c>
-      <x:c r="AK69" s="78" t="n">
-        <x:v>48</x:v>
+      <x:c r="AK69" s="78" t="str">
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="70" s="71" customFormat="1" ht="22" customHeight="1">
@@ -19397,31 +19376,31 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="R70" s="78" t="str">
-        <x:v>PE_GUN_TRIPLESPREAD_MUZZLE_2</x:v>
+        <x:v>PE_BOW_PIERCING_ARROWHEAD_1</x:v>
       </x:c>
       <x:c r="S70" s="78" t="str">
-        <x:v>P_GUN_TRIPLESPREAD_MUZZLE</x:v>
-      </x:c>
-      <x:c r="T70" s="78" t="n">
-        <x:v>2</x:v>
+        <x:v>P_BOW_PIERCING_ARROWHEAD</x:v>
+      </x:c>
+      <x:c r="T70" s="78" t="str">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="U70" s="78" t="str">
-        <x:v>OnEquip</x:v>
+        <x:v>OnCriticalHit</x:v>
       </x:c>
       <x:c r="V70" s="78" t="str">
-        <x:v>StatModifier</x:v>
+        <x:v>UniqueBehavior</x:v>
       </x:c>
       <x:c r="W70" s="78" t="str">
-        <x:v>ConcentrationDegrees</x:v>
+        <x:v>RuntimeBehavior</x:v>
       </x:c>
       <x:c r="X70" s="78" t="str">
         <x:v>Override</x:v>
       </x:c>
-      <x:c r="Y70" s="78" t="n">
-        <x:v>60</x:v>
+      <x:c r="Y70" s="78" t="str">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="Z70" s="78" t="str">
-        <x:v>Part.StatModifier</x:v>
+        <x:v>Part.ProjectilePierceOnCritical</x:v>
       </x:c>
       <x:c r="AA70" s="78" t="str">
         <x:v>None</x:v>
@@ -19432,13 +19411,13 @@
       <x:c r="AC70" s="78" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="AD70" s="78" t="n">
+      <x:c r="AD70" s="78" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AE70" s="78" t="n">
+      <x:c r="AE70" s="78" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AF70" s="78" t="n">
+      <x:c r="AF70" s="78" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AG70" s="78" t="str">
@@ -19451,8 +19430,8 @@
       <x:c r="AJ70" s="78" t="str">
         <x:v>武器插槽C</x:v>
       </x:c>
-      <x:c r="AK70" s="78" t="n">
-        <x:v>48</x:v>
+      <x:c r="AK70" s="78" t="str">
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="71" s="71" customFormat="1" ht="22" customHeight="1">
@@ -19507,16 +19486,16 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="R71" s="78" t="str">
-        <x:v>PE_BOW_SPLIT_ARROWHEAD_1</x:v>
+        <x:v>PE_BOW_CRITBLEED_ARROWHEAD_1</x:v>
       </x:c>
       <x:c r="S71" s="78" t="str">
-        <x:v>P_BOW_SPLIT_ARROWHEAD</x:v>
+        <x:v>P_BOW_CRITBLEED_ARROWHEAD</x:v>
       </x:c>
       <x:c r="T71" s="78" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U71" s="78" t="str">
-        <x:v>OnHit</x:v>
+        <x:v>OnCriticalHit</x:v>
       </x:c>
       <x:c r="V71" s="78" t="str">
         <x:v>UniqueBehavior</x:v>
@@ -19525,13 +19504,13 @@
         <x:v>RuntimeBehavior</x:v>
       </x:c>
       <x:c r="X71" s="78" t="str">
-        <x:v>Multiply</x:v>
+        <x:v>Add</x:v>
       </x:c>
       <x:c r="Y71" s="78" t="str">
-        <x:v>0.5</x:v>
+        <x:v>0.005</x:v>
       </x:c>
       <x:c r="Z71" s="78" t="str">
-        <x:v>Part.ProjectileSplitOnHit</x:v>
+        <x:v>Part.ApplyBleedOnCritical</x:v>
       </x:c>
       <x:c r="AA71" s="78" t="str">
         <x:v>None</x:v>
@@ -19540,29 +19519,31 @@
         <x:v>None</x:v>
       </x:c>
       <x:c r="AC71" s="78" t="str">
-        <x:v>MaxChildren</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="AD71" s="78" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE71" s="78" t="str">
         <x:v>3</x:v>
-      </x:c>
-      <x:c r="AE71" s="78" t="str">
-        <x:v>0</x:v>
       </x:c>
       <x:c r="AF71" s="78" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AG71" s="78" t="str">
-        <x:v>Unique</x:v>
+        <x:v>Stackable</x:v>
       </x:c>
       <x:c r="AH71" s="78" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="AI71" s="78"/>
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="AI71" s="78" t="str">
+        <x:v>策划确认不想要</x:v>
+      </x:c>
       <x:c r="AJ71" s="78" t="str">
         <x:v>武器插槽C</x:v>
       </x:c>
       <x:c r="AK71" s="78" t="str">
-        <x:v>16</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="72" s="71" customFormat="1" ht="22" customHeight="1">
@@ -19613,10 +19594,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="R72" s="78" t="str">
-        <x:v>PE_BOW_EXPLOSIVE_ARROWHEAD_1</x:v>
+        <x:v>PE_BOW_MULTISHOT_ARROWHEAD_1</x:v>
       </x:c>
       <x:c r="S72" s="78" t="str">
-        <x:v>P_BOW_EXPLOSIVE_ARROWHEAD</x:v>
+        <x:v>P_BOW_MULTISHOT_ARROWHEAD</x:v>
       </x:c>
       <x:c r="T72" s="78" t="str">
         <x:v>1</x:v>
@@ -19628,13 +19609,13 @@
         <x:v>StatModifier</x:v>
       </x:c>
       <x:c r="W72" s="78" t="str">
-        <x:v>ExplosionRadius</x:v>
+        <x:v>ProjectileCount</x:v>
       </x:c>
       <x:c r="X72" s="78" t="str">
         <x:v>Override</x:v>
       </x:c>
       <x:c r="Y72" s="78" t="str">
-        <x:v>100</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="Z72" s="78" t="str">
         <x:v>Part.StatModifier</x:v>
@@ -19668,7 +19649,7 @@
         <x:v>武器插槽C</x:v>
       </x:c>
       <x:c r="AK72" s="78" t="str">
-        <x:v>17</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="73" s="71" customFormat="1" ht="22" customHeight="1">
@@ -19719,31 +19700,31 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="R73" s="78" t="str">
-        <x:v>PE_BOW_PIERCING_ARROWHEAD_1</x:v>
+        <x:v>PE_BOW_MULTISHOT_ARROWHEAD_2</x:v>
       </x:c>
       <x:c r="S73" s="78" t="str">
-        <x:v>P_BOW_PIERCING_ARROWHEAD</x:v>
+        <x:v>P_BOW_MULTISHOT_ARROWHEAD</x:v>
       </x:c>
       <x:c r="T73" s="78" t="str">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="U73" s="78" t="str">
-        <x:v>OnCriticalHit</x:v>
+        <x:v>OnEquip</x:v>
       </x:c>
       <x:c r="V73" s="78" t="str">
-        <x:v>UniqueBehavior</x:v>
+        <x:v>StatModifier</x:v>
       </x:c>
       <x:c r="W73" s="78" t="str">
-        <x:v>RuntimeBehavior</x:v>
+        <x:v>ConcentrationDegrees</x:v>
       </x:c>
       <x:c r="X73" s="78" t="str">
         <x:v>Override</x:v>
       </x:c>
       <x:c r="Y73" s="78" t="str">
-        <x:v>1</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="Z73" s="78" t="str">
-        <x:v>Part.ProjectilePierceOnCritical</x:v>
+        <x:v>Part.StatModifier</x:v>
       </x:c>
       <x:c r="AA73" s="78" t="str">
         <x:v>None</x:v>
@@ -19774,7 +19755,7 @@
         <x:v>武器插槽C</x:v>
       </x:c>
       <x:c r="AK73" s="78" t="str">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="74" s="71" customFormat="1" ht="22" customHeight="1">
@@ -19825,16 +19806,16 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="R74" s="78" t="str">
-        <x:v>PE_BOW_CRITBLEED_ARROWHEAD_1</x:v>
+        <x:v>PE_BOW_KILLSHARD_ARROWHEAD_1</x:v>
       </x:c>
       <x:c r="S74" s="78" t="str">
-        <x:v>P_BOW_CRITBLEED_ARROWHEAD</x:v>
+        <x:v>P_BOW_KILLSHARD_ARROWHEAD</x:v>
       </x:c>
       <x:c r="T74" s="78" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U74" s="78" t="str">
-        <x:v>OnCriticalHit</x:v>
+        <x:v>OnKill</x:v>
       </x:c>
       <x:c r="V74" s="78" t="str">
         <x:v>UniqueBehavior</x:v>
@@ -19846,10 +19827,10 @@
         <x:v>Add</x:v>
       </x:c>
       <x:c r="Y74" s="78" t="str">
-        <x:v>0.005</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="Z74" s="78" t="str">
-        <x:v>Part.ApplyBleedOnCritical</x:v>
+        <x:v>Part.DropShardOnKill</x:v>
       </x:c>
       <x:c r="AA74" s="78" t="str">
         <x:v>None</x:v>
@@ -19858,31 +19839,29 @@
         <x:v>None</x:v>
       </x:c>
       <x:c r="AC74" s="78" t="str">
-        <x:v>None</x:v>
+        <x:v>ShardCount</x:v>
       </x:c>
       <x:c r="AD74" s="78" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE74" s="78" t="str">
         <x:v>0</x:v>
-      </x:c>
-      <x:c r="AE74" s="78" t="str">
-        <x:v>3</x:v>
       </x:c>
       <x:c r="AF74" s="78" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AG74" s="78" t="str">
-        <x:v>Stackable</x:v>
+        <x:v>Unique</x:v>
       </x:c>
       <x:c r="AH74" s="78" t="str">
-        <x:v>false</x:v>
-      </x:c>
-      <x:c r="AI74" s="78" t="str">
-        <x:v>策划确认不想要</x:v>
-      </x:c>
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="AI74" s="78"/>
       <x:c r="AJ74" s="78" t="str">
         <x:v>武器插槽C</x:v>
       </x:c>
       <x:c r="AK74" s="78" t="str">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="75" s="71" customFormat="1" ht="22" customHeight="1">
@@ -19933,31 +19912,31 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="R75" s="78" t="str">
-        <x:v>PE_BOW_MULTISHOT_ARROWHEAD_1</x:v>
+        <x:v>PE_BOW_KILLHASTE_BOWSTRING_1</x:v>
       </x:c>
       <x:c r="S75" s="78" t="str">
-        <x:v>P_BOW_MULTISHOT_ARROWHEAD</x:v>
+        <x:v>P_BOW_KILLHASTE_BOWSTRING</x:v>
       </x:c>
       <x:c r="T75" s="78" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U75" s="78" t="str">
-        <x:v>OnEquip</x:v>
+        <x:v>OnKill</x:v>
       </x:c>
       <x:c r="V75" s="78" t="str">
-        <x:v>StatModifier</x:v>
+        <x:v>UniqueBehavior</x:v>
       </x:c>
       <x:c r="W75" s="78" t="str">
-        <x:v>ProjectileCount</x:v>
+        <x:v>RuntimeBehavior</x:v>
       </x:c>
       <x:c r="X75" s="78" t="str">
-        <x:v>Override</x:v>
+        <x:v>Add</x:v>
       </x:c>
       <x:c r="Y75" s="78" t="str">
-        <x:v>3</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="Z75" s="78" t="str">
-        <x:v>Part.StatModifier</x:v>
+        <x:v>Part.MoveSpeedOnKill</x:v>
       </x:c>
       <x:c r="AA75" s="78" t="str">
         <x:v>None</x:v>
@@ -19972,13 +19951,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AE75" s="78" t="str">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AF75" s="78" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AG75" s="78" t="str">
-        <x:v>Unique</x:v>
+        <x:v>IndependentTimed</x:v>
       </x:c>
       <x:c r="AH75" s="78" t="str">
         <x:v>true</x:v>
@@ -19988,7 +19967,7 @@
         <x:v>武器插槽C</x:v>
       </x:c>
       <x:c r="AK75" s="78" t="str">
-        <x:v>20</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="76" s="71" customFormat="1" ht="22" customHeight="1">
@@ -20039,31 +20018,31 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="R76" s="78" t="str">
-        <x:v>PE_BOW_MULTISHOT_ARROWHEAD_2</x:v>
+        <x:v>PE_BOW_COMBOHASTE_BOWSTRING_1</x:v>
       </x:c>
       <x:c r="S76" s="78" t="str">
-        <x:v>P_BOW_MULTISHOT_ARROWHEAD</x:v>
+        <x:v>P_BOW_COMBOHASTE_BOWSTRING</x:v>
       </x:c>
       <x:c r="T76" s="78" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="U76" s="78" t="str">
-        <x:v>OnEquip</x:v>
+        <x:v>OnAttack</x:v>
       </x:c>
       <x:c r="V76" s="78" t="str">
-        <x:v>StatModifier</x:v>
+        <x:v>UniqueBehavior</x:v>
       </x:c>
       <x:c r="W76" s="78" t="str">
-        <x:v>ConcentrationDegrees</x:v>
+        <x:v>RuntimeBehavior</x:v>
       </x:c>
       <x:c r="X76" s="78" t="str">
-        <x:v>Override</x:v>
+        <x:v>Add</x:v>
       </x:c>
       <x:c r="Y76" s="78" t="str">
-        <x:v>60</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="Z76" s="78" t="str">
-        <x:v>Part.StatModifier</x:v>
+        <x:v>Part.AttackMoveSpeedOnAttack</x:v>
       </x:c>
       <x:c r="AA76" s="78" t="str">
         <x:v>None</x:v>
@@ -20072,19 +20051,19 @@
         <x:v>None</x:v>
       </x:c>
       <x:c r="AC76" s="78" t="str">
-        <x:v>None</x:v>
+        <x:v>MaxStacks</x:v>
       </x:c>
       <x:c r="AD76" s="78" t="str">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AE76" s="78" t="str">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AF76" s="78" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AG76" s="78" t="str">
-        <x:v>Unique</x:v>
+        <x:v>IndependentTimed</x:v>
       </x:c>
       <x:c r="AH76" s="78" t="str">
         <x:v>true</x:v>
@@ -20094,7 +20073,7 @@
         <x:v>武器插槽C</x:v>
       </x:c>
       <x:c r="AK76" s="78" t="str">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="77" s="71" customFormat="1" ht="22" customHeight="1">
@@ -20145,16 +20124,16 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="R77" s="78" t="str">
-        <x:v>PE_BOW_KILLSHARD_ARROWHEAD_1</x:v>
+        <x:v>PE_SCYTHE_GROUPGROWTH_ROTARYBLADE_1</x:v>
       </x:c>
       <x:c r="S77" s="78" t="str">
-        <x:v>P_BOW_KILLSHARD_ARROWHEAD</x:v>
+        <x:v>P_SCYTHE_GROUPGROWTH_ROTARYBLADE</x:v>
       </x:c>
       <x:c r="T77" s="78" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U77" s="78" t="str">
-        <x:v>OnKill</x:v>
+        <x:v>OnAttackResolved</x:v>
       </x:c>
       <x:c r="V77" s="78" t="str">
         <x:v>UniqueBehavior</x:v>
@@ -20166,10 +20145,10 @@
         <x:v>Add</x:v>
       </x:c>
       <x:c r="Y77" s="78" t="str">
-        <x:v>1</x:v>
+        <x:v>0.02</x:v>
       </x:c>
       <x:c r="Z77" s="78" t="str">
-        <x:v>Part.DropShardOnKill</x:v>
+        <x:v>Part.RangeOnGroupHit</x:v>
       </x:c>
       <x:c r="AA77" s="78" t="str">
         <x:v>None</x:v>
@@ -20178,19 +20157,19 @@
         <x:v>None</x:v>
       </x:c>
       <x:c r="AC77" s="78" t="str">
-        <x:v>ShardCount</x:v>
+        <x:v>GroupThreshold</x:v>
       </x:c>
       <x:c r="AD77" s="78" t="str">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AE77" s="78" t="str">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AF77" s="78" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AG77" s="78" t="str">
-        <x:v>Unique</x:v>
+        <x:v>IndependentTimed</x:v>
       </x:c>
       <x:c r="AH77" s="78" t="str">
         <x:v>true</x:v>
@@ -20200,7 +20179,7 @@
         <x:v>武器插槽C</x:v>
       </x:c>
       <x:c r="AK77" s="78" t="str">
-        <x:v>21</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="78" s="71" customFormat="1" ht="22" customHeight="1">
@@ -20253,16 +20232,16 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="R78" s="78" t="str">
-        <x:v>PE_BOW_KILLHASTE_BOWSTRING_1</x:v>
+        <x:v>PE_SCYTHE_LIFESTEAL_ROTARYBLADE_1</x:v>
       </x:c>
       <x:c r="S78" s="78" t="str">
-        <x:v>P_BOW_KILLHASTE_BOWSTRING</x:v>
+        <x:v>P_SCYTHE_LIFESTEAL_ROTARYBLADE</x:v>
       </x:c>
       <x:c r="T78" s="78" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U78" s="78" t="str">
-        <x:v>OnKill</x:v>
+        <x:v>OnHit</x:v>
       </x:c>
       <x:c r="V78" s="78" t="str">
         <x:v>UniqueBehavior</x:v>
@@ -20274,10 +20253,10 @@
         <x:v>Add</x:v>
       </x:c>
       <x:c r="Y78" s="78" t="str">
-        <x:v>0.2</x:v>
+        <x:v>0.01</x:v>
       </x:c>
       <x:c r="Z78" s="78" t="str">
-        <x:v>Part.MoveSpeedOnKill</x:v>
+        <x:v>Part.HealOnHit</x:v>
       </x:c>
       <x:c r="AA78" s="78" t="str">
         <x:v>None</x:v>
@@ -20292,13 +20271,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AE78" s="78" t="str">
-        <x:v>5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AF78" s="78" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AG78" s="78" t="str">
-        <x:v>IndependentTimed</x:v>
+        <x:v>Stackable</x:v>
       </x:c>
       <x:c r="AH78" s="78" t="str">
         <x:v>true</x:v>
@@ -20308,7 +20287,7 @@
         <x:v>武器插槽C</x:v>
       </x:c>
       <x:c r="AK78" s="78" t="str">
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="79" s="71" customFormat="1" ht="75" customHeight="1">
@@ -20359,16 +20338,16 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="R79" s="78" t="str">
-        <x:v>PE_BOW_COMBOHASTE_BOWSTRING_1</x:v>
+        <x:v>PE_SCYTHE_STUN_ROTARYBLADE_1</x:v>
       </x:c>
       <x:c r="S79" s="78" t="str">
-        <x:v>P_BOW_COMBOHASTE_BOWSTRING</x:v>
+        <x:v>P_SCYTHE_STUN_ROTARYBLADE</x:v>
       </x:c>
       <x:c r="T79" s="78" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U79" s="78" t="str">
-        <x:v>OnAttack</x:v>
+        <x:v>OnHit</x:v>
       </x:c>
       <x:c r="V79" s="78" t="str">
         <x:v>UniqueBehavior</x:v>
@@ -20380,10 +20359,10 @@
         <x:v>Add</x:v>
       </x:c>
       <x:c r="Y79" s="78" t="str">
-        <x:v>0.04</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="Z79" s="78" t="str">
-        <x:v>Part.AttackMoveSpeedOnAttack</x:v>
+        <x:v>Part.StunOnHit</x:v>
       </x:c>
       <x:c r="AA79" s="78" t="str">
         <x:v>None</x:v>
@@ -20392,19 +20371,19 @@
         <x:v>None</x:v>
       </x:c>
       <x:c r="AC79" s="78" t="str">
-        <x:v>MaxStacks</x:v>
+        <x:v>Chance</x:v>
       </x:c>
       <x:c r="AD79" s="78" t="str">
-        <x:v>5</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="AE79" s="78" t="str">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AF79" s="78" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AG79" s="78" t="str">
-        <x:v>IndependentTimed</x:v>
+        <x:v>NoStack</x:v>
       </x:c>
       <x:c r="AH79" s="78" t="str">
         <x:v>true</x:v>
@@ -20414,7 +20393,7 @@
         <x:v>武器插槽C</x:v>
       </x:c>
       <x:c r="AK79" s="78" t="str">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="80" s="71" customFormat="1" ht="22" customHeight="1">
@@ -20465,16 +20444,16 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="R80" s="78" t="str">
-        <x:v>PE_SCYTHE_GROUPGROWTH_ROTARYBLADE_1</x:v>
+        <x:v>PE_SCYTHE_BLEED_ROTARYBLADE_1</x:v>
       </x:c>
       <x:c r="S80" s="78" t="str">
-        <x:v>P_SCYTHE_GROUPGROWTH_ROTARYBLADE</x:v>
+        <x:v>P_SCYTHE_BLEED_ROTARYBLADE</x:v>
       </x:c>
       <x:c r="T80" s="78" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U80" s="78" t="str">
-        <x:v>OnAttackResolved</x:v>
+        <x:v>OnHit</x:v>
       </x:c>
       <x:c r="V80" s="78" t="str">
         <x:v>UniqueBehavior</x:v>
@@ -20486,10 +20465,10 @@
         <x:v>Add</x:v>
       </x:c>
       <x:c r="Y80" s="78" t="str">
-        <x:v>0.02</x:v>
+        <x:v>0.005</x:v>
       </x:c>
       <x:c r="Z80" s="78" t="str">
-        <x:v>Part.RangeOnGroupHit</x:v>
+        <x:v>Part.BleedEveryTargetHits</x:v>
       </x:c>
       <x:c r="AA80" s="78" t="str">
         <x:v>None</x:v>
@@ -20498,19 +20477,19 @@
         <x:v>None</x:v>
       </x:c>
       <x:c r="AC80" s="78" t="str">
-        <x:v>GroupThreshold</x:v>
+        <x:v>HitThreshold</x:v>
       </x:c>
       <x:c r="AD80" s="78" t="str">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AE80" s="78" t="str">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AF80" s="78" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AG80" s="78" t="str">
-        <x:v>IndependentTimed</x:v>
+        <x:v>Stackable</x:v>
       </x:c>
       <x:c r="AH80" s="78" t="str">
         <x:v>true</x:v>
@@ -20520,7 +20499,7 @@
         <x:v>武器插槽C</x:v>
       </x:c>
       <x:c r="AK80" s="78" t="str">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="81" s="71" customFormat="1" ht="22" customHeight="1">
@@ -20571,10 +20550,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="R81" s="78" t="str">
-        <x:v>PE_SCYTHE_LIFESTEAL_ROTARYBLADE_1</x:v>
+        <x:v>PE_SCYTHE_OUTERRING_ROTARYBLADE_1</x:v>
       </x:c>
       <x:c r="S81" s="78" t="str">
-        <x:v>P_SCYTHE_LIFESTEAL_ROTARYBLADE</x:v>
+        <x:v>P_SCYTHE_OUTERRING_ROTARYBLADE</x:v>
       </x:c>
       <x:c r="T81" s="78" t="str">
         <x:v>1</x:v>
@@ -20592,10 +20571,10 @@
         <x:v>Add</x:v>
       </x:c>
       <x:c r="Y81" s="78" t="str">
-        <x:v>0.01</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="Z81" s="78" t="str">
-        <x:v>Part.HealOnHit</x:v>
+        <x:v>Part.OuterRingDamage</x:v>
       </x:c>
       <x:c r="AA81" s="78" t="str">
         <x:v>None</x:v>
@@ -20604,10 +20583,10 @@
         <x:v>None</x:v>
       </x:c>
       <x:c r="AC81" s="78" t="str">
-        <x:v>None</x:v>
+        <x:v>OuterRingFraction</x:v>
       </x:c>
       <x:c r="AD81" s="78" t="str">
-        <x:v>0</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="AE81" s="78" t="str">
         <x:v>0</x:v>
@@ -20616,7 +20595,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AG81" s="78" t="str">
-        <x:v>Stackable</x:v>
+        <x:v>Unique</x:v>
       </x:c>
       <x:c r="AH81" s="78" t="str">
         <x:v>true</x:v>
@@ -20626,7 +20605,7 @@
         <x:v>武器插槽C</x:v>
       </x:c>
       <x:c r="AK81" s="78" t="str">
-        <x:v>27</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="82" s="71" customFormat="1" ht="22" customHeight="1">
@@ -20677,10 +20656,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="R82" s="78" t="str">
-        <x:v>PE_SCYTHE_STUN_ROTARYBLADE_1</x:v>
+        <x:v>PE_SCYTHE_MOVESTACK_GRIP_1</x:v>
       </x:c>
       <x:c r="S82" s="78" t="str">
-        <x:v>P_SCYTHE_STUN_ROTARYBLADE</x:v>
+        <x:v>P_SCYTHE_MOVESTACK_GRIP</x:v>
       </x:c>
       <x:c r="T82" s="78" t="str">
         <x:v>1</x:v>
@@ -20698,10 +20677,10 @@
         <x:v>Add</x:v>
       </x:c>
       <x:c r="Y82" s="78" t="str">
-        <x:v>0.2</x:v>
+        <x:v>0.01</x:v>
       </x:c>
       <x:c r="Z82" s="78" t="str">
-        <x:v>Part.StunOnHit</x:v>
+        <x:v>Part.MoveSpeedPerHit</x:v>
       </x:c>
       <x:c r="AA82" s="78" t="str">
         <x:v>None</x:v>
@@ -20710,19 +20689,19 @@
         <x:v>None</x:v>
       </x:c>
       <x:c r="AC82" s="78" t="str">
-        <x:v>Chance</x:v>
+        <x:v>MaxStacks</x:v>
       </x:c>
       <x:c r="AD82" s="78" t="str">
-        <x:v>0.2</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="AE82" s="78" t="str">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AF82" s="78" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AG82" s="78" t="str">
-        <x:v>NoStack</x:v>
+        <x:v>IndependentTimed</x:v>
       </x:c>
       <x:c r="AH82" s="78" t="str">
         <x:v>true</x:v>
@@ -20732,7 +20711,7 @@
         <x:v>武器插槽C</x:v>
       </x:c>
       <x:c r="AK82" s="78" t="str">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="83" s="71" customFormat="1" ht="22" customHeight="1">
@@ -20783,31 +20762,31 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="R83" s="78" t="str">
-        <x:v>PE_SCYTHE_BLEED_ROTARYBLADE_1</x:v>
+        <x:v>PE_SCYTHE_GROUPINVULN_GRIP_1</x:v>
       </x:c>
       <x:c r="S83" s="78" t="str">
-        <x:v>P_SCYTHE_BLEED_ROTARYBLADE</x:v>
+        <x:v>P_SCYTHE_GROUPINVULN_GRIP</x:v>
       </x:c>
       <x:c r="T83" s="78" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U83" s="78" t="str">
-        <x:v>OnHit</x:v>
+        <x:v>OnEquip</x:v>
       </x:c>
       <x:c r="V83" s="78" t="str">
-        <x:v>UniqueBehavior</x:v>
+        <x:v>StatModifier</x:v>
       </x:c>
       <x:c r="W83" s="78" t="str">
-        <x:v>RuntimeBehavior</x:v>
+        <x:v>AttackSpeed</x:v>
       </x:c>
       <x:c r="X83" s="78" t="str">
-        <x:v>Add</x:v>
+        <x:v>Multiply</x:v>
       </x:c>
       <x:c r="Y83" s="78" t="str">
-        <x:v>0.005</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="Z83" s="78" t="str">
-        <x:v>Part.BleedEveryTargetHits</x:v>
+        <x:v>Part.StatModifier</x:v>
       </x:c>
       <x:c r="AA83" s="78" t="str">
         <x:v>None</x:v>
@@ -20816,19 +20795,19 @@
         <x:v>None</x:v>
       </x:c>
       <x:c r="AC83" s="78" t="str">
-        <x:v>HitThreshold</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="AD83" s="78" t="str">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AE83" s="78" t="str">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AF83" s="78" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AG83" s="78" t="str">
-        <x:v>Stackable</x:v>
+        <x:v>Unique</x:v>
       </x:c>
       <x:c r="AH83" s="78" t="str">
         <x:v>true</x:v>
@@ -20838,7 +20817,7 @@
         <x:v>武器插槽C</x:v>
       </x:c>
       <x:c r="AK83" s="78" t="str">
-        <x:v>30</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="84" s="71" customFormat="1" ht="22" customHeight="1">
@@ -20889,16 +20868,16 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="R84" s="78" t="str">
-        <x:v>PE_SCYTHE_OUTERRING_ROTARYBLADE_1</x:v>
+        <x:v>PE_SCYTHE_GROUPINVULN_GRIP_2</x:v>
       </x:c>
       <x:c r="S84" s="78" t="str">
-        <x:v>P_SCYTHE_OUTERRING_ROTARYBLADE</x:v>
+        <x:v>P_SCYTHE_GROUPINVULN_GRIP</x:v>
       </x:c>
       <x:c r="T84" s="78" t="str">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="U84" s="78" t="str">
-        <x:v>OnHit</x:v>
+        <x:v>OnAttackResolved</x:v>
       </x:c>
       <x:c r="V84" s="78" t="str">
         <x:v>UniqueBehavior</x:v>
@@ -20907,13 +20886,13 @@
         <x:v>RuntimeBehavior</x:v>
       </x:c>
       <x:c r="X84" s="78" t="str">
-        <x:v>Add</x:v>
+        <x:v>Override</x:v>
       </x:c>
       <x:c r="Y84" s="78" t="str">
-        <x:v>0.4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="Z84" s="78" t="str">
-        <x:v>Part.OuterRingDamage</x:v>
+        <x:v>Part.InvulnerableOnGroupHit</x:v>
       </x:c>
       <x:c r="AA84" s="78" t="str">
         <x:v>None</x:v>
@@ -20922,13 +20901,13 @@
         <x:v>None</x:v>
       </x:c>
       <x:c r="AC84" s="78" t="str">
-        <x:v>OuterRingFraction</x:v>
+        <x:v>GroupThreshold</x:v>
       </x:c>
       <x:c r="AD84" s="78" t="str">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="AE84" s="78" t="str">
         <x:v>0.5</x:v>
-      </x:c>
-      <x:c r="AE84" s="78" t="str">
-        <x:v>0</x:v>
       </x:c>
       <x:c r="AF84" s="78" t="str">
         <x:v>0</x:v>
@@ -20944,7 +20923,7 @@
         <x:v>武器插槽C</x:v>
       </x:c>
       <x:c r="AK84" s="78" t="str">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="85" s="71" customFormat="1" ht="22" customHeight="1">
@@ -20995,10 +20974,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="R85" s="78" t="str">
-        <x:v>PE_SCYTHE_MOVESTACK_GRIP_1</x:v>
+        <x:v>PE_SCYTHE_ATTACKSTACK_GRIP_1</x:v>
       </x:c>
       <x:c r="S85" s="78" t="str">
-        <x:v>P_SCYTHE_MOVESTACK_GRIP</x:v>
+        <x:v>P_SCYTHE_ATTACKSTACK_GRIP</x:v>
       </x:c>
       <x:c r="T85" s="78" t="str">
         <x:v>1</x:v>
@@ -21019,7 +20998,7 @@
         <x:v>0.01</x:v>
       </x:c>
       <x:c r="Z85" s="78" t="str">
-        <x:v>Part.MoveSpeedPerHit</x:v>
+        <x:v>Part.AttackSpeedPerHit</x:v>
       </x:c>
       <x:c r="AA85" s="78" t="str">
         <x:v>None</x:v>
@@ -21050,7 +21029,7 @@
         <x:v>武器插槽C</x:v>
       </x:c>
       <x:c r="AK85" s="78" t="str">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="86" s="71" customFormat="1" ht="45" customHeight="1">
@@ -21103,31 +21082,31 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="R86" s="78" t="str">
-        <x:v>PE_SCYTHE_GROUPINVULN_GRIP_1</x:v>
+        <x:v>PE_SCYTHE_THROWRECALL_GRIP_1</x:v>
       </x:c>
       <x:c r="S86" s="78" t="str">
-        <x:v>P_SCYTHE_GROUPINVULN_GRIP</x:v>
+        <x:v>P_SCYTHE_THROWRECALL_GRIP</x:v>
       </x:c>
       <x:c r="T86" s="78" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U86" s="78" t="str">
-        <x:v>OnEquip</x:v>
+        <x:v>OnActiveAttack</x:v>
       </x:c>
       <x:c r="V86" s="78" t="str">
-        <x:v>StatModifier</x:v>
+        <x:v>UniqueBehavior</x:v>
       </x:c>
       <x:c r="W86" s="78" t="str">
-        <x:v>AttackSpeed</x:v>
+        <x:v>RuntimeBehavior</x:v>
       </x:c>
       <x:c r="X86" s="78" t="str">
         <x:v>Multiply</x:v>
       </x:c>
       <x:c r="Y86" s="78" t="str">
-        <x:v>0.5</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="Z86" s="78" t="str">
-        <x:v>Part.StatModifier</x:v>
+        <x:v>Part.ScytheThrowRecall</x:v>
       </x:c>
       <x:c r="AA86" s="78" t="str">
         <x:v>None</x:v>
@@ -21136,10 +21115,10 @@
         <x:v>None</x:v>
       </x:c>
       <x:c r="AC86" s="78" t="str">
-        <x:v>None</x:v>
+        <x:v>MaxRangeCm</x:v>
       </x:c>
       <x:c r="AD86" s="78" t="str">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="AE86" s="78" t="str">
         <x:v>0</x:v>
@@ -21158,7 +21137,7 @@
         <x:v>武器插槽C</x:v>
       </x:c>
       <x:c r="AK86" s="78" t="str">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="87" s="71" customFormat="1" ht="22" customHeight="1">
@@ -21209,16 +21188,16 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="R87" s="78" t="str">
-        <x:v>PE_SCYTHE_GROUPINVULN_GRIP_2</x:v>
+        <x:v>PE_SCYTHE_THROWRECALL_GRIP_2</x:v>
       </x:c>
       <x:c r="S87" s="78" t="str">
-        <x:v>P_SCYTHE_GROUPINVULN_GRIP</x:v>
+        <x:v>P_SCYTHE_THROWRECALL_GRIP</x:v>
       </x:c>
       <x:c r="T87" s="78" t="str">
         <x:v>2</x:v>
       </x:c>
       <x:c r="U87" s="78" t="str">
-        <x:v>OnAttackResolved</x:v>
+        <x:v>OnActiveAttack</x:v>
       </x:c>
       <x:c r="V87" s="78" t="str">
         <x:v>UniqueBehavior</x:v>
@@ -21227,13 +21206,13 @@
         <x:v>RuntimeBehavior</x:v>
       </x:c>
       <x:c r="X87" s="78" t="str">
-        <x:v>Override</x:v>
+        <x:v>Multiply</x:v>
       </x:c>
       <x:c r="Y87" s="78" t="str">
-        <x:v>1</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="Z87" s="78" t="str">
-        <x:v>Part.InvulnerableOnGroupHit</x:v>
+        <x:v>Part.ScytheThrowRecall</x:v>
       </x:c>
       <x:c r="AA87" s="78" t="str">
         <x:v>None</x:v>
@@ -21242,13 +21221,13 @@
         <x:v>None</x:v>
       </x:c>
       <x:c r="AC87" s="78" t="str">
-        <x:v>GroupThreshold</x:v>
+        <x:v>StationaryDamageMultiplier</x:v>
       </x:c>
       <x:c r="AD87" s="78" t="str">
-        <x:v>4</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="AE87" s="78" t="str">
-        <x:v>0.5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AF87" s="78" t="str">
         <x:v>0</x:v>
@@ -21264,7 +21243,7 @@
         <x:v>武器插槽C</x:v>
       </x:c>
       <x:c r="AK87" s="78" t="str">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="88" s="71" customFormat="1" ht="22" customHeight="1">
@@ -21315,16 +21294,16 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="R88" s="78" t="str">
-        <x:v>PE_SCYTHE_ATTACKSTACK_GRIP_1</x:v>
+        <x:v>PE_LONGSWORD_GROUPGROWTH_SWORDBLADE_1</x:v>
       </x:c>
       <x:c r="S88" s="78" t="str">
-        <x:v>P_SCYTHE_ATTACKSTACK_GRIP</x:v>
+        <x:v>P_LONGSWORD_GROUPGROWTH_SWORDBLADE</x:v>
       </x:c>
       <x:c r="T88" s="78" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U88" s="78" t="str">
-        <x:v>OnHit</x:v>
+        <x:v>OnAttackResolved</x:v>
       </x:c>
       <x:c r="V88" s="78" t="str">
         <x:v>UniqueBehavior</x:v>
@@ -21336,10 +21315,10 @@
         <x:v>Add</x:v>
       </x:c>
       <x:c r="Y88" s="78" t="str">
-        <x:v>0.01</x:v>
+        <x:v>0.02</x:v>
       </x:c>
       <x:c r="Z88" s="78" t="str">
-        <x:v>Part.AttackSpeedPerHit</x:v>
+        <x:v>Part.RangeOnGroupHit</x:v>
       </x:c>
       <x:c r="AA88" s="78" t="str">
         <x:v>None</x:v>
@@ -21348,10 +21327,10 @@
         <x:v>None</x:v>
       </x:c>
       <x:c r="AC88" s="78" t="str">
-        <x:v>MaxStacks</x:v>
+        <x:v>GroupThreshold</x:v>
       </x:c>
       <x:c r="AD88" s="78" t="str">
-        <x:v>30</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AE88" s="78" t="str">
         <x:v>5</x:v>
@@ -21370,7 +21349,7 @@
         <x:v>武器插槽C</x:v>
       </x:c>
       <x:c r="AK88" s="78" t="str">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="89" s="71" customFormat="1" ht="22" customHeight="1">
@@ -21421,16 +21400,16 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="R89" s="78" t="str">
-        <x:v>PE_SCYTHE_THROWRECALL_GRIP_1</x:v>
+        <x:v>PE_LONGSWORD_HITSHARD_SWORDBLADE_1</x:v>
       </x:c>
       <x:c r="S89" s="78" t="str">
-        <x:v>P_SCYTHE_THROWRECALL_GRIP</x:v>
+        <x:v>P_LONGSWORD_HITSHARD_SWORDBLADE</x:v>
       </x:c>
       <x:c r="T89" s="78" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U89" s="78" t="str">
-        <x:v>OnActiveAttack</x:v>
+        <x:v>OnHit</x:v>
       </x:c>
       <x:c r="V89" s="78" t="str">
         <x:v>UniqueBehavior</x:v>
@@ -21439,13 +21418,13 @@
         <x:v>RuntimeBehavior</x:v>
       </x:c>
       <x:c r="X89" s="78" t="str">
-        <x:v>Multiply</x:v>
+        <x:v>Add</x:v>
       </x:c>
       <x:c r="Y89" s="78" t="str">
-        <x:v>0.6</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="Z89" s="78" t="str">
-        <x:v>Part.ScytheThrowRecall</x:v>
+        <x:v>Part.DropShardEveryHits</x:v>
       </x:c>
       <x:c r="AA89" s="78" t="str">
         <x:v>None</x:v>
@@ -21454,10 +21433,10 @@
         <x:v>None</x:v>
       </x:c>
       <x:c r="AC89" s="78" t="str">
-        <x:v>MaxRangeCm</x:v>
+        <x:v>HitThreshold</x:v>
       </x:c>
       <x:c r="AD89" s="78" t="str">
-        <x:v>500</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AE89" s="78" t="str">
         <x:v>0</x:v>
@@ -21466,7 +21445,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AG89" s="78" t="str">
-        <x:v>Unique</x:v>
+        <x:v>Stackable</x:v>
       </x:c>
       <x:c r="AH89" s="78" t="str">
         <x:v>true</x:v>
@@ -21476,7 +21455,7 @@
         <x:v>武器插槽C</x:v>
       </x:c>
       <x:c r="AK89" s="78" t="str">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="90" s="71" customFormat="1" ht="22" customHeight="1">
@@ -21527,16 +21506,16 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="R90" s="78" t="str">
-        <x:v>PE_SCYTHE_THROWRECALL_GRIP_2</x:v>
+        <x:v>PE_LONGSWORD_CRITBLEED_SWORDBLADE_1</x:v>
       </x:c>
       <x:c r="S90" s="78" t="str">
-        <x:v>P_SCYTHE_THROWRECALL_GRIP</x:v>
+        <x:v>P_LONGSWORD_CRITBLEED_SWORDBLADE</x:v>
       </x:c>
       <x:c r="T90" s="78" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="U90" s="78" t="str">
-        <x:v>OnActiveAttack</x:v>
+        <x:v>OnCriticalHit</x:v>
       </x:c>
       <x:c r="V90" s="78" t="str">
         <x:v>UniqueBehavior</x:v>
@@ -21545,13 +21524,13 @@
         <x:v>RuntimeBehavior</x:v>
       </x:c>
       <x:c r="X90" s="78" t="str">
-        <x:v>Multiply</x:v>
+        <x:v>Add</x:v>
       </x:c>
       <x:c r="Y90" s="78" t="str">
-        <x:v>0.2</x:v>
+        <x:v>0.005</x:v>
       </x:c>
       <x:c r="Z90" s="78" t="str">
-        <x:v>Part.ScytheThrowRecall</x:v>
+        <x:v>Part.ApplyBleedOnCritical</x:v>
       </x:c>
       <x:c r="AA90" s="78" t="str">
         <x:v>None</x:v>
@@ -21560,19 +21539,19 @@
         <x:v>None</x:v>
       </x:c>
       <x:c r="AC90" s="78" t="str">
-        <x:v>StationaryDamageMultiplier</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="AD90" s="78" t="str">
-        <x:v>0.2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AE90" s="78" t="str">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AF90" s="78" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AG90" s="78" t="str">
-        <x:v>Unique</x:v>
+        <x:v>Stackable</x:v>
       </x:c>
       <x:c r="AH90" s="78" t="str">
         <x:v>true</x:v>
@@ -21582,7 +21561,7 @@
         <x:v>武器插槽C</x:v>
       </x:c>
       <x:c r="AK90" s="78" t="str">
-        <x:v>35</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="91" s="71" customFormat="1" ht="22" customHeight="1">
@@ -21633,10 +21612,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="R91" s="78" t="str">
-        <x:v>PE_LONGSWORD_GROUPGROWTH_SWORDBLADE_1</x:v>
+        <x:v>PE_LONGSWORD_METEOR_SWORDBLADE_1</x:v>
       </x:c>
       <x:c r="S91" s="78" t="str">
-        <x:v>P_LONGSWORD_GROUPGROWTH_SWORDBLADE</x:v>
+        <x:v>P_LONGSWORD_METEOR_SWORDBLADE</x:v>
       </x:c>
       <x:c r="T91" s="78" t="str">
         <x:v>1</x:v>
@@ -21651,13 +21630,13 @@
         <x:v>RuntimeBehavior</x:v>
       </x:c>
       <x:c r="X91" s="78" t="str">
-        <x:v>Add</x:v>
+        <x:v>Multiply</x:v>
       </x:c>
       <x:c r="Y91" s="78" t="str">
-        <x:v>0.02</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="Z91" s="78" t="str">
-        <x:v>Part.RangeOnGroupHit</x:v>
+        <x:v>Part.MeteorOnGroupHit</x:v>
       </x:c>
       <x:c r="AA91" s="78" t="str">
         <x:v>None</x:v>
@@ -21669,16 +21648,16 @@
         <x:v>GroupThreshold</x:v>
       </x:c>
       <x:c r="AD91" s="78" t="str">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="AE91" s="78" t="str">
-        <x:v>5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AF91" s="78" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AG91" s="78" t="str">
-        <x:v>IndependentTimed</x:v>
+        <x:v>Unique</x:v>
       </x:c>
       <x:c r="AH91" s="78" t="str">
         <x:v>true</x:v>
@@ -21688,7 +21667,7 @@
         <x:v>武器插槽C</x:v>
       </x:c>
       <x:c r="AK91" s="78" t="str">
-        <x:v>38</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="92" s="71" customFormat="1" ht="22" customHeight="1">
@@ -21739,16 +21718,16 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="R92" s="78" t="str">
-        <x:v>PE_LONGSWORD_HITSHARD_SWORDBLADE_1</x:v>
+        <x:v>PE_LONGSWORD_METEOR_SWORDBLADE_2</x:v>
       </x:c>
       <x:c r="S92" s="78" t="str">
-        <x:v>P_LONGSWORD_HITSHARD_SWORDBLADE</x:v>
+        <x:v>P_LONGSWORD_METEOR_SWORDBLADE</x:v>
       </x:c>
       <x:c r="T92" s="78" t="str">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="U92" s="78" t="str">
-        <x:v>OnHit</x:v>
+        <x:v>OnAttackResolved</x:v>
       </x:c>
       <x:c r="V92" s="78" t="str">
         <x:v>UniqueBehavior</x:v>
@@ -21757,13 +21736,13 @@
         <x:v>RuntimeBehavior</x:v>
       </x:c>
       <x:c r="X92" s="78" t="str">
-        <x:v>Add</x:v>
+        <x:v>Override</x:v>
       </x:c>
       <x:c r="Y92" s="78" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="Z92" s="78" t="str">
-        <x:v>Part.DropShardEveryHits</x:v>
+        <x:v>Part.MeteorOnGroupHit</x:v>
       </x:c>
       <x:c r="AA92" s="78" t="str">
         <x:v>None</x:v>
@@ -21772,10 +21751,10 @@
         <x:v>None</x:v>
       </x:c>
       <x:c r="AC92" s="78" t="str">
-        <x:v>HitThreshold</x:v>
+        <x:v>ExplosionRadiusCm</x:v>
       </x:c>
       <x:c r="AD92" s="78" t="str">
-        <x:v>5</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="AE92" s="78" t="str">
         <x:v>0</x:v>
@@ -21784,7 +21763,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AG92" s="78" t="str">
-        <x:v>Stackable</x:v>
+        <x:v>Unique</x:v>
       </x:c>
       <x:c r="AH92" s="78" t="str">
         <x:v>true</x:v>
@@ -21794,7 +21773,7 @@
         <x:v>武器插槽C</x:v>
       </x:c>
       <x:c r="AK92" s="78" t="str">
-        <x:v>40</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="93" s="71" customFormat="1" ht="22" customHeight="1">
@@ -21847,16 +21826,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="R93" s="78" t="str">
-        <x:v>PE_LONGSWORD_CRITBLEED_SWORDBLADE_1</x:v>
+        <x:v>PE_LONGSWORD_MOVESTACK_GRIP_1</x:v>
       </x:c>
       <x:c r="S93" s="78" t="str">
-        <x:v>P_LONGSWORD_CRITBLEED_SWORDBLADE</x:v>
+        <x:v>P_LONGSWORD_MOVESTACK_GRIP</x:v>
       </x:c>
       <x:c r="T93" s="78" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U93" s="78" t="str">
-        <x:v>OnCriticalHit</x:v>
+        <x:v>OnHit</x:v>
       </x:c>
       <x:c r="V93" s="78" t="str">
         <x:v>UniqueBehavior</x:v>
@@ -21868,10 +21847,10 @@
         <x:v>Add</x:v>
       </x:c>
       <x:c r="Y93" s="78" t="str">
-        <x:v>0.005</x:v>
+        <x:v>0.01</x:v>
       </x:c>
       <x:c r="Z93" s="78" t="str">
-        <x:v>Part.ApplyBleedOnCritical</x:v>
+        <x:v>Part.MoveSpeedPerHit</x:v>
       </x:c>
       <x:c r="AA93" s="78" t="str">
         <x:v>None</x:v>
@@ -21880,19 +21859,19 @@
         <x:v>None</x:v>
       </x:c>
       <x:c r="AC93" s="78" t="str">
-        <x:v>None</x:v>
+        <x:v>MaxStacks</x:v>
       </x:c>
       <x:c r="AD93" s="78" t="str">
-        <x:v>0</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="AE93" s="78" t="str">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AF93" s="78" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AG93" s="78" t="str">
-        <x:v>Stackable</x:v>
+        <x:v>IndependentTimed</x:v>
       </x:c>
       <x:c r="AH93" s="78" t="str">
         <x:v>true</x:v>
@@ -21902,7 +21881,7 @@
         <x:v>武器插槽C</x:v>
       </x:c>
       <x:c r="AK93" s="78" t="str">
-        <x:v>41</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="94" s="71" customFormat="1" ht="22" customHeight="1">
@@ -21923,16 +21902,16 @@
       <x:c r="O94" s="74"/>
       <x:c r="P94" s="74"/>
       <x:c r="R94" s="78" t="str">
-        <x:v>PE_LONGSWORD_METEOR_SWORDBLADE_1</x:v>
+        <x:v>PE_LONGSWORD_ATTACKSTACK_GRIP_1</x:v>
       </x:c>
       <x:c r="S94" s="78" t="str">
-        <x:v>P_LONGSWORD_METEOR_SWORDBLADE</x:v>
+        <x:v>P_LONGSWORD_ATTACKSTACK_GRIP</x:v>
       </x:c>
       <x:c r="T94" s="78" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U94" s="78" t="str">
-        <x:v>OnAttackResolved</x:v>
+        <x:v>OnHit</x:v>
       </x:c>
       <x:c r="V94" s="78" t="str">
         <x:v>UniqueBehavior</x:v>
@@ -21941,13 +21920,13 @@
         <x:v>RuntimeBehavior</x:v>
       </x:c>
       <x:c r="X94" s="78" t="str">
-        <x:v>Multiply</x:v>
+        <x:v>Add</x:v>
       </x:c>
       <x:c r="Y94" s="78" t="str">
-        <x:v>1</x:v>
+        <x:v>0.01</x:v>
       </x:c>
       <x:c r="Z94" s="78" t="str">
-        <x:v>Part.MeteorOnGroupHit</x:v>
+        <x:v>Part.AttackSpeedPerHit</x:v>
       </x:c>
       <x:c r="AA94" s="78" t="str">
         <x:v>None</x:v>
@@ -21956,19 +21935,19 @@
         <x:v>None</x:v>
       </x:c>
       <x:c r="AC94" s="78" t="str">
-        <x:v>GroupThreshold</x:v>
+        <x:v>MaxStacks</x:v>
       </x:c>
       <x:c r="AD94" s="78" t="str">
-        <x:v>7</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="AE94" s="78" t="str">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AF94" s="78" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AG94" s="78" t="str">
-        <x:v>Unique</x:v>
+        <x:v>IndependentTimed</x:v>
       </x:c>
       <x:c r="AH94" s="78" t="str">
         <x:v>true</x:v>
@@ -21978,7 +21957,7 @@
         <x:v>武器插槽C</x:v>
       </x:c>
       <x:c r="AK94" s="78" t="str">
-        <x:v>42</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="95" s="71" customFormat="1" ht="22" customHeight="1">
@@ -21999,16 +21978,16 @@
       <x:c r="O95" s="74"/>
       <x:c r="P95" s="74"/>
       <x:c r="R95" s="78" t="str">
-        <x:v>PE_LONGSWORD_METEOR_SWORDBLADE_2</x:v>
+        <x:v>PE_LONGSWORD_STUN_GRIP_1</x:v>
       </x:c>
       <x:c r="S95" s="78" t="str">
-        <x:v>P_LONGSWORD_METEOR_SWORDBLADE</x:v>
+        <x:v>P_LONGSWORD_STUN_GRIP</x:v>
       </x:c>
       <x:c r="T95" s="78" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="U95" s="78" t="str">
-        <x:v>OnAttackResolved</x:v>
+        <x:v>OnHit</x:v>
       </x:c>
       <x:c r="V95" s="78" t="str">
         <x:v>UniqueBehavior</x:v>
@@ -22017,13 +21996,13 @@
         <x:v>RuntimeBehavior</x:v>
       </x:c>
       <x:c r="X95" s="78" t="str">
-        <x:v>Override</x:v>
+        <x:v>Add</x:v>
       </x:c>
       <x:c r="Y95" s="78" t="str">
-        <x:v>1</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="Z95" s="78" t="str">
-        <x:v>Part.MeteorOnGroupHit</x:v>
+        <x:v>Part.StunOnHit</x:v>
       </x:c>
       <x:c r="AA95" s="78" t="str">
         <x:v>None</x:v>
@@ -22032,19 +22011,19 @@
         <x:v>None</x:v>
       </x:c>
       <x:c r="AC95" s="78" t="str">
-        <x:v>ExplosionRadiusCm</x:v>
+        <x:v>Chance</x:v>
       </x:c>
       <x:c r="AD95" s="78" t="str">
-        <x:v>150</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="AE95" s="78" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AF95" s="78" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AG95" s="78" t="str">
-        <x:v>Unique</x:v>
+        <x:v>NoStack</x:v>
       </x:c>
       <x:c r="AH95" s="78" t="str">
         <x:v>true</x:v>
@@ -22054,7 +22033,7 @@
         <x:v>武器插槽C</x:v>
       </x:c>
       <x:c r="AK95" s="78" t="str">
-        <x:v>42</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="96" s="71" customFormat="1" ht="22" customHeight="1">
@@ -22075,31 +22054,31 @@
       <x:c r="O96" s="74"/>
       <x:c r="P96" s="74"/>
       <x:c r="R96" s="78" t="str">
-        <x:v>PE_LONGSWORD_MOVESTACK_GRIP_1</x:v>
+        <x:v>PE_GUN_CHARGED_MUZZLE_1</x:v>
       </x:c>
       <x:c r="S96" s="78" t="str">
-        <x:v>P_LONGSWORD_MOVESTACK_GRIP</x:v>
+        <x:v>P_GUN_CHARGED_MUZZLE</x:v>
       </x:c>
       <x:c r="T96" s="78" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U96" s="78" t="str">
-        <x:v>OnHit</x:v>
+        <x:v>OnEquip</x:v>
       </x:c>
       <x:c r="V96" s="78" t="str">
-        <x:v>UniqueBehavior</x:v>
+        <x:v>StatModifier</x:v>
       </x:c>
       <x:c r="W96" s="78" t="str">
-        <x:v>RuntimeBehavior</x:v>
+        <x:v>AttackSpeed</x:v>
       </x:c>
       <x:c r="X96" s="78" t="str">
-        <x:v>Add</x:v>
+        <x:v>Multiply</x:v>
       </x:c>
       <x:c r="Y96" s="78" t="str">
-        <x:v>0.01</x:v>
+        <x:v>0.166666667</x:v>
       </x:c>
       <x:c r="Z96" s="78" t="str">
-        <x:v>Part.MoveSpeedPerHit</x:v>
+        <x:v>Part.StatModifier</x:v>
       </x:c>
       <x:c r="AA96" s="78" t="str">
         <x:v>None</x:v>
@@ -22108,19 +22087,19 @@
         <x:v>None</x:v>
       </x:c>
       <x:c r="AC96" s="78" t="str">
-        <x:v>MaxStacks</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="AD96" s="78" t="str">
-        <x:v>30</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AE96" s="78" t="str">
-        <x:v>5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AF96" s="78" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AG96" s="78" t="str">
-        <x:v>IndependentTimed</x:v>
+        <x:v>Unique</x:v>
       </x:c>
       <x:c r="AH96" s="78" t="str">
         <x:v>true</x:v>
@@ -22130,7 +22109,7 @@
         <x:v>武器插槽C</x:v>
       </x:c>
       <x:c r="AK96" s="78" t="str">
-        <x:v>44</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="97" s="71" customFormat="1" ht="22" customHeight="1">
@@ -22151,31 +22130,31 @@
       <x:c r="O97" s="74"/>
       <x:c r="P97" s="74"/>
       <x:c r="R97" s="78" t="str">
-        <x:v>PE_LONGSWORD_ATTACKSTACK_GRIP_1</x:v>
+        <x:v>PE_GUN_CHARGED_MUZZLE_2</x:v>
       </x:c>
       <x:c r="S97" s="78" t="str">
-        <x:v>P_LONGSWORD_ATTACKSTACK_GRIP</x:v>
+        <x:v>P_GUN_CHARGED_MUZZLE</x:v>
       </x:c>
       <x:c r="T97" s="78" t="str">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="U97" s="78" t="str">
-        <x:v>OnHit</x:v>
+        <x:v>OnEquip</x:v>
       </x:c>
       <x:c r="V97" s="78" t="str">
-        <x:v>UniqueBehavior</x:v>
+        <x:v>StatModifier</x:v>
       </x:c>
       <x:c r="W97" s="78" t="str">
-        <x:v>RuntimeBehavior</x:v>
+        <x:v>DamageCoefficient</x:v>
       </x:c>
       <x:c r="X97" s="78" t="str">
-        <x:v>Add</x:v>
+        <x:v>Multiply</x:v>
       </x:c>
       <x:c r="Y97" s="78" t="str">
-        <x:v>0.01</x:v>
+        <x:v>2.8</x:v>
       </x:c>
       <x:c r="Z97" s="78" t="str">
-        <x:v>Part.AttackSpeedPerHit</x:v>
+        <x:v>Part.StatModifier</x:v>
       </x:c>
       <x:c r="AA97" s="78" t="str">
         <x:v>None</x:v>
@@ -22184,19 +22163,19 @@
         <x:v>None</x:v>
       </x:c>
       <x:c r="AC97" s="78" t="str">
-        <x:v>MaxStacks</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="AD97" s="78" t="str">
-        <x:v>30</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AE97" s="78" t="str">
-        <x:v>5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AF97" s="78" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AG97" s="78" t="str">
-        <x:v>IndependentTimed</x:v>
+        <x:v>Unique</x:v>
       </x:c>
       <x:c r="AH97" s="78" t="str">
         <x:v>true</x:v>
@@ -22206,7 +22185,7 @@
         <x:v>武器插槽C</x:v>
       </x:c>
       <x:c r="AK97" s="78" t="str">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="98" s="71" customFormat="1" ht="22" customHeight="1">
@@ -22227,31 +22206,31 @@
       <x:c r="O98" s="74"/>
       <x:c r="P98" s="74"/>
       <x:c r="R98" s="78" t="str">
-        <x:v>PE_LONGSWORD_STUN_GRIP_1</x:v>
+        <x:v>PE_GUN_RAPID_MUZZLE_1</x:v>
       </x:c>
       <x:c r="S98" s="78" t="str">
-        <x:v>P_LONGSWORD_STUN_GRIP</x:v>
+        <x:v>P_GUN_RAPID_MUZZLE</x:v>
       </x:c>
       <x:c r="T98" s="78" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U98" s="78" t="str">
-        <x:v>OnHit</x:v>
+        <x:v>OnEquip</x:v>
       </x:c>
       <x:c r="V98" s="78" t="str">
-        <x:v>UniqueBehavior</x:v>
+        <x:v>StatModifier</x:v>
       </x:c>
       <x:c r="W98" s="78" t="str">
-        <x:v>RuntimeBehavior</x:v>
+        <x:v>AttackSpeed</x:v>
       </x:c>
       <x:c r="X98" s="78" t="str">
-        <x:v>Add</x:v>
+        <x:v>Multiply</x:v>
       </x:c>
       <x:c r="Y98" s="78" t="str">
-        <x:v>0.2</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="Z98" s="78" t="str">
-        <x:v>Part.StunOnHit</x:v>
+        <x:v>Part.StatModifier</x:v>
       </x:c>
       <x:c r="AA98" s="78" t="str">
         <x:v>None</x:v>
@@ -22260,29 +22239,31 @@
         <x:v>None</x:v>
       </x:c>
       <x:c r="AC98" s="78" t="str">
-        <x:v>Chance</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="AD98" s="78" t="str">
-        <x:v>0.2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AE98" s="78" t="str">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AF98" s="78" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AG98" s="78" t="str">
-        <x:v>NoStack</x:v>
+        <x:v>Unique</x:v>
       </x:c>
       <x:c r="AH98" s="78" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="AI98" s="78"/>
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="AI98" s="78" t="str">
+        <x:v>策划确认不想要</x:v>
+      </x:c>
       <x:c r="AJ98" s="78" t="str">
         <x:v>武器插槽C</x:v>
       </x:c>
       <x:c r="AK98" s="78" t="str">
-        <x:v>46</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="99" s="71" customFormat="1" ht="22" customHeight="1">
@@ -22303,10 +22284,10 @@
       <x:c r="O99" s="74"/>
       <x:c r="P99" s="74"/>
       <x:c r="R99" s="78" t="str">
-        <x:v>PE_GUN_CHARGED_MUZZLE_1</x:v>
+        <x:v>PE_GUN_EXPLOSIVE_MUZZLE_1</x:v>
       </x:c>
       <x:c r="S99" s="78" t="str">
-        <x:v>P_GUN_CHARGED_MUZZLE</x:v>
+        <x:v>P_GUN_EXPLOSIVE_MUZZLE</x:v>
       </x:c>
       <x:c r="T99" s="78" t="str">
         <x:v>1</x:v>
@@ -22318,13 +22299,13 @@
         <x:v>StatModifier</x:v>
       </x:c>
       <x:c r="W99" s="78" t="str">
-        <x:v>AttackSpeed</x:v>
+        <x:v>ExplosionRadius</x:v>
       </x:c>
       <x:c r="X99" s="78" t="str">
-        <x:v>Multiply</x:v>
+        <x:v>Override</x:v>
       </x:c>
       <x:c r="Y99" s="78" t="str">
-        <x:v>0.166666667</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="Z99" s="78" t="str">
         <x:v>Part.StatModifier</x:v>
@@ -22358,7 +22339,7 @@
         <x:v>武器插槽C</x:v>
       </x:c>
       <x:c r="AK99" s="78" t="str">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="100" s="71" customFormat="1" ht="22" customHeight="1">
@@ -22379,31 +22360,31 @@
       <x:c r="O100" s="74"/>
       <x:c r="P100" s="74"/>
       <x:c r="R100" s="78" t="str">
-        <x:v>PE_GUN_CHARGED_MUZZLE_2</x:v>
+        <x:v>PE_GUN_PIERCING_MUZZLE_1</x:v>
       </x:c>
       <x:c r="S100" s="78" t="str">
-        <x:v>P_GUN_CHARGED_MUZZLE</x:v>
+        <x:v>P_GUN_PIERCING_MUZZLE</x:v>
       </x:c>
       <x:c r="T100" s="78" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="U100" s="78" t="str">
-        <x:v>OnEquip</x:v>
+        <x:v>OnCriticalHit</x:v>
       </x:c>
       <x:c r="V100" s="78" t="str">
-        <x:v>StatModifier</x:v>
+        <x:v>UniqueBehavior</x:v>
       </x:c>
       <x:c r="W100" s="78" t="str">
-        <x:v>PhysicalCoefficient</x:v>
+        <x:v>RuntimeBehavior</x:v>
       </x:c>
       <x:c r="X100" s="78" t="str">
-        <x:v>Multiply</x:v>
+        <x:v>Override</x:v>
       </x:c>
       <x:c r="Y100" s="78" t="str">
-        <x:v>2.8</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="Z100" s="78" t="str">
-        <x:v>Part.StatModifier</x:v>
+        <x:v>Part.ProjectilePierceOnCritical</x:v>
       </x:c>
       <x:c r="AA100" s="78" t="str">
         <x:v>None</x:v>
@@ -22434,7 +22415,7 @@
         <x:v>武器插槽C</x:v>
       </x:c>
       <x:c r="AK100" s="78" t="str">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="101" s="71" customFormat="1" ht="22" customHeight="1">
@@ -22455,31 +22436,31 @@
       <x:c r="O101" s="74"/>
       <x:c r="P101" s="74"/>
       <x:c r="R101" s="78" t="str">
-        <x:v>PE_GUN_CHARGED_MUZZLE_3</x:v>
+        <x:v>PE_GUN_BLEED_MUZZLE_1</x:v>
       </x:c>
       <x:c r="S101" s="78" t="str">
-        <x:v>P_GUN_CHARGED_MUZZLE</x:v>
+        <x:v>P_GUN_BLEED_MUZZLE</x:v>
       </x:c>
       <x:c r="T101" s="78" t="str">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="U101" s="78" t="str">
-        <x:v>OnEquip</x:v>
+        <x:v>OnHit</x:v>
       </x:c>
       <x:c r="V101" s="78" t="str">
-        <x:v>StatModifier</x:v>
+        <x:v>UniqueBehavior</x:v>
       </x:c>
       <x:c r="W101" s="78" t="str">
-        <x:v>ElementalCoefficient</x:v>
+        <x:v>RuntimeBehavior</x:v>
       </x:c>
       <x:c r="X101" s="78" t="str">
-        <x:v>Multiply</x:v>
+        <x:v>Add</x:v>
       </x:c>
       <x:c r="Y101" s="78" t="str">
-        <x:v>2.8</x:v>
+        <x:v>0.005</x:v>
       </x:c>
       <x:c r="Z101" s="78" t="str">
-        <x:v>Part.StatModifier</x:v>
+        <x:v>Part.ApplyBleedOnHitChance</x:v>
       </x:c>
       <x:c r="AA101" s="78" t="str">
         <x:v>None</x:v>
@@ -22488,19 +22469,19 @@
         <x:v>None</x:v>
       </x:c>
       <x:c r="AC101" s="78" t="str">
-        <x:v>None</x:v>
+        <x:v>Chance</x:v>
       </x:c>
       <x:c r="AD101" s="78" t="str">
-        <x:v>0</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="AE101" s="78" t="str">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AF101" s="78" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AG101" s="78" t="str">
-        <x:v>Unique</x:v>
+        <x:v>Stackable</x:v>
       </x:c>
       <x:c r="AH101" s="78" t="str">
         <x:v>true</x:v>
@@ -22510,7 +22491,7 @@
         <x:v>武器插槽C</x:v>
       </x:c>
       <x:c r="AK101" s="78" t="str">
-        <x:v>49</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="102" s="71" customFormat="1" ht="22" customHeight="1">
@@ -22531,31 +22512,31 @@
       <x:c r="O102" s="74"/>
       <x:c r="P102" s="74"/>
       <x:c r="R102" s="78" t="str">
-        <x:v>PE_GUN_RAPID_MUZZLE_1</x:v>
+        <x:v>PE_GUN_LIFESTEAL_GUNACTION_1</x:v>
       </x:c>
       <x:c r="S102" s="78" t="str">
-        <x:v>P_GUN_RAPID_MUZZLE</x:v>
+        <x:v>P_GUN_LIFESTEAL_GUNACTION</x:v>
       </x:c>
       <x:c r="T102" s="78" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U102" s="78" t="str">
-        <x:v>OnEquip</x:v>
+        <x:v>OnHit</x:v>
       </x:c>
       <x:c r="V102" s="78" t="str">
-        <x:v>StatModifier</x:v>
+        <x:v>UniqueBehavior</x:v>
       </x:c>
       <x:c r="W102" s="78" t="str">
-        <x:v>AttackSpeed</x:v>
+        <x:v>RuntimeBehavior</x:v>
       </x:c>
       <x:c r="X102" s="78" t="str">
-        <x:v>Multiply</x:v>
+        <x:v>Add</x:v>
       </x:c>
       <x:c r="Y102" s="78" t="str">
-        <x:v>1.5</x:v>
+        <x:v>0.01</x:v>
       </x:c>
       <x:c r="Z102" s="78" t="str">
-        <x:v>Part.StatModifier</x:v>
+        <x:v>Part.HealOnHit</x:v>
       </x:c>
       <x:c r="AA102" s="78" t="str">
         <x:v>None</x:v>
@@ -22576,19 +22557,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AG102" s="78" t="str">
-        <x:v>Unique</x:v>
+        <x:v>Stackable</x:v>
       </x:c>
       <x:c r="AH102" s="78" t="str">
-        <x:v>false</x:v>
-      </x:c>
-      <x:c r="AI102" s="78" t="str">
-        <x:v>策划确认不想要</x:v>
-      </x:c>
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="AI102" s="78"/>
       <x:c r="AJ102" s="78" t="str">
         <x:v>武器插槽C</x:v>
       </x:c>
       <x:c r="AK102" s="78" t="str">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="103" s="71" customFormat="1" ht="22" customHeight="1">
@@ -22609,31 +22588,31 @@
       <x:c r="O103" s="74"/>
       <x:c r="P103" s="74"/>
       <x:c r="R103" s="78" t="str">
-        <x:v>PE_GUN_EXPLOSIVE_MUZZLE_1</x:v>
+        <x:v>PE_GUN_HITSHARD_GUNACTION_1</x:v>
       </x:c>
       <x:c r="S103" s="78" t="str">
-        <x:v>P_GUN_EXPLOSIVE_MUZZLE</x:v>
+        <x:v>P_GUN_HITSHARD_GUNACTION</x:v>
       </x:c>
       <x:c r="T103" s="78" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U103" s="78" t="str">
-        <x:v>OnEquip</x:v>
+        <x:v>OnHit</x:v>
       </x:c>
       <x:c r="V103" s="78" t="str">
-        <x:v>StatModifier</x:v>
+        <x:v>UniqueBehavior</x:v>
       </x:c>
       <x:c r="W103" s="78" t="str">
-        <x:v>ExplosionRadius</x:v>
+        <x:v>RuntimeBehavior</x:v>
       </x:c>
       <x:c r="X103" s="78" t="str">
-        <x:v>Override</x:v>
+        <x:v>Add</x:v>
       </x:c>
       <x:c r="Y103" s="78" t="str">
-        <x:v>100</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="Z103" s="78" t="str">
-        <x:v>Part.StatModifier</x:v>
+        <x:v>Part.DropShardEveryHits</x:v>
       </x:c>
       <x:c r="AA103" s="78" t="str">
         <x:v>None</x:v>
@@ -22642,10 +22621,10 @@
         <x:v>None</x:v>
       </x:c>
       <x:c r="AC103" s="78" t="str">
-        <x:v>None</x:v>
+        <x:v>HitThreshold</x:v>
       </x:c>
       <x:c r="AD103" s="78" t="str">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AE103" s="78" t="str">
         <x:v>0</x:v>
@@ -22654,7 +22633,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AG103" s="78" t="str">
-        <x:v>Unique</x:v>
+        <x:v>Stackable</x:v>
       </x:c>
       <x:c r="AH103" s="78" t="str">
         <x:v>true</x:v>
@@ -22664,7 +22643,7 @@
         <x:v>武器插槽C</x:v>
       </x:c>
       <x:c r="AK103" s="78" t="str">
-        <x:v>51</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="104" s="71" customFormat="1" ht="22" customHeight="1">
@@ -22685,16 +22664,16 @@
       <x:c r="O104" s="74"/>
       <x:c r="P104" s="74"/>
       <x:c r="R104" s="78" t="str">
-        <x:v>PE_GUN_PIERCING_MUZZLE_1</x:v>
+        <x:v>PE_GUN_ATTACKSTACK_GUNACTION_1</x:v>
       </x:c>
       <x:c r="S104" s="78" t="str">
-        <x:v>P_GUN_PIERCING_MUZZLE</x:v>
+        <x:v>P_GUN_ATTACKSTACK_GUNACTION</x:v>
       </x:c>
       <x:c r="T104" s="78" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U104" s="78" t="str">
-        <x:v>OnCriticalHit</x:v>
+        <x:v>OnAttack</x:v>
       </x:c>
       <x:c r="V104" s="78" t="str">
         <x:v>UniqueBehavior</x:v>
@@ -22703,13 +22682,13 @@
         <x:v>RuntimeBehavior</x:v>
       </x:c>
       <x:c r="X104" s="78" t="str">
-        <x:v>Override</x:v>
+        <x:v>Add</x:v>
       </x:c>
       <x:c r="Y104" s="78" t="str">
-        <x:v>1</x:v>
+        <x:v>0.01</x:v>
       </x:c>
       <x:c r="Z104" s="78" t="str">
-        <x:v>Part.ProjectilePierceOnCritical</x:v>
+        <x:v>Part.AttackSpeedOnAttack</x:v>
       </x:c>
       <x:c r="AA104" s="78" t="str">
         <x:v>None</x:v>
@@ -22718,19 +22697,19 @@
         <x:v>None</x:v>
       </x:c>
       <x:c r="AC104" s="78" t="str">
-        <x:v>None</x:v>
+        <x:v>MaxStacks</x:v>
       </x:c>
       <x:c r="AD104" s="78" t="str">
-        <x:v>0</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="AE104" s="78" t="str">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AF104" s="78" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AG104" s="78" t="str">
-        <x:v>Unique</x:v>
+        <x:v>IndependentTimed</x:v>
       </x:c>
       <x:c r="AH104" s="78" t="str">
         <x:v>true</x:v>
@@ -22740,7 +22719,7 @@
         <x:v>武器插槽C</x:v>
       </x:c>
       <x:c r="AK104" s="78" t="str">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="105" s="71" customFormat="1" ht="22" customHeight="1">
@@ -22760,64 +22739,26 @@
       <x:c r="N105" s="74"/>
       <x:c r="O105" s="74"/>
       <x:c r="P105" s="74"/>
-      <x:c r="R105" s="78" t="str">
-        <x:v>PE_GUN_BLEED_MUZZLE_1</x:v>
-      </x:c>
-      <x:c r="S105" s="78" t="str">
-        <x:v>P_GUN_BLEED_MUZZLE</x:v>
-      </x:c>
-      <x:c r="T105" s="78" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U105" s="78" t="str">
-        <x:v>OnHit</x:v>
-      </x:c>
-      <x:c r="V105" s="78" t="str">
-        <x:v>UniqueBehavior</x:v>
-      </x:c>
-      <x:c r="W105" s="78" t="str">
-        <x:v>RuntimeBehavior</x:v>
-      </x:c>
-      <x:c r="X105" s="78" t="str">
-        <x:v>Add</x:v>
-      </x:c>
-      <x:c r="Y105" s="78" t="str">
-        <x:v>0.005</x:v>
-      </x:c>
-      <x:c r="Z105" s="78" t="str">
-        <x:v>Part.ApplyBleedOnHitChance</x:v>
-      </x:c>
-      <x:c r="AA105" s="78" t="str">
-        <x:v>None</x:v>
-      </x:c>
-      <x:c r="AB105" s="78" t="str">
-        <x:v>None</x:v>
-      </x:c>
-      <x:c r="AC105" s="78" t="str">
-        <x:v>Chance</x:v>
-      </x:c>
-      <x:c r="AD105" s="78" t="str">
-        <x:v>0.3</x:v>
-      </x:c>
-      <x:c r="AE105" s="78" t="str">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="AF105" s="78" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AG105" s="78" t="str">
-        <x:v>Stackable</x:v>
-      </x:c>
-      <x:c r="AH105" s="78" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="AI105" s="78"/>
-      <x:c r="AJ105" s="78" t="str">
-        <x:v>武器插槽C</x:v>
-      </x:c>
-      <x:c r="AK105" s="78" t="str">
-        <x:v>53</x:v>
-      </x:c>
+      <x:c r="R105"/>
+      <x:c r="S105"/>
+      <x:c r="T105"/>
+      <x:c r="U105"/>
+      <x:c r="V105"/>
+      <x:c r="W105"/>
+      <x:c r="X105"/>
+      <x:c r="Y105"/>
+      <x:c r="Z105"/>
+      <x:c r="AA105"/>
+      <x:c r="AB105"/>
+      <x:c r="AC105"/>
+      <x:c r="AD105"/>
+      <x:c r="AE105"/>
+      <x:c r="AF105"/>
+      <x:c r="AG105"/>
+      <x:c r="AH105"/>
+      <x:c r="AI105"/>
+      <x:c r="AJ105"/>
+      <x:c r="AK105"/>
     </x:row>
     <x:row r="106" s="71" customFormat="1" ht="22" customHeight="1">
       <x:c r="A106" s="74"/>
@@ -22836,64 +22777,26 @@
       <x:c r="N106" s="74"/>
       <x:c r="O106" s="74"/>
       <x:c r="P106" s="74"/>
-      <x:c r="R106" s="78" t="str">
-        <x:v>PE_GUN_LIFESTEAL_GUNACTION_1</x:v>
-      </x:c>
-      <x:c r="S106" s="78" t="str">
-        <x:v>P_GUN_LIFESTEAL_GUNACTION</x:v>
-      </x:c>
-      <x:c r="T106" s="78" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U106" s="78" t="str">
-        <x:v>OnHit</x:v>
-      </x:c>
-      <x:c r="V106" s="78" t="str">
-        <x:v>UniqueBehavior</x:v>
-      </x:c>
-      <x:c r="W106" s="78" t="str">
-        <x:v>RuntimeBehavior</x:v>
-      </x:c>
-      <x:c r="X106" s="78" t="str">
-        <x:v>Add</x:v>
-      </x:c>
-      <x:c r="Y106" s="78" t="str">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="Z106" s="78" t="str">
-        <x:v>Part.HealOnHit</x:v>
-      </x:c>
-      <x:c r="AA106" s="78" t="str">
-        <x:v>None</x:v>
-      </x:c>
-      <x:c r="AB106" s="78" t="str">
-        <x:v>None</x:v>
-      </x:c>
-      <x:c r="AC106" s="78" t="str">
-        <x:v>None</x:v>
-      </x:c>
-      <x:c r="AD106" s="78" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AE106" s="78" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AF106" s="78" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AG106" s="78" t="str">
-        <x:v>Stackable</x:v>
-      </x:c>
-      <x:c r="AH106" s="78" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="AI106" s="78"/>
-      <x:c r="AJ106" s="78" t="str">
-        <x:v>武器插槽C</x:v>
-      </x:c>
-      <x:c r="AK106" s="78" t="str">
-        <x:v>54</x:v>
-      </x:c>
+      <x:c r="R106"/>
+      <x:c r="S106"/>
+      <x:c r="T106"/>
+      <x:c r="U106"/>
+      <x:c r="V106"/>
+      <x:c r="W106"/>
+      <x:c r="X106"/>
+      <x:c r="Y106"/>
+      <x:c r="Z106"/>
+      <x:c r="AA106"/>
+      <x:c r="AB106"/>
+      <x:c r="AC106"/>
+      <x:c r="AD106"/>
+      <x:c r="AE106"/>
+      <x:c r="AF106"/>
+      <x:c r="AG106"/>
+      <x:c r="AH106"/>
+      <x:c r="AI106"/>
+      <x:c r="AJ106"/>
+      <x:c r="AK106"/>
     </x:row>
     <x:row r="107" s="71" customFormat="1" ht="75" customHeight="1">
       <x:c r="A107" s="74"/>
@@ -22912,64 +22815,26 @@
       <x:c r="N107" s="74"/>
       <x:c r="O107" s="74"/>
       <x:c r="P107" s="74"/>
-      <x:c r="R107" s="78" t="str">
-        <x:v>PE_GUN_HITSHARD_GUNACTION_1</x:v>
-      </x:c>
-      <x:c r="S107" s="78" t="str">
-        <x:v>P_GUN_HITSHARD_GUNACTION</x:v>
-      </x:c>
-      <x:c r="T107" s="78" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U107" s="78" t="str">
-        <x:v>OnHit</x:v>
-      </x:c>
-      <x:c r="V107" s="78" t="str">
-        <x:v>UniqueBehavior</x:v>
-      </x:c>
-      <x:c r="W107" s="78" t="str">
-        <x:v>RuntimeBehavior</x:v>
-      </x:c>
-      <x:c r="X107" s="78" t="str">
-        <x:v>Add</x:v>
-      </x:c>
-      <x:c r="Y107" s="78" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Z107" s="78" t="str">
-        <x:v>Part.DropShardEveryHits</x:v>
-      </x:c>
-      <x:c r="AA107" s="78" t="str">
-        <x:v>None</x:v>
-      </x:c>
-      <x:c r="AB107" s="78" t="str">
-        <x:v>None</x:v>
-      </x:c>
-      <x:c r="AC107" s="78" t="str">
-        <x:v>HitThreshold</x:v>
-      </x:c>
-      <x:c r="AD107" s="78" t="str">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="AE107" s="78" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AF107" s="78" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AG107" s="78" t="str">
-        <x:v>Stackable</x:v>
-      </x:c>
-      <x:c r="AH107" s="78" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="AI107" s="78"/>
-      <x:c r="AJ107" s="78" t="str">
-        <x:v>武器插槽C</x:v>
-      </x:c>
-      <x:c r="AK107" s="78" t="str">
-        <x:v>55</x:v>
-      </x:c>
+      <x:c r="R107"/>
+      <x:c r="S107"/>
+      <x:c r="T107"/>
+      <x:c r="U107"/>
+      <x:c r="V107"/>
+      <x:c r="W107"/>
+      <x:c r="X107"/>
+      <x:c r="Y107"/>
+      <x:c r="Z107"/>
+      <x:c r="AA107"/>
+      <x:c r="AB107"/>
+      <x:c r="AC107"/>
+      <x:c r="AD107"/>
+      <x:c r="AE107"/>
+      <x:c r="AF107"/>
+      <x:c r="AG107"/>
+      <x:c r="AH107"/>
+      <x:c r="AI107"/>
+      <x:c r="AJ107"/>
+      <x:c r="AK107"/>
     </x:row>
     <x:row r="108" s="71" customFormat="1" ht="22" customHeight="1">
       <x:c r="A108" s="74"/>
@@ -22988,64 +22853,26 @@
       <x:c r="N108" s="74"/>
       <x:c r="O108" s="74"/>
       <x:c r="P108" s="74"/>
-      <x:c r="R108" s="78" t="str">
-        <x:v>PE_GUN_ATTACKSTACK_GUNACTION_1</x:v>
-      </x:c>
-      <x:c r="S108" s="78" t="str">
-        <x:v>P_GUN_ATTACKSTACK_GUNACTION</x:v>
-      </x:c>
-      <x:c r="T108" s="78" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U108" s="78" t="str">
-        <x:v>OnAttack</x:v>
-      </x:c>
-      <x:c r="V108" s="78" t="str">
-        <x:v>UniqueBehavior</x:v>
-      </x:c>
-      <x:c r="W108" s="78" t="str">
-        <x:v>RuntimeBehavior</x:v>
-      </x:c>
-      <x:c r="X108" s="78" t="str">
-        <x:v>Add</x:v>
-      </x:c>
-      <x:c r="Y108" s="78" t="str">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="Z108" s="78" t="str">
-        <x:v>Part.AttackSpeedOnAttack</x:v>
-      </x:c>
-      <x:c r="AA108" s="78" t="str">
-        <x:v>None</x:v>
-      </x:c>
-      <x:c r="AB108" s="78" t="str">
-        <x:v>None</x:v>
-      </x:c>
-      <x:c r="AC108" s="78" t="str">
-        <x:v>MaxStacks</x:v>
-      </x:c>
-      <x:c r="AD108" s="78" t="str">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="AE108" s="78" t="str">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="AF108" s="78" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AG108" s="78" t="str">
-        <x:v>IndependentTimed</x:v>
-      </x:c>
-      <x:c r="AH108" s="78" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="AI108" s="78"/>
-      <x:c r="AJ108" s="78" t="str">
-        <x:v>武器插槽C</x:v>
-      </x:c>
-      <x:c r="AK108" s="78" t="str">
-        <x:v>56</x:v>
-      </x:c>
+      <x:c r="R108"/>
+      <x:c r="S108"/>
+      <x:c r="T108"/>
+      <x:c r="U108"/>
+      <x:c r="V108"/>
+      <x:c r="W108"/>
+      <x:c r="X108"/>
+      <x:c r="Y108"/>
+      <x:c r="Z108"/>
+      <x:c r="AA108"/>
+      <x:c r="AB108"/>
+      <x:c r="AC108"/>
+      <x:c r="AD108"/>
+      <x:c r="AE108"/>
+      <x:c r="AF108"/>
+      <x:c r="AG108"/>
+      <x:c r="AH108"/>
+      <x:c r="AI108"/>
+      <x:c r="AJ108"/>
+      <x:c r="AK108"/>
     </x:row>
     <x:row r="109" s="71" customFormat="1" ht="22" customHeight="1">
       <x:c r="A109" s="74"/>
@@ -23558,7 +23385,7 @@
       <x:c r="P123" s="68" t="n"/>
     </x:row>
   </x:sheetData>
-  <sheetProtection xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="0" sort="0"/>
+  <x:sheetProtection xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="0" sort="0"/>
   <x:mergeCells>
     <x:mergeCell ref="A17:D17"/>
     <x:mergeCell ref="P44:S44"/>
@@ -23646,10 +23473,10 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="4">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9e0a0b3e269c41c9"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf22681908872442d"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref37438e40c743cf"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R27c6326bbce146ed"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Radaa1e5471e84320"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2bdc8979eb8b44cd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfa01a99fefc649fb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb0cb2b5d95742f3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -23706,7 +23533,7 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <sheetProtection xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
+  <x:sheetProtection xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
@@ -24245,7 +24072,7 @@
       <x:c r="K11" s="78" t="n"/>
     </x:row>
   </x:sheetData>
-  <sheetProtection xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="0" sort="0"/>
+  <x:sheetProtection xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="0" sort="0"/>
   <x:mergeCells>
     <x:mergeCell ref="A1:K1"/>
     <x:mergeCell ref="A2:D2"/>
@@ -24272,7 +24099,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfed64682911f42b4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R010b879bc92b471a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -24907,13 +24734,13 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <sheetProtection xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="0"/>
+  <x:sheetProtection xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="4">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb969ac79b9a34a6b"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d1c3b270ee84b49"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4d57b25284f24bcf"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R07db0d465c0b48f8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b4f568fb0bf4570"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R52e2e1cce5ef48e0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R327a791c20d549ba"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R52631c77d03e46b2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Design/Data/ReEchoData.xlsx
+++ b/Design/Data/ReEchoData.xlsx
@@ -19464,15 +19464,17 @@
         <x:v>Grip|UniqueBehavior|ActiveAttack</x:v>
       </x:c>
       <x:c r="I71" s="78" t="str">
-        <x:v>true</x:v>
+        <x:v>false</x:v>
       </x:c>
       <x:c r="J71" s="78" t="str">
         <x:v>Approved</x:v>
       </x:c>
       <x:c r="K71" s="78" t="str">
-        <x:v>Implemented</x:v>
-      </x:c>
-      <x:c r="L71" s="78"/>
+        <x:v>Disabled</x:v>
+      </x:c>
+      <x:c r="L71" s="78" t="str">
+        <x:v>策划确认禁用</x:v>
+      </x:c>
       <x:c r="M71" s="78" t="str">
         <x:v>武器插槽C</x:v>
       </x:c>
@@ -19480,10 +19482,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="O71" s="78" t="str">
-        <x:v>true</x:v>
+        <x:v>false</x:v>
       </x:c>
       <x:c r="P71" s="78" t="str">
-        <x:v>45</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="R71" s="78" t="str">
         <x:v>PE_BOW_CRITBLEED_ARROWHEAD_1</x:v>
@@ -20210,15 +20212,17 @@
         <x:v>SwordBlade|UniqueBehavior|Meteor</x:v>
       </x:c>
       <x:c r="I78" s="78" t="str">
-        <x:v>true</x:v>
+        <x:v>false</x:v>
       </x:c>
       <x:c r="J78" s="78" t="str">
         <x:v>Approved</x:v>
       </x:c>
       <x:c r="K78" s="78" t="str">
-        <x:v>Implemented</x:v>
-      </x:c>
-      <x:c r="L78" s="78"/>
+        <x:v>Disabled</x:v>
+      </x:c>
+      <x:c r="L78" s="78" t="str">
+        <x:v>策划确认禁用</x:v>
+      </x:c>
       <x:c r="M78" s="78" t="str">
         <x:v>武器插槽C</x:v>
       </x:c>
@@ -20226,10 +20230,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="O78" s="78" t="str">
-        <x:v>true</x:v>
+        <x:v>false</x:v>
       </x:c>
       <x:c r="P78" s="78" t="str">
-        <x:v>45</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="R78" s="78" t="str">
         <x:v>PE_SCYTHE_LIFESTEAL_ROTARYBLADE_1</x:v>
@@ -21130,9 +21134,11 @@
         <x:v>Unique</x:v>
       </x:c>
       <x:c r="AH86" s="78" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="AI86" s="78"/>
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="AI86" s="78" t="str">
+        <x:v>策划确认禁用</x:v>
+      </x:c>
       <x:c r="AJ86" s="78" t="str">
         <x:v>武器插槽C</x:v>
       </x:c>
@@ -21236,9 +21242,11 @@
         <x:v>Unique</x:v>
       </x:c>
       <x:c r="AH87" s="78" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="AI87" s="78"/>
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="AI87" s="78" t="str">
+        <x:v>策划确认禁用</x:v>
+      </x:c>
       <x:c r="AJ87" s="78" t="str">
         <x:v>武器插槽C</x:v>
       </x:c>
@@ -21660,9 +21668,11 @@
         <x:v>Unique</x:v>
       </x:c>
       <x:c r="AH91" s="78" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="AI91" s="78"/>
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="AI91" s="78" t="str">
+        <x:v>策划确认禁用</x:v>
+      </x:c>
       <x:c r="AJ91" s="78" t="str">
         <x:v>武器插槽C</x:v>
       </x:c>
@@ -21766,9 +21776,11 @@
         <x:v>Unique</x:v>
       </x:c>
       <x:c r="AH92" s="78" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="AI92" s="78"/>
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="AI92" s="78" t="str">
+        <x:v>策划确认禁用</x:v>
+      </x:c>
       <x:c r="AJ92" s="78" t="str">
         <x:v>武器插槽C</x:v>
       </x:c>

--- a/Design/Data/ReEchoData.xlsx
+++ b/Design/Data/ReEchoData.xlsx
@@ -17486,10 +17486,10 @@
         <x:v>AttackSpeed</x:v>
       </x:c>
       <x:c r="X52" s="78" t="str">
-        <x:v>Multiply</x:v>
+        <x:v>Add</x:v>
       </x:c>
       <x:c r="Y52" s="78" t="n">
-        <x:v>1.6</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="Z52" s="78" t="str">
         <x:v>Part.StatModifier</x:v>
@@ -17698,10 +17698,10 @@
         <x:v>AttackSpeed</x:v>
       </x:c>
       <x:c r="X54" s="78" t="str">
-        <x:v>Multiply</x:v>
+        <x:v>Add</x:v>
       </x:c>
       <x:c r="Y54" s="78" t="n">
-        <x:v>0.7</x:v>
+        <x:v>-0.3</x:v>
       </x:c>
       <x:c r="Z54" s="78" t="str">
         <x:v>Part.StatModifier</x:v>
@@ -17910,10 +17910,10 @@
         <x:v>AttackSpeed</x:v>
       </x:c>
       <x:c r="X56" s="78" t="str">
-        <x:v>Multiply</x:v>
+        <x:v>Add</x:v>
       </x:c>
       <x:c r="Y56" s="78" t="n">
-        <x:v>1.4</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="Z56" s="78" t="str">
         <x:v>Part.StatModifier</x:v>
@@ -18334,10 +18334,10 @@
         <x:v>AttackSpeed</x:v>
       </x:c>
       <x:c r="X60" s="78" t="str">
-        <x:v>Multiply</x:v>
+        <x:v>Add</x:v>
       </x:c>
       <x:c r="Y60" s="78" t="n">
-        <x:v>0.8</x:v>
+        <x:v>-0.2</x:v>
       </x:c>
       <x:c r="Z60" s="78" t="str">
         <x:v>Part.StatModifier</x:v>
@@ -18652,10 +18652,10 @@
         <x:v>AttackSpeed</x:v>
       </x:c>
       <x:c r="X63" s="78" t="str">
-        <x:v>Multiply</x:v>
+        <x:v>Add</x:v>
       </x:c>
       <x:c r="Y63" s="78" t="n">
-        <x:v>1.2</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="Z63" s="78" t="str">
         <x:v>Part.StatModifier</x:v>
@@ -18758,10 +18758,10 @@
         <x:v>AttackSpeed</x:v>
       </x:c>
       <x:c r="X64" s="78" t="str">
-        <x:v>Multiply</x:v>
+        <x:v>Add</x:v>
       </x:c>
       <x:c r="Y64" s="78" t="n">
-        <x:v>0.7</x:v>
+        <x:v>-0.3</x:v>
       </x:c>
       <x:c r="Z64" s="78" t="str">
         <x:v>Part.StatModifier</x:v>
@@ -20780,10 +20780,10 @@
         <x:v>AttackSpeed</x:v>
       </x:c>
       <x:c r="X83" s="78" t="str">
-        <x:v>Multiply</x:v>
+        <x:v>Add</x:v>
       </x:c>
       <x:c r="Y83" s="78" t="str">
-        <x:v>0.5</x:v>
+        <x:v>-0.5</x:v>
       </x:c>
       <x:c r="Z83" s="78" t="str">
         <x:v>Part.StatModifier</x:v>
@@ -22072,10 +22072,10 @@
         <x:v>AttackSpeed</x:v>
       </x:c>
       <x:c r="X96" s="78" t="str">
-        <x:v>Multiply</x:v>
+        <x:v>Add</x:v>
       </x:c>
       <x:c r="Y96" s="78" t="str">
-        <x:v>0.166666667</x:v>
+        <x:v>-5</x:v>
       </x:c>
       <x:c r="Z96" s="78" t="str">
         <x:v>Part.StatModifier</x:v>
@@ -22224,10 +22224,10 @@
         <x:v>AttackSpeed</x:v>
       </x:c>
       <x:c r="X98" s="78" t="str">
-        <x:v>Multiply</x:v>
+        <x:v>Add</x:v>
       </x:c>
       <x:c r="Y98" s="78" t="str">
-        <x:v>1.5</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="Z98" s="78" t="str">
         <x:v>Part.StatModifier</x:v>

--- a/Design/Data/ReEchoData.xlsx
+++ b/Design/Data/ReEchoData.xlsx
@@ -17592,10 +17592,10 @@
         <x:v>DamageCoefficient</x:v>
       </x:c>
       <x:c r="X53" s="78" t="str">
-        <x:v>Multiply</x:v>
+        <x:v>Add</x:v>
       </x:c>
       <x:c r="Y53" s="78" t="n">
-        <x:v>0.6</x:v>
+        <x:v>-0.4</x:v>
       </x:c>
       <x:c r="Z53" s="78" t="str">
         <x:v>Part.StatModifier</x:v>
@@ -17804,10 +17804,10 @@
         <x:v>DamageCoefficient</x:v>
       </x:c>
       <x:c r="X55" s="78" t="str">
-        <x:v>Multiply</x:v>
+        <x:v>Add</x:v>
       </x:c>
       <x:c r="Y55" s="78" t="n">
-        <x:v>1.5</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="Z55" s="78" t="str">
         <x:v>Part.StatModifier</x:v>
@@ -18864,10 +18864,10 @@
         <x:v>DamageCoefficient</x:v>
       </x:c>
       <x:c r="X65" s="78" t="str">
-        <x:v>Multiply</x:v>
+        <x:v>Add</x:v>
       </x:c>
       <x:c r="Y65" s="78" t="n">
-        <x:v>1.5</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="Z65" s="78" t="str">
         <x:v>Part.StatModifier</x:v>
@@ -22160,10 +22160,10 @@
         <x:v>DamageCoefficient</x:v>
       </x:c>
       <x:c r="X97" s="78" t="str">
-        <x:v>Multiply</x:v>
+        <x:v>Add</x:v>
       </x:c>
       <x:c r="Y97" s="78" t="str">
-        <x:v>2.8</x:v>
+        <x:v>1.8</x:v>
       </x:c>
       <x:c r="Z97" s="78" t="str">
         <x:v>Part.StatModifier</x:v>

--- a/Design/Data/ReEchoData.xlsx
+++ b/Design/Data/ReEchoData.xlsx
@@ -24427,16 +24427,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C24" s="82" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D24" s="82" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D24" s="82" t="n">
-        <x:v>4</x:v>
-      </x:c>
       <x:c r="E24" s="82" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="F24" s="82" t="n"/>
-      <x:c r="G24" s="82" t="n"/>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F24" s="82"/>
+      <x:c r="G24" s="82"/>
       <x:c r="H24" s="82" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">投放系统</x:t>
@@ -24459,16 +24459,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C25" s="82" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D25" s="82" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D25" s="82" t="n">
-        <x:v>4</x:v>
-      </x:c>
       <x:c r="E25" s="82" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="F25" s="82" t="n"/>
-      <x:c r="G25" s="82" t="n"/>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F25" s="82"/>
+      <x:c r="G25" s="82"/>
       <x:c r="H25" s="82" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">投放系统</x:t>
@@ -24488,7 +24488,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B26" s="82" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C26" s="82" t="n">
         <x:v>3</x:v>
@@ -24497,13 +24497,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E26" s="82" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F26" s="82" t="n">
-        <x:v>10</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G26" s="82" t="n">
-        <x:v>13</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H26" s="82" t="inlineStr">
         <x:is>
@@ -24524,7 +24524,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B27" s="82" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C27" s="82" t="n">
         <x:v>3</x:v>
@@ -24533,13 +24533,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E27" s="82" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F27" s="82" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F27" s="82" t="n">
-        <x:v>10</x:v>
-      </x:c>
       <x:c r="G27" s="82" t="n">
-        <x:v>13</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H27" s="82" t="inlineStr">
         <x:is>
@@ -24560,22 +24560,22 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B28" s="82" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C28" s="82" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D28" s="82" t="n">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E28" s="82" t="n">
-        <x:v>9</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F28" s="82" t="n">
-        <x:v>15</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G28" s="82" t="n">
-        <x:v>20</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H28" s="82" t="inlineStr">
         <x:is>
@@ -24596,22 +24596,22 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B29" s="82" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C29" s="82" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D29" s="82" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E29" s="82" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F29" s="82" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="E29" s="82" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F29" s="82" t="n">
-        <x:v>15</x:v>
-      </x:c>
       <x:c r="G29" s="82" t="n">
-        <x:v>20</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H29" s="82" t="inlineStr">
         <x:is>
@@ -24632,22 +24632,22 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B30" s="82" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C30" s="82" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D30" s="82" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E30" s="82" t="n">
-        <x:v>9</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F30" s="82" t="n">
-        <x:v>15</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G30" s="82" t="n">
-        <x:v>20</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H30" s="82" t="inlineStr">
         <x:is>
@@ -24668,22 +24668,22 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B31" s="82" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C31" s="82" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D31" s="82" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="E31" s="82" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="F31" s="82" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="F31" s="82" t="n">
-        <x:v>15</x:v>
-      </x:c>
       <x:c r="G31" s="82" t="n">
-        <x:v>20</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="H31" s="82" t="inlineStr">
         <x:is>

--- a/Design/Data/ReEchoData.xlsx
+++ b/Design/Data/ReEchoData.xlsx
@@ -32882,282 +32882,290 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="81" t="n">
+      <c r="A24" s="81">
         <v>1</v>
       </c>
-      <c r="B24" s="82" t="n">
+      <c r="B24" s="82">
         <v>2</v>
       </c>
-      <c r="C24" s="82" t="n">
+      <c r="C24" s="82">
         <v>2</v>
       </c>
-      <c r="D24" s="82" t="n">
+      <c r="D24" s="82">
         <v>3</v>
       </c>
-      <c r="E24" s="82" t="n">
+      <c r="E24" s="82">
         <v>3</v>
       </c>
-      <c r="F24" s="82" t="n"/>
-      <c r="G24" s="82" t="n"/>
+      <c r="F24" s="82">
+        <v>4</v>
+      </c>
+      <c r="G24" s="82">
+        <v>4</v>
+      </c>
       <c r="H24" s="82" t="inlineStr">
         <is>
-          <t>投放系统</t>
-        </is>
-      </c>
-      <c r="I24" s="82" t="n">
+          <t xml:space="preserve">投放系统</t>
+        </is>
+      </c>
+      <c r="I24" s="82">
         <v>40</v>
       </c>
       <c r="J24" s="82" t="inlineStr">
         <is>
-          <t>Elite blank: no elite reward in this encounter.</t>
+          <t xml:space="preserve">怪物掉落时间碎片配置</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="81" t="n">
+      <c r="A25" s="81">
         <v>2</v>
       </c>
-      <c r="B25" s="82" t="n">
+      <c r="B25" s="82">
         <v>2</v>
       </c>
-      <c r="C25" s="82" t="n">
+      <c r="C25" s="82">
         <v>2</v>
       </c>
-      <c r="D25" s="82" t="n">
+      <c r="D25" s="82">
         <v>3</v>
       </c>
-      <c r="E25" s="82" t="n">
+      <c r="E25" s="82">
         <v>3</v>
       </c>
-      <c r="F25" s="82" t="n"/>
-      <c r="G25" s="82" t="n"/>
+      <c r="F25" s="82">
+        <v>4</v>
+      </c>
+      <c r="G25" s="82">
+        <v>4</v>
+      </c>
       <c r="H25" s="82" t="inlineStr">
         <is>
-          <t>投放系统</t>
-        </is>
-      </c>
-      <c r="I25" s="82" t="n">
+          <t xml:space="preserve">投放系统</t>
+        </is>
+      </c>
+      <c r="I25" s="82">
         <v>41</v>
       </c>
       <c r="J25" s="82" t="inlineStr">
         <is>
-          <t>Elite blank: no elite reward in this encounter.</t>
+          <t xml:space="preserve">怪物掉落时间碎片配置</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="81" t="n">
+      <c r="A26" s="81">
         <v>3</v>
       </c>
-      <c r="B26" s="82" t="n">
+      <c r="B26" s="82">
         <v>3</v>
       </c>
-      <c r="C26" s="82" t="n">
+      <c r="C26" s="82">
         <v>3</v>
       </c>
-      <c r="D26" s="82" t="n">
+      <c r="D26" s="82">
         <v>4</v>
       </c>
-      <c r="E26" s="82" t="n">
+      <c r="E26" s="82">
         <v>4</v>
       </c>
-      <c r="F26" s="82" t="n">
+      <c r="F26" s="82">
         <v>5</v>
       </c>
-      <c r="G26" s="82" t="n">
+      <c r="G26" s="82">
         <v>5</v>
       </c>
       <c r="H26" s="82" t="inlineStr">
         <is>
-          <t>投放系统</t>
-        </is>
-      </c>
-      <c r="I26" s="82" t="n">
+          <t xml:space="preserve">投放系统</t>
+        </is>
+      </c>
+      <c r="I26" s="82">
         <v>42</v>
       </c>
       <c r="J26" s="82" t="inlineStr">
         <is>
-          <t>怪物掉落时间碎片配置</t>
+          <t xml:space="preserve">怪物掉落时间碎片配置</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="81" t="n">
+      <c r="A27" s="81">
         <v>4</v>
       </c>
-      <c r="B27" s="82" t="n">
+      <c r="B27" s="82">
         <v>3</v>
       </c>
-      <c r="C27" s="82" t="n">
+      <c r="C27" s="82">
         <v>3</v>
       </c>
-      <c r="D27" s="82" t="n">
+      <c r="D27" s="82">
         <v>4</v>
       </c>
-      <c r="E27" s="82" t="n">
+      <c r="E27" s="82">
         <v>4</v>
       </c>
-      <c r="F27" s="82" t="n">
+      <c r="F27" s="82">
         <v>6</v>
       </c>
-      <c r="G27" s="82" t="n">
+      <c r="G27" s="82">
         <v>6</v>
       </c>
       <c r="H27" s="82" t="inlineStr">
         <is>
-          <t>投放系统</t>
-        </is>
-      </c>
-      <c r="I27" s="82" t="n">
+          <t xml:space="preserve">投放系统</t>
+        </is>
+      </c>
+      <c r="I27" s="82">
         <v>43</v>
       </c>
       <c r="J27" s="82" t="inlineStr">
         <is>
-          <t>怪物掉落时间碎片配置</t>
+          <t xml:space="preserve">怪物掉落时间碎片配置</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="81" t="n">
+      <c r="A28" s="81">
         <v>5</v>
       </c>
-      <c r="B28" s="82" t="n">
+      <c r="B28" s="82">
         <v>3</v>
       </c>
-      <c r="C28" s="82" t="n">
+      <c r="C28" s="82">
         <v>3</v>
       </c>
-      <c r="D28" s="82" t="n">
+      <c r="D28" s="82">
         <v>5</v>
       </c>
-      <c r="E28" s="82" t="n">
+      <c r="E28" s="82">
         <v>5</v>
       </c>
-      <c r="F28" s="82" t="n">
+      <c r="F28" s="82">
         <v>6</v>
       </c>
-      <c r="G28" s="82" t="n">
+      <c r="G28" s="82">
         <v>6</v>
       </c>
       <c r="H28" s="82" t="inlineStr">
         <is>
-          <t>投放系统</t>
-        </is>
-      </c>
-      <c r="I28" s="82" t="n">
+          <t xml:space="preserve">投放系统</t>
+        </is>
+      </c>
+      <c r="I28" s="82">
         <v>44</v>
       </c>
       <c r="J28" s="82" t="inlineStr">
         <is>
-          <t>怪物掉落时间碎片配置</t>
+          <t xml:space="preserve">怪物掉落时间碎片配置</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="81" t="n">
+      <c r="A29" s="81">
         <v>6</v>
       </c>
-      <c r="B29" s="82" t="n">
+      <c r="B29" s="82">
         <v>4</v>
       </c>
-      <c r="C29" s="82" t="n">
+      <c r="C29" s="82">
         <v>4</v>
       </c>
-      <c r="D29" s="82" t="n">
+      <c r="D29" s="82">
         <v>5</v>
       </c>
-      <c r="E29" s="82" t="n">
+      <c r="E29" s="82">
         <v>5</v>
       </c>
-      <c r="F29" s="82" t="n">
+      <c r="F29" s="82">
         <v>7</v>
       </c>
-      <c r="G29" s="82" t="n">
+      <c r="G29" s="82">
         <v>7</v>
       </c>
       <c r="H29" s="82" t="inlineStr">
         <is>
-          <t>投放系统</t>
-        </is>
-      </c>
-      <c r="I29" s="82" t="n">
+          <t xml:space="preserve">投放系统</t>
+        </is>
+      </c>
+      <c r="I29" s="82">
         <v>45</v>
       </c>
       <c r="J29" s="82" t="inlineStr">
         <is>
-          <t>怪物掉落时间碎片配置</t>
+          <t xml:space="preserve">怪物掉落时间碎片配置</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="81" t="n">
+      <c r="A30" s="81">
         <v>7</v>
       </c>
-      <c r="B30" s="82" t="n">
+      <c r="B30" s="82">
         <v>4</v>
       </c>
-      <c r="C30" s="82" t="n">
+      <c r="C30" s="82">
         <v>4</v>
       </c>
-      <c r="D30" s="82" t="n">
+      <c r="D30" s="82">
         <v>6</v>
       </c>
-      <c r="E30" s="82" t="n">
+      <c r="E30" s="82">
         <v>6</v>
       </c>
-      <c r="F30" s="82" t="n">
+      <c r="F30" s="82">
         <v>8</v>
       </c>
-      <c r="G30" s="82" t="n">
+      <c r="G30" s="82">
         <v>8</v>
       </c>
       <c r="H30" s="82" t="inlineStr">
         <is>
-          <t>投放系统</t>
-        </is>
-      </c>
-      <c r="I30" s="82" t="n">
+          <t xml:space="preserve">投放系统</t>
+        </is>
+      </c>
+      <c r="I30" s="82">
         <v>46</v>
       </c>
       <c r="J30" s="82" t="inlineStr">
         <is>
-          <t>怪物掉落时间碎片配置</t>
+          <t xml:space="preserve">怪物掉落时间碎片配置</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="81" t="n">
+      <c r="A31" s="81">
         <v>8</v>
       </c>
-      <c r="B31" s="82" t="n">
+      <c r="B31" s="82">
         <v>4</v>
       </c>
-      <c r="C31" s="82" t="n">
+      <c r="C31" s="82">
         <v>4</v>
       </c>
-      <c r="D31" s="82" t="n">
+      <c r="D31" s="82">
         <v>7</v>
       </c>
-      <c r="E31" s="82" t="n">
+      <c r="E31" s="82">
         <v>7</v>
       </c>
-      <c r="F31" s="82" t="n">
+      <c r="F31" s="82">
         <v>9</v>
       </c>
-      <c r="G31" s="82" t="n">
+      <c r="G31" s="82">
         <v>9</v>
       </c>
       <c r="H31" s="82" t="inlineStr">
         <is>
-          <t>投放系统</t>
-        </is>
-      </c>
-      <c r="I31" s="82" t="n">
+          <t xml:space="preserve">投放系统</t>
+        </is>
+      </c>
+      <c r="I31" s="82">
         <v>47</v>
       </c>
       <c r="J31" s="82" t="inlineStr">
         <is>
-          <t>怪物掉落时间碎片配置</t>
+          <t xml:space="preserve">怪物掉落时间碎片配置</t>
         </is>
       </c>
     </row>

--- a/Design/Data/ReEchoData.xlsx
+++ b/Design/Data/ReEchoData.xlsx
@@ -3420,12 +3420,12 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CL68"/>
+  <dimension ref="A1:CJ66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <cols>
     <col width="15" customWidth="1" style="22" min="1" max="1"/>
@@ -7020,23 +7020,21 @@
         </is>
       </c>
     </row>
-    <row r="67"/>
-    <row r="68"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="2">
-    <tablePart r:id="rId1"/>
-    <tablePart r:id="rId2"/>
-  </tableParts>
   <dataValidations count="2">
-    <dataValidation type="list" sqref="C4" ns2:uid="{00000000-0002-0000-0B00-000000000000}">
+    <dataValidation sqref="C4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"true,false"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="J4 O4" ns2:uid="{00000000-0002-0000-0B00-000001000000}">
+    <dataValidation sqref="J4 O4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Add,Multiply,Override"</formula1>
     </dataValidation>
   </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="2">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -7047,7 +7045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <sheetData>
     <row r="1">
@@ -7383,8 +7381,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11"/>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="1" sort="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7395,12 +7391,12 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <cols>
     <col width="18" customWidth="1" style="41" min="1" max="3"/>
@@ -7428,7 +7424,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="43" t="inlineStr">
         <is>
@@ -7480,7 +7475,7 @@
           <t>Interval</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K4" s="43" t="inlineStr">
         <is>
           <t>MinCardPackTier</t>
         </is>
@@ -7923,51 +7918,49 @@
       </c>
       <c r="M11" s="30" t="inlineStr"/>
     </row>
-    <row r="12"/>
-    <row r="13"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="2">
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A1:L1"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
   <dataValidations count="7">
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="B5:B11" ns2:uid="{00000000-0002-0000-0D00-000000000000}">
+    <dataValidation sqref="B5:B11" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>INDIRECT("tblCharacters[Id]")</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="D5:D11" ns2:uid="{00000000-0002-0000-0D00-000001000000}">
+    <dataValidation sqref="D5:D11" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>"OnBuildInitialized,OnEncounterCompleted,OnTraitChoiceApplied,OnHealthChanged"</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="E5:E11" ns2:uid="{00000000-0002-0000-0D00-000002000000}">
+    <dataValidation sqref="E5:E11" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>"StatModifier,ExtraCardChoice"</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="F5:F11" ns2:uid="{00000000-0002-0000-0D00-000003000000}">
+    <dataValidation sqref="F5:F11" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>"MovementSpeed,CriticalRate,CriticalEffect,ReactionEfficiency,TraitCardChoice,PhysicalAttack,ElementalAttack"</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="G5:G11" ns2:uid="{00000000-0002-0000-0D00-000004000000}">
+    <dataValidation sqref="G5:G11" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>"Add"</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="I5:I11" ns2:uid="{00000000-0002-0000-0D00-000005000000}">
+    <dataValidation sqref="I5:I11" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>"Character.StaticStat,Character.PersistentGrowth,Character.EveryNth,Character.MissingHealthSteps"</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="L5:L11" ns2:uid="{00000000-0002-0000-0D00-000006000000}">
+    <dataValidation sqref="L5:L11" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>"true,false"</formula1>
     </dataValidation>
   </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T20"/>
+  <dimension ref="A1:R18"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="13.81640625" defaultRowHeight="13"/>
   <cols>
     <col width="25" customWidth="1" style="41" min="1" max="2"/>
@@ -8232,9 +8225,6 @@
       </c>
       <c r="J7" s="29" t="inlineStr"/>
     </row>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
     <row r="11" ht="25" customHeight="1" s="41">
       <c r="A11" s="42" t="inlineStr">
         <is>
@@ -8832,8 +8822,6 @@
       </c>
       <c r="R18" s="29" t="inlineStr"/>
     </row>
-    <row r="19"/>
-    <row r="20"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="3">
@@ -8841,62 +8829,62 @@
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A11:D11"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="2">
-    <tablePart r:id="rId1"/>
-    <tablePart r:id="rId2"/>
-  </tableParts>
   <dataValidations count="13">
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="A4:A7" ns2:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation sqref="A4:A7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_Elements_Id</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="B4:B7" ns2:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation sqref="B4:B7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_Elements_SourceWorkbookId</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="C4:C7" ns2:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation sqref="C4:C7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_Elements_Role</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="H4:H7" ns2:uid="{00000000-0002-0000-0100-000003000000}">
+    <dataValidation sqref="H4:H7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_Elements_VisualKey</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="I4:I7" ns2:uid="{00000000-0002-0000-0100-000004000000}">
+    <dataValidation sqref="I4:I7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_Elements_Enabled</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="D13:E18" ns2:uid="{00000000-0002-0000-0100-000005000000}">
+    <dataValidation sqref="D13:E18" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>INDIRECT("tblElements[Id]")</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="F13:F18" ns2:uid="{00000000-0002-0000-0100-000007000000}">
+    <dataValidation sqref="F13:F18" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_Reactions_BehaviorId</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="G13:G18" ns2:uid="{00000000-0002-0000-0100-000008000000}">
+    <dataValidation sqref="G13:G18" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_Reactions_FormulaId</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="K13:K18" ns2:uid="{00000000-0002-0000-0100-000009000000}">
+    <dataValidation sqref="K13:K18" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_Reactions_StatusId</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="N13:N18" ns2:uid="{00000000-0002-0000-0100-00000A000000}">
+    <dataValidation sqref="N13:N18" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_Reactions_CanCrit</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="O13:O18" ns2:uid="{00000000-0002-0000-0100-00000B000000}">
+    <dataValidation sqref="O13:O18" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_Reactions_AffectedByEchoEfficiency</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="P13:P18" ns2:uid="{00000000-0002-0000-0100-00000C000000}">
+    <dataValidation sqref="P13:P18" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_Reactions_ClearsAttachment</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="Q13:Q18" ns2:uid="{00000000-0002-0000-0100-00000D000000}">
+    <dataValidation sqref="Q13:Q18" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_Reactions_Enabled</formula1>
     </dataValidation>
   </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="2">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC114"/>
+  <dimension ref="A1:AA112"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="13.81640625" defaultRowHeight="13"/>
   <cols>
     <col width="25" customWidth="1" style="41" min="1" max="2"/>
@@ -12054,7 +12042,7 @@
       </c>
       <c r="E29" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">你的回响每击杀15名敌人，物攻&amp;元攻永久+1
+          <t>你的回响每击杀15名敌人，物攻&amp;元攻永久+1
 你每击杀15名敌人，回响效能永久+2%</t>
         </is>
       </c>
@@ -13126,7 +13114,7 @@
       </c>
       <c r="E38" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">你获得1000时间碎片，随机承受：
+          <t>你获得1000时间碎片，随机承受：
 你将不能再刷新商店/你将不能再购买额外卡牌组/敌人将不再掉落时间碎片</t>
         </is>
       </c>
@@ -14440,7 +14428,7 @@
       </c>
       <c r="E49" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">完成任一任务后，获得666时间碎片：
+          <t>完成任一任务后，获得666时间碎片：
 击杀111个敌人/结束战斗时≥22生命值/结束战斗时≤3生命值</t>
         </is>
       </c>
@@ -15393,7 +15381,7 @@
       </c>
       <c r="E57" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">你可以在商店赊账，欠款会收取10%利息/每关
+          <t>你可以在商店赊账，欠款会收取10%利息/每关
 第8关时，如果你还没有还清，会有很不好的事情发生！！</t>
         </is>
       </c>
@@ -16822,7 +16810,8 @@
       </c>
       <c r="E69" s="39" t="inlineStr">
         <is>
-          <t>每关结束后，你的时间碎片余额随机+150%或-50%；然后获得30时间碎片</t>
+          <t>每关结束后，你的时间碎片随机+200%或-50%；然后获得50时间碎片
+——策划 爆培嘉 敬上</t>
         </is>
       </c>
       <c r="F69" s="39" t="inlineStr">
@@ -16941,7 +16930,8 @@
       </c>
       <c r="E70" s="39" t="inlineStr">
         <is>
-          <t>随机获得以下任意数量项效果：1、暴击率+30%；2、物理攻击力+15；3、生命值调整为3</t>
+          <t>随机获得任意数量项效果：1、暴击率+50%；2、物理攻击力+15；3、生命值调整为5
+——策划 斑 敬上</t>
         </is>
       </c>
       <c r="F70" s="39" t="inlineStr">
@@ -17060,7 +17050,8 @@
       </c>
       <c r="E71" s="39" t="inlineStr">
         <is>
-          <t>回响接触到敌方单位时，对其造成12点物理伤害；接触到玩家时，为玩家回复6点生命值</t>
+          <t>回响触碰到敌方单位，会对其造成15物理伤害；触碰到你，转而回复10生命值。
+——策划 麦麦熊 敬上</t>
         </is>
       </c>
       <c r="F71" s="39" t="inlineStr">
@@ -17179,7 +17170,8 @@
       </c>
       <c r="E72" s="39" t="inlineStr">
         <is>
-          <t>失去所有时间碎片；每15时间碎片随机获得一项：生命值+1、物攻+1、元攻+1、暴击率+5%、暴击效果+10%、回响效能+5%、元素反应效能+5%；不足15的余数只会失去</t>
+          <t>失去所有时间碎片。每失去15时间碎片，随机获得一些属性！
+——策划 呕乐兮 敬上</t>
         </is>
       </c>
       <c r="F72" s="39" t="inlineStr">
@@ -17298,7 +17290,8 @@
       </c>
       <c r="E73" s="39" t="inlineStr">
         <is>
-          <t>每0.5秒，令自身4m范围内随机1个敌方单位眩晕1秒；范围内没有敌人时不触发</t>
+          <t>每0.5秒，令身边4m内的随机1名敌人【眩晕】至本关结束
+——特别鸣谢 程序 T爷</t>
         </is>
       </c>
       <c r="F73" s="39" t="inlineStr">
@@ -17417,7 +17410,8 @@
       </c>
       <c r="E74" s="39" t="inlineStr">
         <is>
-          <t>累计受到55点实际伤害后，随机获得5张尚未拥有的普通卡牌；卡池不足时获得实际剩余数量，只触发一次</t>
+          <t>你累计承受55伤害后，随机获得5张卡牌
+——特别鸣谢 程序 Jo爷</t>
         </is>
       </c>
       <c r="F74" s="39" t="inlineStr">
@@ -17536,7 +17530,8 @@
       </c>
       <c r="E75" s="39" t="inlineStr">
         <is>
-          <t>玩家与回响造成的物理伤害最终固定为0/10/100/1000/10000，对应概率15%/35%/40%/8%/2%</t>
+          <t>造成的所有物理伤害，随机被修正为可能带有很多0的数字！
+——特别鸣谢 美术 00</t>
         </is>
       </c>
       <c r="F75" s="39" t="inlineStr">
@@ -17655,7 +17650,8 @@
       </c>
       <c r="E76" s="39" t="inlineStr">
         <is>
-          <t>本关获得的时间碎片总量与上一关相比：每多5点，下一关获得量-1%；每少5点，下一关获得量+5%；每关结束重新结算</t>
+          <t>你的时间碎片获取方式，被赋予“ELO”机制
+——特别鸣谢 美术 子涵</t>
         </is>
       </c>
       <c r="F76" s="39" t="inlineStr">
@@ -17774,7 +17770,8 @@
       </c>
       <c r="E77" s="39" t="inlineStr">
         <is>
-          <t>每关结束时，生命值与生命上限+10、元素攻击力+1、物理攻击力+1</t>
+          <t>每一关卡结束后，获得15生命值&amp;2元攻&amp;2物攻
+——特别鸣谢 美术 雯雯</t>
         </is>
       </c>
       <c r="F77" s="39" t="inlineStr">
@@ -20107,79 +20104,77 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113"/>
-    <row r="114"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="1" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1"/>
   <mergeCells count="2">
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="2">
-    <tablePart r:id="rId1"/>
-    <tablePart r:id="rId2"/>
-  </tableParts>
   <dataValidations count="16">
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="F4:F77" ns2:uid="{00000000-0002-0000-0200-000000000000}">
+    <dataValidation sqref="F4:F77" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_Cards_Tags</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="G4:G77" ns2:uid="{00000000-0002-0000-0200-000001000000}" errorStyle="stop">
+    <dataValidation sqref="G4:G77" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
       <formula1>DV_Logic_Cards_PromotionRoleId</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="H4:H77" ns2:uid="{00000000-0002-0000-0200-000002000000}">
+    <dataValidation sqref="H4:H77" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_Cards_OfferGroup</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="I4:I77" ns2:uid="{00000000-0002-0000-0200-000003000000}">
+    <dataValidation sqref="I4:I77" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_Cards_Enabled</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="J4:J77" ns2:uid="{00000000-0002-0000-0200-000004000000}">
+    <dataValidation sqref="J4:J77" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_Cards_Offerable</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="K4:K77" ns2:uid="{00000000-0002-0000-0200-000005000000}">
+    <dataValidation sqref="K4:K77" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_Cards_StackPolicy</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="L4:L77" ns2:uid="{00000000-0002-0000-0200-000006000000}">
+    <dataValidation sqref="L4:L77" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_Cards_ConflictPolicy</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="M4:M77" ns2:uid="{00000000-0002-0000-0200-000007000000}">
+    <dataValidation sqref="M4:M77" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_Cards_ReviewStatus</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="H4:H77" ns2:uid="{00000000-0002-0000-0200-000008000000}">
+    <dataValidation sqref="H4:H77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Trait,Disabled"</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="R4:R104" ns2:uid="{00000000-0002-0000-0200-000009000000}">
+    <dataValidation sqref="R4:R104" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>INDIRECT("tblCards[Id]")</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="T4:T104" ns2:uid="{00000000-0002-0000-0200-00000A000000}">
+    <dataValidation sqref="T4:T104" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_CardEffects_Trigger</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="U4:U104" ns2:uid="{00000000-0002-0000-0200-00000B000000}">
+    <dataValidation sqref="U4:U104" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_CardEffects_EffectKind</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="V4:V104" ns2:uid="{00000000-0002-0000-0200-00000C000000}">
+    <dataValidation sqref="V4:V104" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_CardEffects_Target</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="W4:W104" ns2:uid="{00000000-0002-0000-0200-00000D000000}">
+    <dataValidation sqref="W4:W104" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_CardEffects_ValueOp</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="Y4:Y104" ns2:uid="{00000000-0002-0000-0200-00000E000000}">
+    <dataValidation sqref="Y4:Y104" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_CardEffects_BehaviorId</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="Z4:Z104" ns2:uid="{00000000-0002-0000-0200-00000F000000}">
+    <dataValidation sqref="Z4:Z104" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_CardEffects_ParamName</formula1>
     </dataValidation>
   </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="2">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y20"/>
+  <dimension ref="A1:W18"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="13.81640625" defaultRowHeight="13"/>
   <cols>
     <col width="14" customWidth="1" style="41" min="1" max="2"/>
@@ -20716,8 +20711,6 @@
       <c r="V8" s="24" t="n"/>
       <c r="W8" s="24" t="n"/>
     </row>
-    <row r="9"/>
-    <row r="10"/>
     <row r="11" ht="25" customHeight="1" s="41">
       <c r="A11" s="42" t="inlineStr">
         <is>
@@ -20844,8 +20837,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="3">
@@ -20853,44 +20844,44 @@
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="2">
-    <tablePart r:id="rId1"/>
-    <tablePart r:id="rId2"/>
-  </tableParts>
   <dataValidations count="7">
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="E4:E7" ns2:uid="{00000000-0002-0000-0300-000000000000}">
+    <dataValidation sqref="E4:E7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>"true,false"</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="G4:G7" ns2:uid="{00000000-0002-0000-0300-000001000000}">
+    <dataValidation sqref="G4:G7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>"Hunter,Poet,Brave,Sage"</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="I4:I7" ns2:uid="{00000000-0002-0000-0300-000002000000}">
+    <dataValidation sqref="I4:I7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>INDIRECT("tblWeapons[Id]")</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="J4:J7" ns2:uid="{00000000-0002-0000-0300-000003000000}">
+    <dataValidation sqref="J4:J7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_Characters_AppearanceId</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="K4:K7" ns2:uid="{00000000-0002-0000-0300-000004000000}">
+    <dataValidation sqref="K4:K7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_Characters_PassiveBehaviorId</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="W4:W7" ns2:uid="{00000000-0002-0000-0300-000005000000}">
+    <dataValidation sqref="W4:W7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_Characters_RandomElementProjectiles</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="B13:B18" ns2:uid="{00000000-0002-0000-0300-000006000000}">
+    <dataValidation sqref="B13:B18" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>INDIRECT("tblCharacters[Id]")</formula1>
     </dataValidation>
   </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="2">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W40"/>
+  <dimension ref="A1:U38"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="13.81640625" defaultRowHeight="13"/>
   <cols>
     <col width="25" customWidth="1" style="41" min="1" max="2"/>
@@ -21015,7 +21006,7 @@
       </c>
       <c r="C4" s="34" t="inlineStr">
         <is>
-          <t xml:space="preserve">挥剑攻击正面的所有敌人，造成较多伤害，攻击范围较远
+          <t>挥剑攻击正面的所有敌人，造成较多伤害，攻击范围较远
 ——剑锋交错往复，以沉稳的力量扫清前路。</t>
         </is>
       </c>
@@ -21092,7 +21083,7 @@
       </c>
       <c r="C5" s="34" t="inlineStr">
         <is>
-          <t xml:space="preserve">挥动镰刀，攻击身边所有的敌人，造成中等伤害，攻击范围较近
+          <t>挥动镰刀，攻击身边所有的敌人，造成中等伤害，攻击范围较近
 ——镰刃环身而舞，弧光舒展之处，锋芒正盛。</t>
         </is>
       </c>
@@ -21169,7 +21160,7 @@
       </c>
       <c r="C6" s="34" t="inlineStr">
         <is>
-          <t xml:space="preserve">射速较慢，但单发伤害较高
+          <t>射速较慢，但单发伤害较高
 ——弦响虽迟，离弦之箭却足以贯穿远方的噩梦。</t>
         </is>
       </c>
@@ -21246,7 +21237,7 @@
       </c>
       <c r="C7" s="34" t="inlineStr">
         <is>
-          <t xml:space="preserve">射速较快，但单发伤害较低
+          <t>射速较快，但单发伤害较低
 ——枪火追逐倒流的刻度，以疾风骤雨撕碎漫漫长夜。</t>
         </is>
       </c>
@@ -21902,8 +21893,6 @@
       <c r="T20" s="24" t="n"/>
       <c r="U20" s="24" t="n"/>
     </row>
-    <row r="21"/>
-    <row r="22"/>
     <row r="23" ht="25" customHeight="1" s="41">
       <c r="A23" s="42" t="inlineStr">
         <is>
@@ -22711,8 +22700,6 @@
       <c r="S38" s="24" t="n"/>
       <c r="T38" s="24" t="n"/>
     </row>
-    <row r="39"/>
-    <row r="40"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="4">
@@ -22721,72 +22708,72 @@
     <mergeCell ref="A13:D13"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="3">
-    <tablePart r:id="rId1"/>
-    <tablePart r:id="rId2"/>
-    <tablePart r:id="rId3"/>
-  </tableParts>
   <dataValidations count="16">
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="A4:A7" ns2:uid="{00000000-0002-0000-0400-000000000000}">
+    <dataValidation sqref="A4:A7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_WeaponTypes_Id</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="D4:D7" ns2:uid="{00000000-0002-0000-0400-000001000000}">
+    <dataValidation sqref="D4:D7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_WeaponTypes_BaseAttackPatternId</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="E4:E7" ns2:uid="{00000000-0002-0000-0400-000002000000}">
+    <dataValidation sqref="E4:E7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>INDIRECT("tblSlotProfiles[Id]")</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="M4:M7" ns2:uid="{00000000-0002-0000-0400-000003000000}">
+    <dataValidation sqref="M4:M7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_WeaponTypes_Enabled</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="B15:B18" ns2:uid="{00000000-0002-0000-0400-000004000000}">
+    <dataValidation sqref="B15:B18" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>INDIRECT("tblWeaponTypes[Id]")</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="D15:D18" ns2:uid="{00000000-0002-0000-0400-000005000000}">
+    <dataValidation sqref="D15:D18" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_Weapons_VisualKey</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="E15:E18" ns2:uid="{00000000-0002-0000-0400-000006000000}">
+    <dataValidation sqref="E15:E18" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_Weapons_InputSlot</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="F15:F18" ns2:uid="{00000000-0002-0000-0400-000007000000}">
+    <dataValidation sqref="F15:F18" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_Weapons_StartSelectable</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="H15:H18" ns2:uid="{00000000-0002-0000-0400-000008000000}">
+    <dataValidation sqref="H15:H18" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_Weapons_AttackPatternId</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="B25:B29" ns2:uid="{00000000-0002-0000-0400-000009000000}">
+    <dataValidation sqref="B25:B29" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_AttackSteps_AttackPatternId</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="Q15:Q18" ns2:uid="{00000000-0002-0000-0400-00000A000000}">
+    <dataValidation sqref="Q15:Q18" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_Weapons_Enabled</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="L25:L29" ns2:uid="{00000000-0002-0000-0400-00000B000000}">
+    <dataValidation sqref="L25:L29" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_AttackSteps_Invulnerable</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="M25:M29" ns2:uid="{00000000-0002-0000-0400-00000C000000}">
+    <dataValidation sqref="M25:M29" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_AttackSteps_BehaviorId</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="N25:N29" ns2:uid="{00000000-0002-0000-0400-00000D000000}">
+    <dataValidation sqref="N25:N29" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_AttackSteps_FormulaId</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="O25:O29" ns2:uid="{00000000-0002-0000-0400-00000E000000}">
+    <dataValidation sqref="O25:O29" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_AttackSteps_ConditionId</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="P25:P29" ns2:uid="{00000000-0002-0000-0400-00000F000000}">
+    <dataValidation sqref="P25:P29" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_AttackSteps_Enabled</formula1>
     </dataValidation>
   </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="3">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM193"/>
+  <dimension ref="A1:AK191"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="13.81640625" defaultRowHeight="13"/>
   <cols>
     <col width="25" customWidth="1" style="41" min="1" max="4"/>
@@ -23114,7 +23101,6 @@
       <c r="E15" s="24" t="n"/>
       <c r="F15" s="24" t="n"/>
     </row>
-    <row r="16"/>
     <row r="17" ht="25" customHeight="1" s="41">
       <c r="A17" s="42" t="inlineStr">
         <is>
@@ -23736,10 +23722,6 @@
       <c r="H39" s="24" t="n"/>
       <c r="I39" s="24" t="n"/>
     </row>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
     <row r="44" ht="25" customHeight="1" s="41">
       <c r="A44" s="42" t="inlineStr">
         <is>
@@ -23957,7 +23939,8 @@
       </c>
       <c r="F46" s="33" t="inlineStr">
         <is>
-          <t>——怀表逆转前，万物都曾拥有最初的刻度。 / 造成物理伤害，受物理攻击力影响</t>
+          <t>造成物理伤害，受物理攻击力影响
+——怀表逆转前，万物都曾拥有最初的刻度。</t>
         </is>
       </c>
       <c r="G46" s="29" t="inlineStr">
@@ -24125,7 +24108,8 @@
       </c>
       <c r="F47" s="33" t="inlineStr">
         <is>
-          <t>——倒流的雨滴穿过钟面，汇成梦境深处的潮汐。 / 造成水元素伤害，受元素攻击力影响</t>
+          <t>造成水元素伤害，受元素攻击力影响
+——倒流的雨滴穿过钟面，汇成梦境深处的潮汐。</t>
         </is>
       </c>
       <c r="G47" s="29" t="inlineStr">
@@ -24293,7 +24277,8 @@
       </c>
       <c r="F48" s="33" t="inlineStr">
         <is>
-          <t>——森林不会死去，落叶收存着未完的愿望。 / 造成草元素伤害，受元素攻击力影响</t>
+          <t>造成草元素伤害，受元素攻击力影响
+——森林不会死去，落叶收存着未完的愿望。</t>
         </is>
       </c>
       <c r="G48" s="29" t="inlineStr">
@@ -24461,7 +24446,8 @@
       </c>
       <c r="F49" s="33" t="inlineStr">
         <is>
-          <t>——噩梦烧尽美梦，余烬仍等待再次燃起。 / 造成火元素伤害，受元素攻击力影响</t>
+          <t>造成火元素伤害，受元素攻击力影响
+——噩梦烧尽美梦，余烬仍等待再次燃起。</t>
         </is>
       </c>
       <c r="G49" s="29" t="inlineStr">
@@ -24629,7 +24615,8 @@
       </c>
       <c r="F50" s="33" t="inlineStr">
         <is>
-          <t>——梦境森林的雷声，来自沉睡者骤然裂开的梦魇。 / 造成雷元素伤害，受元素攻击力影响</t>
+          <t>造成雷元素伤害，受元素攻击力影响
+——梦境森林的雷声，来自沉睡者骤然裂开的梦魇。</t>
         </is>
       </c>
       <c r="G50" s="29" t="inlineStr">
@@ -24797,7 +24784,8 @@
       </c>
       <c r="F51" s="33" t="inlineStr">
         <is>
-          <t>——唯有不被定义的光，才能在每一次回响中折射出新的色彩。 / 造成随机元素伤害，受元素攻击力影响</t>
+          <t>造成随机元素伤害，受元素攻击力影响
+——唯有不被定义的光，才能在每一次回响中折射出新的色彩。</t>
         </is>
       </c>
       <c r="G51" s="29" t="inlineStr">
@@ -24965,7 +24953,7 @@
       </c>
       <c r="F52" s="33" t="inlineStr">
         <is>
-          <t>命中敌人后，分裂为若干箭矢飞向其周围的敌人，至多分裂出3支箭 / 这些分裂的箭伤害倍率-50%</t>
+          <t>箭矢命中后，会分裂为小箭矢，至多分裂出3支</t>
         </is>
       </c>
       <c r="G52" s="29" t="inlineStr">
@@ -25133,7 +25121,7 @@
       </c>
       <c r="F53" s="35" t="inlineStr">
         <is>
-          <t>命中敌人后，分裂为若干箭矢飞向其周围的敌人，至多分裂出4支箭 / 这些分裂的箭伤害倍率-50%</t>
+          <t>箭矢命中后，会分裂为小箭矢，至多分裂出4支</t>
         </is>
       </c>
       <c r="G53" s="29" t="inlineStr">
@@ -25301,7 +25289,7 @@
       </c>
       <c r="F54" s="35" t="inlineStr">
         <is>
-          <t>命中敌人后，分裂为若干箭矢飞向其周围的敌人，至多分裂出5支箭 / 这些分裂的箭伤害倍率-50%</t>
+          <t>箭矢命中后，会分裂为小箭矢，至多分裂出5支</t>
         </is>
       </c>
       <c r="G54" s="29" t="inlineStr">
@@ -25469,7 +25457,7 @@
       </c>
       <c r="F55" s="33" t="inlineStr">
         <is>
-          <t>箭矢命中敌人后，会发生爆炸。爆炸范围3m</t>
+          <t>箭矢会爆炸</t>
         </is>
       </c>
       <c r="G55" s="29" t="inlineStr">
@@ -25637,7 +25625,7 @@
       </c>
       <c r="F56" s="35" t="inlineStr">
         <is>
-          <t>箭矢命中敌人后，会发生爆炸。爆炸范围4m</t>
+          <t>箭矢会爆炸，范围更大</t>
         </is>
       </c>
       <c r="G56" s="29" t="inlineStr">
@@ -25805,7 +25793,7 @@
       </c>
       <c r="F57" s="35" t="inlineStr">
         <is>
-          <t>箭矢命中敌人后，会发生爆炸。爆炸范围5m</t>
+          <t>箭矢会爆炸，范围更更更大！</t>
         </is>
       </c>
       <c r="G57" s="29" t="inlineStr">
@@ -25973,7 +25961,7 @@
       </c>
       <c r="F58" s="35" t="inlineStr">
         <is>
-          <t>弹道固定为3，武器集中性固定为60° / 这些箭伤害倍率-50%</t>
+          <t>一次可以射出3发箭矢，但是会散射</t>
         </is>
       </c>
       <c r="G58" s="29" t="inlineStr">
@@ -26141,7 +26129,7 @@
       </c>
       <c r="F59" s="35" t="inlineStr">
         <is>
-          <t>弹道固定为4，武器集中性固定为60° / 这些箭伤害倍率-50%</t>
+          <t>一次可以射出4发箭矢，但是会散射</t>
         </is>
       </c>
       <c r="G59" s="29" t="inlineStr">
@@ -26309,7 +26297,7 @@
       </c>
       <c r="F60" s="33" t="inlineStr">
         <is>
-          <t>弹道固定为5，武器集中性固定为60° / 这些箭伤害倍率-50%</t>
+          <t>一次可以射出5发箭矢，但是会散射</t>
         </is>
       </c>
       <c r="G60" s="29" t="inlineStr">
@@ -26981,7 +26969,7 @@
       </c>
       <c r="F64" s="33" t="inlineStr">
         <is>
-          <t>箭命中敌人且暴击后，会穿透该敌人</t>
+          <t>箭矢触发暴击时，会穿透这名敌人</t>
         </is>
       </c>
       <c r="G64" s="29" t="inlineStr">
@@ -27153,7 +27141,7 @@
       </c>
       <c r="F65" s="33" t="inlineStr">
         <is>
-          <t>箭命中敌人且暴击后，敌人获得【流血】，持续3秒，可以叠加</t>
+          <t>箭矢触发暴击时，会令敌人【流血】，持续3秒</t>
         </is>
       </c>
       <c r="G65" s="29" t="inlineStr">
@@ -28333,7 +28321,7 @@
       </c>
       <c r="F72" s="33" t="inlineStr">
         <is>
-          <t>击杀敌人后，移动速度+30%，持续5s。不可叠加</t>
+          <t>击杀一名敌方单位后，移动速度+30%，持续5s。不可叠加</t>
         </is>
       </c>
       <c r="G72" s="29" t="inlineStr">
@@ -28501,7 +28489,7 @@
       </c>
       <c r="F73" s="33" t="inlineStr">
         <is>
-          <t>击杀敌人后，移动速度+40%，持续5s。不可叠加</t>
+          <t>击杀一名敌方单位后，移动速度+40%，持续5s。不可叠加</t>
         </is>
       </c>
       <c r="G73" s="29" t="inlineStr">
@@ -28669,7 +28657,7 @@
       </c>
       <c r="F74" s="33" t="inlineStr">
         <is>
-          <t>击杀敌人后，移动速度+50%，持续5s。不可叠加</t>
+          <t>击杀一名敌方单位后，移动速度+50%，持续5s。不可叠加</t>
         </is>
       </c>
       <c r="G74" s="29" t="inlineStr">
@@ -29341,7 +29329,7 @@
       </c>
       <c r="F78" s="29" t="inlineStr">
         <is>
-          <t>每次攻击同时命中3名敌人后，攻击范围+4%，持续至关卡结束，可以叠加</t>
+          <t>每次攻击同时命中3名敌人后，攻击范围+4%</t>
         </is>
       </c>
       <c r="G78" s="29" t="inlineStr">
@@ -29509,7 +29497,7 @@
       </c>
       <c r="F79" s="33" t="inlineStr">
         <is>
-          <t>每次攻击同时命中3名敌人后，攻击范围+6%，持续至关卡结束，可以叠加</t>
+          <t>每次攻击同时命中3名敌人后，攻击范围+6%</t>
         </is>
       </c>
       <c r="G79" s="29" t="inlineStr">
@@ -29677,7 +29665,7 @@
       </c>
       <c r="F80" s="33" t="inlineStr">
         <is>
-          <t>每次攻击同时命中3名敌人后，攻击范围+8%，持续至关卡结束，可以叠加</t>
+          <t>每次攻击同时命中3名敌人后，攻击范围+8%</t>
         </is>
       </c>
       <c r="G80" s="29" t="inlineStr">
@@ -29845,7 +29833,7 @@
       </c>
       <c r="F81" s="33" t="inlineStr">
         <is>
-          <t>每命中1名敌方单位，回复自身2%最大生命值</t>
+          <t>每命中1名敌方单位，回复自身2%生命值</t>
         </is>
       </c>
       <c r="G81" s="29" t="inlineStr">
@@ -30013,7 +30001,7 @@
       </c>
       <c r="F82" s="33" t="inlineStr">
         <is>
-          <t>每命中1名敌方单位，回复自身4%最大生命值</t>
+          <t>每命中1名敌方单位，回复自身4%生命值</t>
         </is>
       </c>
       <c r="G82" s="29" t="inlineStr">
@@ -30181,7 +30169,7 @@
       </c>
       <c r="F83" s="33" t="inlineStr">
         <is>
-          <t>每命中1名敌方单位，回复自身6%最大生命值</t>
+          <t>每命中1名敌方单位，回复自身6%生命值</t>
         </is>
       </c>
       <c r="G83" s="29" t="inlineStr">
@@ -30349,7 +30337,7 @@
       </c>
       <c r="F84" s="33" t="inlineStr">
         <is>
-          <t>每次攻击有30%概率将敌人【晕眩】，持续1s</t>
+          <t>攻击有30%概率将敌人【晕眩】，持续1s</t>
         </is>
       </c>
       <c r="G84" s="29" t="inlineStr">
@@ -30517,7 +30505,7 @@
       </c>
       <c r="F85" s="33" t="inlineStr">
         <is>
-          <t>每次攻击有40%概率将敌人【晕眩】，持续1s</t>
+          <t>攻击有40%概率将敌人【晕眩】，持续1s</t>
         </is>
       </c>
       <c r="G85" s="29" t="inlineStr">
@@ -30685,7 +30673,7 @@
       </c>
       <c r="F86" s="29" t="inlineStr">
         <is>
-          <t>每次攻击有50%概率将敌人【晕眩】，持续1s</t>
+          <t>攻击有50%概率将敌人【晕眩】，持续1s</t>
         </is>
       </c>
       <c r="G86" s="29" t="inlineStr">
@@ -31529,7 +31517,7 @@
       </c>
       <c r="F91" s="33" t="inlineStr">
         <is>
-          <t>命中敌人且触发暴击时，敌人获得【流血】，持续3s，可以叠加</t>
+          <t>触发暴击时，会令敌人【流血】，持续3秒</t>
         </is>
       </c>
       <c r="G91" s="29" t="inlineStr">
@@ -31701,7 +31689,7 @@
       </c>
       <c r="F92" s="33" t="inlineStr">
         <is>
-          <t>每命中1名敌方单位，获得1%移动速度，持续至关卡结束，可以叠加</t>
+          <t>每命中1名敌方单位，获得1%移动速度</t>
         </is>
       </c>
       <c r="G92" s="29" t="inlineStr">
@@ -31869,7 +31857,7 @@
       </c>
       <c r="F93" s="29" t="inlineStr">
         <is>
-          <t>每命中1名敌方单位，获得1.5%移动速度，持续至关卡结束，可以叠加</t>
+          <t>每命中1名敌方单位，获得1.5%移动速度</t>
         </is>
       </c>
       <c r="G93" s="29" t="inlineStr">
@@ -32037,7 +32025,7 @@
       </c>
       <c r="F94" s="33" t="inlineStr">
         <is>
-          <t>每命中1名敌方单位，获得2%移动速度，持续至关卡结束，可以叠加</t>
+          <t>每命中1名敌方单位，获得2%移动速度</t>
         </is>
       </c>
       <c r="G94" s="29" t="inlineStr">
@@ -32205,7 +32193,7 @@
       </c>
       <c r="F95" s="29" t="inlineStr">
         <is>
-          <t>同时命中3名敌方单位时，获得【无敌】，持续0.3秒</t>
+          <t>每次攻击，同时命中3名敌方单位时，获得【无敌】，持续0.3秒</t>
         </is>
       </c>
       <c r="G95" s="29" t="inlineStr">
@@ -32373,7 +32361,7 @@
       </c>
       <c r="F96" s="29" t="inlineStr">
         <is>
-          <t>同时命中3名敌方单位时，获得【无敌】，持续0.4秒</t>
+          <t>每次攻击，同时命中3名敌方单位时，获得【无敌】，持续0.4秒</t>
         </is>
       </c>
       <c r="G96" s="29" t="inlineStr">
@@ -32541,7 +32529,7 @@
       </c>
       <c r="F97" s="29" t="inlineStr">
         <is>
-          <t>同时命中3名敌方单位时，获得【无敌】，持续0.5秒</t>
+          <t>每次攻击，同时命中3名敌方单位时，获得【无敌】，持续0.5秒</t>
         </is>
       </c>
       <c r="G97" s="29" t="inlineStr">
@@ -32709,7 +32697,7 @@
       </c>
       <c r="F98" s="29" t="inlineStr">
         <is>
-          <t>每命中一名敌方单位，获得1%攻击速度，持续至关卡结束，可以叠加</t>
+          <t>每命中一名敌方单位，获得1%攻击速度</t>
         </is>
       </c>
       <c r="G98" s="29" t="inlineStr">
@@ -32877,7 +32865,7 @@
       </c>
       <c r="F99" s="29" t="inlineStr">
         <is>
-          <t>每命中一名敌方单位，获得1.5%攻击速度，持续至关卡结束，可以叠加</t>
+          <t>每命中一名敌方单位，获得1.5%攻击速度</t>
         </is>
       </c>
       <c r="G99" s="29" t="inlineStr">
@@ -33045,7 +33033,7 @@
       </c>
       <c r="F100" s="29" t="inlineStr">
         <is>
-          <t>每命中一名敌方单位，获得2%攻击速度，持续至关卡结束，可以叠加</t>
+          <t>每命中一名敌方单位，获得2%攻击速度</t>
         </is>
       </c>
       <c r="G100" s="29" t="inlineStr">
@@ -33889,7 +33877,7 @@
       </c>
       <c r="F105" s="29" t="inlineStr">
         <is>
-          <t>每次攻击同时命中3名敌人后，攻击范围+4%，持续至关卡结束，可以叠加</t>
+          <t>每次攻击同时命中3名敌人后，攻击范围+4%</t>
         </is>
       </c>
       <c r="G105" s="29" t="inlineStr">
@@ -34057,7 +34045,7 @@
       </c>
       <c r="F106" s="29" t="inlineStr">
         <is>
-          <t>每次攻击同时命中3名敌人后，攻击范围+6%，持续至关卡结束，可以叠加</t>
+          <t>每次攻击同时命中3名敌人后，攻击范围+6%</t>
         </is>
       </c>
       <c r="G106" s="29" t="inlineStr">
@@ -34225,7 +34213,7 @@
       </c>
       <c r="F107" s="32" t="inlineStr">
         <is>
-          <t>每次攻击同时命中3名敌人后，攻击范围+8%，持续至关卡结束，可以叠加</t>
+          <t>每次攻击同时命中3名敌人后，攻击范围+8%</t>
         </is>
       </c>
       <c r="G107" s="32" t="inlineStr">
@@ -34393,7 +34381,7 @@
       </c>
       <c r="F108" s="32" t="inlineStr">
         <is>
-          <t>每击杀一名敌方单位，回复5%最大生命值</t>
+          <t>每击杀一名敌方单位，回复5%生命值</t>
         </is>
       </c>
       <c r="G108" s="32" t="inlineStr">
@@ -34561,7 +34549,7 @@
       </c>
       <c r="F109" s="32" t="inlineStr">
         <is>
-          <t>每击杀一名敌方单位，回复7.5%最大生命值</t>
+          <t>每击杀一名敌方单位，回复7.5%生命值</t>
         </is>
       </c>
       <c r="G109" s="32" t="inlineStr">
@@ -34729,7 +34717,7 @@
       </c>
       <c r="F110" s="32" t="inlineStr">
         <is>
-          <t>每击杀一名敌方单位，回复10%最大生命值</t>
+          <t>每击杀一名敌方单位，回复10%生命值</t>
         </is>
       </c>
       <c r="G110" s="32" t="inlineStr">
@@ -35401,7 +35389,7 @@
       </c>
       <c r="F114" s="32" t="inlineStr">
         <is>
-          <t>攻击速度-30%，攻击范围+50%</t>
+          <t>攻击速度-20%，攻击范围+30%</t>
         </is>
       </c>
       <c r="G114" s="32" t="inlineStr">
@@ -35573,7 +35561,7 @@
       </c>
       <c r="F115" s="32" t="inlineStr">
         <is>
-          <t>命中敌方且暴击时，敌方单位获得【流血】，持续3s，可以叠加</t>
+          <t>触发暴击时，敌方单位获得【流血】，持续3s，可以叠加</t>
         </is>
       </c>
       <c r="G115" s="32" t="inlineStr">
@@ -36421,7 +36409,7 @@
       </c>
       <c r="F120" s="32" t="inlineStr">
         <is>
-          <t>每命中1名敌方单位，获得1%移动速度，持续至关卡结束，可以叠加</t>
+          <t>每命中1名敌方单位，获得1%移动速度</t>
         </is>
       </c>
       <c r="G120" s="32" t="inlineStr">
@@ -36589,7 +36577,7 @@
       </c>
       <c r="F121" s="32" t="inlineStr">
         <is>
-          <t>每命中1名敌方单位，获得1.5%移动速度，持续至关卡结束，可以叠加</t>
+          <t>每命中1名敌方单位，获得1.5%移动速度</t>
         </is>
       </c>
       <c r="G121" s="32" t="inlineStr">
@@ -36757,7 +36745,7 @@
       </c>
       <c r="F122" s="32" t="inlineStr">
         <is>
-          <t>每命中1名敌方单位，获得2%移动速度，持续至关卡结束，可以叠加</t>
+          <t>每命中1名敌方单位，获得2%移动速度</t>
         </is>
       </c>
       <c r="G122" s="32" t="inlineStr">
@@ -36925,7 +36913,7 @@
       </c>
       <c r="F123" s="32" t="inlineStr">
         <is>
-          <t>每命中一名敌方单位，获得1%攻击速度，持续至关卡结束，可以叠加</t>
+          <t>每命中一名敌方单位，获得1%攻击速度</t>
         </is>
       </c>
       <c r="G123" s="32" t="inlineStr">
@@ -37093,7 +37081,7 @@
       </c>
       <c r="F124" s="32" t="inlineStr">
         <is>
-          <t>每命中一名敌方单位，获得1.5%攻击速度，持续至关卡结束，可以叠加</t>
+          <t>每命中一名敌方单位，获得1.5%攻击速度</t>
         </is>
       </c>
       <c r="G124" s="32" t="inlineStr">
@@ -37261,7 +37249,7 @@
       </c>
       <c r="F125" s="32" t="inlineStr">
         <is>
-          <t>每命中一名敌方单位，获得2%攻击速度，持续至关卡结束，可以叠加</t>
+          <t>每命中一名敌方单位，获得2%攻击速度</t>
         </is>
       </c>
       <c r="G125" s="32" t="inlineStr">
@@ -37429,7 +37417,7 @@
       </c>
       <c r="F126" s="32" t="inlineStr">
         <is>
-          <t>每次攻击有30%概率将敌人【晕眩】，持续1s</t>
+          <t>攻击有30%概率将敌人【晕眩】，持续1s</t>
         </is>
       </c>
       <c r="G126" s="32" t="inlineStr">
@@ -37597,7 +37585,7 @@
       </c>
       <c r="F127" s="32" t="inlineStr">
         <is>
-          <t>每次攻击有40%概率将敌人【晕眩】，持续1s</t>
+          <t>攻击有40%概率将敌人【晕眩】，持续1s</t>
         </is>
       </c>
       <c r="G127" s="32" t="inlineStr">
@@ -37765,7 +37753,7 @@
       </c>
       <c r="F128" s="32" t="inlineStr">
         <is>
-          <t>每次攻击有50%概率将敌人【晕眩】，持续1s</t>
+          <t>攻击有50%概率将敌人【晕眩】，持续1s</t>
         </is>
       </c>
       <c r="G128" s="32" t="inlineStr">
@@ -39445,7 +39433,7 @@
       </c>
       <c r="F138" s="32" t="inlineStr">
         <is>
-          <t>子弹命中敌人后，会发生爆炸。爆炸范围2m</t>
+          <t>子弹会爆炸</t>
         </is>
       </c>
       <c r="G138" s="32" t="inlineStr">
@@ -39613,7 +39601,7 @@
       </c>
       <c r="F139" s="32" t="inlineStr">
         <is>
-          <t>子弹命中敌人后，会发生爆炸。爆炸范围3m</t>
+          <t>子弹会爆炸，爆炸范围更大</t>
         </is>
       </c>
       <c r="G139" s="32" t="inlineStr">
@@ -39781,7 +39769,7 @@
       </c>
       <c r="F140" s="32" t="inlineStr">
         <is>
-          <t>子弹命中敌人后，会发生爆炸。爆炸范围4m</t>
+          <t>子弹会爆炸，爆炸范围更更大！</t>
         </is>
       </c>
       <c r="G140" s="32" t="inlineStr">
@@ -39949,7 +39937,7 @@
       </c>
       <c r="F141" s="32" t="inlineStr">
         <is>
-          <t>子弹命中敌人且暴击后，会穿透该敌人</t>
+          <t>子弹触发暴击后，会穿透该敌人</t>
         </is>
       </c>
       <c r="G141" s="32" t="inlineStr">
@@ -40121,7 +40109,7 @@
       </c>
       <c r="F142" s="32" t="inlineStr">
         <is>
-          <t>每次命中敌方单位时，敌方单位有15%概率获得【流血】，持续3s，可以叠加</t>
+          <t>每次命中敌方单位时，有30%概率令敌人【流血】，持续3s</t>
         </is>
       </c>
       <c r="G142" s="32" t="inlineStr">
@@ -40465,7 +40453,7 @@
       </c>
       <c r="F144" s="32" t="inlineStr">
         <is>
-          <t>每次命中敌方单位，回复1%最大生命值</t>
+          <t>每次命中敌方单位，回复1%生命值</t>
         </is>
       </c>
       <c r="G144" s="32" t="inlineStr">
@@ -40633,7 +40621,7 @@
       </c>
       <c r="F145" s="32" t="inlineStr">
         <is>
-          <t>每次命中敌方单位，回复2%最大生命值</t>
+          <t>每次命中敌方单位，回复2%生命值</t>
         </is>
       </c>
       <c r="G145" s="32" t="inlineStr">
@@ -40801,7 +40789,7 @@
       </c>
       <c r="F146" s="32" t="inlineStr">
         <is>
-          <t>每次命中敌方单位，回复3%最大生命值</t>
+          <t>每次命中敌方单位，回复3%生命值</t>
         </is>
       </c>
       <c r="G146" s="32" t="inlineStr">
@@ -40969,7 +40957,7 @@
       </c>
       <c r="F147" s="32" t="inlineStr">
         <is>
-          <t>每命中5次任意敌方单位，掉落3时间碎片</t>
+          <t>每命中5次，获得3时间碎片</t>
         </is>
       </c>
       <c r="G147" s="32" t="inlineStr">
@@ -41137,7 +41125,7 @@
       </c>
       <c r="F148" s="32" t="inlineStr">
         <is>
-          <t>每命中5次任意敌方单位，掉落4时间碎片</t>
+          <t>每命中5次，获得4时间碎片</t>
         </is>
       </c>
       <c r="G148" s="32" t="inlineStr">
@@ -41305,7 +41293,7 @@
       </c>
       <c r="F149" s="32" t="inlineStr">
         <is>
-          <t>每命中5次任意敌方单位，掉落5时间碎片</t>
+          <t>每命中5次，获得5时间碎片</t>
         </is>
       </c>
       <c r="G149" s="32" t="inlineStr">
@@ -41473,7 +41461,7 @@
       </c>
       <c r="F150" s="32" t="inlineStr">
         <is>
-          <t>每次攻击，获得1%攻击速度，持续至关卡结束，可以叠加</t>
+          <t>每次攻击，获得1%攻击速度</t>
         </is>
       </c>
       <c r="G150" s="32" t="inlineStr">
@@ -41641,7 +41629,7 @@
       </c>
       <c r="F151" s="32" t="inlineStr">
         <is>
-          <t>每次攻击，获得1.5%攻击速度，持续至关卡结束，可以叠加</t>
+          <t>每次攻击，获得1.5%攻击速度</t>
         </is>
       </c>
       <c r="G151" s="32" t="inlineStr">
@@ -41809,7 +41797,7 @@
       </c>
       <c r="F152" s="32" t="inlineStr">
         <is>
-          <t>每次攻击，获得2%攻击速度，持续至关卡结束，可以叠加</t>
+          <t>每次攻击，获得2%攻击速度</t>
         </is>
       </c>
       <c r="G152" s="32" t="inlineStr">
@@ -41977,7 +41965,7 @@
       </c>
       <c r="F153" s="32" t="inlineStr">
         <is>
-          <t>每次攻击，获得1%移动速度，持续至关卡结束，可以叠加</t>
+          <t>每次攻击，获得1%移动速度</t>
         </is>
       </c>
       <c r="G153" s="32" t="inlineStr">
@@ -42145,7 +42133,7 @@
       </c>
       <c r="F154" s="32" t="inlineStr">
         <is>
-          <t>每次攻击，获得1.5%移动速度，持续至关卡结束，可以叠加</t>
+          <t>每次攻击，获得1.5%移动速度</t>
         </is>
       </c>
       <c r="G154" s="32" t="inlineStr">
@@ -42313,7 +42301,7 @@
       </c>
       <c r="F155" s="32" t="inlineStr">
         <is>
-          <t>每次攻击，获得2%移动速度，持续至关卡结束，可以叠加</t>
+          <t>每次攻击，获得2%移动速度</t>
         </is>
       </c>
       <c r="G155" s="32" t="inlineStr">
@@ -44999,8 +44987,6 @@
       <c r="O191" s="24" t="n"/>
       <c r="P191" s="24" t="n"/>
     </row>
-    <row r="192"/>
-    <row r="193"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="5">
@@ -45010,85 +44996,85 @@
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A44:D44"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="4">
-    <tablePart r:id="rId1"/>
-    <tablePart r:id="rId2"/>
-    <tablePart r:id="rId3"/>
-    <tablePart r:id="rId4"/>
-  </tableParts>
   <dataValidations count="23">
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="C4:C12" ns2:uid="{00000000-0002-0000-0500-000000000000}">
+    <dataValidation sqref="C4:C12" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_SlotTypes_Enabled</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="B19:B30" ns2:uid="{00000000-0002-0000-0500-000001000000}">
+    <dataValidation sqref="B19:B30" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_SlotProfiles_WeaponTypeId</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="C19:C30 D46:D156" ns2:uid="{00000000-0002-0000-0500-000002000000}">
+    <dataValidation sqref="C19:C30 D46:D156" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>INDIRECT("tblSlotTypes[Id]")</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="E19:E30" ns2:uid="{00000000-0002-0000-0500-000003000000}">
+    <dataValidation sqref="E19:E30" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_SlotProfiles_Required</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="F19:F30" ns2:uid="{00000000-0002-0000-0500-000004000000}">
+    <dataValidation sqref="F19:F30" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_SlotProfiles_Enabled</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="C46:C156" ns2:uid="{00000000-0002-0000-0500-000005000000}">
+    <dataValidation sqref="C46:C156" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_Parts_WeaponTypeId</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="G46:G156" ns2:uid="{00000000-0002-0000-0500-000007000000}">
+    <dataValidation sqref="G46:G156" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_Parts_Rarity</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="H46:H123" ns2:uid="{00000000-0002-0000-0500-000008000000}">
+    <dataValidation sqref="H46:H123" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_Parts_Tags</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="I46:I156 O46:O156" ns2:uid="{00000000-0002-0000-0500-000009000000}">
+    <dataValidation sqref="I46:I156 O46:O156" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_Parts_Enabled</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="J46:J156" ns2:uid="{00000000-0002-0000-0500-00000A000000}">
+    <dataValidation sqref="J46:J156" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_Parts_ReviewStatus</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="K46:K156" ns2:uid="{00000000-0002-0000-0500-00000B000000}">
+    <dataValidation sqref="K46:K156" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_Parts_ImplementationStatus</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="S46:S174" ns2:uid="{00000000-0002-0000-0500-00000C000000}">
+    <dataValidation sqref="S46:S174" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>INDIRECT("tblParts[PartId]")</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="U46:U174" ns2:uid="{00000000-0002-0000-0500-00000D000000}">
+    <dataValidation sqref="U46:U174" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_PartEffects_Trigger</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="V46:V174" ns2:uid="{00000000-0002-0000-0500-00000E000000}">
+    <dataValidation sqref="V46:V174" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_PartEffects_EffectKind</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="W46:W174" ns2:uid="{00000000-0002-0000-0500-00000F000000}">
+    <dataValidation sqref="W46:W174" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_PartEffects_Target</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="X46:X174" ns2:uid="{00000000-0002-0000-0500-000010000000}">
+    <dataValidation sqref="X46:X174" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_PartEffects_ValueOp</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="Z46:Z174" ns2:uid="{00000000-0002-0000-0500-000011000000}">
+    <dataValidation sqref="Z46:Z174" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_PartEffects_BehaviorId</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="AA46:AA174" ns2:uid="{00000000-0002-0000-0500-000012000000}">
+    <dataValidation sqref="AA46:AA174" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_PartEffects_FormulaId</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="AB46:AB174" ns2:uid="{00000000-0002-0000-0500-000013000000}">
+    <dataValidation sqref="AB46:AB174" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_PartEffects_AttackPatternId</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="AC46:AC174" ns2:uid="{00000000-0002-0000-0500-000014000000}">
+    <dataValidation sqref="AC46:AC174" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_PartEffects_ParamName</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="AG46:AG174" ns2:uid="{00000000-0002-0000-0500-000015000000}">
+    <dataValidation sqref="AG46:AG174" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_PartEffects_StackPolicy</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="AH46:AH174" ns2:uid="{00000000-0002-0000-0500-000016000000}">
+    <dataValidation sqref="AH46:AH174" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_PartEffects_Enabled</formula1>
     </dataValidation>
-    <dataValidation type="whole" showInputMessage="1" showErrorMessage="1" errorTitle="无效数值" error="请输入 0 到 100000 之间的整数。" promptTitle="商店价格" prompt="未上架填 0；上架符文必须填写正整数价格。" sqref="P46:P123" ns2:uid="{00000000-0002-0000-0500-000018000000}">
+    <dataValidation sqref="P46:P123" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效数值" error="请输入 0 到 100000 之间的整数。" promptTitle="商店价格" prompt="未上架填 0；上架符文必须填写正整数价格。" type="whole">
       <formula1>0</formula1>
       <formula2>100000</formula2>
     </dataValidation>
   </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="4">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -45153,12 +45139,12 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="13.81640625" defaultRowHeight="13"/>
   <cols>
     <col width="25" customWidth="1" style="41" min="1" max="1"/>
@@ -45723,38 +45709,36 @@
       </c>
       <c r="K12" s="29" t="inlineStr"/>
     </row>
-    <row r="13"/>
-    <row r="14"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="2">
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
   <dataValidations count="6">
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="D4:D12" ns2:uid="{00000000-0002-0000-0700-000000000000}">
+    <dataValidation sqref="D4:D12" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_Statuses_BehaviorId</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="F4:F12" ns2:uid="{00000000-0002-0000-0700-000001000000}">
+    <dataValidation sqref="F4:F12" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_Statuses_StackPolicy</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="G4:G12" ns2:uid="{00000000-0002-0000-0700-000002000000}">
+    <dataValidation sqref="G4:G12" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_Statuses_RefreshPolicy</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="H4:H12" ns2:uid="{00000000-0002-0000-0700-000003000000}">
+    <dataValidation sqref="H4:H12" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_Statuses_MutexGroup</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="I4:I12" ns2:uid="{00000000-0002-0000-0700-000004000000}">
+    <dataValidation sqref="I4:I12" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_Statuses_Tags</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" sqref="J4:J12" ns2:uid="{00000000-0002-0000-0700-000005000000}">
+    <dataValidation sqref="J4:J12" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_Statuses_Enabled</formula1>
     </dataValidation>
   </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -45764,7 +45748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N37"/>
+  <dimension ref="A1:L35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="13.81640625" defaultRowHeight="13"/>
   <cols>
     <col width="16" customWidth="1" style="41" min="1" max="1"/>
@@ -45935,8 +45919,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="43" t="inlineStr">
         <is>
@@ -46074,8 +46056,6 @@
       <c r="B20" s="32" t="inlineStr"/>
       <c r="C20" s="32" t="inlineStr"/>
     </row>
-    <row r="21"/>
-    <row r="22"/>
     <row r="23">
       <c r="A23" s="43" t="inlineStr">
         <is>
@@ -46544,8 +46524,6 @@
         </is>
       </c>
     </row>
-    <row r="32"/>
-    <row r="33"/>
     <row r="34">
       <c r="A34" s="43" t="inlineStr">
         <is>
@@ -46600,8 +46578,6 @@
         </is>
       </c>
     </row>
-    <row r="36"/>
-    <row r="37"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Design/Data/ReEchoData.xlsx
+++ b/Design/Data/ReEchoData.xlsx
@@ -9063,7 +9063,7 @@
       </c>
       <c r="E4" s="33" t="inlineStr">
         <is>
-          <t>移动速度+8%</t>
+          <t>移动速度+6%</t>
         </is>
       </c>
       <c r="F4" s="29" t="inlineStr">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="X4" s="29" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="Y4" s="29" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="E5" s="33" t="inlineStr">
         <is>
-          <t>生命值与生命上限+6</t>
+          <t>生命值与生命上限+5</t>
         </is>
       </c>
       <c r="F5" s="29" t="inlineStr">
@@ -9259,7 +9259,7 @@
       </c>
       <c r="X5" s="29" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y5" s="29" t="inlineStr">
@@ -9301,7 +9301,7 @@
       </c>
       <c r="E6" s="33" t="inlineStr">
         <is>
-          <t>物理攻击力+3</t>
+          <t>物理攻击力+2</t>
         </is>
       </c>
       <c r="F6" s="29" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="X6" s="29" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y6" s="29" t="inlineStr">
@@ -9420,7 +9420,7 @@
       </c>
       <c r="E7" s="33" t="inlineStr">
         <is>
-          <t>元素攻击力+3</t>
+          <t>元素攻击力+2</t>
         </is>
       </c>
       <c r="F7" s="29" t="inlineStr">
@@ -9497,7 +9497,7 @@
       </c>
       <c r="X7" s="29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y7" s="29" t="inlineStr">
@@ -9539,7 +9539,7 @@
       </c>
       <c r="E8" s="33" t="inlineStr">
         <is>
-          <t>暴击率+10%，暴击效果+25%</t>
+          <t>暴击率+7%，暴击效果+15%</t>
         </is>
       </c>
       <c r="F8" s="29" t="inlineStr">
@@ -9616,7 +9616,7 @@
       </c>
       <c r="X8" s="29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y8" s="29" t="inlineStr">
@@ -9658,7 +9658,7 @@
       </c>
       <c r="E9" s="33" t="inlineStr">
         <is>
-          <t>元素反应效能+20%</t>
+          <t>元素反应效能+12%</t>
         </is>
       </c>
       <c r="F9" s="29" t="inlineStr">
@@ -9735,7 +9735,7 @@
       </c>
       <c r="X9" s="29" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="Y9" s="29" t="inlineStr">
@@ -9777,7 +9777,7 @@
       </c>
       <c r="E10" s="33" t="inlineStr">
         <is>
-          <t>回响效能+8%</t>
+          <t>回响效能+6%</t>
         </is>
       </c>
       <c r="F10" s="29" t="inlineStr">
@@ -9854,7 +9854,7 @@
       </c>
       <c r="X10" s="29" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="Y10" s="29" t="inlineStr">
@@ -9977,7 +9977,7 @@
       </c>
       <c r="X11" s="29" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="Y11" s="29" t="inlineStr">
@@ -10096,7 +10096,7 @@
       </c>
       <c r="X12" s="29" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="Y12" s="29" t="inlineStr">
@@ -21355,8 +21355,6 @@
       <c r="O10" s="24" t="n"/>
       <c r="P10" s="24" t="n"/>
     </row>
-    <row r="11"/>
-    <row r="12"/>
     <row r="13" ht="25" customHeight="1" s="41">
       <c r="A13" s="42" t="inlineStr">
         <is>

--- a/Design/Data/ReEchoData.xlsx
+++ b/Design/Data/ReEchoData.xlsx
@@ -846,7 +846,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="tblCardEffects" displayName="tblCardEffects" ref="Q3:AA104" headerRowCount="1" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="tblCardEffects" displayName="tblCardEffects" ref="Q3:AA106" headerRowCount="1" totalsRowShown="0">
   <tableColumns count="11">
     <tableColumn id="1" name="Id"/>
     <tableColumn id="2" name="CardId"/>
@@ -8879,12 +8879,12 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA112"/>
+  <dimension ref="A1:AA114"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="13.81640625" defaultRowHeight="13"/>
   <cols>
     <col width="25" customWidth="1" style="41" min="1" max="2"/>
@@ -12042,7 +12042,7 @@
       </c>
       <c r="E29" s="33" t="inlineStr">
         <is>
-          <t>你的回响每击杀15名敌人，物攻&amp;元攻永久+1
+          <t xml:space="preserve">你的回响每击杀15名敌人，物攻&amp;元攻永久+1
 你每击杀15名敌人，回响效能永久+2%</t>
         </is>
       </c>
@@ -13114,7 +13114,7 @@
       </c>
       <c r="E38" s="33" t="inlineStr">
         <is>
-          <t>你获得1000时间碎片，随机承受：
+          <t xml:space="preserve">你获得1000时间碎片，随机承受：
 你将不能再刷新商店/你将不能再购买额外卡牌组/敌人将不再掉落时间碎片</t>
         </is>
       </c>
@@ -14428,7 +14428,7 @@
       </c>
       <c r="E49" s="33" t="inlineStr">
         <is>
-          <t>完成任一任务后，获得666时间碎片：
+          <t xml:space="preserve">完成任一任务后，获得666时间碎片：
 击杀111个敌人/结束战斗时≥22生命值/结束战斗时≤3生命值</t>
         </is>
       </c>
@@ -15381,7 +15381,7 @@
       </c>
       <c r="E57" s="33" t="inlineStr">
         <is>
-          <t>你可以在商店赊账，欠款会收取10%利息/每关
+          <t xml:space="preserve">你可以在商店赊账，欠款会收取10%利息/每关
 第8关时，如果你还没有还清，会有很不好的事情发生！！</t>
         </is>
       </c>
@@ -16810,7 +16810,7 @@
       </c>
       <c r="E69" s="39" t="inlineStr">
         <is>
-          <t>每关结束后，你的时间碎片随机+200%或-50%；然后获得50时间碎片
+          <t xml:space="preserve">每关结束后，赌一把大的！攒够了家底以后，商店刷新永远为你开放！
 ——策划 爆培嘉 敬上</t>
         </is>
       </c>
@@ -16930,7 +16930,7 @@
       </c>
       <c r="E70" s="39" t="inlineStr">
         <is>
-          <t>随机获得任意数量项效果：1、暴击率+50%；2、物理攻击力+15；3、生命值调整为5
+          <t xml:space="preserve">选择后，你可能拥有至高无上的暴击数值，也可能从此一蹶不振！
 ——策划 斑 敬上</t>
         </is>
       </c>
@@ -17050,7 +17050,7 @@
       </c>
       <c r="E71" s="39" t="inlineStr">
         <is>
-          <t>回响触碰到敌方单位，会对其造成15物理伤害；触碰到你，转而回复10生命值。
+          <t xml:space="preserve">回响触碰到敌人，造成20物理伤害；如果是你，你回复10生命值。数值每关翻倍！
 ——策划 麦麦熊 敬上</t>
         </is>
       </c>
@@ -17170,7 +17170,7 @@
       </c>
       <c r="E72" s="39" t="inlineStr">
         <is>
-          <t>失去所有时间碎片。每失去15时间碎片，随机获得一些属性！
+          <t xml:space="preserve">失去所有时间碎片。每失去15时间碎片，随机获得一些属性！
 ——策划 呕乐兮 敬上</t>
         </is>
       </c>
@@ -17290,7 +17290,7 @@
       </c>
       <c r="E73" s="39" t="inlineStr">
         <is>
-          <t>每0.5秒，令身边4m内的随机1名敌人【眩晕】至本关结束
+          <t xml:space="preserve">身边的敌人都被你迷倒了！
 ——特别鸣谢 程序 T爷</t>
         </is>
       </c>
@@ -17410,7 +17410,7 @@
       </c>
       <c r="E74" s="39" t="inlineStr">
         <is>
-          <t>你累计承受55伤害后，随机获得5张卡牌
+          <t xml:space="preserve">你努力奔跑。下一关，1滴血换1张1级卡牌
 ——特别鸣谢 程序 Jo爷</t>
         </is>
       </c>
@@ -17530,7 +17530,7 @@
       </c>
       <c r="E75" s="39" t="inlineStr">
         <is>
-          <t>造成的所有物理伤害，随机被修正为可能带有很多0的数字！
+          <t xml:space="preserve">神秘人往你的物理伤害后面加随机个0
 ——特别鸣谢 美术 00</t>
         </is>
       </c>
@@ -17650,7 +17650,7 @@
       </c>
       <c r="E76" s="39" t="inlineStr">
         <is>
-          <t>你的时间碎片获取方式，被赋予“ELO”机制
+          <t xml:space="preserve">经济系统被赋予“ELO”机制
 ——特别鸣谢 美术 子涵</t>
         </is>
       </c>
@@ -17770,7 +17770,7 @@
       </c>
       <c r="E77" s="39" t="inlineStr">
         <is>
-          <t>每一关卡结束后，获得15生命值&amp;2元攻&amp;2物攻
+          <t xml:space="preserve">每一关卡结束后，随机获得巨额生命值/元攻/物攻
 ——特别鸣谢 美术 雯雯</t>
         </is>
       </c>
@@ -18017,7 +18017,7 @@
       <c r="K80" s="43" t="n"/>
       <c r="Q80" s="29" t="inlineStr">
         <is>
-          <t>G_4_1_SWING_BONUS</t>
+          <t xml:space="preserve">G_4_1_REFRESH</t>
         </is>
       </c>
       <c r="R80" s="29" t="inlineStr">
@@ -18042,33 +18042,29 @@
       </c>
       <c r="V80" s="29" t="inlineStr">
         <is>
-          <t>TimeShards</t>
+          <t xml:space="preserve">FreeShopRefresh</t>
         </is>
       </c>
       <c r="W80" s="29" t="inlineStr">
         <is>
-          <t>Add</t>
-        </is>
-      </c>
-      <c r="X80" s="29" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+          <t xml:space="preserve">Override</t>
+        </is>
+      </c>
+      <c r="X80" s="29" t="n">
+        <v>2000</v>
       </c>
       <c r="Y80" s="29" t="inlineStr">
         <is>
-          <t>Card.EasterShardSwing</t>
+          <t xml:space="preserve">Card.EasterShardThreshold</t>
         </is>
       </c>
       <c r="Z80" s="29" t="inlineStr">
         <is>
-          <t>Bonus</t>
-        </is>
-      </c>
-      <c r="AA80" s="29" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+          <t xml:space="preserve">Threshold</t>
+        </is>
+      </c>
+      <c r="AA80" s="29" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="81" ht="22" customHeight="1" s="41">
@@ -18118,10 +18114,8 @@
           <t>Add</t>
         </is>
       </c>
-      <c r="X81" s="29" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="X81" s="29" t="n">
+        <v>1</v>
       </c>
       <c r="Y81" s="29" t="inlineStr">
         <is>
@@ -18153,7 +18147,7 @@
       <c r="K82" s="43" t="n"/>
       <c r="Q82" s="29" t="inlineStr">
         <is>
-          <t>G_4_2_PHYSICAL</t>
+          <t xml:space="preserve">G_4_2_CRIT_EFFECT</t>
         </is>
       </c>
       <c r="R82" s="29" t="inlineStr">
@@ -18178,7 +18172,7 @@
       </c>
       <c r="V82" s="29" t="inlineStr">
         <is>
-          <t>PhysicalAttack</t>
+          <t xml:space="preserve">CriticalEffect</t>
         </is>
       </c>
       <c r="W82" s="29" t="inlineStr">
@@ -18186,10 +18180,8 @@
           <t>Add</t>
         </is>
       </c>
-      <c r="X82" s="29" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="X82" s="29" t="n">
+        <v>3</v>
       </c>
       <c r="Y82" s="29" t="inlineStr">
         <is>
@@ -18293,22 +18285,20 @@
       <c r="K84" s="43" t="n"/>
       <c r="Q84" s="29" t="inlineStr">
         <is>
-          <t>G_4_3_CONTACT_DAMAGE</t>
+          <t xml:space="preserve">G_4_2_CRIT_PENALTY</t>
         </is>
       </c>
       <c r="R84" s="29" t="inlineStr">
         <is>
-          <t>G_4_3</t>
-        </is>
-      </c>
-      <c r="S84" s="29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t xml:space="preserve">G_4_2</t>
+        </is>
+      </c>
+      <c r="S84" s="29" t="n">
+        <v>4</v>
       </c>
       <c r="T84" s="29" t="inlineStr">
         <is>
-          <t>OnCompileRules</t>
+          <t xml:space="preserve">OnGrant</t>
         </is>
       </c>
       <c r="U84" s="29" t="inlineStr">
@@ -18318,33 +18308,29 @@
       </c>
       <c r="V84" s="29" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t xml:space="preserve">CritNegateAmplification</t>
         </is>
       </c>
       <c r="W84" s="29" t="inlineStr">
         <is>
-          <t>Add</t>
-        </is>
-      </c>
-      <c r="X84" s="29" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+          <t xml:space="preserve">Override</t>
+        </is>
+      </c>
+      <c r="X84" s="29" t="n">
+        <v>1</v>
       </c>
       <c r="Y84" s="29" t="inlineStr">
         <is>
-          <t>Card.EasterEchoContact</t>
+          <t xml:space="preserve">Card.EasterIndependentGrant</t>
         </is>
       </c>
       <c r="Z84" s="29" t="inlineStr">
         <is>
-          <t>PlayerHealing</t>
-        </is>
-      </c>
-      <c r="AA84" s="29" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+          <t xml:space="preserve">Chance</t>
+        </is>
+      </c>
+      <c r="AA84" s="29" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="85" ht="22" customHeight="1" s="41">
@@ -18361,12 +18347,12 @@
       <c r="K85" s="43" t="n"/>
       <c r="Q85" s="29" t="inlineStr">
         <is>
-          <t>G_4_4_HP</t>
+          <t xml:space="preserve">G_4_3_CONTACT_DAMAGE</t>
         </is>
       </c>
       <c r="R85" s="29" t="inlineStr">
         <is>
-          <t>G_4_4</t>
+          <t xml:space="preserve">G_4_3</t>
         </is>
       </c>
       <c r="S85" s="29" t="inlineStr">
@@ -18376,7 +18362,7 @@
       </c>
       <c r="T85" s="29" t="inlineStr">
         <is>
-          <t>OnGrant</t>
+          <t xml:space="preserve">OnCompileRules</t>
         </is>
       </c>
       <c r="U85" s="29" t="inlineStr">
@@ -18386,7 +18372,7 @@
       </c>
       <c r="V85" s="29" t="inlineStr">
         <is>
-          <t>HpMaxAndPoint</t>
+          <t xml:space="preserve">Damage</t>
         </is>
       </c>
       <c r="W85" s="29" t="inlineStr">
@@ -18394,25 +18380,21 @@
           <t>Add</t>
         </is>
       </c>
-      <c r="X85" s="29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="X85" s="29" t="n">
+        <v>20</v>
       </c>
       <c r="Y85" s="29" t="inlineStr">
         <is>
-          <t>Card.EasterShardSacrifice</t>
+          <t xml:space="preserve">Card.EasterEchoContact</t>
         </is>
       </c>
       <c r="Z85" s="29" t="inlineStr">
         <is>
-          <t>ShardUnit</t>
-        </is>
-      </c>
-      <c r="AA85" s="29" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+          <t xml:space="preserve">PlayerHealing</t>
+        </is>
+      </c>
+      <c r="AA85" s="29" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="86" ht="22" customHeight="1" s="41">
@@ -18429,7 +18411,7 @@
       <c r="K86" s="43" t="n"/>
       <c r="Q86" s="39" t="inlineStr">
         <is>
-          <t>G_4_4_PHYSICAL</t>
+          <t xml:space="preserve">G_4_4_HP</t>
         </is>
       </c>
       <c r="R86" s="39" t="inlineStr">
@@ -18437,10 +18419,8 @@
           <t>G_4_4</t>
         </is>
       </c>
-      <c r="S86" s="39" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="S86" s="39" t="n">
+        <v>1</v>
       </c>
       <c r="T86" s="39" t="inlineStr">
         <is>
@@ -18454,7 +18434,7 @@
       </c>
       <c r="V86" s="39" t="inlineStr">
         <is>
-          <t>PhysicalAttack</t>
+          <t xml:space="preserve">HpMaxAndPoint</t>
         </is>
       </c>
       <c r="W86" s="39" t="inlineStr">
@@ -18497,7 +18477,7 @@
       <c r="K87" s="43" t="n"/>
       <c r="Q87" s="39" t="inlineStr">
         <is>
-          <t>G_4_4_ELEMENTAL</t>
+          <t xml:space="preserve">G_4_4_PHYSICAL</t>
         </is>
       </c>
       <c r="R87" s="39" t="inlineStr">
@@ -18505,10 +18485,8 @@
           <t>G_4_4</t>
         </is>
       </c>
-      <c r="S87" s="39" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="S87" s="39" t="n">
+        <v>2</v>
       </c>
       <c r="T87" s="39" t="inlineStr">
         <is>
@@ -18522,7 +18500,7 @@
       </c>
       <c r="V87" s="39" t="inlineStr">
         <is>
-          <t>ElementalAttack</t>
+          <t xml:space="preserve">PhysicalAttack</t>
         </is>
       </c>
       <c r="W87" s="39" t="inlineStr">
@@ -18565,7 +18543,7 @@
       <c r="K88" s="43" t="n"/>
       <c r="Q88" s="39" t="inlineStr">
         <is>
-          <t>G_4_4_CRIT_RATE</t>
+          <t xml:space="preserve">G_4_4_ELEMENTAL</t>
         </is>
       </c>
       <c r="R88" s="39" t="inlineStr">
@@ -18573,10 +18551,8 @@
           <t>G_4_4</t>
         </is>
       </c>
-      <c r="S88" s="39" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="S88" s="39" t="n">
+        <v>3</v>
       </c>
       <c r="T88" s="39" t="inlineStr">
         <is>
@@ -18590,7 +18566,7 @@
       </c>
       <c r="V88" s="39" t="inlineStr">
         <is>
-          <t>CriticalRate</t>
+          <t xml:space="preserve">ElementalAttack</t>
         </is>
       </c>
       <c r="W88" s="39" t="inlineStr">
@@ -18598,10 +18574,8 @@
           <t>Add</t>
         </is>
       </c>
-      <c r="X88" s="39" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
+      <c r="X88" s="39" t="n">
+        <v>1</v>
       </c>
       <c r="Y88" s="39" t="inlineStr">
         <is>
@@ -18633,7 +18607,7 @@
       <c r="K89" s="43" t="n"/>
       <c r="Q89" s="39" t="inlineStr">
         <is>
-          <t>G_4_4_CRIT_EFFECT</t>
+          <t xml:space="preserve">G_4_4_CRIT_RATE</t>
         </is>
       </c>
       <c r="R89" s="39" t="inlineStr">
@@ -18641,10 +18615,8 @@
           <t>G_4_4</t>
         </is>
       </c>
-      <c r="S89" s="39" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="S89" s="39" t="n">
+        <v>4</v>
       </c>
       <c r="T89" s="39" t="inlineStr">
         <is>
@@ -18658,7 +18630,7 @@
       </c>
       <c r="V89" s="39" t="inlineStr">
         <is>
-          <t>CriticalEffect</t>
+          <t xml:space="preserve">CriticalRate</t>
         </is>
       </c>
       <c r="W89" s="39" t="inlineStr">
@@ -18666,10 +18638,8 @@
           <t>Add</t>
         </is>
       </c>
-      <c r="X89" s="39" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
+      <c r="X89" s="39" t="n">
+        <v>0.05</v>
       </c>
       <c r="Y89" s="39" t="inlineStr">
         <is>
@@ -18701,7 +18671,7 @@
       <c r="K90" s="43" t="n"/>
       <c r="Q90" s="39" t="inlineStr">
         <is>
-          <t>G_4_4_ECHO</t>
+          <t xml:space="preserve">G_4_4_CRIT_EFFECT</t>
         </is>
       </c>
       <c r="R90" s="39" t="inlineStr">
@@ -18709,10 +18679,8 @@
           <t>G_4_4</t>
         </is>
       </c>
-      <c r="S90" s="39" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="S90" s="39" t="n">
+        <v>5</v>
       </c>
       <c r="T90" s="39" t="inlineStr">
         <is>
@@ -18726,7 +18694,7 @@
       </c>
       <c r="V90" s="39" t="inlineStr">
         <is>
-          <t>EchoEfficiency</t>
+          <t xml:space="preserve">CriticalEffect</t>
         </is>
       </c>
       <c r="W90" s="39" t="inlineStr">
@@ -18734,10 +18702,8 @@
           <t>Add</t>
         </is>
       </c>
-      <c r="X90" s="39" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
+      <c r="X90" s="39" t="n">
+        <v>0.1</v>
       </c>
       <c r="Y90" s="39" t="inlineStr">
         <is>
@@ -18769,7 +18735,7 @@
       <c r="K91" s="43" t="n"/>
       <c r="Q91" s="39" t="inlineStr">
         <is>
-          <t>G_4_4_REACTION</t>
+          <t xml:space="preserve">G_4_4_ECHO</t>
         </is>
       </c>
       <c r="R91" s="39" t="inlineStr">
@@ -18777,10 +18743,8 @@
           <t>G_4_4</t>
         </is>
       </c>
-      <c r="S91" s="39" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="S91" s="39" t="n">
+        <v>6</v>
       </c>
       <c r="T91" s="39" t="inlineStr">
         <is>
@@ -18794,7 +18758,7 @@
       </c>
       <c r="V91" s="39" t="inlineStr">
         <is>
-          <t>ReactionEfficiency</t>
+          <t xml:space="preserve">EchoEfficiency</t>
         </is>
       </c>
       <c r="W91" s="39" t="inlineStr">
@@ -18837,22 +18801,20 @@
       <c r="K92" s="43" t="n"/>
       <c r="Q92" s="39" t="inlineStr">
         <is>
-          <t>G_4_5_STUN</t>
+          <t xml:space="preserve">G_4_4_REACTION</t>
         </is>
       </c>
       <c r="R92" s="39" t="inlineStr">
         <is>
-          <t>G_4_5</t>
-        </is>
-      </c>
-      <c r="S92" s="39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t xml:space="preserve">G_4_4</t>
+        </is>
+      </c>
+      <c r="S92" s="39" t="n">
+        <v>7</v>
       </c>
       <c r="T92" s="39" t="inlineStr">
         <is>
-          <t>OnEncounterTick</t>
+          <t xml:space="preserve">OnGrant</t>
         </is>
       </c>
       <c r="U92" s="39" t="inlineStr">
@@ -18862,33 +18824,29 @@
       </c>
       <c r="V92" s="39" t="inlineStr">
         <is>
-          <t>Stun</t>
+          <t xml:space="preserve">ReactionEfficiency</t>
         </is>
       </c>
       <c r="W92" s="39" t="inlineStr">
         <is>
-          <t>Override</t>
-        </is>
-      </c>
-      <c r="X92" s="39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t xml:space="preserve">Add</t>
+        </is>
+      </c>
+      <c r="X92" s="39" t="n">
+        <v>0.05</v>
       </c>
       <c r="Y92" s="39" t="inlineStr">
         <is>
-          <t>Card.EasterRandomStun</t>
+          <t xml:space="preserve">Card.EasterShardSacrifice</t>
         </is>
       </c>
       <c r="Z92" s="39" t="inlineStr">
         <is>
-          <t>PulseInterval</t>
-        </is>
-      </c>
-      <c r="AA92" s="39" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+          <t xml:space="preserve">ShardUnit</t>
+        </is>
+      </c>
+      <c r="AA92" s="39" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="93" ht="22" customHeight="1" s="41">
@@ -18905,7 +18863,7 @@
       <c r="K93" s="43" t="n"/>
       <c r="Q93" s="39" t="inlineStr">
         <is>
-          <t>G_4_5_RADIUS</t>
+          <t xml:space="preserve">G_4_5_STUN</t>
         </is>
       </c>
       <c r="R93" s="39" t="inlineStr">
@@ -18913,10 +18871,8 @@
           <t>G_4_5</t>
         </is>
       </c>
-      <c r="S93" s="39" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="S93" s="39" t="n">
+        <v>1</v>
       </c>
       <c r="T93" s="39" t="inlineStr">
         <is>
@@ -18930,7 +18886,7 @@
       </c>
       <c r="V93" s="39" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t xml:space="preserve">Stun</t>
         </is>
       </c>
       <c r="W93" s="39" t="inlineStr">
@@ -18938,10 +18894,8 @@
           <t>Override</t>
         </is>
       </c>
-      <c r="X93" s="39" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
+      <c r="X93" s="39" t="n">
+        <v>1</v>
       </c>
       <c r="Y93" s="39" t="inlineStr">
         <is>
@@ -18950,13 +18904,11 @@
       </c>
       <c r="Z93" s="39" t="inlineStr">
         <is>
-          <t>RadiusCm</t>
-        </is>
-      </c>
-      <c r="AA93" s="39" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
+          <t xml:space="preserve">PulseInterval</t>
+        </is>
+      </c>
+      <c r="AA93" s="39" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="94" ht="22" customHeight="1" s="41">
@@ -18973,22 +18925,20 @@
       <c r="K94" s="43" t="n"/>
       <c r="Q94" s="39" t="inlineStr">
         <is>
-          <t>G_4_6_THRESHOLD</t>
+          <t xml:space="preserve">G_4_5_RADIUS</t>
         </is>
       </c>
       <c r="R94" s="39" t="inlineStr">
         <is>
-          <t>G_4_6</t>
-        </is>
-      </c>
-      <c r="S94" s="39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t xml:space="preserve">G_4_5</t>
+        </is>
+      </c>
+      <c r="S94" s="39" t="n">
+        <v>2</v>
       </c>
       <c r="T94" s="39" t="inlineStr">
         <is>
-          <t>OnDamageResolved</t>
+          <t xml:space="preserve">OnEncounterTick</t>
         </is>
       </c>
       <c r="U94" s="39" t="inlineStr">
@@ -19003,28 +18953,24 @@
       </c>
       <c r="W94" s="39" t="inlineStr">
         <is>
-          <t>Add</t>
-        </is>
-      </c>
-      <c r="X94" s="39" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
+          <t xml:space="preserve">Override</t>
+        </is>
+      </c>
+      <c r="X94" s="39" t="n">
+        <v>500</v>
       </c>
       <c r="Y94" s="39" t="inlineStr">
         <is>
-          <t>Card.EasterDamageCards</t>
+          <t xml:space="preserve">Card.EasterRandomStun</t>
         </is>
       </c>
       <c r="Z94" s="39" t="inlineStr">
         <is>
-          <t>GrantCount</t>
-        </is>
-      </c>
-      <c r="AA94" s="39" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+          <t xml:space="preserve">RadiusCm</t>
+        </is>
+      </c>
+      <c r="AA94" s="39" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="95" ht="22" customHeight="1" s="41">
@@ -19041,22 +18987,20 @@
       <c r="K95" s="43" t="n"/>
       <c r="Q95" s="39" t="inlineStr">
         <is>
-          <t>G_4_7_ZERO</t>
+          <t xml:space="preserve">G_4_5_COUNT</t>
         </is>
       </c>
       <c r="R95" s="39" t="inlineStr">
         <is>
-          <t>G_4_7</t>
-        </is>
-      </c>
-      <c r="S95" s="39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t xml:space="preserve">G_4_5</t>
+        </is>
+      </c>
+      <c r="S95" s="39" t="n">
+        <v>3</v>
       </c>
       <c r="T95" s="39" t="inlineStr">
         <is>
-          <t>BeforeOutgoingHit</t>
+          <t xml:space="preserve">OnEncounterTick</t>
         </is>
       </c>
       <c r="U95" s="39" t="inlineStr">
@@ -19066,7 +19010,7 @@
       </c>
       <c r="V95" s="39" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t xml:space="preserve">Stun</t>
         </is>
       </c>
       <c r="W95" s="39" t="inlineStr">
@@ -19074,25 +19018,21 @@
           <t>Override</t>
         </is>
       </c>
-      <c r="X95" s="39" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="X95" s="39" t="n">
+        <v>5</v>
       </c>
       <c r="Y95" s="39" t="inlineStr">
         <is>
-          <t>Card.EasterPhysicalLottery</t>
+          <t xml:space="preserve">Card.EasterRandomStun</t>
         </is>
       </c>
       <c r="Z95" s="39" t="inlineStr">
         <is>
-          <t>Probability</t>
-        </is>
-      </c>
-      <c r="AA95" s="39" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
+          <t xml:space="preserve">TargetCount</t>
+        </is>
+      </c>
+      <c r="AA95" s="39" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="96" ht="22" customHeight="1" s="41">
@@ -19109,22 +19049,20 @@
       <c r="K96" s="43" t="n"/>
       <c r="Q96" s="39" t="inlineStr">
         <is>
-          <t>G_4_7_TEN</t>
+          <t xml:space="preserve">G_4_6_REWARD</t>
         </is>
       </c>
       <c r="R96" s="39" t="inlineStr">
         <is>
-          <t>G_4_7</t>
-        </is>
-      </c>
-      <c r="S96" s="39" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+          <t xml:space="preserve">G_4_6</t>
+        </is>
+      </c>
+      <c r="S96" s="39" t="n">
+        <v>1</v>
       </c>
       <c r="T96" s="39" t="inlineStr">
         <is>
-          <t>BeforeOutgoingHit</t>
+          <t xml:space="preserve">OnEncounterEnd</t>
         </is>
       </c>
       <c r="U96" s="39" t="inlineStr">
@@ -19134,7 +19072,7 @@
       </c>
       <c r="V96" s="39" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t xml:space="preserve">MinimumGuaranteedTier</t>
         </is>
       </c>
       <c r="W96" s="39" t="inlineStr">
@@ -19142,25 +19080,21 @@
           <t>Override</t>
         </is>
       </c>
-      <c r="X96" s="39" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="X96" s="39" t="n">
+        <v>1</v>
       </c>
       <c r="Y96" s="39" t="inlineStr">
         <is>
-          <t>Card.EasterPhysicalLottery</t>
+          <t xml:space="preserve">Card.EasterDamageCards</t>
         </is>
       </c>
       <c r="Z96" s="39" t="inlineStr">
         <is>
-          <t>Probability</t>
-        </is>
-      </c>
-      <c r="AA96" s="39" t="inlineStr">
-        <is>
-          <t>0.35</t>
-        </is>
+          <t xml:space="preserve">GrantTier</t>
+        </is>
+      </c>
+      <c r="AA96" s="39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="97" ht="22" customHeight="1" s="41">
@@ -19177,7 +19111,7 @@
       <c r="K97" s="43" t="n"/>
       <c r="Q97" s="39" t="inlineStr">
         <is>
-          <t>G_4_7_HUNDRED</t>
+          <t xml:space="preserve">G_4_7_ZERO</t>
         </is>
       </c>
       <c r="R97" s="39" t="inlineStr">
@@ -19185,10 +19119,8 @@
           <t>G_4_7</t>
         </is>
       </c>
-      <c r="S97" s="39" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="S97" s="39" t="n">
+        <v>1</v>
       </c>
       <c r="T97" s="39" t="inlineStr">
         <is>
@@ -19210,10 +19142,8 @@
           <t>Override</t>
         </is>
       </c>
-      <c r="X97" s="39" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
+      <c r="X97" s="39" t="n">
+        <v>0</v>
       </c>
       <c r="Y97" s="39" t="inlineStr">
         <is>
@@ -19225,10 +19155,8 @@
           <t>Probability</t>
         </is>
       </c>
-      <c r="AA97" s="39" t="inlineStr">
-        <is>
-          <t>0.4</t>
-        </is>
+      <c r="AA97" s="39" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="98" ht="22" customHeight="1" s="41">
@@ -19245,7 +19173,7 @@
       <c r="K98" s="43" t="n"/>
       <c r="Q98" s="39" t="inlineStr">
         <is>
-          <t>G_4_7_THOUSAND</t>
+          <t xml:space="preserve">G_4_7_TEN</t>
         </is>
       </c>
       <c r="R98" s="39" t="inlineStr">
@@ -19253,10 +19181,8 @@
           <t>G_4_7</t>
         </is>
       </c>
-      <c r="S98" s="39" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="S98" s="39" t="n">
+        <v>2</v>
       </c>
       <c r="T98" s="39" t="inlineStr">
         <is>
@@ -19278,10 +19204,8 @@
           <t>Override</t>
         </is>
       </c>
-      <c r="X98" s="39" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
+      <c r="X98" s="39" t="n">
+        <v>10</v>
       </c>
       <c r="Y98" s="39" t="inlineStr">
         <is>
@@ -19293,10 +19217,8 @@
           <t>Probability</t>
         </is>
       </c>
-      <c r="AA98" s="39" t="inlineStr">
-        <is>
-          <t>0.08</t>
-        </is>
+      <c r="AA98" s="39" t="n">
+        <v>0.35</v>
       </c>
     </row>
     <row r="99" ht="22" customHeight="1" s="41">
@@ -19313,7 +19235,7 @@
       <c r="K99" s="43" t="n"/>
       <c r="Q99" s="39" t="inlineStr">
         <is>
-          <t>G_4_7_TEN_THOUSAND</t>
+          <t xml:space="preserve">G_4_7_HUNDRED</t>
         </is>
       </c>
       <c r="R99" s="39" t="inlineStr">
@@ -19321,10 +19243,8 @@
           <t>G_4_7</t>
         </is>
       </c>
-      <c r="S99" s="39" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="S99" s="39" t="n">
+        <v>3</v>
       </c>
       <c r="T99" s="39" t="inlineStr">
         <is>
@@ -19346,10 +19266,8 @@
           <t>Override</t>
         </is>
       </c>
-      <c r="X99" s="39" t="inlineStr">
-        <is>
-          <t>10000</t>
-        </is>
+      <c r="X99" s="39" t="n">
+        <v>100</v>
       </c>
       <c r="Y99" s="39" t="inlineStr">
         <is>
@@ -19361,10 +19279,8 @@
           <t>Probability</t>
         </is>
       </c>
-      <c r="AA99" s="39" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
+      <c r="AA99" s="39" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="100" ht="22" customHeight="1" s="41">
@@ -19381,22 +19297,20 @@
       <c r="K100" s="43" t="n"/>
       <c r="Q100" s="39" t="inlineStr">
         <is>
-          <t>G_4_8_MORE</t>
+          <t xml:space="preserve">G_4_7_THOUSAND</t>
         </is>
       </c>
       <c r="R100" s="39" t="inlineStr">
         <is>
-          <t>G_4_8</t>
-        </is>
-      </c>
-      <c r="S100" s="39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t xml:space="preserve">G_4_7</t>
+        </is>
+      </c>
+      <c r="S100" s="39" t="n">
+        <v>4</v>
       </c>
       <c r="T100" s="39" t="inlineStr">
         <is>
-          <t>OnEncounterEnd</t>
+          <t xml:space="preserve">BeforeOutgoingHit</t>
         </is>
       </c>
       <c r="U100" s="39" t="inlineStr">
@@ -19406,33 +19320,29 @@
       </c>
       <c r="V100" s="39" t="inlineStr">
         <is>
-          <t>TimeShards</t>
+          <t xml:space="preserve">Damage</t>
         </is>
       </c>
       <c r="W100" s="39" t="inlineStr">
         <is>
-          <t>Multiply</t>
-        </is>
-      </c>
-      <c r="X100" s="39" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
+          <t xml:space="preserve">Override</t>
+        </is>
+      </c>
+      <c r="X100" s="39" t="n">
+        <v>1000</v>
       </c>
       <c r="Y100" s="39" t="inlineStr">
         <is>
-          <t>Card.EasterShardComparison</t>
+          <t xml:space="preserve">Card.EasterPhysicalLottery</t>
         </is>
       </c>
       <c r="Z100" s="39" t="inlineStr">
         <is>
-          <t>Step</t>
-        </is>
-      </c>
-      <c r="AA100" s="39" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+          <t xml:space="preserve">Probability</t>
+        </is>
+      </c>
+      <c r="AA100" s="39" t="n">
+        <v>0.09</v>
       </c>
     </row>
     <row r="101" ht="22" customHeight="1" s="41">
@@ -19449,22 +19359,20 @@
       <c r="K101" s="43" t="n"/>
       <c r="Q101" s="39" t="inlineStr">
         <is>
-          <t>G_4_8_LESS</t>
+          <t xml:space="preserve">G_4_7_TEN_THOUSAND</t>
         </is>
       </c>
       <c r="R101" s="39" t="inlineStr">
         <is>
-          <t>G_4_8</t>
-        </is>
-      </c>
-      <c r="S101" s="39" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+          <t xml:space="preserve">G_4_7</t>
+        </is>
+      </c>
+      <c r="S101" s="39" t="n">
+        <v>5</v>
       </c>
       <c r="T101" s="39" t="inlineStr">
         <is>
-          <t>OnEncounterEnd</t>
+          <t xml:space="preserve">BeforeOutgoingHit</t>
         </is>
       </c>
       <c r="U101" s="39" t="inlineStr">
@@ -19474,33 +19382,29 @@
       </c>
       <c r="V101" s="39" t="inlineStr">
         <is>
-          <t>TimeShards</t>
+          <t xml:space="preserve">Damage</t>
         </is>
       </c>
       <c r="W101" s="39" t="inlineStr">
         <is>
-          <t>Multiply</t>
-        </is>
-      </c>
-      <c r="X101" s="39" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
+          <t xml:space="preserve">Override</t>
+        </is>
+      </c>
+      <c r="X101" s="39" t="n">
+        <v>10000</v>
       </c>
       <c r="Y101" s="39" t="inlineStr">
         <is>
-          <t>Card.EasterShardComparison</t>
+          <t xml:space="preserve">Card.EasterPhysicalLottery</t>
         </is>
       </c>
       <c r="Z101" s="39" t="inlineStr">
         <is>
-          <t>Step</t>
-        </is>
-      </c>
-      <c r="AA101" s="39" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+          <t xml:space="preserve">Probability</t>
+        </is>
+      </c>
+      <c r="AA101" s="39" t="n">
+        <v>0.01</v>
       </c>
     </row>
     <row r="102" ht="22" customHeight="1" s="41">
@@ -19517,12 +19421,12 @@
       <c r="K102" s="43" t="n"/>
       <c r="Q102" s="39" t="inlineStr">
         <is>
-          <t>G_4_9_HP</t>
+          <t xml:space="preserve">G_4_8_MORE</t>
         </is>
       </c>
       <c r="R102" s="39" t="inlineStr">
         <is>
-          <t>G_4_9</t>
+          <t xml:space="preserve">G_4_8</t>
         </is>
       </c>
       <c r="S102" s="39" t="inlineStr">
@@ -19542,33 +19446,29 @@
       </c>
       <c r="V102" s="39" t="inlineStr">
         <is>
-          <t>HpMaxAndPoint</t>
+          <t xml:space="preserve">TimeShards</t>
         </is>
       </c>
       <c r="W102" s="39" t="inlineStr">
         <is>
-          <t>Add</t>
-        </is>
-      </c>
-      <c r="X102" s="39" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+          <t xml:space="preserve">Multiply</t>
+        </is>
+      </c>
+      <c r="X102" s="39" t="n">
+        <v>-0.01</v>
       </c>
       <c r="Y102" s="39" t="inlineStr">
         <is>
-          <t>Card.EasterAttendance</t>
+          <t xml:space="preserve">Card.EasterShardComparison</t>
         </is>
       </c>
       <c r="Z102" s="39" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="AA102" s="39" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t xml:space="preserve">Step</t>
+        </is>
+      </c>
+      <c r="AA102" s="39" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="103" ht="26" customHeight="1" s="41">
@@ -19585,12 +19485,12 @@
       <c r="K103" s="43" t="n"/>
       <c r="Q103" s="39" t="inlineStr">
         <is>
-          <t>G_4_9_ELEMENTAL</t>
+          <t xml:space="preserve">G_4_8_LESS</t>
         </is>
       </c>
       <c r="R103" s="39" t="inlineStr">
         <is>
-          <t>G_4_9</t>
+          <t xml:space="preserve">G_4_8</t>
         </is>
       </c>
       <c r="S103" s="39" t="inlineStr">
@@ -19610,39 +19510,35 @@
       </c>
       <c r="V103" s="39" t="inlineStr">
         <is>
-          <t>ElementalAttack</t>
+          <t xml:space="preserve">TimeShards</t>
         </is>
       </c>
       <c r="W103" s="39" t="inlineStr">
         <is>
-          <t>Add</t>
-        </is>
-      </c>
-      <c r="X103" s="39" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+          <t xml:space="preserve">Multiply</t>
+        </is>
+      </c>
+      <c r="X103" s="39" t="n">
+        <v>0.05</v>
       </c>
       <c r="Y103" s="39" t="inlineStr">
         <is>
-          <t>Card.EasterAttendance</t>
+          <t xml:space="preserve">Card.EasterShardComparison</t>
         </is>
       </c>
       <c r="Z103" s="39" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="AA103" s="39" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t xml:space="preserve">Step</t>
+        </is>
+      </c>
+      <c r="AA103" s="39" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="104" ht="26" customHeight="1" s="41">
       <c r="Q104" s="39" t="inlineStr">
         <is>
-          <t>G_4_9_PHYSICAL</t>
+          <t xml:space="preserve">G_4_9_HP</t>
         </is>
       </c>
       <c r="R104" s="39" t="inlineStr">
@@ -19650,10 +19546,8 @@
           <t>G_4_9</t>
         </is>
       </c>
-      <c r="S104" s="39" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="S104" s="39" t="n">
+        <v>1</v>
       </c>
       <c r="T104" s="39" t="inlineStr">
         <is>
@@ -19667,7 +19561,7 @@
       </c>
       <c r="V104" s="39" t="inlineStr">
         <is>
-          <t>PhysicalAttack</t>
+          <t xml:space="preserve">HpMaxAndPoint</t>
         </is>
       </c>
       <c r="W104" s="39" t="inlineStr">
@@ -19675,10 +19569,8 @@
           <t>Add</t>
         </is>
       </c>
-      <c r="X104" s="39" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="X104" s="39" t="n">
+        <v>1</v>
       </c>
       <c r="Y104" s="39" t="inlineStr">
         <is>
@@ -19687,121 +19579,119 @@
       </c>
       <c r="Z104" s="39" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="AA104" s="39" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t xml:space="preserve">Max</t>
+        </is>
+      </c>
+      <c r="AA104" s="39" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="105" ht="26" customHeight="1" s="41">
-      <c r="Q105" s="46" t="inlineStr">
-        <is>
-          <t>G_4_7_HUNDRED</t>
-        </is>
-      </c>
-      <c r="R105" s="46" t="inlineStr">
-        <is>
-          <t>G_4_7</t>
-        </is>
-      </c>
-      <c r="S105" s="46" t="n">
+      <c r="Q105" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G_4_9_ELEMENTAL</t>
+        </is>
+      </c>
+      <c r="R105" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G_4_9</t>
+        </is>
+      </c>
+      <c r="S105" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="T105" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OnEncounterEnd</t>
+        </is>
+      </c>
+      <c r="U105" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CardBehavior</t>
+        </is>
+      </c>
+      <c r="V105" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ElementalAttack</t>
+        </is>
+      </c>
+      <c r="W105" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Add</t>
+        </is>
+      </c>
+      <c r="X105" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y105" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Card.EasterAttendance</t>
+        </is>
+      </c>
+      <c r="Z105" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Max</t>
+        </is>
+      </c>
+      <c r="AA105" s="39" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="106" ht="26" customHeight="1" s="41">
+      <c r="Q106" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G_4_9_PHYSICAL</t>
+        </is>
+      </c>
+      <c r="R106" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G_4_9</t>
+        </is>
+      </c>
+      <c r="S106" s="39" t="n">
         <v>3</v>
       </c>
-      <c r="T105" s="46" t="inlineStr">
-        <is>
-          <t>BeforeOutgoingHit</t>
-        </is>
-      </c>
-      <c r="U105" s="46" t="inlineStr">
-        <is>
-          <t>CardBehavior</t>
-        </is>
-      </c>
-      <c r="V105" s="46" t="inlineStr">
-        <is>
-          <t>Damage</t>
-        </is>
-      </c>
-      <c r="W105" s="46" t="inlineStr">
-        <is>
-          <t>Override</t>
-        </is>
-      </c>
-      <c r="X105" s="46" t="n">
-        <v>100</v>
-      </c>
-      <c r="Y105" s="46" t="inlineStr">
-        <is>
-          <t>Card.EasterPhysicalLottery</t>
-        </is>
-      </c>
-      <c r="Z105" s="46" t="inlineStr">
-        <is>
-          <t>Probability</t>
-        </is>
-      </c>
-      <c r="AA105" s="46" t="n">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="106" ht="26" customHeight="1" s="41">
-      <c r="Q106" s="46" t="inlineStr">
-        <is>
-          <t>G_4_7_THOUSAND</t>
-        </is>
-      </c>
-      <c r="R106" s="46" t="inlineStr">
-        <is>
-          <t>G_4_7</t>
-        </is>
-      </c>
-      <c r="S106" s="46" t="n">
-        <v>4</v>
-      </c>
-      <c r="T106" s="46" t="inlineStr">
-        <is>
-          <t>BeforeOutgoingHit</t>
-        </is>
-      </c>
-      <c r="U106" s="46" t="inlineStr">
-        <is>
-          <t>CardBehavior</t>
-        </is>
-      </c>
-      <c r="V106" s="46" t="inlineStr">
-        <is>
-          <t>Damage</t>
-        </is>
-      </c>
-      <c r="W106" s="46" t="inlineStr">
-        <is>
-          <t>Override</t>
-        </is>
-      </c>
-      <c r="X106" s="46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y106" s="46" t="inlineStr">
-        <is>
-          <t>Card.EasterPhysicalLottery</t>
-        </is>
-      </c>
-      <c r="Z106" s="46" t="inlineStr">
-        <is>
-          <t>Probability</t>
-        </is>
-      </c>
-      <c r="AA106" s="46" t="n">
-        <v>0.08</v>
+      <c r="T106" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OnEncounterEnd</t>
+        </is>
+      </c>
+      <c r="U106" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CardBehavior</t>
+        </is>
+      </c>
+      <c r="V106" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PhysicalAttack</t>
+        </is>
+      </c>
+      <c r="W106" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Add</t>
+        </is>
+      </c>
+      <c r="X106" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y106" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Card.EasterAttendance</t>
+        </is>
+      </c>
+      <c r="Z106" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Max</t>
+        </is>
+      </c>
+      <c r="AA106" s="39" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="107" ht="26" customHeight="1" s="41">
       <c r="Q107" s="46" t="inlineStr">
         <is>
-          <t>G_4_7_TEN_THOUSAND</t>
+          <t>G_4_7_HUNDRED</t>
         </is>
       </c>
       <c r="R107" s="46" t="inlineStr">
@@ -19810,7 +19700,7 @@
         </is>
       </c>
       <c r="S107" s="46" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T107" s="46" t="inlineStr">
         <is>
@@ -19833,7 +19723,7 @@
         </is>
       </c>
       <c r="X107" s="46" t="n">
-        <v>10000</v>
+        <v>100</v>
       </c>
       <c r="Y107" s="46" t="inlineStr">
         <is>
@@ -19846,26 +19736,26 @@
         </is>
       </c>
       <c r="AA107" s="46" t="n">
-        <v>0.02</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="108" ht="26" customHeight="1" s="41">
       <c r="Q108" s="46" t="inlineStr">
         <is>
-          <t>G_4_8_MORE</t>
+          <t>G_4_7_THOUSAND</t>
         </is>
       </c>
       <c r="R108" s="46" t="inlineStr">
         <is>
-          <t>G_4_8</t>
+          <t>G_4_7</t>
         </is>
       </c>
       <c r="S108" s="46" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T108" s="46" t="inlineStr">
         <is>
-          <t>OnEncounterEnd</t>
+          <t>BeforeOutgoingHit</t>
         </is>
       </c>
       <c r="U108" s="46" t="inlineStr">
@@ -19875,48 +19765,48 @@
       </c>
       <c r="V108" s="46" t="inlineStr">
         <is>
-          <t>TimeShards</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="W108" s="46" t="inlineStr">
         <is>
-          <t>Multiply</t>
+          <t>Override</t>
         </is>
       </c>
       <c r="X108" s="46" t="n">
-        <v>-0.01</v>
+        <v>1000</v>
       </c>
       <c r="Y108" s="46" t="inlineStr">
         <is>
-          <t>Card.EasterShardComparison</t>
+          <t>Card.EasterPhysicalLottery</t>
         </is>
       </c>
       <c r="Z108" s="46" t="inlineStr">
         <is>
-          <t>Step</t>
+          <t>Probability</t>
         </is>
       </c>
       <c r="AA108" s="46" t="n">
-        <v>5</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="109" ht="26" customHeight="1" s="41">
       <c r="Q109" s="46" t="inlineStr">
         <is>
-          <t>G_4_8_LESS</t>
+          <t>G_4_7_TEN_THOUSAND</t>
         </is>
       </c>
       <c r="R109" s="46" t="inlineStr">
         <is>
-          <t>G_4_8</t>
+          <t>G_4_7</t>
         </is>
       </c>
       <c r="S109" s="46" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T109" s="46" t="inlineStr">
         <is>
-          <t>OnEncounterEnd</t>
+          <t>BeforeOutgoingHit</t>
         </is>
       </c>
       <c r="U109" s="46" t="inlineStr">
@@ -19926,40 +19816,40 @@
       </c>
       <c r="V109" s="46" t="inlineStr">
         <is>
-          <t>TimeShards</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="W109" s="46" t="inlineStr">
         <is>
-          <t>Multiply</t>
+          <t>Override</t>
         </is>
       </c>
       <c r="X109" s="46" t="n">
-        <v>0.05</v>
+        <v>10000</v>
       </c>
       <c r="Y109" s="46" t="inlineStr">
         <is>
-          <t>Card.EasterShardComparison</t>
+          <t>Card.EasterPhysicalLottery</t>
         </is>
       </c>
       <c r="Z109" s="46" t="inlineStr">
         <is>
-          <t>Step</t>
+          <t>Probability</t>
         </is>
       </c>
       <c r="AA109" s="46" t="n">
-        <v>5</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="110" ht="26" customHeight="1" s="41">
       <c r="Q110" s="46" t="inlineStr">
         <is>
-          <t>G_4_9_HP</t>
+          <t>G_4_8_MORE</t>
         </is>
       </c>
       <c r="R110" s="46" t="inlineStr">
         <is>
-          <t>G_4_9</t>
+          <t>G_4_8</t>
         </is>
       </c>
       <c r="S110" s="46" t="n">
@@ -19977,40 +19867,40 @@
       </c>
       <c r="V110" s="46" t="inlineStr">
         <is>
-          <t>HpMaxAndPoint</t>
+          <t>TimeShards</t>
         </is>
       </c>
       <c r="W110" s="46" t="inlineStr">
         <is>
-          <t>Add</t>
+          <t>Multiply</t>
         </is>
       </c>
       <c r="X110" s="46" t="n">
-        <v>10</v>
+        <v>-0.01</v>
       </c>
       <c r="Y110" s="46" t="inlineStr">
         <is>
-          <t>Card.EasterAttendance</t>
+          <t>Card.EasterShardComparison</t>
         </is>
       </c>
       <c r="Z110" s="46" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Step</t>
         </is>
       </c>
       <c r="AA110" s="46" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="111" ht="26" customHeight="1" s="41">
       <c r="Q111" s="46" t="inlineStr">
         <is>
-          <t>G_4_9_ELEMENTAL</t>
+          <t>G_4_8_LESS</t>
         </is>
       </c>
       <c r="R111" s="46" t="inlineStr">
         <is>
-          <t>G_4_9</t>
+          <t>G_4_8</t>
         </is>
       </c>
       <c r="S111" s="46" t="n">
@@ -20028,79 +19918,181 @@
       </c>
       <c r="V111" s="46" t="inlineStr">
         <is>
-          <t>ElementalAttack</t>
+          <t>TimeShards</t>
         </is>
       </c>
       <c r="W111" s="46" t="inlineStr">
         <is>
-          <t>Add</t>
+          <t>Multiply</t>
         </is>
       </c>
       <c r="X111" s="46" t="n">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="Y111" s="46" t="inlineStr">
         <is>
-          <t>Card.EasterAttendance</t>
+          <t>Card.EasterShardComparison</t>
         </is>
       </c>
       <c r="Z111" s="46" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Step</t>
         </is>
       </c>
       <c r="AA111" s="46" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="112" ht="26" customHeight="1" s="41">
       <c r="Q112" s="46" t="inlineStr">
         <is>
+          <t>G_4_9_HP</t>
+        </is>
+      </c>
+      <c r="R112" s="46" t="inlineStr">
+        <is>
+          <t>G_4_9</t>
+        </is>
+      </c>
+      <c r="S112" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="T112" s="46" t="inlineStr">
+        <is>
+          <t>OnEncounterEnd</t>
+        </is>
+      </c>
+      <c r="U112" s="46" t="inlineStr">
+        <is>
+          <t>CardBehavior</t>
+        </is>
+      </c>
+      <c r="V112" s="46" t="inlineStr">
+        <is>
+          <t>HpMaxAndPoint</t>
+        </is>
+      </c>
+      <c r="W112" s="46" t="inlineStr">
+        <is>
+          <t>Add</t>
+        </is>
+      </c>
+      <c r="X112" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y112" s="46" t="inlineStr">
+        <is>
+          <t>Card.EasterAttendance</t>
+        </is>
+      </c>
+      <c r="Z112" s="46" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AA112" s="46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="Q113" s="46" t="inlineStr">
+        <is>
+          <t>G_4_9_ELEMENTAL</t>
+        </is>
+      </c>
+      <c r="R113" s="46" t="inlineStr">
+        <is>
+          <t>G_4_9</t>
+        </is>
+      </c>
+      <c r="S113" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="T113" s="46" t="inlineStr">
+        <is>
+          <t>OnEncounterEnd</t>
+        </is>
+      </c>
+      <c r="U113" s="46" t="inlineStr">
+        <is>
+          <t>CardBehavior</t>
+        </is>
+      </c>
+      <c r="V113" s="46" t="inlineStr">
+        <is>
+          <t>ElementalAttack</t>
+        </is>
+      </c>
+      <c r="W113" s="46" t="inlineStr">
+        <is>
+          <t>Add</t>
+        </is>
+      </c>
+      <c r="X113" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y113" s="46" t="inlineStr">
+        <is>
+          <t>Card.EasterAttendance</t>
+        </is>
+      </c>
+      <c r="Z113" s="46" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AA113" s="46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="Q114" s="46" t="inlineStr">
+        <is>
           <t>G_4_9_PHYSICAL</t>
         </is>
       </c>
-      <c r="R112" s="46" t="inlineStr">
+      <c r="R114" s="46" t="inlineStr">
         <is>
           <t>G_4_9</t>
         </is>
       </c>
-      <c r="S112" s="46" t="n">
+      <c r="S114" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="T112" s="46" t="inlineStr">
+      <c r="T114" s="46" t="inlineStr">
         <is>
           <t>OnEncounterEnd</t>
         </is>
       </c>
-      <c r="U112" s="46" t="inlineStr">
+      <c r="U114" s="46" t="inlineStr">
         <is>
           <t>CardBehavior</t>
         </is>
       </c>
-      <c r="V112" s="46" t="inlineStr">
+      <c r="V114" s="46" t="inlineStr">
         <is>
           <t>PhysicalAttack</t>
         </is>
       </c>
-      <c r="W112" s="46" t="inlineStr">
+      <c r="W114" s="46" t="inlineStr">
         <is>
           <t>Add</t>
         </is>
       </c>
-      <c r="X112" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y112" s="46" t="inlineStr">
+      <c r="X114" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y114" s="46" t="inlineStr">
         <is>
           <t>Card.EasterAttendance</t>
         </is>
       </c>
-      <c r="Z112" s="46" t="inlineStr">
+      <c r="Z114" s="46" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="AA112" s="46" t="n">
+      <c r="AA114" s="46" t="n">
         <v>0</v>
       </c>
     </row>
@@ -20138,32 +20130,32 @@
     <dataValidation sqref="H4:H77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Trait,Disabled"</formula1>
     </dataValidation>
-    <dataValidation sqref="R4:R104" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
+    <dataValidation sqref="R4:R106" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>INDIRECT("tblCards[Id]")</formula1>
     </dataValidation>
-    <dataValidation sqref="T4:T104" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
+    <dataValidation sqref="T4:T106" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_CardEffects_Trigger</formula1>
     </dataValidation>
-    <dataValidation sqref="U4:U104" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
+    <dataValidation sqref="U4:U106" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_CardEffects_EffectKind</formula1>
     </dataValidation>
-    <dataValidation sqref="V4:V104" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
+    <dataValidation sqref="V4:V106" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_CardEffects_Target</formula1>
     </dataValidation>
-    <dataValidation sqref="W4:W104" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
+    <dataValidation sqref="W4:W106" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_CardEffects_ValueOp</formula1>
     </dataValidation>
-    <dataValidation sqref="Y4:Y104" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
+    <dataValidation sqref="Y4:Y106" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_CardEffects_BehaviorId</formula1>
     </dataValidation>
-    <dataValidation sqref="Z4:Z104" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
+    <dataValidation sqref="Z4:Z106" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_CardEffects_ParamName</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="2">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>

--- a/Design/Data/ReEchoData.xlsx
+++ b/Design/Data/ReEchoData.xlsx
@@ -824,7 +824,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="tblCards" displayName="tblCards" ref="A3:N77" headerRowCount="1" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="tblCards" displayName="tblCards" ref="A3:N78" headerRowCount="1" totalsRowShown="0">
   <tableColumns count="14">
     <tableColumn id="1" name="Id"/>
     <tableColumn id="2" name="SourceWorkbookId"/>
@@ -846,7 +846,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="tblCardEffects" displayName="tblCardEffects" ref="Q3:AA106" headerRowCount="1" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="tblCardEffects" displayName="tblCardEffects" ref="Q3:AA108" headerRowCount="1" totalsRowShown="0">
   <tableColumns count="11">
     <tableColumn id="1" name="Id"/>
     <tableColumn id="2" name="CardId"/>
@@ -17868,17 +17868,68 @@
       </c>
     </row>
     <row r="78" ht="22" customHeight="1" s="41">
-      <c r="A78" s="43" t="n"/>
-      <c r="B78" s="43" t="n"/>
-      <c r="C78" s="43" t="n"/>
-      <c r="D78" s="43" t="n"/>
-      <c r="E78" s="43" t="n"/>
-      <c r="F78" s="43" t="n"/>
-      <c r="G78" s="43" t="n"/>
-      <c r="H78" s="43" t="n"/>
-      <c r="I78" s="43" t="n"/>
-      <c r="J78" s="43" t="n"/>
-      <c r="K78" s="43" t="n"/>
+      <c r="A78" s="39" t="inlineStr">
+        <is>
+          <t>G_4_10</t>
+        </is>
+      </c>
+      <c r="B78" s="39" t="inlineStr">
+        <is>
+          <t>G_4_10</t>
+        </is>
+      </c>
+      <c r="C78" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" s="39" t="inlineStr">
+        <is>
+          <t>符合预期</t>
+        </is>
+      </c>
+      <c r="E78" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">选择后，攻击力永久增加5。
+策划：为什么表现是这样的？
+程序：单子上是这么写的，符合预期</t>
+        </is>
+      </c>
+      <c r="F78" s="39" t="inlineStr">
+        <is>
+          <t>EasterEgg|Attack</t>
+        </is>
+      </c>
+      <c r="G78" s="39" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H78" s="39" t="inlineStr">
+        <is>
+          <t>EasterEgg</t>
+        </is>
+      </c>
+      <c r="I78" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="J78" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="K78" s="39" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="L78" s="39" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M78" s="39" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="N78" s="39" t="inlineStr"/>
       <c r="Q78" s="29" t="inlineStr">
         <is>
           <t>G_4_1_SWING_POS</t>
@@ -19689,105 +19740,105 @@
       </c>
     </row>
     <row r="107" ht="26" customHeight="1" s="41">
-      <c r="Q107" s="46" t="inlineStr">
-        <is>
-          <t>G_4_7_HUNDRED</t>
-        </is>
-      </c>
-      <c r="R107" s="46" t="inlineStr">
-        <is>
-          <t>G_4_7</t>
-        </is>
-      </c>
-      <c r="S107" s="46" t="n">
-        <v>3</v>
-      </c>
-      <c r="T107" s="46" t="inlineStr">
-        <is>
-          <t>BeforeOutgoingHit</t>
-        </is>
-      </c>
-      <c r="U107" s="46" t="inlineStr">
+      <c r="Q107" s="39" t="inlineStr">
+        <is>
+          <t>G_4_10_PLAYER_ATTACK</t>
+        </is>
+      </c>
+      <c r="R107" s="39" t="inlineStr">
+        <is>
+          <t>G_4_10</t>
+        </is>
+      </c>
+      <c r="S107" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="T107" s="39" t="inlineStr">
+        <is>
+          <t>OnGrant</t>
+        </is>
+      </c>
+      <c r="U107" s="39" t="inlineStr">
         <is>
           <t>CardBehavior</t>
         </is>
       </c>
-      <c r="V107" s="46" t="inlineStr">
-        <is>
-          <t>Damage</t>
-        </is>
-      </c>
-      <c r="W107" s="46" t="inlineStr">
-        <is>
-          <t>Override</t>
-        </is>
-      </c>
-      <c r="X107" s="46" t="n">
-        <v>100</v>
-      </c>
-      <c r="Y107" s="46" t="inlineStr">
-        <is>
-          <t>Card.EasterPhysicalLottery</t>
-        </is>
-      </c>
-      <c r="Z107" s="46" t="inlineStr">
-        <is>
-          <t>Probability</t>
-        </is>
-      </c>
-      <c r="AA107" s="46" t="n">
-        <v>0.4</v>
+      <c r="V107" s="39" t="inlineStr">
+        <is>
+          <t>PhysicalAndElementalAttack</t>
+        </is>
+      </c>
+      <c r="W107" s="39" t="inlineStr">
+        <is>
+          <t>Add</t>
+        </is>
+      </c>
+      <c r="X107" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y107" s="39" t="inlineStr">
+        <is>
+          <t>Card.ExpectedOutcome</t>
+        </is>
+      </c>
+      <c r="Z107" s="39" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AA107" s="39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="108" ht="26" customHeight="1" s="41">
-      <c r="Q108" s="46" t="inlineStr">
-        <is>
-          <t>G_4_7_THOUSAND</t>
-        </is>
-      </c>
-      <c r="R108" s="46" t="inlineStr">
-        <is>
-          <t>G_4_7</t>
-        </is>
-      </c>
-      <c r="S108" s="46" t="n">
-        <v>4</v>
-      </c>
-      <c r="T108" s="46" t="inlineStr">
-        <is>
-          <t>BeforeOutgoingHit</t>
-        </is>
-      </c>
-      <c r="U108" s="46" t="inlineStr">
+      <c r="Q108" s="39" t="inlineStr">
+        <is>
+          <t>G_4_10_ENEMY_ATTACK</t>
+        </is>
+      </c>
+      <c r="R108" s="39" t="inlineStr">
+        <is>
+          <t>G_4_10</t>
+        </is>
+      </c>
+      <c r="S108" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="T108" s="39" t="inlineStr">
+        <is>
+          <t>OnCompileRules</t>
+        </is>
+      </c>
+      <c r="U108" s="39" t="inlineStr">
         <is>
           <t>CardBehavior</t>
         </is>
       </c>
-      <c r="V108" s="46" t="inlineStr">
-        <is>
-          <t>Damage</t>
-        </is>
-      </c>
-      <c r="W108" s="46" t="inlineStr">
-        <is>
-          <t>Override</t>
-        </is>
-      </c>
-      <c r="X108" s="46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y108" s="46" t="inlineStr">
-        <is>
-          <t>Card.EasterPhysicalLottery</t>
-        </is>
-      </c>
-      <c r="Z108" s="46" t="inlineStr">
-        <is>
-          <t>Probability</t>
-        </is>
-      </c>
-      <c r="AA108" s="46" t="n">
-        <v>0.08</v>
+      <c r="V108" s="39" t="inlineStr">
+        <is>
+          <t>EnemyAttackFlatBonus</t>
+        </is>
+      </c>
+      <c r="W108" s="39" t="inlineStr">
+        <is>
+          <t>Add</t>
+        </is>
+      </c>
+      <c r="X108" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y108" s="39" t="inlineStr">
+        <is>
+          <t>Card.ExpectedOutcome</t>
+        </is>
+      </c>
+      <c r="Z108" s="39" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AA108" s="39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109" ht="26" customHeight="1" s="41">
@@ -20103,52 +20154,52 @@
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <dataValidations count="16">
-    <dataValidation sqref="F4:F77" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
+    <dataValidation sqref="F4:F78" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_Cards_Tags</formula1>
     </dataValidation>
-    <dataValidation sqref="G4:G77" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
+    <dataValidation sqref="G4:G78" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list" errorStyle="stop">
       <formula1>DV_Logic_Cards_PromotionRoleId</formula1>
     </dataValidation>
-    <dataValidation sqref="H4:H77" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
+    <dataValidation sqref="H4:H78" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_Cards_OfferGroup</formula1>
     </dataValidation>
-    <dataValidation sqref="I4:I77" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
+    <dataValidation sqref="I4:I78" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_Cards_Enabled</formula1>
     </dataValidation>
-    <dataValidation sqref="J4:J77" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
+    <dataValidation sqref="J4:J78" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_Cards_Offerable</formula1>
     </dataValidation>
-    <dataValidation sqref="K4:K77" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
+    <dataValidation sqref="K4:K78" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_Cards_StackPolicy</formula1>
     </dataValidation>
-    <dataValidation sqref="L4:L77" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
+    <dataValidation sqref="L4:L78" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_Cards_ConflictPolicy</formula1>
     </dataValidation>
-    <dataValidation sqref="M4:M77" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
+    <dataValidation sqref="M4:M78" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_Cards_ReviewStatus</formula1>
     </dataValidation>
-    <dataValidation sqref="H4:H77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="H4:H78" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Trait,Disabled"</formula1>
     </dataValidation>
-    <dataValidation sqref="R4:R106" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
+    <dataValidation sqref="R4:R108" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>INDIRECT("tblCards[Id]")</formula1>
     </dataValidation>
-    <dataValidation sqref="T4:T106" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
+    <dataValidation sqref="T4:T108" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_CardEffects_Trigger</formula1>
     </dataValidation>
-    <dataValidation sqref="U4:U106" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
+    <dataValidation sqref="U4:U108" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_CardEffects_EffectKind</formula1>
     </dataValidation>
-    <dataValidation sqref="V4:V106" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
+    <dataValidation sqref="V4:V108" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_CardEffects_Target</formula1>
     </dataValidation>
-    <dataValidation sqref="W4:W106" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
+    <dataValidation sqref="W4:W108" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_CardEffects_ValueOp</formula1>
     </dataValidation>
-    <dataValidation sqref="Y4:Y106" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
+    <dataValidation sqref="Y4:Y108" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_CardEffects_BehaviorId</formula1>
     </dataValidation>
-    <dataValidation sqref="Z4:Z106" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
+    <dataValidation sqref="Z4:Z108" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效选项" error="只能从下拉列表中选择有效值。" promptTitle="请选择" prompt="请从下拉列表选择，不能输入列表外的值。" type="list">
       <formula1>DV_Logic_CardEffects_ParamName</formula1>
     </dataValidation>
   </dataValidations>

--- a/Design/Data/ReEchoData.xlsx
+++ b/Design/Data/ReEchoData.xlsx
@@ -9182,7 +9182,7 @@
       </c>
       <c r="E5" s="33" t="inlineStr">
         <is>
-          <t>生命值与生命上限+5</t>
+          <t>生命值与生命上限+8</t>
         </is>
       </c>
       <c r="F5" s="29" t="inlineStr">
@@ -9259,7 +9259,7 @@
       </c>
       <c r="X5" s="29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y5" s="29" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="X6" s="29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y6" s="29" t="inlineStr">
@@ -11328,7 +11328,7 @@
       </c>
       <c r="E23" s="33" t="inlineStr">
         <is>
-          <t>你的商店获得10%折扣。你每消费1次，你的生命值和生命上限+3</t>
+          <t>你的商店获得20%折扣。你每购买1次任意商品，你的生命值和生命上限+2</t>
         </is>
       </c>
       <c r="F23" s="29" t="inlineStr">
@@ -11643,7 +11643,7 @@
       </c>
       <c r="X25" s="29" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y25" s="29" t="inlineStr">
@@ -11762,7 +11762,7 @@
       </c>
       <c r="X26" s="29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y26" s="29" t="inlineStr">
@@ -11923,7 +11923,7 @@
       </c>
       <c r="E28" s="33" t="inlineStr">
         <is>
-          <t>你的回响拥有你3倍的生命值，但其无法攻击且不断吸引周围的敌人。每当它被击杀，你的最大生命值和当前生命值永久+3</t>
+          <t>你的回响继承你的生命值*2，但其无法攻击，且永久获得【嘲讽】状态。每当它被怪物击败，你的最大生命值和当前生命值永久+5</t>
         </is>
       </c>
       <c r="F28" s="29" t="inlineStr">
@@ -15024,7 +15024,7 @@
       </c>
       <c r="E54" s="33" t="inlineStr">
         <is>
-          <t>当你击杀100只史莱姆后，生命上限翻倍，并回满生命。</t>
+          <t>当你击杀50只史莱姆后，你对史莱姆的伤害将令其获得【诅咒】</t>
         </is>
       </c>
       <c r="F54" s="29" t="inlineStr">
@@ -16153,7 +16153,7 @@
       </c>
       <c r="T63" s="29" t="inlineStr">
         <is>
-          <t>OnHitResolved</t>
+          <t>BeforeOutgoingHit</t>
         </is>
       </c>
       <c r="U63" s="29" t="inlineStr">
@@ -16163,22 +16163,22 @@
       </c>
       <c r="V63" s="29" t="inlineStr">
         <is>
-          <t>HpMax</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="W63" s="29" t="inlineStr">
         <is>
-          <t>Multiply</t>
+          <t>Add</t>
         </is>
       </c>
       <c r="X63" s="29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y63" s="29" t="inlineStr">
         <is>
-          <t>Card.KillThresholdStatBoost</t>
+          <t>Card.TargetKillCurse</t>
         </is>
       </c>
       <c r="Z63" s="29" t="inlineStr">
@@ -16188,7 +16188,7 @@
       </c>
       <c r="AA63" s="29" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
     </row>

--- a/Design/Data/ReEchoData.xlsx
+++ b/Design/Data/ReEchoData.xlsx
@@ -8879,7 +8879,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -9063,7 +9063,7 @@
       </c>
       <c r="E4" s="33" t="inlineStr">
         <is>
-          <t>移动速度+6%</t>
+          <t>绉诲姩閫熷害+1%</t>
         </is>
       </c>
       <c r="F4" s="29" t="inlineStr">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="X4" s="29" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="Y4" s="29" t="inlineStr">
@@ -12042,7 +12042,7 @@
       </c>
       <c r="E29" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">你的回响每击杀15名敌人，物攻&amp;元攻永久+1
+          <t>你的回响每击杀15名敌人，物攻&amp;元攻永久+1
 你每击杀15名敌人，回响效能永久+2%</t>
         </is>
       </c>
@@ -13114,7 +13114,7 @@
       </c>
       <c r="E38" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">你获得1000时间碎片，随机承受：
+          <t>你获得1000时间碎片，随机承受：
 你将不能再刷新商店/你将不能再购买额外卡牌组/敌人将不再掉落时间碎片</t>
         </is>
       </c>
@@ -14428,7 +14428,7 @@
       </c>
       <c r="E49" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">完成任一任务后，获得666时间碎片：
+          <t>完成任一任务后，获得666时间碎片：
 击杀111个敌人/结束战斗时≥22生命值/结束战斗时≤3生命值</t>
         </is>
       </c>
@@ -15381,7 +15381,7 @@
       </c>
       <c r="E57" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">你可以在商店赊账，欠款会收取10%利息/每关
+          <t>你可以在商店赊账，欠款会收取10%利息/每关
 第8关时，如果你还没有还清，会有很不好的事情发生！！</t>
         </is>
       </c>
@@ -16810,7 +16810,7 @@
       </c>
       <c r="E69" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">每关结束后，赌一把大的！攒够了家底以后，商店刷新永远为你开放！
+          <t>每关结束后，赌一把大的！攒够了家底以后，商店刷新永远为你开放！
 ——策划 爆培嘉 敬上</t>
         </is>
       </c>
@@ -16930,7 +16930,7 @@
       </c>
       <c r="E70" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">选择后，你可能拥有至高无上的暴击数值，也可能从此一蹶不振！
+          <t>选择后，你可能拥有至高无上的暴击数值，也可能从此一蹶不振！
 ——策划 斑 敬上</t>
         </is>
       </c>
@@ -17050,7 +17050,7 @@
       </c>
       <c r="E71" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">回响触碰到敌人，造成20物理伤害；如果是你，你回复10生命值。数值每关翻倍！
+          <t>回响触碰到敌人，造成20物理伤害；如果是你，你回复10生命值。数值每关翻倍！
 ——策划 麦麦熊 敬上</t>
         </is>
       </c>
@@ -17170,7 +17170,7 @@
       </c>
       <c r="E72" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">失去所有时间碎片。每失去15时间碎片，随机获得一些属性！
+          <t>失去所有时间碎片。每失去15时间碎片，随机获得一些属性！
 ——策划 呕乐兮 敬上</t>
         </is>
       </c>
@@ -17290,7 +17290,7 @@
       </c>
       <c r="E73" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">身边的敌人都被你迷倒了！
+          <t>身边的敌人都被你迷倒了！
 ——特别鸣谢 程序 T爷</t>
         </is>
       </c>
@@ -17410,7 +17410,7 @@
       </c>
       <c r="E74" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">你努力奔跑。下一关，1滴血换1张1级卡牌
+          <t>你努力奔跑。下一关，1滴血换1张1级卡牌
 ——特别鸣谢 程序 Jo爷</t>
         </is>
       </c>
@@ -17530,7 +17530,7 @@
       </c>
       <c r="E75" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">神秘人往你的物理伤害后面加随机个0
+          <t>神秘人往你的物理伤害后面加随机个0
 ——特别鸣谢 美术 00</t>
         </is>
       </c>
@@ -17650,7 +17650,7 @@
       </c>
       <c r="E76" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">经济系统被赋予“ELO”机制
+          <t>经济系统被赋予“ELO”机制
 ——特别鸣谢 美术 子涵</t>
         </is>
       </c>
@@ -17770,7 +17770,7 @@
       </c>
       <c r="E77" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">每一关卡结束后，随机获得巨额生命值/元攻/物攻
+          <t>每一关卡结束后，随机获得巨额生命值/元攻/物攻
 ——特别鸣谢 美术 雯雯</t>
         </is>
       </c>
@@ -17888,8 +17888,8 @@
       </c>
       <c r="E78" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">选择后，攻击力永久增加5。
-策划：为什么表现是这样的？
+          <t>选择后，攻击力永久增加5。
+策划：为什么表现是这样的？
 程序：单子上是这么写的，符合预期</t>
         </is>
       </c>
@@ -18068,7 +18068,7 @@
       <c r="K80" s="43" t="n"/>
       <c r="Q80" s="29" t="inlineStr">
         <is>
-          <t xml:space="preserve">G_4_1_REFRESH</t>
+          <t>G_4_1_REFRESH</t>
         </is>
       </c>
       <c r="R80" s="29" t="inlineStr">
@@ -18093,12 +18093,12 @@
       </c>
       <c r="V80" s="29" t="inlineStr">
         <is>
-          <t xml:space="preserve">FreeShopRefresh</t>
+          <t>FreeShopRefresh</t>
         </is>
       </c>
       <c r="W80" s="29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Override</t>
+          <t>Override</t>
         </is>
       </c>
       <c r="X80" s="29" t="n">
@@ -18106,12 +18106,12 @@
       </c>
       <c r="Y80" s="29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Card.EasterShardThreshold</t>
+          <t>Card.EasterShardThreshold</t>
         </is>
       </c>
       <c r="Z80" s="29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Threshold</t>
+          <t>Threshold</t>
         </is>
       </c>
       <c r="AA80" s="29" t="n">
@@ -18198,7 +18198,7 @@
       <c r="K82" s="43" t="n"/>
       <c r="Q82" s="29" t="inlineStr">
         <is>
-          <t xml:space="preserve">G_4_2_CRIT_EFFECT</t>
+          <t>G_4_2_CRIT_EFFECT</t>
         </is>
       </c>
       <c r="R82" s="29" t="inlineStr">
@@ -18223,7 +18223,7 @@
       </c>
       <c r="V82" s="29" t="inlineStr">
         <is>
-          <t xml:space="preserve">CriticalEffect</t>
+          <t>CriticalEffect</t>
         </is>
       </c>
       <c r="W82" s="29" t="inlineStr">
@@ -18336,12 +18336,12 @@
       <c r="K84" s="43" t="n"/>
       <c r="Q84" s="29" t="inlineStr">
         <is>
-          <t xml:space="preserve">G_4_2_CRIT_PENALTY</t>
+          <t>G_4_2_CRIT_PENALTY</t>
         </is>
       </c>
       <c r="R84" s="29" t="inlineStr">
         <is>
-          <t xml:space="preserve">G_4_2</t>
+          <t>G_4_2</t>
         </is>
       </c>
       <c r="S84" s="29" t="n">
@@ -18349,7 +18349,7 @@
       </c>
       <c r="T84" s="29" t="inlineStr">
         <is>
-          <t xml:space="preserve">OnGrant</t>
+          <t>OnGrant</t>
         </is>
       </c>
       <c r="U84" s="29" t="inlineStr">
@@ -18359,12 +18359,12 @@
       </c>
       <c r="V84" s="29" t="inlineStr">
         <is>
-          <t xml:space="preserve">CritNegateAmplification</t>
+          <t>CritNegateAmplification</t>
         </is>
       </c>
       <c r="W84" s="29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Override</t>
+          <t>Override</t>
         </is>
       </c>
       <c r="X84" s="29" t="n">
@@ -18372,12 +18372,12 @@
       </c>
       <c r="Y84" s="29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Card.EasterIndependentGrant</t>
+          <t>Card.EasterIndependentGrant</t>
         </is>
       </c>
       <c r="Z84" s="29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chance</t>
+          <t>Chance</t>
         </is>
       </c>
       <c r="AA84" s="29" t="n">
@@ -18398,12 +18398,12 @@
       <c r="K85" s="43" t="n"/>
       <c r="Q85" s="29" t="inlineStr">
         <is>
-          <t xml:space="preserve">G_4_3_CONTACT_DAMAGE</t>
+          <t>G_4_3_CONTACT_DAMAGE</t>
         </is>
       </c>
       <c r="R85" s="29" t="inlineStr">
         <is>
-          <t xml:space="preserve">G_4_3</t>
+          <t>G_4_3</t>
         </is>
       </c>
       <c r="S85" s="29" t="inlineStr">
@@ -18413,7 +18413,7 @@
       </c>
       <c r="T85" s="29" t="inlineStr">
         <is>
-          <t xml:space="preserve">OnCompileRules</t>
+          <t>OnCompileRules</t>
         </is>
       </c>
       <c r="U85" s="29" t="inlineStr">
@@ -18423,7 +18423,7 @@
       </c>
       <c r="V85" s="29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Damage</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="W85" s="29" t="inlineStr">
@@ -18436,12 +18436,12 @@
       </c>
       <c r="Y85" s="29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Card.EasterEchoContact</t>
+          <t>Card.EasterEchoContact</t>
         </is>
       </c>
       <c r="Z85" s="29" t="inlineStr">
         <is>
-          <t xml:space="preserve">PlayerHealing</t>
+          <t>PlayerHealing</t>
         </is>
       </c>
       <c r="AA85" s="29" t="n">
@@ -18462,7 +18462,7 @@
       <c r="K86" s="43" t="n"/>
       <c r="Q86" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">G_4_4_HP</t>
+          <t>G_4_4_HP</t>
         </is>
       </c>
       <c r="R86" s="39" t="inlineStr">
@@ -18485,7 +18485,7 @@
       </c>
       <c r="V86" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">HpMaxAndPoint</t>
+          <t>HpMaxAndPoint</t>
         </is>
       </c>
       <c r="W86" s="39" t="inlineStr">
@@ -18528,7 +18528,7 @@
       <c r="K87" s="43" t="n"/>
       <c r="Q87" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">G_4_4_PHYSICAL</t>
+          <t>G_4_4_PHYSICAL</t>
         </is>
       </c>
       <c r="R87" s="39" t="inlineStr">
@@ -18551,7 +18551,7 @@
       </c>
       <c r="V87" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">PhysicalAttack</t>
+          <t>PhysicalAttack</t>
         </is>
       </c>
       <c r="W87" s="39" t="inlineStr">
@@ -18594,7 +18594,7 @@
       <c r="K88" s="43" t="n"/>
       <c r="Q88" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">G_4_4_ELEMENTAL</t>
+          <t>G_4_4_ELEMENTAL</t>
         </is>
       </c>
       <c r="R88" s="39" t="inlineStr">
@@ -18617,7 +18617,7 @@
       </c>
       <c r="V88" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">ElementalAttack</t>
+          <t>ElementalAttack</t>
         </is>
       </c>
       <c r="W88" s="39" t="inlineStr">
@@ -18658,7 +18658,7 @@
       <c r="K89" s="43" t="n"/>
       <c r="Q89" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">G_4_4_CRIT_RATE</t>
+          <t>G_4_4_CRIT_RATE</t>
         </is>
       </c>
       <c r="R89" s="39" t="inlineStr">
@@ -18681,7 +18681,7 @@
       </c>
       <c r="V89" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">CriticalRate</t>
+          <t>CriticalRate</t>
         </is>
       </c>
       <c r="W89" s="39" t="inlineStr">
@@ -18722,7 +18722,7 @@
       <c r="K90" s="43" t="n"/>
       <c r="Q90" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">G_4_4_CRIT_EFFECT</t>
+          <t>G_4_4_CRIT_EFFECT</t>
         </is>
       </c>
       <c r="R90" s="39" t="inlineStr">
@@ -18745,7 +18745,7 @@
       </c>
       <c r="V90" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">CriticalEffect</t>
+          <t>CriticalEffect</t>
         </is>
       </c>
       <c r="W90" s="39" t="inlineStr">
@@ -18786,7 +18786,7 @@
       <c r="K91" s="43" t="n"/>
       <c r="Q91" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">G_4_4_ECHO</t>
+          <t>G_4_4_ECHO</t>
         </is>
       </c>
       <c r="R91" s="39" t="inlineStr">
@@ -18809,7 +18809,7 @@
       </c>
       <c r="V91" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">EchoEfficiency</t>
+          <t>EchoEfficiency</t>
         </is>
       </c>
       <c r="W91" s="39" t="inlineStr">
@@ -18852,12 +18852,12 @@
       <c r="K92" s="43" t="n"/>
       <c r="Q92" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">G_4_4_REACTION</t>
+          <t>G_4_4_REACTION</t>
         </is>
       </c>
       <c r="R92" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">G_4_4</t>
+          <t>G_4_4</t>
         </is>
       </c>
       <c r="S92" s="39" t="n">
@@ -18865,7 +18865,7 @@
       </c>
       <c r="T92" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">OnGrant</t>
+          <t>OnGrant</t>
         </is>
       </c>
       <c r="U92" s="39" t="inlineStr">
@@ -18875,12 +18875,12 @@
       </c>
       <c r="V92" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">ReactionEfficiency</t>
+          <t>ReactionEfficiency</t>
         </is>
       </c>
       <c r="W92" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Add</t>
+          <t>Add</t>
         </is>
       </c>
       <c r="X92" s="39" t="n">
@@ -18888,12 +18888,12 @@
       </c>
       <c r="Y92" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Card.EasterShardSacrifice</t>
+          <t>Card.EasterShardSacrifice</t>
         </is>
       </c>
       <c r="Z92" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">ShardUnit</t>
+          <t>ShardUnit</t>
         </is>
       </c>
       <c r="AA92" s="39" t="n">
@@ -18914,7 +18914,7 @@
       <c r="K93" s="43" t="n"/>
       <c r="Q93" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">G_4_5_STUN</t>
+          <t>G_4_5_STUN</t>
         </is>
       </c>
       <c r="R93" s="39" t="inlineStr">
@@ -18937,7 +18937,7 @@
       </c>
       <c r="V93" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stun</t>
+          <t>Stun</t>
         </is>
       </c>
       <c r="W93" s="39" t="inlineStr">
@@ -18955,7 +18955,7 @@
       </c>
       <c r="Z93" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">PulseInterval</t>
+          <t>PulseInterval</t>
         </is>
       </c>
       <c r="AA93" s="39" t="n">
@@ -18976,12 +18976,12 @@
       <c r="K94" s="43" t="n"/>
       <c r="Q94" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">G_4_5_RADIUS</t>
+          <t>G_4_5_RADIUS</t>
         </is>
       </c>
       <c r="R94" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">G_4_5</t>
+          <t>G_4_5</t>
         </is>
       </c>
       <c r="S94" s="39" t="n">
@@ -18989,7 +18989,7 @@
       </c>
       <c r="T94" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">OnEncounterTick</t>
+          <t>OnEncounterTick</t>
         </is>
       </c>
       <c r="U94" s="39" t="inlineStr">
@@ -19004,7 +19004,7 @@
       </c>
       <c r="W94" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Override</t>
+          <t>Override</t>
         </is>
       </c>
       <c r="X94" s="39" t="n">
@@ -19012,12 +19012,12 @@
       </c>
       <c r="Y94" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Card.EasterRandomStun</t>
+          <t>Card.EasterRandomStun</t>
         </is>
       </c>
       <c r="Z94" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">RadiusCm</t>
+          <t>RadiusCm</t>
         </is>
       </c>
       <c r="AA94" s="39" t="n">
@@ -19038,12 +19038,12 @@
       <c r="K95" s="43" t="n"/>
       <c r="Q95" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">G_4_5_COUNT</t>
+          <t>G_4_5_COUNT</t>
         </is>
       </c>
       <c r="R95" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">G_4_5</t>
+          <t>G_4_5</t>
         </is>
       </c>
       <c r="S95" s="39" t="n">
@@ -19051,7 +19051,7 @@
       </c>
       <c r="T95" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">OnEncounterTick</t>
+          <t>OnEncounterTick</t>
         </is>
       </c>
       <c r="U95" s="39" t="inlineStr">
@@ -19061,7 +19061,7 @@
       </c>
       <c r="V95" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stun</t>
+          <t>Stun</t>
         </is>
       </c>
       <c r="W95" s="39" t="inlineStr">
@@ -19074,12 +19074,12 @@
       </c>
       <c r="Y95" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Card.EasterRandomStun</t>
+          <t>Card.EasterRandomStun</t>
         </is>
       </c>
       <c r="Z95" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">TargetCount</t>
+          <t>TargetCount</t>
         </is>
       </c>
       <c r="AA95" s="39" t="n">
@@ -19100,12 +19100,12 @@
       <c r="K96" s="43" t="n"/>
       <c r="Q96" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">G_4_6_REWARD</t>
+          <t>G_4_6_REWARD</t>
         </is>
       </c>
       <c r="R96" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">G_4_6</t>
+          <t>G_4_6</t>
         </is>
       </c>
       <c r="S96" s="39" t="n">
@@ -19113,7 +19113,7 @@
       </c>
       <c r="T96" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">OnEncounterEnd</t>
+          <t>OnEncounterEnd</t>
         </is>
       </c>
       <c r="U96" s="39" t="inlineStr">
@@ -19123,7 +19123,7 @@
       </c>
       <c r="V96" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">MinimumGuaranteedTier</t>
+          <t>MinimumGuaranteedTier</t>
         </is>
       </c>
       <c r="W96" s="39" t="inlineStr">
@@ -19136,12 +19136,12 @@
       </c>
       <c r="Y96" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Card.EasterDamageCards</t>
+          <t>Card.EasterDamageCards</t>
         </is>
       </c>
       <c r="Z96" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">GrantTier</t>
+          <t>GrantTier</t>
         </is>
       </c>
       <c r="AA96" s="39" t="n">
@@ -19162,7 +19162,7 @@
       <c r="K97" s="43" t="n"/>
       <c r="Q97" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">G_4_7_ZERO</t>
+          <t>G_4_7_ZERO</t>
         </is>
       </c>
       <c r="R97" s="39" t="inlineStr">
@@ -19224,7 +19224,7 @@
       <c r="K98" s="43" t="n"/>
       <c r="Q98" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">G_4_7_TEN</t>
+          <t>G_4_7_TEN</t>
         </is>
       </c>
       <c r="R98" s="39" t="inlineStr">
@@ -19286,7 +19286,7 @@
       <c r="K99" s="43" t="n"/>
       <c r="Q99" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">G_4_7_HUNDRED</t>
+          <t>G_4_7_HUNDRED</t>
         </is>
       </c>
       <c r="R99" s="39" t="inlineStr">
@@ -19348,12 +19348,12 @@
       <c r="K100" s="43" t="n"/>
       <c r="Q100" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">G_4_7_THOUSAND</t>
+          <t>G_4_7_THOUSAND</t>
         </is>
       </c>
       <c r="R100" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">G_4_7</t>
+          <t>G_4_7</t>
         </is>
       </c>
       <c r="S100" s="39" t="n">
@@ -19361,7 +19361,7 @@
       </c>
       <c r="T100" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">BeforeOutgoingHit</t>
+          <t>BeforeOutgoingHit</t>
         </is>
       </c>
       <c r="U100" s="39" t="inlineStr">
@@ -19371,12 +19371,12 @@
       </c>
       <c r="V100" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Damage</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="W100" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Override</t>
+          <t>Override</t>
         </is>
       </c>
       <c r="X100" s="39" t="n">
@@ -19384,12 +19384,12 @@
       </c>
       <c r="Y100" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Card.EasterPhysicalLottery</t>
+          <t>Card.EasterPhysicalLottery</t>
         </is>
       </c>
       <c r="Z100" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Probability</t>
+          <t>Probability</t>
         </is>
       </c>
       <c r="AA100" s="39" t="n">
@@ -19410,12 +19410,12 @@
       <c r="K101" s="43" t="n"/>
       <c r="Q101" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">G_4_7_TEN_THOUSAND</t>
+          <t>G_4_7_TEN_THOUSAND</t>
         </is>
       </c>
       <c r="R101" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">G_4_7</t>
+          <t>G_4_7</t>
         </is>
       </c>
       <c r="S101" s="39" t="n">
@@ -19423,7 +19423,7 @@
       </c>
       <c r="T101" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">BeforeOutgoingHit</t>
+          <t>BeforeOutgoingHit</t>
         </is>
       </c>
       <c r="U101" s="39" t="inlineStr">
@@ -19433,12 +19433,12 @@
       </c>
       <c r="V101" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Damage</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="W101" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Override</t>
+          <t>Override</t>
         </is>
       </c>
       <c r="X101" s="39" t="n">
@@ -19446,12 +19446,12 @@
       </c>
       <c r="Y101" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Card.EasterPhysicalLottery</t>
+          <t>Card.EasterPhysicalLottery</t>
         </is>
       </c>
       <c r="Z101" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Probability</t>
+          <t>Probability</t>
         </is>
       </c>
       <c r="AA101" s="39" t="n">
@@ -19472,12 +19472,12 @@
       <c r="K102" s="43" t="n"/>
       <c r="Q102" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">G_4_8_MORE</t>
+          <t>G_4_8_MORE</t>
         </is>
       </c>
       <c r="R102" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">G_4_8</t>
+          <t>G_4_8</t>
         </is>
       </c>
       <c r="S102" s="39" t="inlineStr">
@@ -19497,12 +19497,12 @@
       </c>
       <c r="V102" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">TimeShards</t>
+          <t>TimeShards</t>
         </is>
       </c>
       <c r="W102" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Multiply</t>
+          <t>Multiply</t>
         </is>
       </c>
       <c r="X102" s="39" t="n">
@@ -19510,12 +19510,12 @@
       </c>
       <c r="Y102" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Card.EasterShardComparison</t>
+          <t>Card.EasterShardComparison</t>
         </is>
       </c>
       <c r="Z102" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Step</t>
+          <t>Step</t>
         </is>
       </c>
       <c r="AA102" s="39" t="n">
@@ -19536,12 +19536,12 @@
       <c r="K103" s="43" t="n"/>
       <c r="Q103" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">G_4_8_LESS</t>
+          <t>G_4_8_LESS</t>
         </is>
       </c>
       <c r="R103" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">G_4_8</t>
+          <t>G_4_8</t>
         </is>
       </c>
       <c r="S103" s="39" t="inlineStr">
@@ -19561,12 +19561,12 @@
       </c>
       <c r="V103" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">TimeShards</t>
+          <t>TimeShards</t>
         </is>
       </c>
       <c r="W103" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Multiply</t>
+          <t>Multiply</t>
         </is>
       </c>
       <c r="X103" s="39" t="n">
@@ -19574,12 +19574,12 @@
       </c>
       <c r="Y103" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Card.EasterShardComparison</t>
+          <t>Card.EasterShardComparison</t>
         </is>
       </c>
       <c r="Z103" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Step</t>
+          <t>Step</t>
         </is>
       </c>
       <c r="AA103" s="39" t="n">
@@ -19589,7 +19589,7 @@
     <row r="104" ht="26" customHeight="1" s="41">
       <c r="Q104" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">G_4_9_HP</t>
+          <t>G_4_9_HP</t>
         </is>
       </c>
       <c r="R104" s="39" t="inlineStr">
@@ -19612,7 +19612,7 @@
       </c>
       <c r="V104" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">HpMaxAndPoint</t>
+          <t>HpMaxAndPoint</t>
         </is>
       </c>
       <c r="W104" s="39" t="inlineStr">
@@ -19630,7 +19630,7 @@
       </c>
       <c r="Z104" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Max</t>
+          <t>Max</t>
         </is>
       </c>
       <c r="AA104" s="39" t="n">
@@ -19640,12 +19640,12 @@
     <row r="105" ht="26" customHeight="1" s="41">
       <c r="Q105" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">G_4_9_ELEMENTAL</t>
+          <t>G_4_9_ELEMENTAL</t>
         </is>
       </c>
       <c r="R105" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">G_4_9</t>
+          <t>G_4_9</t>
         </is>
       </c>
       <c r="S105" s="39" t="n">
@@ -19653,22 +19653,22 @@
       </c>
       <c r="T105" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">OnEncounterEnd</t>
+          <t>OnEncounterEnd</t>
         </is>
       </c>
       <c r="U105" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">CardBehavior</t>
+          <t>CardBehavior</t>
         </is>
       </c>
       <c r="V105" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">ElementalAttack</t>
+          <t>ElementalAttack</t>
         </is>
       </c>
       <c r="W105" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Add</t>
+          <t>Add</t>
         </is>
       </c>
       <c r="X105" s="39" t="n">
@@ -19676,12 +19676,12 @@
       </c>
       <c r="Y105" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Card.EasterAttendance</t>
+          <t>Card.EasterAttendance</t>
         </is>
       </c>
       <c r="Z105" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Max</t>
+          <t>Max</t>
         </is>
       </c>
       <c r="AA105" s="39" t="n">
@@ -19691,12 +19691,12 @@
     <row r="106" ht="26" customHeight="1" s="41">
       <c r="Q106" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">G_4_9_PHYSICAL</t>
+          <t>G_4_9_PHYSICAL</t>
         </is>
       </c>
       <c r="R106" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">G_4_9</t>
+          <t>G_4_9</t>
         </is>
       </c>
       <c r="S106" s="39" t="n">
@@ -19704,22 +19704,22 @@
       </c>
       <c r="T106" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">OnEncounterEnd</t>
+          <t>OnEncounterEnd</t>
         </is>
       </c>
       <c r="U106" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">CardBehavior</t>
+          <t>CardBehavior</t>
         </is>
       </c>
       <c r="V106" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">PhysicalAttack</t>
+          <t>PhysicalAttack</t>
         </is>
       </c>
       <c r="W106" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Add</t>
+          <t>Add</t>
         </is>
       </c>
       <c r="X106" s="39" t="n">
@@ -19727,12 +19727,12 @@
       </c>
       <c r="Y106" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Card.EasterAttendance</t>
+          <t>Card.EasterAttendance</t>
         </is>
       </c>
       <c r="Z106" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Max</t>
+          <t>Max</t>
         </is>
       </c>
       <c r="AA106" s="39" t="n">
@@ -20205,8 +20205,8 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="2">
-    <tablePart r:id="rId1"/>
-    <tablePart r:id="rId2"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>

--- a/Design/Data/ReEchoData.xlsx
+++ b/Design/Data/ReEchoData.xlsx
@@ -17410,7 +17410,7 @@
       </c>
       <c r="E74" s="39" t="inlineStr">
         <is>
-          <t>你努力奔跑。下一关，1滴血换1张1级卡牌
+          <t>下一关卡结束后，你获得X张随机1级卡牌。X=你下一关卡受到的伤害
 ——特别鸣谢 程序 Jo爷</t>
         </is>
       </c>
@@ -19141,11 +19141,13 @@
       </c>
       <c r="Z96" s="39" t="inlineStr">
         <is>
-          <t>GrantTier</t>
-        </is>
-      </c>
-      <c r="AA96" s="39" t="n">
-        <v>1</v>
+          <t>DamageToCards</t>
+        </is>
+      </c>
+      <c r="AA96" s="39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="97" ht="22" customHeight="1" s="41">

--- a/Design/Data/ReEchoData.xlsx
+++ b/Design/Data/ReEchoData.xlsx
@@ -16810,7 +16810,7 @@
       </c>
       <c r="E69" s="39" t="inlineStr">
         <is>
-          <t>每关结束后，赌一把大的！攒够了家底以后，商店刷新永远为你开放！
+          <t>每关结束后，赌一把大的！攒够了家底以后，获得来自程序邱孙红的宝库。
 ——策划 爆培嘉 敬上</t>
         </is>
       </c>
@@ -17050,7 +17050,7 @@
       </c>
       <c r="E71" s="39" t="inlineStr">
         <is>
-          <t>回响触碰到敌人，造成20物理伤害；如果是你，你回复10生命值。数值每关翻倍！
+          <t>回响触碰到敌人，造成1000物理伤害；如果是你，你回复1000生命值。数值每关翻倍！
 ——策划 麦麦熊 敬上</t>
         </is>
       </c>
@@ -17170,7 +17170,7 @@
       </c>
       <c r="E72" s="39" t="inlineStr">
         <is>
-          <t>失去所有时间碎片。每失去15时间碎片，随机获得一些属性！
+          <t>用更高的效率把所有的时间碎片转化为随机属性。你觉得这个怎么样？
 ——策划 呕乐兮 敬上</t>
         </is>
       </c>
@@ -17290,7 +17290,7 @@
       </c>
       <c r="E73" s="39" t="inlineStr">
         <is>
-          <t>身边的敌人都被你迷倒了！
+          <t>身边的所有敌人都被你彻彻底底迷晕了，迷倒了！
 ——特别鸣谢 程序 T爷</t>
         </is>
       </c>
@@ -17410,7 +17410,7 @@
       </c>
       <c r="E74" s="39" t="inlineStr">
         <is>
-          <t>下一关卡结束后，你获得X张随机1级卡牌。X=你下一关卡受到的伤害
+          <t>“野狗不需要墓碑”，你快要飞升成神了。下一关，1滴血换10张1级卡牌
 ——特别鸣谢 程序 Jo爷</t>
         </is>
       </c>
@@ -17530,7 +17530,7 @@
       </c>
       <c r="E75" s="39" t="inlineStr">
         <is>
-          <t>神秘人往你的物理伤害后面加随机个0
+          <t>往你的物理伤害后面加随机个、很多个、真的很多0！
 ——特别鸣谢 美术 00</t>
         </is>
       </c>
@@ -17650,7 +17650,7 @@
       </c>
       <c r="E76" s="39" t="inlineStr">
         <is>
-          <t>经济系统被赋予“ELO”机制
+          <t>经济系统被赋予被彻底魔改的“ELO”机制
 ——特别鸣谢 美术 子涵</t>
         </is>
       </c>
@@ -17770,7 +17770,7 @@
       </c>
       <c r="E77" s="39" t="inlineStr">
         <is>
-          <t>每一关卡结束后，随机获得巨额生命值/元攻/物攻
+          <t>每一关卡结束后，随机获得巨额生命值/元攻/物攻（真的是巨额！）
 ——特别鸣谢 美术 雯雯</t>
         </is>
       </c>
